--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -38,13 +38,13 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00047857"/>
+      <color rgb="00B91C1C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00B91C1C"/>
+      <color rgb="00047857"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -85,7 +85,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -457,14 +459,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,240 +484,697 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Claim No</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Claim Date</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Area Office</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Dealer Name</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Dealer Branch</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Scheme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Hold Reasons / Remarks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Processed Date</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Chassis No</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 19:42:51</t>
+          <t>LYL27A000024</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>SARWAN KUMAR</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>NEXGEN SOLUTIONS TECHNOLOGIES (P)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>HAZARIBAGH</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [SARWA CD-1782281211888.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Invoice [SARWA INV-1782281212011.pdf]: Invoice Number mismatch. Extracted: 'INVZ/200100167', Expected: 'INV27A000167', Invoice [SARWA INV-1782281212011.pdf]: Failed to extract bonus amount from invoice (Expected: 5000.0), Ledger [SAWA LED-1782281211751.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 5000.0, Ledger [SAWA LED-1782281211751.pdf]: Welcome Bonus amount mismatch in ledger. Expected: 5000.0</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:44:35</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>T6D11505</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>GSSK ENTERPRISES</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+          <t>LYL27A000026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>RAMESHWAR SAW</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>NEXGEN SOLUTIONS TECHNOLOGIES (P)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>HAZARIBAGH</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Invoice [INVOICE-1782102623562.pdf]: Invoice Number mismatch. Extracted: 'INV27400119', Expected: 'INV27A000191', Cross-Validation Mismatch: Customer signature is missing on one or both documents., Cross-Validation Mismatch: Printed customer name found in both documents., Cross-Validation Mismatch: Scheme amount extraction successful.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 19:46:05</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [RAM CD-1782281811250.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:49:30</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>T6E13150</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>MUNNA KUMAR</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+          <t>LYL27A000025</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>CHHOTU RAUT</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>NEXGEN SOLUTIONS TECHNOLOGIES (P)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>HAZARIBAGH</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Invoice [INV-1782026200103.pdf]: Amount has invalid format: Welcome Bonus Amount is Rs.5000.00-(inclusive of GST)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 19:51:00</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [CHHOTU CD-1782281511956.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Invoice [CHHOTU INV-1782281512087.pdf]: Invoice Number mismatch. Extracted: 'INZ/74/A000199', Expected: 'INV27A000190'</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:52:04</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>T6D12144</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>LALU KUMAR YADAV</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 21:02:50</t>
+          <t>LYL27A000024</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SARWAN KUMAR</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>NEXGEN SOLUTIONS TECHNOLOGIES (P)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>HAZARIBAGH</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [SARWA CD-1782281211888.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Invoice [SARWA INV-1782281212011.pdf]: Invoice Number mismatch. Extracted: 'INVZ200105276', Expected: 'INV27A000167', Invoice [SARWA INV-1782281212011.pdf]: Failed to extract bonus amount from invoice (Expected: 5000.0), Ledger [SAWA LED-1782281211751.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 5000.0, Ledger [SAWA LED-1782281211751.pdf]: Welcome Bonus amount mismatch in ledger. Expected: 5000.0, Cross-Validation Mismatch: Stamp is missing on one or both documents., Cross-Validation Mismatch: All required names extracted successfully., Cross-Validation Mismatch: Good image quality, clear stamps and signatures.</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:54:23</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>T6D11505</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>RISWAT SAH</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 21:04:13</t>
+          <t>LYL27A000113</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SHREE BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>TITANIA MOTOCORP PVT LTD</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>ORMANJHI</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DISC-1782278876823.pdf]: Customer name mismatch (30.8% similarity), Disclaimer [DISC-1782278876823.pdf]: Welcome Bonus amount invalid format, Invoice [INV-1782278876968.pdf]: Failed to extract bonus amount from invoice (Expected: 15000.0), Relationship document: No Aadhaar/PAN found for relative 'SHREE BALAJI ENTERPRISES' (Relationship: Partnership)</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:58:52</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>T6E15949</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>MANORANJAN SINGH</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+          <t>LYL27A000015</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>23 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Mukesh Kumar</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>SHASHANK AUTO PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>MUZAFFARPUR SHOWROOM</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 21:05:35</t>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:05:47</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>T6E12836</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>AFTAB ALAM</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 21:06:56</t>
+          <t>LYL27A000070</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>GSSK ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOCOACH PVT.LTD.</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>JAMSHEDPUR</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Invoice [INVOICE-1782102623562.pdf]: Invoice Number mismatch. Extracted: 'INV27400119', Expected: 'INV27A000191'</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:09:52</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>T6D15451</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>VIKASH KUMAR GUPTA</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+          <t>LYL27F000007</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>21 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>MUNNA KUMAR</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>KURZI_PATLIPUTRA_SH</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 21:08:17</t>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:16:47</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>T6A10843</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SANTOSH KUMAR MISHRA</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
+          <t>LYL27D000037</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>21 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>LALU KUMAR YADAV</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 21:09:39</t>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:25:43</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>T6E12979</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000036</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>21 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>RISWAT SAH</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:27:06</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>T6E16530</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ANKUSH KUMAR</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000035</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>21 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>MANORANJAN SINGH</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23 21:11:01</t>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:28:28</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>T6D12058</t>
         </is>
       </c>
     </row>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1178,6 +1178,122 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000037</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>21 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>LALU KUMAR YADAV</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DIS-1782026113285.pdf]: Chassis No mismatch (doc: T6212797 vs web: T6E12979)</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 15:43:14</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>T6E12979</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000037</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>21 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>LALU KUMAR YADAV</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:12:12</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>T6E12979</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L377"/>
+  <dimension ref="A1:L378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22951,6 +22951,66 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B378" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D378" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E378" s="4" t="inlineStr">
+        <is>
+          <t>Dinesh Sah</t>
+        </is>
+      </c>
+      <c r="F378" s="4" t="inlineStr">
+        <is>
+          <t>SHREE R C ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G378" s="4" t="inlineStr">
+        <is>
+          <t>MOTIHARI</t>
+        </is>
+      </c>
+      <c r="H378" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I378" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J378" s="4" t="inlineStr">
+        <is>
+          <t>Invoice [bill(1)-1782299742590.pdf]: OpenAI Validation Failed - Customer signature is missing.</t>
+        </is>
+      </c>
+      <c r="K378" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:24:16</t>
+        </is>
+      </c>
+      <c r="L378" s="4" t="inlineStr">
+        <is>
+          <t>T6C11232</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L378"/>
+  <dimension ref="A1:L484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23011,6 +23011,6362 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B379" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000365</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E379" s="4" t="inlineStr">
+        <is>
+          <t>SONALI NAYAK</t>
+        </is>
+      </c>
+      <c r="F379" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G379" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H379" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I379" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J379" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: Customer name mismatch (37.5% similarity), Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: New Vehicle Model mismatch (portal model 'SUPRO-MT' not found in disclaimer), Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: Invoice No mismatch (doc: None vs web: INV27A000877), Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: Welcome Bonus mismatch (doc: 55000.0 vs expected: 5000.0)</t>
+        </is>
+      </c>
+      <c r="K379" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:08:54</t>
+        </is>
+      </c>
+      <c r="L379" s="4" t="inlineStr">
+        <is>
+          <t>T6C10044</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B380" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000364</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>SATYABHAMA PRADHAN</t>
+        </is>
+      </c>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G380" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H380" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I380" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J380" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Customer name mismatch (51.9% similarity), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Chassis No mismatch (doc: NOT6D14496 vs web: T6E16670), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice No mismatch (doc: None vs web: INV27A000806), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice Date mismatch (doc: 08 May 2026 vs web: 26 May 2026), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Welcome Bonus mismatch (doc: 515000.0 vs expected: 15000.0), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Customer name mismatch (16.7% similarity), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Dealership name mismatch. Extracted: 'Orissa LTD', Expected: 'ADITYA MOTORS', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Invoice Number mismatch. Extracted: 'INV2/A00O546NaMC', Expected: 'INV27A000806', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Amount mismatch. Extracted Bonus: 115515000001151.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Failed to identify vehicle model on invoice, Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: Customer name mismatch (46.7% similarity), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K380" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:16:29</t>
+        </is>
+      </c>
+      <c r="L380" s="4" t="inlineStr">
+        <is>
+          <t>T6E16670</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B381" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C381" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D381" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E381" s="4" t="inlineStr">
+        <is>
+          <t>Rohit Gajendra</t>
+        </is>
+      </c>
+      <c r="F381" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G381" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H381" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I381" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J381" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K381" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:16:36</t>
+        </is>
+      </c>
+      <c r="L381" s="4" t="inlineStr">
+        <is>
+          <t>T2D72269</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B382" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000058</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E382" s="4" t="inlineStr">
+        <is>
+          <t>SANJAY BHOI</t>
+        </is>
+      </c>
+      <c r="F382" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G382" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H382" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I382" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J382" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K382" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:16:42</t>
+        </is>
+      </c>
+      <c r="L382" s="4" t="inlineStr">
+        <is>
+          <t>T1E90124</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B383" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000057</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E383" s="4" t="inlineStr">
+        <is>
+          <t>DIBYANSHU KATARI</t>
+        </is>
+      </c>
+      <c r="F383" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G383" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H383" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I383" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J383" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K383" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:16:48</t>
+        </is>
+      </c>
+      <c r="L383" s="4" t="inlineStr">
+        <is>
+          <t>T6E25145</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B384" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000160</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="inlineStr">
+        <is>
+          <t>RAM CHANDRA ORAM</t>
+        </is>
+      </c>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G384" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H384" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I384" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J384" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K384" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:16:55</t>
+        </is>
+      </c>
+      <c r="L384" s="4" t="inlineStr">
+        <is>
+          <t>T1D87625</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B385" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000247</t>
+        </is>
+      </c>
+      <c r="C385" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E385" s="4" t="inlineStr">
+        <is>
+          <t>IBEXX ORGANICS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F385" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CENTRE</t>
+        </is>
+      </c>
+      <c r="G385" s="4" t="inlineStr">
+        <is>
+          <t>BILASPUR</t>
+        </is>
+      </c>
+      <c r="H385" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I385" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J385" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DS (8)-1782366699875.pdf]: Chassis No mismatch (doc: MATUVZCVXTBA15194ENGINENO vs web: T6A15194), Disclaimer [DS (8)-1782366699875.pdf]: Invoice No mismatch (doc: None vs web: INV27B000312), Disclaimer [DS (8)-1782366699875.pdf]: Invoice Date mismatch (doc: 16/0342026 vs web: 16 May 2026), Disclaimer [DS (8)-1782366699875.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Invoice [INV-1782366700041.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [INV-1782366700041.pdf]: Dealership name mismatch. Extracted: 'IBEXI ORGANICS PRIVATE LIMITED', Expected: 'AUTO CENTRE', Invoice [INV-1782366700041.pdf]: Invoice Number mismatch. Extracted: 'DELALLE', Expected: 'INV27B000312', Invoice [INV-1782366700041.pdf]: Failed to extract bonus amount from invoice (Expected: 15000.0), Invoice [INV-1782366700041.pdf]: Failed to identify vehicle model on invoice, Invoice [INV-1782366700041.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [LES-1782366699695.pdf]: Stamp/signature missing or invalid, Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K385" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:24:19</t>
+        </is>
+      </c>
+      <c r="L385" s="4" t="inlineStr">
+        <is>
+          <t>T6A15194</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B386" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000337</t>
+        </is>
+      </c>
+      <c r="C386" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E386" s="4" t="inlineStr">
+        <is>
+          <t>Subala Daleei</t>
+        </is>
+      </c>
+      <c r="F386" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G386" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H386" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I386" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J386" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K386" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:24:26</t>
+        </is>
+      </c>
+      <c r="L386" s="4" t="inlineStr">
+        <is>
+          <t>T6E60920</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B387" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000062</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D387" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E387" s="4" t="inlineStr">
+        <is>
+          <t>Poornima Netam</t>
+        </is>
+      </c>
+      <c r="F387" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G387" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H387" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I387" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J387" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K387" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:24:32</t>
+        </is>
+      </c>
+      <c r="L387" s="4" t="inlineStr">
+        <is>
+          <t>T2D71946</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B388" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000053</t>
+        </is>
+      </c>
+      <c r="C388" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E388" s="4" t="inlineStr">
+        <is>
+          <t>Ankit Bhasin</t>
+        </is>
+      </c>
+      <c r="F388" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G388" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H388" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I388" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J388" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K388" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:24:39</t>
+        </is>
+      </c>
+      <c r="L388" s="4" t="inlineStr">
+        <is>
+          <t>S6C68602</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B389" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000216</t>
+        </is>
+      </c>
+      <c r="C389" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D389" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E389" s="4" t="inlineStr">
+        <is>
+          <t>GANESH RAM SAHU</t>
+        </is>
+      </c>
+      <c r="F389" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G389" s="4" t="inlineStr">
+        <is>
+          <t>BOLANGIR</t>
+        </is>
+      </c>
+      <c r="H389" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I389" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J389" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K389" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:24:44</t>
+        </is>
+      </c>
+      <c r="L389" s="4" t="inlineStr">
+        <is>
+          <t>T2E26985</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B390" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000126</t>
+        </is>
+      </c>
+      <c r="C390" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D390" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E390" s="4" t="inlineStr">
+        <is>
+          <t>Seema Tikariha</t>
+        </is>
+      </c>
+      <c r="F390" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G390" s="4" t="inlineStr">
+        <is>
+          <t>BHILAI_3S</t>
+        </is>
+      </c>
+      <c r="H390" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I390" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J390" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K390" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:24:50</t>
+        </is>
+      </c>
+      <c r="L390" s="4" t="inlineStr">
+        <is>
+          <t>T6D67907</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B391" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000319</t>
+        </is>
+      </c>
+      <c r="C391" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D391" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E391" s="4" t="inlineStr">
+        <is>
+          <t>Puspita Sahoo</t>
+        </is>
+      </c>
+      <c r="F391" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G391" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H391" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I391" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J391" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K391" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:24:56</t>
+        </is>
+      </c>
+      <c r="L391" s="4" t="inlineStr">
+        <is>
+          <t>T6E56913</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B392" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000068</t>
+        </is>
+      </c>
+      <c r="C392" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="inlineStr">
+        <is>
+          <t>Rajesh Tellewar</t>
+        </is>
+      </c>
+      <c r="F392" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G392" s="4" t="inlineStr">
+        <is>
+          <t>MOWA</t>
+        </is>
+      </c>
+      <c r="H392" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I392" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J392" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K392" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:25:02</t>
+        </is>
+      </c>
+      <c r="L392" s="4" t="inlineStr">
+        <is>
+          <t>T6D69218</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B393" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000364</t>
+        </is>
+      </c>
+      <c r="C393" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>SATYABHAMA PRADHAN</t>
+        </is>
+      </c>
+      <c r="F393" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H393" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I393" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J393" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Customer name mismatch (51.9% similarity), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Chassis No mismatch (doc: NOT6D14496 vs web: T6E16670), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice No mismatch (doc: None vs web: INV27A000806), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice Date mismatch (doc: 08 May 2026 vs web: 26 May 2026), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Welcome Bonus mismatch (doc: 515000.0 vs expected: 15000.0), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Customer name mismatch (16.7% similarity), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Dealership name mismatch. Extracted: 'Orissa LTD', Expected: 'ADITYA MOTORS', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Invoice Number mismatch. Extracted: 'INV2/A00O546NaMC', Expected: 'INV27A000806', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Amount mismatch. Extracted Bonus: 115515000001151.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Failed to identify vehicle model on invoice, Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: Customer name mismatch (46.7% similarity), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K393" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:45:16</t>
+        </is>
+      </c>
+      <c r="L393" s="4" t="inlineStr">
+        <is>
+          <t>T6E16670</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B394" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C394" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>Rohit Gajendra</t>
+        </is>
+      </c>
+      <c r="F394" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G394" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H394" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I394" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J394" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K394" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:45:24</t>
+        </is>
+      </c>
+      <c r="L394" s="4" t="inlineStr">
+        <is>
+          <t>T2D72269</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B395" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000058</t>
+        </is>
+      </c>
+      <c r="C395" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D395" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E395" s="4" t="inlineStr">
+        <is>
+          <t>SANJAY BHOI</t>
+        </is>
+      </c>
+      <c r="F395" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G395" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H395" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I395" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J395" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K395" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:45:30</t>
+        </is>
+      </c>
+      <c r="L395" s="4" t="inlineStr">
+        <is>
+          <t>T1E90124</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B396" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000057</t>
+        </is>
+      </c>
+      <c r="C396" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E396" s="4" t="inlineStr">
+        <is>
+          <t>DIBYANSHU KATARI</t>
+        </is>
+      </c>
+      <c r="F396" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G396" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H396" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I396" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J396" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K396" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:45:36</t>
+        </is>
+      </c>
+      <c r="L396" s="4" t="inlineStr">
+        <is>
+          <t>T6E25145</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B397" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000160</t>
+        </is>
+      </c>
+      <c r="C397" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D397" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E397" s="4" t="inlineStr">
+        <is>
+          <t>RAM CHANDRA ORAM</t>
+        </is>
+      </c>
+      <c r="F397" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G397" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H397" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I397" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J397" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K397" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:45:44</t>
+        </is>
+      </c>
+      <c r="L397" s="4" t="inlineStr">
+        <is>
+          <t>T1D87625</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B398" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000365</t>
+        </is>
+      </c>
+      <c r="C398" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="inlineStr">
+        <is>
+          <t>SONALI NAYAK</t>
+        </is>
+      </c>
+      <c r="F398" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G398" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H398" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I398" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J398" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: Customer name mismatch (37.5% similarity), Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: New Vehicle Model mismatch (portal model 'SUPRO-MT' not found in disclaimer), Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: Invoice No mismatch (doc: None vs web: INV27A000877), Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: Welcome Bonus mismatch (doc: 55000.0 vs expected: 5000.0)</t>
+        </is>
+      </c>
+      <c r="K398" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:57:07</t>
+        </is>
+      </c>
+      <c r="L398" s="4" t="inlineStr">
+        <is>
+          <t>T6C10044</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B399" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000364</t>
+        </is>
+      </c>
+      <c r="C399" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D399" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E399" s="4" t="inlineStr">
+        <is>
+          <t>SATYABHAMA PRADHAN</t>
+        </is>
+      </c>
+      <c r="F399" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G399" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H399" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I399" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J399" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Customer name mismatch (51.9% similarity), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Chassis No mismatch (doc: NOT6D14496 vs web: T6E16670), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice No mismatch (doc: None vs web: INV27A000806), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice Date mismatch (doc: 08 May 2026 vs web: 26 May 2026), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Welcome Bonus mismatch (doc: 515000.0 vs expected: 15000.0), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Customer name mismatch (16.7% similarity), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Dealership name mismatch. Extracted: 'Orissa LTD', Expected: 'ADITYA MOTORS', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Invoice Number mismatch. Extracted: 'INV2/A00O546NaMC', Expected: 'INV27A000806', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Amount mismatch. Extracted Bonus: 115515000001151.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Failed to identify vehicle model on invoice, Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: Customer name mismatch (46.7% similarity), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K399" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:04:54</t>
+        </is>
+      </c>
+      <c r="L399" s="4" t="inlineStr">
+        <is>
+          <t>T6E16670</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C400" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>Rohit Gajendra</t>
+        </is>
+      </c>
+      <c r="F400" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G400" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H400" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I400" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J400" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K400" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:05:07</t>
+        </is>
+      </c>
+      <c r="L400" s="4" t="inlineStr">
+        <is>
+          <t>T2D72269</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B401" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000058</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>SANJAY BHOI</t>
+        </is>
+      </c>
+      <c r="F401" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G401" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H401" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I401" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J401" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K401" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:05:20</t>
+        </is>
+      </c>
+      <c r="L401" s="4" t="inlineStr">
+        <is>
+          <t>T1E90124</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B402" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000057</t>
+        </is>
+      </c>
+      <c r="C402" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>DIBYANSHU KATARI</t>
+        </is>
+      </c>
+      <c r="F402" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G402" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H402" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I402" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J402" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K402" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:05:34</t>
+        </is>
+      </c>
+      <c r="L402" s="4" t="inlineStr">
+        <is>
+          <t>T6E25145</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B403" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000160</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D403" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>RAM CHANDRA ORAM</t>
+        </is>
+      </c>
+      <c r="F403" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G403" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H403" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I403" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J403" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K403" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:05:50</t>
+        </is>
+      </c>
+      <c r="L403" s="4" t="inlineStr">
+        <is>
+          <t>T1D87625</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B404" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000247</t>
+        </is>
+      </c>
+      <c r="C404" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D404" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E404" s="4" t="inlineStr">
+        <is>
+          <t>IBEXX ORGANICS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F404" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CENTRE</t>
+        </is>
+      </c>
+      <c r="G404" s="4" t="inlineStr">
+        <is>
+          <t>BILASPUR</t>
+        </is>
+      </c>
+      <c r="H404" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I404" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J404" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DS (8)-1782366699875.pdf]: Chassis No mismatch (doc: MATUVZCVXTBA15194ENGINENO vs web: T6A15194), Disclaimer [DS (8)-1782366699875.pdf]: Invoice No mismatch (doc: None vs web: INV27B000312), Disclaimer [DS (8)-1782366699875.pdf]: Invoice Date mismatch (doc: 16/0342026 vs web: 16 May 2026), Disclaimer [DS (8)-1782366699875.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Invoice [INV-1782366700041.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [INV-1782366700041.pdf]: Dealership name mismatch. Extracted: 'IBEXI ORGANICS PRIVATE LIMITED', Expected: 'AUTO CENTRE', Invoice [INV-1782366700041.pdf]: Invoice Number mismatch. Extracted: 'DELALLE', Expected: 'INV27B000312', Invoice [INV-1782366700041.pdf]: Failed to extract bonus amount from invoice (Expected: 15000.0), Invoice [INV-1782366700041.pdf]: Failed to identify vehicle model on invoice, Invoice [INV-1782366700041.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [LES-1782366699695.pdf]: Stamp/signature missing or invalid, Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K404" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:14:03</t>
+        </is>
+      </c>
+      <c r="L404" s="4" t="inlineStr">
+        <is>
+          <t>T6A15194</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B405" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000337</t>
+        </is>
+      </c>
+      <c r="C405" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>Subala Daleei</t>
+        </is>
+      </c>
+      <c r="F405" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G405" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H405" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I405" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J405" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K405" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:14:18</t>
+        </is>
+      </c>
+      <c r="L405" s="4" t="inlineStr">
+        <is>
+          <t>T6E60920</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B406" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000062</t>
+        </is>
+      </c>
+      <c r="C406" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>Poornima Netam</t>
+        </is>
+      </c>
+      <c r="F406" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G406" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H406" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I406" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J406" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K406" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:14:35</t>
+        </is>
+      </c>
+      <c r="L406" s="4" t="inlineStr">
+        <is>
+          <t>T2D71946</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B407" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000053</t>
+        </is>
+      </c>
+      <c r="C407" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D407" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>Ankit Bhasin</t>
+        </is>
+      </c>
+      <c r="F407" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G407" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H407" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I407" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J407" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K407" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:14:51</t>
+        </is>
+      </c>
+      <c r="L407" s="4" t="inlineStr">
+        <is>
+          <t>S6C68602</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B408" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000216</t>
+        </is>
+      </c>
+      <c r="C408" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E408" s="4" t="inlineStr">
+        <is>
+          <t>GANESH RAM SAHU</t>
+        </is>
+      </c>
+      <c r="F408" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G408" s="4" t="inlineStr">
+        <is>
+          <t>BOLANGIR</t>
+        </is>
+      </c>
+      <c r="H408" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I408" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J408" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K408" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:15:05</t>
+        </is>
+      </c>
+      <c r="L408" s="4" t="inlineStr">
+        <is>
+          <t>T2E26985</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B409" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000126</t>
+        </is>
+      </c>
+      <c r="C409" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D409" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E409" s="4" t="inlineStr">
+        <is>
+          <t>Seema Tikariha</t>
+        </is>
+      </c>
+      <c r="F409" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G409" s="4" t="inlineStr">
+        <is>
+          <t>BHILAI_3S</t>
+        </is>
+      </c>
+      <c r="H409" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I409" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J409" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K409" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:15:21</t>
+        </is>
+      </c>
+      <c r="L409" s="4" t="inlineStr">
+        <is>
+          <t>T6D67907</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B410" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000319</t>
+        </is>
+      </c>
+      <c r="C410" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D410" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E410" s="4" t="inlineStr">
+        <is>
+          <t>Puspita Sahoo</t>
+        </is>
+      </c>
+      <c r="F410" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G410" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H410" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I410" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J410" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K410" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:15:37</t>
+        </is>
+      </c>
+      <c r="L410" s="4" t="inlineStr">
+        <is>
+          <t>T6E56913</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B411" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000068</t>
+        </is>
+      </c>
+      <c r="C411" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D411" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E411" s="4" t="inlineStr">
+        <is>
+          <t>Rajesh Tellewar</t>
+        </is>
+      </c>
+      <c r="F411" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G411" s="4" t="inlineStr">
+        <is>
+          <t>MOWA</t>
+        </is>
+      </c>
+      <c r="H411" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I411" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J411" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K411" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:15:53</t>
+        </is>
+      </c>
+      <c r="L411" s="4" t="inlineStr">
+        <is>
+          <t>T6D69218</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B412" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000365</t>
+        </is>
+      </c>
+      <c r="C412" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D412" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E412" s="4" t="inlineStr">
+        <is>
+          <t>SONALI NAYAK</t>
+        </is>
+      </c>
+      <c r="F412" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G412" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H412" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I412" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J412" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: New Vehicle Model mismatch (portal model 'SUPRO-MT' not found in disclaimer), Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: Welcome Bonus mismatch (doc: 55000.0 vs expected: 5000.0), East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K412" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:45:24</t>
+        </is>
+      </c>
+      <c r="L412" s="4" t="inlineStr">
+        <is>
+          <t>T6C10044</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000364</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D413" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>SATYABHAMA PRADHAN</t>
+        </is>
+      </c>
+      <c r="F413" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G413" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H413" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I413" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J413" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Customer name mismatch (51.9% similarity), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Chassis No mismatch (doc: NOT6D14496 vs web: T6E16670), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice No mismatch (doc: LNV27AO00546 vs web: INV27A000806), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice Date mismatch (doc: 08 May 2026 vs web: 26 May 2026), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Customer name mismatch (16.7% similarity), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Dealership name mismatch. Extracted: 'Orissa LTD', Expected: 'ADITYA MOTORS', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Invoice Number mismatch. Extracted: 'INV2/A00O546NaMC', Expected: 'INV27A000806', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Amount mismatch. Extracted Bonus: 115515000001151.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Failed to identify vehicle model on invoice, Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: Customer name mismatch (46.7% similarity), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K413" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:53:14</t>
+        </is>
+      </c>
+      <c r="L413" s="4" t="inlineStr">
+        <is>
+          <t>T6E16670</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B414" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000355</t>
+        </is>
+      </c>
+      <c r="C414" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D414" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E414" s="4" t="inlineStr">
+        <is>
+          <t>Rakesh Nigam</t>
+        </is>
+      </c>
+      <c r="F414" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G414" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H414" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I414" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J414" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K414" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:53:22</t>
+        </is>
+      </c>
+      <c r="L414" s="4" t="inlineStr">
+        <is>
+          <t>T2C48500</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C415" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D415" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E415" s="4" t="inlineStr">
+        <is>
+          <t>Rohit Gajendra</t>
+        </is>
+      </c>
+      <c r="F415" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G415" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H415" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I415" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J415" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K415" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:53:28</t>
+        </is>
+      </c>
+      <c r="L415" s="4" t="inlineStr">
+        <is>
+          <t>T2D72269</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B416" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000058</t>
+        </is>
+      </c>
+      <c r="C416" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D416" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E416" s="4" t="inlineStr">
+        <is>
+          <t>SANJAY BHOI</t>
+        </is>
+      </c>
+      <c r="F416" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G416" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H416" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I416" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J416" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K416" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:53:35</t>
+        </is>
+      </c>
+      <c r="L416" s="4" t="inlineStr">
+        <is>
+          <t>T1E90124</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B417" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000057</t>
+        </is>
+      </c>
+      <c r="C417" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D417" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E417" s="4" t="inlineStr">
+        <is>
+          <t>DIBYANSHU KATARI</t>
+        </is>
+      </c>
+      <c r="F417" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G417" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H417" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I417" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J417" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K417" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:53:41</t>
+        </is>
+      </c>
+      <c r="L417" s="4" t="inlineStr">
+        <is>
+          <t>T6E25145</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B418" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000160</t>
+        </is>
+      </c>
+      <c r="C418" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D418" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E418" s="4" t="inlineStr">
+        <is>
+          <t>RAM CHANDRA ORAM</t>
+        </is>
+      </c>
+      <c r="F418" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G418" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H418" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I418" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J418" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K418" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 12:53:47</t>
+        </is>
+      </c>
+      <c r="L418" s="4" t="inlineStr">
+        <is>
+          <t>T1D87625</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B419" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000365</t>
+        </is>
+      </c>
+      <c r="C419" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D419" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E419" s="4" t="inlineStr">
+        <is>
+          <t>SONALI NAYAK</t>
+        </is>
+      </c>
+      <c r="F419" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G419" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H419" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I419" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J419" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [SONALI NAYAK DIS-1782400416409.pdf]: New Vehicle Model mismatch (portal model 'SUPRO-MT' not found in disclaimer), East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K419" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:10:44</t>
+        </is>
+      </c>
+      <c r="L419" s="4" t="inlineStr">
+        <is>
+          <t>T6C10044</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B420" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000364</t>
+        </is>
+      </c>
+      <c r="C420" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D420" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="inlineStr">
+        <is>
+          <t>SATYABHAMA PRADHAN</t>
+        </is>
+      </c>
+      <c r="F420" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G420" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H420" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I420" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J420" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Customer name mismatch (17.4% similarity), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Chassis No mismatch (doc: NOT6D14496 vs web: T6E16670), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice No mismatch (doc: LNV27AO00546 vs web: INV27A000806), Disclaimer [ASHOK KUMAR DASH DIS-1782400276191.pdf]: Invoice Date mismatch (doc: 08 May 2026 vs web: 26 May 2026), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Customer name mismatch (18.5% similarity), Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Dealership name mismatch. Extracted: 'Orissa LTD', Expected: 'ADITYA MOTORS', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Invoice Number mismatch. Extracted: 'INV2/A00O546NaMC', Expected: 'INV27A000806', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Amount mismatch. Extracted Bonus: 115000001151.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: Failed to identify vehicle model on invoice, Invoice [ASHOK KUMAR DASH INV-1782400276331.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Ledger [ASHOK KUMAR DASH LEDGER_0001-1782400276029.pdf]: Customer name mismatch (46.7% similarity), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K420" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:25:18</t>
+        </is>
+      </c>
+      <c r="L420" s="4" t="inlineStr">
+        <is>
+          <t>T6E16670</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B421" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000355</t>
+        </is>
+      </c>
+      <c r="C421" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D421" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E421" s="4" t="inlineStr">
+        <is>
+          <t>Rakesh Nigam</t>
+        </is>
+      </c>
+      <c r="F421" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G421" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H421" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I421" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J421" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K421" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:25:30</t>
+        </is>
+      </c>
+      <c r="L421" s="4" t="inlineStr">
+        <is>
+          <t>T2C48500</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B422" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C422" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D422" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E422" s="4" t="inlineStr">
+        <is>
+          <t>Rohit Gajendra</t>
+        </is>
+      </c>
+      <c r="F422" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G422" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H422" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I422" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J422" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K422" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:25:38</t>
+        </is>
+      </c>
+      <c r="L422" s="4" t="inlineStr">
+        <is>
+          <t>T2D72269</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B423" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000058</t>
+        </is>
+      </c>
+      <c r="C423" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D423" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E423" s="4" t="inlineStr">
+        <is>
+          <t>SANJAY BHOI</t>
+        </is>
+      </c>
+      <c r="F423" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G423" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H423" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I423" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J423" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K423" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:25:46</t>
+        </is>
+      </c>
+      <c r="L423" s="4" t="inlineStr">
+        <is>
+          <t>T1E90124</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B424" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000057</t>
+        </is>
+      </c>
+      <c r="C424" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D424" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E424" s="4" t="inlineStr">
+        <is>
+          <t>DIBYANSHU KATARI</t>
+        </is>
+      </c>
+      <c r="F424" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G424" s="4" t="inlineStr">
+        <is>
+          <t>BARGARH_3S</t>
+        </is>
+      </c>
+      <c r="H424" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I424" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J424" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K424" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:25:57</t>
+        </is>
+      </c>
+      <c r="L424" s="4" t="inlineStr">
+        <is>
+          <t>T6E25145</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B425" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000160</t>
+        </is>
+      </c>
+      <c r="C425" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D425" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E425" s="4" t="inlineStr">
+        <is>
+          <t>RAM CHANDRA ORAM</t>
+        </is>
+      </c>
+      <c r="F425" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G425" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H425" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I425" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J425" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K425" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:26:05</t>
+        </is>
+      </c>
+      <c r="L425" s="4" t="inlineStr">
+        <is>
+          <t>T1D87625</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B426" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000158</t>
+        </is>
+      </c>
+      <c r="C426" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D426" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="inlineStr">
+        <is>
+          <t>Jitendra Kumar Sahoo</t>
+        </is>
+      </c>
+      <c r="F426" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G426" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H426" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I426" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J426" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K426" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:26:13</t>
+        </is>
+      </c>
+      <c r="L426" s="4" t="inlineStr">
+        <is>
+          <t>T6E58673</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B427" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000157</t>
+        </is>
+      </c>
+      <c r="C427" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D427" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E427" s="4" t="inlineStr">
+        <is>
+          <t>SUNANDA MAHAPATRA</t>
+        </is>
+      </c>
+      <c r="F427" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G427" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H427" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I427" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J427" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K427" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:26:21</t>
+        </is>
+      </c>
+      <c r="L427" s="4" t="inlineStr">
+        <is>
+          <t>R6L61743</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B428" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000155</t>
+        </is>
+      </c>
+      <c r="C428" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D428" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E428" s="4" t="inlineStr">
+        <is>
+          <t>Ashutosh Panda</t>
+        </is>
+      </c>
+      <c r="F428" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G428" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H428" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I428" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J428" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K428" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:26:30</t>
+        </is>
+      </c>
+      <c r="L428" s="4" t="inlineStr">
+        <is>
+          <t>S2L23209</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B429" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000247</t>
+        </is>
+      </c>
+      <c r="C429" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D429" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E429" s="4" t="inlineStr">
+        <is>
+          <t>IBEXX ORGANICS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F429" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CENTRE</t>
+        </is>
+      </c>
+      <c r="G429" s="4" t="inlineStr">
+        <is>
+          <t>BILASPUR</t>
+        </is>
+      </c>
+      <c r="H429" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I429" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J429" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DS (8)-1782366699875.pdf]: Chassis No mismatch (doc: MATUVZCVXTBA15194ENGINENO vs web: T6A15194), Disclaimer [DS (8)-1782366699875.pdf]: Invoice No mismatch (doc: None vs web: INV27B000312), Disclaimer [DS (8)-1782366699875.pdf]: Invoice Date mismatch (doc: 16/0342026 vs web: 16 May 2026), Disclaimer [DS (8)-1782366699875.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Invoice [INV-1782366700041.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [INV-1782366700041.pdf]: Dealership name mismatch. Extracted: 'IBEXI ORGANICS PRIVATE LIMITED', Expected: 'AUTO CENTRE', Invoice [INV-1782366700041.pdf]: Invoice Number mismatch. Extracted: 'DELALLE', Expected: 'INV27B000312', Invoice [INV-1782366700041.pdf]: Failed to extract bonus amount from invoice (Expected: 15000.0), Invoice [INV-1782366700041.pdf]: Failed to identify vehicle model on invoice, Invoice [INV-1782366700041.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [LES-1782366699695.pdf]: Stamp/signature missing or invalid, Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K429" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:41:06</t>
+        </is>
+      </c>
+      <c r="L429" s="4" t="inlineStr">
+        <is>
+          <t>T6A15194</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B430" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000337</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D430" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E430" s="4" t="inlineStr">
+        <is>
+          <t>Subala Daleei</t>
+        </is>
+      </c>
+      <c r="F430" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H430" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I430" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J430" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K430" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:41:17</t>
+        </is>
+      </c>
+      <c r="L430" s="4" t="inlineStr">
+        <is>
+          <t>T6E60920</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B431" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000062</t>
+        </is>
+      </c>
+      <c r="C431" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D431" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E431" s="4" t="inlineStr">
+        <is>
+          <t>Poornima Netam</t>
+        </is>
+      </c>
+      <c r="F431" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G431" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H431" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I431" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J431" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K431" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:41:25</t>
+        </is>
+      </c>
+      <c r="L431" s="4" t="inlineStr">
+        <is>
+          <t>T2D71946</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B432" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000053</t>
+        </is>
+      </c>
+      <c r="C432" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D432" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>Ankit Bhasin</t>
+        </is>
+      </c>
+      <c r="F432" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G432" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H432" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I432" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J432" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K432" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:41:33</t>
+        </is>
+      </c>
+      <c r="L432" s="4" t="inlineStr">
+        <is>
+          <t>S6C68602</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B433" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000216</t>
+        </is>
+      </c>
+      <c r="C433" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D433" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E433" s="4" t="inlineStr">
+        <is>
+          <t>GANESH RAM SAHU</t>
+        </is>
+      </c>
+      <c r="F433" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G433" s="4" t="inlineStr">
+        <is>
+          <t>BOLANGIR</t>
+        </is>
+      </c>
+      <c r="H433" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I433" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J433" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K433" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:41:41</t>
+        </is>
+      </c>
+      <c r="L433" s="4" t="inlineStr">
+        <is>
+          <t>T2E26985</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B434" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000126</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D434" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E434" s="4" t="inlineStr">
+        <is>
+          <t>Seema Tikariha</t>
+        </is>
+      </c>
+      <c r="F434" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G434" s="4" t="inlineStr">
+        <is>
+          <t>BHILAI_3S</t>
+        </is>
+      </c>
+      <c r="H434" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I434" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J434" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K434" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:41:51</t>
+        </is>
+      </c>
+      <c r="L434" s="4" t="inlineStr">
+        <is>
+          <t>T6D67907</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000319</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D435" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E435" s="4" t="inlineStr">
+        <is>
+          <t>Puspita Sahoo</t>
+        </is>
+      </c>
+      <c r="F435" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G435" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H435" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I435" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J435" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K435" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:41:58</t>
+        </is>
+      </c>
+      <c r="L435" s="4" t="inlineStr">
+        <is>
+          <t>T6E56913</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000068</t>
+        </is>
+      </c>
+      <c r="C436" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D436" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E436" s="4" t="inlineStr">
+        <is>
+          <t>Rajesh Tellewar</t>
+        </is>
+      </c>
+      <c r="F436" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G436" s="4" t="inlineStr">
+        <is>
+          <t>MOWA</t>
+        </is>
+      </c>
+      <c r="H436" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I436" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J436" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K436" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:42:06</t>
+        </is>
+      </c>
+      <c r="L436" s="4" t="inlineStr">
+        <is>
+          <t>T6D69218</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B437" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000099</t>
+        </is>
+      </c>
+      <c r="C437" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D437" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E437" s="4" t="inlineStr">
+        <is>
+          <t>ABIR BHATTACHARYA</t>
+        </is>
+      </c>
+      <c r="F437" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CARRIAGE PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G437" s="4" t="inlineStr">
+        <is>
+          <t>TOLLYGUNJ</t>
+        </is>
+      </c>
+      <c r="H437" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I437" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J437" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [LOYALTY-1782303385146.pdf]: Chassis No mismatch (doc: INVOICE vs web: T1C78660), Disclaimer [LOYALTY-1782303385146.pdf]: Invoice No mismatch (doc: None vs web: INV27A000202), Disclaimer [LOYALTY-1782303385146.pdf]: Invoice Date mismatch (doc: 30/04/2026 vs web: 28 Apr 2026), Invoice [TALLY_INV_merged-1782303385251.pdf]: Invoice Number mismatch. Extracted: 'RM/COMS/16/26-27', Expected: 'INV27A000202', Invoice [TALLY_INV_merged-1782303385251.pdf]: Failed to identify vehicle model on invoice, Invoice [TALLY_INV_merged-1782303385251.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K437" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:57:57</t>
+        </is>
+      </c>
+      <c r="L437" s="4" t="inlineStr">
+        <is>
+          <t>T1C78660</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B438" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000067</t>
+        </is>
+      </c>
+      <c r="C438" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D438" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E438" s="4" t="inlineStr">
+        <is>
+          <t>JD HARDSCAPES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F438" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G438" s="4" t="inlineStr">
+        <is>
+          <t>MOWA</t>
+        </is>
+      </c>
+      <c r="H438" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I438" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J438" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K438" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:58:07</t>
+        </is>
+      </c>
+      <c r="L438" s="4" t="inlineStr">
+        <is>
+          <t>T5E13622</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B439" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000098</t>
+        </is>
+      </c>
+      <c r="C439" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D439" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E439" s="4" t="inlineStr">
+        <is>
+          <t>ABIR BHATTACHARYA</t>
+        </is>
+      </c>
+      <c r="F439" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CARRIAGE PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G439" s="4" t="inlineStr">
+        <is>
+          <t>TOLLYGUNJ</t>
+        </is>
+      </c>
+      <c r="H439" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I439" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J439" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [LOYALTY-1782303385146.pdf]: Chassis No mismatch (doc: INVOICE vs web: T1D78995), Disclaimer [LOYALTY-1782303385146.pdf]: Invoice No mismatch (doc: None vs web: INV27A000203), Disclaimer [LOYALTY-1782303385146.pdf]: Invoice Date mismatch (doc: 30/04/2026 vs web: 28 Apr 2026), Invoice [TALLY_INV_merged-1782303385251.pdf]: Invoice Number mismatch. Extracted: 'RM/COMS/16/26-27', Expected: 'INV27A000203', Invoice [TALLY_INV_merged-1782303385251.pdf]: Failed to identify vehicle model on invoice, Invoice [TALLY_INV_merged-1782303385251.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K439" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:06:39</t>
+        </is>
+      </c>
+      <c r="L439" s="4" t="inlineStr">
+        <is>
+          <t>T1D78995</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B440" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000317</t>
+        </is>
+      </c>
+      <c r="C440" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D440" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E440" s="4" t="inlineStr">
+        <is>
+          <t>Iswar Chandra Behera</t>
+        </is>
+      </c>
+      <c r="F440" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G440" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H440" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I440" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J440" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K440" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:06:50</t>
+        </is>
+      </c>
+      <c r="L440" s="4" t="inlineStr">
+        <is>
+          <t>T6D68667</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B441" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000316</t>
+        </is>
+      </c>
+      <c r="C441" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D441" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E441" s="4" t="inlineStr">
+        <is>
+          <t>Rajendra Prasad Rout</t>
+        </is>
+      </c>
+      <c r="F441" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G441" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H441" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I441" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K441" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:06:58</t>
+        </is>
+      </c>
+      <c r="L441" s="4" t="inlineStr">
+        <is>
+          <t>T2D85502</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B442" s="4" t="inlineStr">
+        <is>
+          <t>LYL27F000012</t>
+        </is>
+      </c>
+      <c r="C442" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D442" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E442" s="4" t="inlineStr">
+        <is>
+          <t>Manindra Mondal</t>
+        </is>
+      </c>
+      <c r="F442" s="4" t="inlineStr">
+        <is>
+          <t>S. N. MOTORS PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G442" s="4" t="inlineStr">
+        <is>
+          <t>RAIGANJ_3S</t>
+        </is>
+      </c>
+      <c r="H442" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I442" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J442" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K442" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:08:23</t>
+        </is>
+      </c>
+      <c r="L442" s="4" t="inlineStr">
+        <is>
+          <t>T6E16144</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B443" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000315</t>
+        </is>
+      </c>
+      <c r="C443" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D443" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E443" s="4" t="inlineStr">
+        <is>
+          <t>PRASANNA KUMAR MAHARANA</t>
+        </is>
+      </c>
+      <c r="F443" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G443" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H443" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I443" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J443" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K443" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:08:33</t>
+        </is>
+      </c>
+      <c r="L443" s="4" t="inlineStr">
+        <is>
+          <t>T5E15967</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B444" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C444" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D444" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E444" s="4" t="inlineStr">
+        <is>
+          <t>Dinesh Sah</t>
+        </is>
+      </c>
+      <c r="F444" s="4" t="inlineStr">
+        <is>
+          <t>SHREE R C ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G444" s="4" t="inlineStr">
+        <is>
+          <t>MOTIHARI</t>
+        </is>
+      </c>
+      <c r="H444" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I444" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J444" s="4" t="inlineStr">
+        <is>
+          <t>Invoice [bill(1)-1782299742590.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [bill(1)-1782299742590.pdf]: Dealership name mismatch. Extracted: 'Mahindra Ltd', Expected: 'SHREE R C ENTERPRISES', Invoice [bill(1)-1782299742590.pdf]: Failed to extract bonus amount from invoice (Expected: 5000.0), Invoice [bill(1)-1782299742590.pdf]: Failed to identify vehicle model on invoice, Invoice [bill(1)-1782299742590.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Disclaimer [dis(2)-1782299742405.pdf]: Invoice No mismatch (doc: INV2ZAOOO235_INVOICEDATE25/05/2026 vs web: INV27A000235), Disclaimer [dis(2)-1782299742405.pdf]: Disclaimer Date Validation HOLD - Invoice date not readable, Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K444" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:20:31</t>
+        </is>
+      </c>
+      <c r="L444" s="4" t="inlineStr">
+        <is>
+          <t>T6C11232</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B445" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000310</t>
+        </is>
+      </c>
+      <c r="C445" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D445" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E445" s="4" t="inlineStr">
+        <is>
+          <t>Dibakar Mahapatra</t>
+        </is>
+      </c>
+      <c r="F445" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G445" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H445" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I445" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J445" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K445" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:20:42</t>
+        </is>
+      </c>
+      <c r="L445" s="4" t="inlineStr">
+        <is>
+          <t>T2E27168</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B446" s="4" t="inlineStr">
+        <is>
+          <t>LYL27O000010</t>
+        </is>
+      </c>
+      <c r="C446" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D446" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E446" s="4" t="inlineStr">
+        <is>
+          <t>VIJAY KUMAR JOSHI</t>
+        </is>
+      </c>
+      <c r="F446" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G446" s="4" t="inlineStr">
+        <is>
+          <t>BHUBANESHWAR_SH</t>
+        </is>
+      </c>
+      <c r="H446" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I446" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J446" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K446" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:20:50</t>
+        </is>
+      </c>
+      <c r="L446" s="4" t="inlineStr">
+        <is>
+          <t>T2E33167</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B447" s="4" t="inlineStr">
+        <is>
+          <t>LYL27O000007</t>
+        </is>
+      </c>
+      <c r="C447" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D447" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E447" s="4" t="inlineStr">
+        <is>
+          <t>BALARAM BARIK</t>
+        </is>
+      </c>
+      <c r="F447" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G447" s="4" t="inlineStr">
+        <is>
+          <t>BHUBANESHWAR_SH</t>
+        </is>
+      </c>
+      <c r="H447" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I447" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J447" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K447" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:20:59</t>
+        </is>
+      </c>
+      <c r="L447" s="4" t="inlineStr">
+        <is>
+          <t>T6D67029</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B448" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000057</t>
+        </is>
+      </c>
+      <c r="C448" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D448" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E448" s="4" t="inlineStr">
+        <is>
+          <t>GOUTAM PAUL</t>
+        </is>
+      </c>
+      <c r="F448" s="4" t="inlineStr">
+        <is>
+          <t>SONA WHEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G448" s="4" t="inlineStr">
+        <is>
+          <t>EKTIASAL -SILIGURI</t>
+        </is>
+      </c>
+      <c r="H448" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I448" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J448" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K448" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:22:24</t>
+        </is>
+      </c>
+      <c r="L448" s="4" t="inlineStr">
+        <is>
+          <t>T6E15801</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B449" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000097</t>
+        </is>
+      </c>
+      <c r="C449" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D449" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E449" s="4" t="inlineStr">
+        <is>
+          <t>Anjani Kumar Mishra</t>
+        </is>
+      </c>
+      <c r="F449" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CENTRE</t>
+        </is>
+      </c>
+      <c r="G449" s="4" t="inlineStr">
+        <is>
+          <t>RAIGARH</t>
+        </is>
+      </c>
+      <c r="H449" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I449" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J449" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K449" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:22:33</t>
+        </is>
+      </c>
+      <c r="L449" s="4" t="inlineStr">
+        <is>
+          <t>R2K76480</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B450" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000076</t>
+        </is>
+      </c>
+      <c r="C450" s="4" t="inlineStr">
+        <is>
+          <t>23 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>AYNAL HOSSAIN MONDAL</t>
+        </is>
+      </c>
+      <c r="F450" s="4" t="inlineStr">
+        <is>
+          <t>SHREE AUTOMOTIVE PVT LTD.</t>
+        </is>
+      </c>
+      <c r="G450" s="4" t="inlineStr">
+        <is>
+          <t>BARASAT</t>
+        </is>
+      </c>
+      <c r="H450" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I450" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J450" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K450" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:23:57</t>
+        </is>
+      </c>
+      <c r="L450" s="4" t="inlineStr">
+        <is>
+          <t>T6C13491</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B451" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000074</t>
+        </is>
+      </c>
+      <c r="C451" s="4" t="inlineStr">
+        <is>
+          <t>23 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D451" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E451" s="4" t="inlineStr">
+        <is>
+          <t>GHOSH TRAVELS &amp; TRANSPORT</t>
+        </is>
+      </c>
+      <c r="F451" s="4" t="inlineStr">
+        <is>
+          <t>SHREE AUTOMOTIVE PVT LTD.</t>
+        </is>
+      </c>
+      <c r="G451" s="4" t="inlineStr">
+        <is>
+          <t>BARASAT</t>
+        </is>
+      </c>
+      <c r="H451" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I451" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J451" s="4" t="inlineStr">
+        <is>
+          <t>Relationship Document Missing: Claimed 'Proprietorship' but neither GST Document nor Affidavit is uploaded., Relationship document: No Aadhaar/PAN found for relative 'MONOJIT GHOSH' (Relationship: Proprietorship), East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K451" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:25:23</t>
+        </is>
+      </c>
+      <c r="L451" s="4" t="inlineStr">
+        <is>
+          <t>T6B16721</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B452" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000123</t>
+        </is>
+      </c>
+      <c r="C452" s="4" t="inlineStr">
+        <is>
+          <t>23 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D452" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E452" s="4" t="inlineStr">
+        <is>
+          <t>POONDAS KOSLE</t>
+        </is>
+      </c>
+      <c r="F452" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G452" s="4" t="inlineStr">
+        <is>
+          <t>BHILAI_3S</t>
+        </is>
+      </c>
+      <c r="H452" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I452" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J452" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K452" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:26:49</t>
+        </is>
+      </c>
+      <c r="L452" s="4" t="inlineStr">
+        <is>
+          <t>T6A10636</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B453" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000122</t>
+        </is>
+      </c>
+      <c r="C453" s="4" t="inlineStr">
+        <is>
+          <t>23 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D453" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E453" s="4" t="inlineStr">
+        <is>
+          <t>DIKESH KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F453" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G453" s="4" t="inlineStr">
+        <is>
+          <t>BHILAI_3S</t>
+        </is>
+      </c>
+      <c r="H453" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I453" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J453" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K453" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:28:17</t>
+        </is>
+      </c>
+      <c r="L453" s="4" t="inlineStr">
+        <is>
+          <t>T6C18363</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B454" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000057</t>
+        </is>
+      </c>
+      <c r="C454" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D454" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>GOUTAM PAUL</t>
+        </is>
+      </c>
+      <c r="F454" s="4" t="inlineStr">
+        <is>
+          <t>SONA WHEELS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G454" s="4" t="inlineStr">
+        <is>
+          <t>EKTIASAL -SILIGURI</t>
+        </is>
+      </c>
+      <c r="H454" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I454" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J454" s="4" t="inlineStr">
+        <is>
+          <t>Invoice [INV GOUTAM PAUL-1782293029542.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [INV GOUTAM PAUL-1782293029542.pdf]: Invoice Number mismatch. Extracted: 'None', Expected: 'INV27A000493', Invoice [INV GOUTAM PAUL-1782293029542.pdf]: Amount mismatch. Extracted Bonus: 30000.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [INV GOUTAM PAUL-1782293029542.pdf]: Failed to identify vehicle model on invoice, Invoice [INV GOUTAM PAUL-1782293029542.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Disclaimer [INV GOUTAM PAUL-1782293029542.pdf]: Invoice No mismatch (doc: None vs web: INV27A000493), Disclaimer [INV GOUTAM PAUL-1782293029542.pdf]: Disclaimer Date Validation HOLD - Invoice date not readable, Disclaimer [INV GOUTAM PAUL-1782293029542.pdf]: Welcome Bonus mismatch (doc: 30000.0 vs expected: 15000.0), Ledger [LEDGER GOUTAM PAUL-1782293029184.pdf]: Customer name mismatch (75.0% similarity), Disclaimer [WELCOME DIS GOUTAM PAUL-1782293029418.pdf]: Invoice No mismatch (doc: None vs web: INV27A000493), Disclaimer [WELCOME DIS GOUTAM PAUL-1782293029418.pdf]: Disclaimer Date Validation HOLD - Invoice date not readable, Disclaimer [WELCOME DIS GOUTAM PAUL-1782293029418.pdf]: Welcome Bonus mismatch (doc: 30000.0 vs expected: 15000.0), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K454" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:48:33</t>
+        </is>
+      </c>
+      <c r="L454" s="4" t="inlineStr">
+        <is>
+          <t>T6E15801</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B455" s="4" t="inlineStr">
+        <is>
+          <t>LYL27F000044</t>
+        </is>
+      </c>
+      <c r="C455" s="4" t="inlineStr">
+        <is>
+          <t>20 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D455" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E455" s="4" t="inlineStr">
+        <is>
+          <t>PRAMOD KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="F455" s="4" t="inlineStr">
+        <is>
+          <t>CHANDAMAMA MOTORS</t>
+        </is>
+      </c>
+      <c r="G455" s="4" t="inlineStr">
+        <is>
+          <t>HAJIPUR_SH</t>
+        </is>
+      </c>
+      <c r="H455" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I455" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J455" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DISC-1781945515427.pdf]: Customer name mismatch (17.4% similarity), Disclaimer [DISC-1781945515427.pdf]: New Vehicle Model mismatch (portal model 'SUPRO-MT' not found in disclaimer), Disclaimer [DISC-1781945515427.pdf]: Chassis No mismatch (doc: MODEL vs web: T6D11589), Disclaimer [DISC-1781945515427.pdf]: Invoice No mismatch (doc: None vs web: INV27F000044), Disclaimer [DISC-1781945515427.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Disclaimer [DISC-1781945515427.pdf]: Welcome Bonus amount invalid format, Invoice [INV-1781945515551.pdf]: Customer name mismatch (17.4% similarity), Invoice [INV-1781945515551.pdf]: Dealership name mismatch. Extracted: 'Mahindra Ltd', Expected: 'CHANDAMAMA MOTORS', Invoice [INV-1781945515551.pdf]: Invoice Number mismatch. Extracted: 'INV27FO00036R270179514', Expected: 'INV27F000044', Invoice [INV-1781945515551.pdf]: Failed to identify vehicle model on invoice, Invoice [INV-1781945515551.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [LEDGER-1781945515285.pdf]: Customer name mismatch (66.7% similarity), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K455" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:58:46</t>
+        </is>
+      </c>
+      <c r="L455" s="4" t="inlineStr">
+        <is>
+          <t>T6D11589</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B456" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000009</t>
+        </is>
+      </c>
+      <c r="C456" s="4" t="inlineStr">
+        <is>
+          <t>20 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D456" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E456" s="4" t="inlineStr">
+        <is>
+          <t>NAHOLIA BOKULONI GAON PANCHAYET SAMABHI SAMITY LIMITED</t>
+        </is>
+      </c>
+      <c r="F456" s="4" t="inlineStr">
+        <is>
+          <t>R.D.AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G456" s="4" t="inlineStr">
+        <is>
+          <t>DULIJAN SALES</t>
+        </is>
+      </c>
+      <c r="H456" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I456" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J456" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K456" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 15:07:17</t>
+        </is>
+      </c>
+      <c r="L456" s="4" t="inlineStr">
+        <is>
+          <t>T1C76215</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B457" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000096</t>
+        </is>
+      </c>
+      <c r="C457" s="4" t="inlineStr">
+        <is>
+          <t>20 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D457" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E457" s="4" t="inlineStr">
+        <is>
+          <t>IMROJ MALLICK</t>
+        </is>
+      </c>
+      <c r="F457" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CARRIAGE PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G457" s="4" t="inlineStr">
+        <is>
+          <t>TOLLYGUNJ</t>
+        </is>
+      </c>
+      <c r="H457" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I457" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J457" s="4" t="inlineStr">
+        <is>
+          <t>Invoice [INV-1782379051929.pdf]: Customer name mismatch (17.4% similarity), Invoice [INV-1782379051929.pdf]: Invoice Number mismatch. Extracted: 'AVIJITDAS', Expected: 'INV27A000561', Invoice [INV-1782379051929.pdf]: Amount mismatch. Extracted Bonus: 30000.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [INV-1782379051929.pdf]: Failed to identify vehicle model on invoice, Invoice [INV-1782379051929.pdf]: OpenAI Validation Failed - API Error: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions, Ledger [LEDGER-1782379052109.pdf]: Customer name mismatch (48.0% similarity), Disclaimer [LOYALTY-1782379052335.pdf]: Customer name mismatch (11.1% similarity), Disclaimer [LOYALTY-1782379052335.pdf]: Chassis No mismatch (doc: MAIUVZCVXTGE16075 vs web: T6C13730), Disclaimer [LOYALTY-1782379052335.pdf]: Invoice No mismatch (doc: None vs web: INV27A000561), Disclaimer [LOYALTY-1782379052335.pdf]: Welcome Bonus mismatch (doc: 30000.0 vs expected: 15000.0), Cross-Validation Mismatch: API Error during cross-validation: 429 Client Error: Too Many Requests for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K457" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 15:13:42</t>
+        </is>
+      </c>
+      <c r="L457" s="4" t="inlineStr">
+        <is>
+          <t>T6C13730</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B458" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000139</t>
+        </is>
+      </c>
+      <c r="C458" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D458" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E458" s="4" t="inlineStr">
+        <is>
+          <t>TATTARA CH MARAK</t>
+        </is>
+      </c>
+      <c r="F458" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G458" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H458" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I458" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J458" s="4" t="inlineStr">
+        <is>
+          <t>Ledger [tatara ledger-1780988153066.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [tatara ledger-1780988153066.pdf]: Customer name mismatch (0.0% similarity), Disclaimer [tattar disv-1780988153164.pdf]: Invoice Date mismatch (doc: 10/9/26 vs web: 10 Apr 2026), Disclaimer [tattar disv-1780988153164.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K458" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 15:45:18</t>
+        </is>
+      </c>
+      <c r="L458" s="4" t="inlineStr">
+        <is>
+          <t>T5C33700</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B459" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000140</t>
+        </is>
+      </c>
+      <c r="C459" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D459" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E459" s="4" t="inlineStr">
+        <is>
+          <t>Shamborlin L mawlong</t>
+        </is>
+      </c>
+      <c r="F459" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G459" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H459" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I459" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J459" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [shamborlin disc-1782200767663.pdf]: New Vehicle Model mismatch (portal model 'PICK UP' not found in disclaimer), Ledger [shamborlin ledger-1782200767875.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K459" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:13:54</t>
+        </is>
+      </c>
+      <c r="L459" s="4" t="inlineStr">
+        <is>
+          <t>T1D80533</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B460" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000140</t>
+        </is>
+      </c>
+      <c r="C460" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D460" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E460" s="4" t="inlineStr">
+        <is>
+          <t>Shamborlin L mawlong</t>
+        </is>
+      </c>
+      <c r="F460" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G460" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H460" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I460" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J460" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [shamborlin disc-1782200767663.pdf]: New Vehicle Model mismatch (portal model 'PICK UP' not found in disclaimer), Ledger [shamborlin ledger-1782200767875.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [shamborlin ledger-1782200767875.pdf]: Stamp/signature missing or invalid, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K460" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:33:30</t>
+        </is>
+      </c>
+      <c r="L460" s="4" t="inlineStr">
+        <is>
+          <t>T1D80533</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B461" s="4" t="inlineStr">
+        <is>
+          <t>LYL27F000059</t>
+        </is>
+      </c>
+      <c r="C461" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D461" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E461" s="4" t="inlineStr">
+        <is>
+          <t>VRN CONSTRUCTION COMPANY</t>
+        </is>
+      </c>
+      <c r="F461" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G461" s="4" t="inlineStr">
+        <is>
+          <t>PALASUNI COMMERCIAL</t>
+        </is>
+      </c>
+      <c r="H461" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I461" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J461" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DISC-1782211717150.pdf]: Customer name mismatch (23.3% similarity), Invoice [INV-1782211717460.pdf]: Invoice Number mismatch. Extracted: 'INV-202306041', Expected: 'INV27F000201', Invoice [INV-1782211717460.pdf]: OpenAI Validation Failed - Missing customer signature and authorized signature, Ledger [LEDGER-1782211717307.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [LEDGER-1782211717307.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Cross-Validation Mismatch: Extracted customer name from the invoice and disclaimer successfully., Cross-Validation Mismatch: Dealer stamps were identified in both images., Cross-Validation Mismatch: Printed customer name mismatch across documents: score 0, Cross-Validation Mismatch: WARNING: AI extracted dealership name instead of customer name in invoice. Corrected to null.</t>
+        </is>
+      </c>
+      <c r="K461" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:49:09</t>
+        </is>
+      </c>
+      <c r="L461" s="4" t="inlineStr">
+        <is>
+          <t>T6E13072</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B462" s="4" t="inlineStr">
+        <is>
+          <t>LYL27F000059</t>
+        </is>
+      </c>
+      <c r="C462" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D462" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E462" s="4" t="inlineStr">
+        <is>
+          <t>VRN CONSTRUCTION COMPANY</t>
+        </is>
+      </c>
+      <c r="F462" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G462" s="4" t="inlineStr">
+        <is>
+          <t>PALASUNI COMMERCIAL</t>
+        </is>
+      </c>
+      <c r="H462" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I462" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J462" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DISC-1782211717150.pdf]: Customer name mismatch (23.3% similarity), Invoice [INV-1782211717460.pdf]: Invoice Number mismatch. Extracted: 'INV-2023-00141', Expected: 'INV27F000201', Invoice [INV-1782211717460.pdf]: OpenAI Validation Failed - Missing customer signature and authorized signature, Ledger [LEDGER-1782211717307.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [LEDGER-1782211717307.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Cross-Validation Mismatch: Printed customer name mismatch across documents: score 0, Cross-Validation Mismatch: Customer signature is missing on one or both documents., Cross-Validation Mismatch: Printed customer name found in the Declaration/Disclaimer document., Cross-Validation Mismatch: Handwritten signature found in the Declaration/Disclaimer document.</t>
+        </is>
+      </c>
+      <c r="K462" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:04:08</t>
+        </is>
+      </c>
+      <c r="L462" s="4" t="inlineStr">
+        <is>
+          <t>T6E13072</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B463" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000140</t>
+        </is>
+      </c>
+      <c r="C463" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D463" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E463" s="4" t="inlineStr">
+        <is>
+          <t>Shamborlin L mawlong</t>
+        </is>
+      </c>
+      <c r="F463" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G463" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H463" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I463" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J463" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [shamborlin disc-1782200767663.pdf]: New Vehicle Model mismatch (portal model 'PICK UP' not found in disclaimer), Ledger [shamborlin ledger-1782200767875.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [shamborlin ledger-1782200767875.pdf]: Stamp/signature missing or invalid, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K463" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:17:51</t>
+        </is>
+      </c>
+      <c r="L463" s="4" t="inlineStr">
+        <is>
+          <t>T1D80533</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B464" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000139</t>
+        </is>
+      </c>
+      <c r="C464" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D464" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E464" s="4" t="inlineStr">
+        <is>
+          <t>TATTARA CH MARAK</t>
+        </is>
+      </c>
+      <c r="F464" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G464" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H464" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I464" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J464" s="4" t="inlineStr">
+        <is>
+          <t>Ledger [tatara ledger-1780988153066.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [tatara ledger-1780988153066.pdf]: Customer name mismatch (0.0% similarity), Disclaimer [tattar disv-1780988153164.pdf]: Invoice Date mismatch (doc: 10/9/26 vs web: 10 Apr 2026), Disclaimer [tattar disv-1780988153164.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K464" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:31:53</t>
+        </is>
+      </c>
+      <c r="L464" s="4" t="inlineStr">
+        <is>
+          <t>T5C33700</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B465" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000133</t>
+        </is>
+      </c>
+      <c r="C465" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D465" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E465" s="4" t="inlineStr">
+        <is>
+          <t>SATYA NARAYAN BERIWAL</t>
+        </is>
+      </c>
+      <c r="F465" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G465" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H465" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I465" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J465" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [satya disc-1782199690123.pdf]: New Vehicle Model mismatch (portal model 'PICK UP' not found in disclaimer), Disclaimer [satya disc-1782199690123.pdf]: Chassis No mismatch (doc: MA1ZC4MTKID065574 vs web: T1D80574), Disclaimer [satya disc-1782199690123.pdf]: Invoice No mismatch (doc: 9N027A600118 vs web: INV27A000118), Disclaimer [satya disc-1782199690123.pdf]: Invoice Date mismatch (doc: 21/4/26 vs web: 21 Apr 2026), Disclaimer [satya disc-1782199690123.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Ledger [satya ledger-1782199690292.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [satya ledger-1782199690292.pdf]: Stamp/signature missing or invalid, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K465" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 18:17:17</t>
+        </is>
+      </c>
+      <c r="L465" s="4" t="inlineStr">
+        <is>
+          <t>T1D80574</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B466" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000059</t>
+        </is>
+      </c>
+      <c r="C466" s="4" t="inlineStr">
+        <is>
+          <t>10 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D466" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E466" s="4" t="inlineStr">
+        <is>
+          <t>SHOME BROTHERS</t>
+        </is>
+      </c>
+      <c r="F466" s="4" t="inlineStr">
+        <is>
+          <t>SABITA AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G466" s="4" t="inlineStr">
+        <is>
+          <t>LARSINGPAR</t>
+        </is>
+      </c>
+      <c r="H466" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I466" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J466" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [CD-1781090960621.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [CD-1781090960621.pdf]: Chassis No mismatch (doc: RGZ16926 vs web: R6J16966), Disclaimer [CD-1781090960621.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Document [L-1781090960488.pdf]: File is named/classified as Invoice, but contains Ledger content, Invoice [L-1781090960488.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [L-1781090960488.pdf]: Amount mismatch. Extracted Bonus: 12711.86, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [L-1781090960488.pdf]: Failed to identify vehicle model on invoice, Invoice [L-1781090960488.pdf]: OpenAI Validation Failed - Customer signature is missing, Relationship document: No Aadhaar/PAN found for relative 'PIYAL JYOTI SHOME' (Relationship: Partnership), Cross-Validation Mismatch: Handwritten name not found in both images., Cross-Validation Mismatch: Customer signature is missing on one or both documents., Cross-Validation Mismatch: Printed name found in disclaimer., Cross-Validation Mismatch: Printed customer name mismatch across documents: score 0, East Zone Welcome Bonus Validation: Missing mandatory document(s): Ledger</t>
+        </is>
+      </c>
+      <c r="K466" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 18:42:37</t>
+        </is>
+      </c>
+      <c r="L466" s="4" t="inlineStr">
+        <is>
+          <t>R6J16966</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B467" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000059</t>
+        </is>
+      </c>
+      <c r="C467" s="4" t="inlineStr">
+        <is>
+          <t>10 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D467" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E467" s="4" t="inlineStr">
+        <is>
+          <t>SHOME BROTHERS</t>
+        </is>
+      </c>
+      <c r="F467" s="4" t="inlineStr">
+        <is>
+          <t>SABITA AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G467" s="4" t="inlineStr">
+        <is>
+          <t>LARSINGPAR</t>
+        </is>
+      </c>
+      <c r="H467" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I467" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J467" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [CD-1781090960621.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [CD-1781090960621.pdf]: Chassis No mismatch (doc: RG716296 vs web: R6J16966), Disclaimer [CD-1781090960621.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Document [L-1781090960488.pdf]: File is named/classified as Invoice, but contains Ledger content, Invoice [L-1781090960488.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [L-1781090960488.pdf]: Amount mismatch. Extracted Bonus: 12711.86, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [L-1781090960488.pdf]: Failed to identify vehicle model on invoice, Invoice [L-1781090960488.pdf]: OpenAI Validation Failed - Customer Signature is missing, Relationship document: No Aadhaar/PAN found for relative 'PIYAL JYOTI SHOME' (Relationship: Partnership), East Zone Welcome Bonus Validation: Missing mandatory document(s): Ledger</t>
+        </is>
+      </c>
+      <c r="K467" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 18:54:49</t>
+        </is>
+      </c>
+      <c r="L467" s="4" t="inlineStr">
+        <is>
+          <t>R6J16966</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B468" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000059</t>
+        </is>
+      </c>
+      <c r="C468" s="4" t="inlineStr">
+        <is>
+          <t>10 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D468" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E468" s="4" t="inlineStr">
+        <is>
+          <t>SHOME BROTHERS</t>
+        </is>
+      </c>
+      <c r="F468" s="4" t="inlineStr">
+        <is>
+          <t>SABITA AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G468" s="4" t="inlineStr">
+        <is>
+          <t>LARSINGPAR</t>
+        </is>
+      </c>
+      <c r="H468" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I468" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J468" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [CD-1781090960621.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [CD-1781090960621.pdf]: Chassis No mismatch (doc: RG716926 vs web: R6J16966), Disclaimer [CD-1781090960621.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Document [L-1781090960488.pdf]: File is named/classified as Invoice, but contains Ledger content, Invoice [L-1781090960488.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [L-1781090960488.pdf]: Amount mismatch. Extracted Bonus: 12711.86, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [L-1781090960488.pdf]: Failed to identify vehicle model on invoice, Invoice [L-1781090960488.pdf]: OpenAI Validation Failed - Customer signature is missing, Relationship document: No Aadhaar/PAN found for relative 'PIYAL JYOTI SHOME' (Relationship: Partnership), Cross-Validation Mismatch: Printed customer name mismatch across documents: score 0, Cross-Validation Mismatch: Handwritten signature found in both documents., Cross-Validation Mismatch: Printed name found in declaration document., East Zone Welcome Bonus Validation: Missing mandatory document(s): Ledger</t>
+        </is>
+      </c>
+      <c r="K468" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 19:03:48</t>
+        </is>
+      </c>
+      <c r="L468" s="4" t="inlineStr">
+        <is>
+          <t>R6J16966</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B469" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000059</t>
+        </is>
+      </c>
+      <c r="C469" s="4" t="inlineStr">
+        <is>
+          <t>10 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D469" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E469" s="4" t="inlineStr">
+        <is>
+          <t>SHOME BROTHERS</t>
+        </is>
+      </c>
+      <c r="F469" s="4" t="inlineStr">
+        <is>
+          <t>SABITA AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G469" s="4" t="inlineStr">
+        <is>
+          <t>LARSINGPAR</t>
+        </is>
+      </c>
+      <c r="H469" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I469" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J469" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [CD-1781090960621.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [CD-1781090960621.pdf]: Chassis No mismatch (doc: RG716926 vs web: R6J16966), Disclaimer [CD-1781090960621.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Document [L-1781090960488.pdf]: File is named/classified as Invoice, but contains Ledger content, Invoice [L-1781090960488.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [L-1781090960488.pdf]: Amount mismatch. Extracted Bonus: 12711.86, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [L-1781090960488.pdf]: Failed to identify vehicle model on invoice, Invoice [L-1781090960488.pdf]: OpenAI Validation Failed - Customer signature is missing, Relationship document: No Aadhaar/PAN found for relative 'PIYAL JYOTI SHOME' (Relationship: Partnership), East Zone Welcome Bonus Validation: Missing mandatory document(s): Ledger</t>
+        </is>
+      </c>
+      <c r="K469" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30 19:17:58</t>
+        </is>
+      </c>
+      <c r="L469" s="4" t="inlineStr">
+        <is>
+          <t>R6J16966</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B470" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000139</t>
+        </is>
+      </c>
+      <c r="C470" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D470" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E470" s="4" t="inlineStr">
+        <is>
+          <t>TATTARA CH MARAK</t>
+        </is>
+      </c>
+      <c r="F470" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G470" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H470" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I470" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J470" s="4" t="inlineStr">
+        <is>
+          <t>Ledger [tatara ledger-1780988153066.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [tatara ledger-1780988153066.pdf]: Customer name mismatch (0.0% similarity), Disclaimer [tattar disv-1780988153164.pdf]: Invoice Date mismatch (doc: 10/9/26 vs web: 10 Apr 2026), Disclaimer [tattar disv-1780988153164.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:50:12</t>
+        </is>
+      </c>
+      <c r="L470" s="4" t="inlineStr">
+        <is>
+          <t>T5C33700</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B471" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000139</t>
+        </is>
+      </c>
+      <c r="C471" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D471" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E471" s="4" t="inlineStr">
+        <is>
+          <t>TATTARA CH MARAK</t>
+        </is>
+      </c>
+      <c r="F471" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G471" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H471" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I471" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J471" s="4" t="inlineStr">
+        <is>
+          <t>Ledger [tatara ledger-1780988153066.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [tatara ledger-1780988153066.pdf]: Customer name mismatch (0.0% similarity), Disclaimer [tattar disv-1780988153164.pdf]: Invoice Date mismatch (doc: 10/9/26 vs web: 10 Apr 2026), Disclaimer [tattar disv-1780988153164.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K471" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 12:01:11</t>
+        </is>
+      </c>
+      <c r="L471" s="4" t="inlineStr">
+        <is>
+          <t>T5C33700</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B472" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000043</t>
+        </is>
+      </c>
+      <c r="C472" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E472" s="4" t="inlineStr">
+        <is>
+          <t>GAGAN BIHARI MISHRA</t>
+        </is>
+      </c>
+      <c r="F472" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G472" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H472" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I472" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J472" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K472" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 12:06:42</t>
+        </is>
+      </c>
+      <c r="L472" s="4" t="inlineStr">
+        <is>
+          <t>T2E26887</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B473" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000140</t>
+        </is>
+      </c>
+      <c r="C473" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D473" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E473" s="4" t="inlineStr">
+        <is>
+          <t>Shamborlin L mawlong</t>
+        </is>
+      </c>
+      <c r="F473" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G473" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H473" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I473" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J473" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [shamborlin disc-1782200767663.pdf]: New Vehicle Model mismatch (portal model 'PICK UP' not found in disclaimer), Ledger [shamborlin ledger-1782200767875.pdf]: Amount mismatch for 'Welcome Bonus' entry. Expected: 4237.28, Ledger [shamborlin ledger-1782200767875.pdf]: Stamp/signature missing or invalid, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K473" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 12:19:39</t>
+        </is>
+      </c>
+      <c r="L473" s="4" t="inlineStr">
+        <is>
+          <t>T1D80533</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B474" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000037</t>
+        </is>
+      </c>
+      <c r="C474" s="4" t="inlineStr">
+        <is>
+          <t>12 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D474" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E474" s="4" t="inlineStr">
+        <is>
+          <t>Pradeep Jaisawal</t>
+        </is>
+      </c>
+      <c r="F474" s="4" t="inlineStr">
+        <is>
+          <t>STAR AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G474" s="4" t="inlineStr">
+        <is>
+          <t>AJABNAGAR</t>
+        </is>
+      </c>
+      <c r="H474" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I474" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J474" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K474" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:02:23</t>
+        </is>
+      </c>
+      <c r="L474" s="4" t="inlineStr">
+        <is>
+          <t>T2C59638</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B475" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000194</t>
+        </is>
+      </c>
+      <c r="C475" s="4" t="inlineStr">
+        <is>
+          <t>12 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D475" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E475" s="4" t="inlineStr">
+        <is>
+          <t>RAMCHANDRA MURMU</t>
+        </is>
+      </c>
+      <c r="F475" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G475" s="4" t="inlineStr">
+        <is>
+          <t>BOLANGIR</t>
+        </is>
+      </c>
+      <c r="H475" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I475" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J475" s="4" t="inlineStr"/>
+      <c r="K475" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:11:03</t>
+        </is>
+      </c>
+      <c r="L475" s="4" t="inlineStr">
+        <is>
+          <t>T6A14750</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B476" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000190</t>
+        </is>
+      </c>
+      <c r="C476" s="4" t="inlineStr">
+        <is>
+          <t>12 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D476" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E476" s="4" t="inlineStr">
+        <is>
+          <t>RAM KRISHNA NAIK</t>
+        </is>
+      </c>
+      <c r="F476" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G476" s="4" t="inlineStr">
+        <is>
+          <t>BOLANGIR</t>
+        </is>
+      </c>
+      <c r="H476" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I476" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J476" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K476" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:12:27</t>
+        </is>
+      </c>
+      <c r="L476" s="4" t="inlineStr">
+        <is>
+          <t>T6C18929</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B477" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000018</t>
+        </is>
+      </c>
+      <c r="C477" s="4" t="inlineStr">
+        <is>
+          <t>12 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D477" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E477" s="4" t="inlineStr">
+        <is>
+          <t>Saiyad Mukhtar Hussain</t>
+        </is>
+      </c>
+      <c r="F477" s="4" t="inlineStr">
+        <is>
+          <t>STAR AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G477" s="4" t="inlineStr">
+        <is>
+          <t>MANENDRA GARH</t>
+        </is>
+      </c>
+      <c r="H477" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I477" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J477" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K477" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:12:34</t>
+        </is>
+      </c>
+      <c r="L477" s="4" t="inlineStr">
+        <is>
+          <t>T6D61847</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B478" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000034</t>
+        </is>
+      </c>
+      <c r="C478" s="4" t="inlineStr">
+        <is>
+          <t>11 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D478" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E478" s="4" t="inlineStr">
+        <is>
+          <t>AJAY KUMAR KUSHWAHA</t>
+        </is>
+      </c>
+      <c r="F478" s="4" t="inlineStr">
+        <is>
+          <t>STAR AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G478" s="4" t="inlineStr">
+        <is>
+          <t>AJABNAGAR</t>
+        </is>
+      </c>
+      <c r="H478" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I478" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J478" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K478" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:12:42</t>
+        </is>
+      </c>
+      <c r="L478" s="4" t="inlineStr">
+        <is>
+          <t>T1E93833</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B479" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000014</t>
+        </is>
+      </c>
+      <c r="C479" s="4" t="inlineStr">
+        <is>
+          <t>11 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D479" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E479" s="4" t="inlineStr">
+        <is>
+          <t>INAMUL KORIM</t>
+        </is>
+      </c>
+      <c r="F479" s="4" t="inlineStr">
+        <is>
+          <t>G.D. MOTORS</t>
+        </is>
+      </c>
+      <c r="G479" s="4" t="inlineStr">
+        <is>
+          <t>MORIGAON_SS</t>
+        </is>
+      </c>
+      <c r="H479" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I479" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J479" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice, Disclaimer, Ledger</t>
+        </is>
+      </c>
+      <c r="K479" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:14:03</t>
+        </is>
+      </c>
+      <c r="L479" s="4" t="inlineStr">
+        <is>
+          <t>T6D11862</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B480" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000059</t>
+        </is>
+      </c>
+      <c r="C480" s="4" t="inlineStr">
+        <is>
+          <t>10 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D480" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E480" s="4" t="inlineStr">
+        <is>
+          <t>SHOME BROTHERS</t>
+        </is>
+      </c>
+      <c r="F480" s="4" t="inlineStr">
+        <is>
+          <t>SABITA AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G480" s="4" t="inlineStr">
+        <is>
+          <t>LARSINGPAR</t>
+        </is>
+      </c>
+      <c r="H480" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I480" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J480" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [CD-1781090960621.pdf]: New Vehicle Model mismatch (portal model 'VEERO' not found in disclaimer), Disclaimer [CD-1781090960621.pdf]: Chassis No mismatch (doc: RGZ16926C vs web: R6J16966), Disclaimer [CD-1781090960621.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Document [L-1781090960488.pdf]: File is named/classified as Invoice, but contains Ledger content, Invoice [L-1781090960488.pdf]: Not a valid tax/GST invoice (Neither 'TAX INVOICE' nor 'GST INVOICE' found), Invoice [L-1781090960488.pdf]: Amount mismatch. Extracted Bonus: 5000.0, Expected: 15000.0 (or GST-inclusive) for model 'None', Invoice [L-1781090960488.pdf]: Failed to identify vehicle model on invoice, Invoice [L-1781090960488.pdf]: OpenAI Validation Failed - Customer signature is missing, Relationship document: No Aadhaar/PAN found for relative 'PIYAL JYOTI SHOME' (Relationship: Partnership), Cross-Validation Mismatch: Printed name found in disclaimer document., Cross-Validation Mismatch: Dealer stamp present on both documents., Cross-Validation Mismatch: Printed customer name mismatch across documents: score 0, East Zone Welcome Bonus Validation: Missing mandatory document(s): Ledger</t>
+        </is>
+      </c>
+      <c r="K480" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:19:17</t>
+        </is>
+      </c>
+      <c r="L480" s="4" t="inlineStr">
+        <is>
+          <t>R6J16966</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B481" s="4" t="inlineStr">
+        <is>
+          <t>LYL27F000059</t>
+        </is>
+      </c>
+      <c r="C481" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D481" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E481" s="4" t="inlineStr">
+        <is>
+          <t>VRN CONSTRUCTION COMPANY</t>
+        </is>
+      </c>
+      <c r="F481" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G481" s="4" t="inlineStr">
+        <is>
+          <t>PALASUNI COMMERCIAL</t>
+        </is>
+      </c>
+      <c r="H481" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I481" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J481" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [DISC-1782211717150.pdf]: Customer name mismatch (20.5% similarity), Invoice [INV-1782211717460.pdf]: Invoice Number mismatch. Extracted: 'INV-202306041', Expected: 'INV27F000201', Invoice [INV-1782211717460.pdf]: OpenAI Validation Failed - Missing Customer Signature and Authorized Signature, Ledger [LEDGER-1782211717307.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [LEDGER-1782211717307.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Cross-Validation Mismatch: Extracted customer names from both documents., Cross-Validation Mismatch: Detected dealer stamps on both images., Cross-Validation Mismatch: Printed customer name mismatch across documents: score 0, Cross-Validation Mismatch: WARNING: AI extracted dealership name instead of customer name in invoice. Corrected to null.</t>
+        </is>
+      </c>
+      <c r="K481" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:27:26</t>
+        </is>
+      </c>
+      <c r="L481" s="4" t="inlineStr">
+        <is>
+          <t>T6E13072</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B482" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000140</t>
+        </is>
+      </c>
+      <c r="C482" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D482" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E482" s="4" t="inlineStr">
+        <is>
+          <t>Shamborlin L mawlong</t>
+        </is>
+      </c>
+      <c r="F482" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G482" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H482" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I482" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J482" s="4" t="inlineStr">
+        <is>
+          <t>East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K482" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:33:54</t>
+        </is>
+      </c>
+      <c r="L482" s="4" t="inlineStr">
+        <is>
+          <t>T1D80533</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B483" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000139</t>
+        </is>
+      </c>
+      <c r="C483" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D483" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E483" s="4" t="inlineStr">
+        <is>
+          <t>TATTARA CH MARAK</t>
+        </is>
+      </c>
+      <c r="F483" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G483" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H483" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I483" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J483" s="4" t="inlineStr">
+        <is>
+          <t>Ledger [tatara ledger-1780988153066.pdf]: Customer name mismatch (0.0% similarity), Disclaimer [tattar disv-1780988153164.pdf]: Invoice Date mismatch (doc: 10/9/26 vs web: 10 Apr 2026), Disclaimer [tattar disv-1780988153164.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K483" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:41:03</t>
+        </is>
+      </c>
+      <c r="L483" s="4" t="inlineStr">
+        <is>
+          <t>T5C33700</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B484" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000133</t>
+        </is>
+      </c>
+      <c r="C484" s="4" t="inlineStr">
+        <is>
+          <t>09 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D484" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E484" s="4" t="inlineStr">
+        <is>
+          <t>SATYA NARAYAN BERIWAL</t>
+        </is>
+      </c>
+      <c r="F484" s="4" t="inlineStr">
+        <is>
+          <t>SL ROKLAND MOTORE LLP</t>
+        </is>
+      </c>
+      <c r="G484" s="4" t="inlineStr">
+        <is>
+          <t>SHILLONG</t>
+        </is>
+      </c>
+      <c r="H484" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I484" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J484" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer [satya disc-1782199690123.pdf]: New Vehicle Model mismatch (portal model 'PICK UP' not found in disclaimer), Disclaimer [satya disc-1782199690123.pdf]: Invoice No mismatch (doc: 9N027A600118 vs web: INV27A000118), Disclaimer [satya disc-1782199690123.pdf]: Invoice Date mismatch (doc: 21/4/26 vs web: 21 Apr 2026), Disclaimer [satya disc-1782199690123.pdf]: Disclaimer Date Validation HOLD - Disclaimer date not readable, Ledger [satya ledger-1782199690292.pdf]: Stamp/signature missing or invalid, East Zone Welcome Bonus Validation: Missing mandatory document(s): Invoice</t>
+        </is>
+      </c>
+      <c r="K484" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 13:45:29</t>
+        </is>
+      </c>
+      <c r="L484" s="4" t="inlineStr">
+        <is>
+          <t>T1D80574</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L484"/>
+  <dimension ref="A1:L486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29367,6 +29367,126 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B485" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000355</t>
+        </is>
+      </c>
+      <c r="C485" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D485" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E485" s="4" t="inlineStr">
+        <is>
+          <t>Rakesh Nigam</t>
+        </is>
+      </c>
+      <c r="F485" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G485" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H485" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I485" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J485" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K485" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:23:53</t>
+        </is>
+      </c>
+      <c r="L485" s="4" t="inlineStr">
+        <is>
+          <t>T2C48500</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B486" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000111</t>
+        </is>
+      </c>
+      <c r="C486" s="4" t="inlineStr">
+        <is>
+          <t>20 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D486" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E486" s="4" t="inlineStr">
+        <is>
+          <t>MARSHAL POHTAM</t>
+        </is>
+      </c>
+      <c r="F486" s="4" t="inlineStr">
+        <is>
+          <t>SWARAN AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G486" s="4" t="inlineStr">
+        <is>
+          <t>JORABAT_3S</t>
+        </is>
+      </c>
+      <c r="H486" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I486" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J486" s="4" t="inlineStr">
+        <is>
+          <t>Ledger [led-1782303900469.pdf]: 'Welcome Bonus' entry not found in ledger, Ledger [led-1782303900469.pdf]: 'Welcome Bonus' not found in ledger (Required for East Zone), Ledger [led-1782303900469.pdf]: Customer name mismatch (32.0% similarity)</t>
+        </is>
+      </c>
+      <c r="K486" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:30:58</t>
+        </is>
+      </c>
+      <c r="L486" s="4" t="inlineStr">
+        <is>
+          <t>T6C10824</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L486"/>
+  <dimension ref="A1:L494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29487,6 +29487,486 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B487" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000049</t>
+        </is>
+      </c>
+      <c r="C487" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D487" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E487" s="4" t="inlineStr">
+        <is>
+          <t>Bhismadev Dhrua</t>
+        </is>
+      </c>
+      <c r="F487" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G487" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H487" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I487" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J487" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K487" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:11:51</t>
+        </is>
+      </c>
+      <c r="L487" s="4" t="inlineStr">
+        <is>
+          <t>T2D18346</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B488" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000048</t>
+        </is>
+      </c>
+      <c r="C488" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D488" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>PRITAM PRATAP NAIK</t>
+        </is>
+      </c>
+      <c r="F488" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G488" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H488" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I488" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J488" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K488" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:11:57</t>
+        </is>
+      </c>
+      <c r="L488" s="4" t="inlineStr">
+        <is>
+          <t>T2E32959</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B489" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000117</t>
+        </is>
+      </c>
+      <c r="C489" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D489" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E489" s="4" t="inlineStr">
+        <is>
+          <t>KONARK EARTHMOVER PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F489" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G489" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H489" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I489" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J489" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K489" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:12:02</t>
+        </is>
+      </c>
+      <c r="L489" s="4" t="inlineStr">
+        <is>
+          <t>T5A19991</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B490" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000116</t>
+        </is>
+      </c>
+      <c r="C490" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D490" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E490" s="4" t="inlineStr">
+        <is>
+          <t>Dibyasom Puhan</t>
+        </is>
+      </c>
+      <c r="F490" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G490" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H490" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I490" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J490" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K490" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:12:07</t>
+        </is>
+      </c>
+      <c r="L490" s="4" t="inlineStr">
+        <is>
+          <t>T6E57252</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B491" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000115</t>
+        </is>
+      </c>
+      <c r="C491" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D491" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>Dhananjay Das</t>
+        </is>
+      </c>
+      <c r="F491" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G491" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H491" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I491" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J491" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K491" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:12:12</t>
+        </is>
+      </c>
+      <c r="L491" s="4" t="inlineStr">
+        <is>
+          <t>S2D13108</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B492" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000114</t>
+        </is>
+      </c>
+      <c r="C492" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D492" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E492" s="4" t="inlineStr">
+        <is>
+          <t>Deepak Kumar Verma</t>
+        </is>
+      </c>
+      <c r="F492" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G492" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H492" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I492" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J492" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K492" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:12:17</t>
+        </is>
+      </c>
+      <c r="L492" s="4" t="inlineStr">
+        <is>
+          <t>T6E59092</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B493" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000113</t>
+        </is>
+      </c>
+      <c r="C493" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D493" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E493" s="4" t="inlineStr">
+        <is>
+          <t>BIJAY KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F493" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G493" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H493" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I493" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J493" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K493" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:12:22</t>
+        </is>
+      </c>
+      <c r="L493" s="4" t="inlineStr">
+        <is>
+          <t>T6D66629</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B494" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000112</t>
+        </is>
+      </c>
+      <c r="C494" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D494" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>Azhar Nawab</t>
+        </is>
+      </c>
+      <c r="F494" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G494" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H494" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I494" s="7" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J494" s="4" t="inlineStr">
+        <is>
+          <t>Scheme is 'Scrappage Bonus' — only Welcome Bonus processed</t>
+        </is>
+      </c>
+      <c r="K494" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:12:26</t>
+        </is>
+      </c>
+      <c r="L494" s="4" t="inlineStr">
+        <is>
+          <t>T2E73684</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L690"/>
+  <dimension ref="A1:L737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40685,6 +40685,2649 @@
         </is>
       </c>
     </row>
+    <row r="691">
+      <c r="A691" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B691" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000049</t>
+        </is>
+      </c>
+      <c r="C691" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D691" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E691" s="4" t="inlineStr">
+        <is>
+          <t>Bhismadev Dhrua</t>
+        </is>
+      </c>
+      <c r="F691" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G691" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H691" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I691" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J691" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD20226510LC5C5376' does not match old vehicle chassis: 'COD20260470DL7CC4465'); New Chassis mismatch (Document Chassis: 'MA1NBX72T1E065269' does not match last 8 digits of dashboard: 'T2D18346')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K691" s="3" t="inlineStr"/>
+      <c r="L691" s="4" t="inlineStr">
+        <is>
+          <t>T2D18346</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B692" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000048</t>
+        </is>
+      </c>
+      <c r="C692" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D692" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E692" s="4" t="inlineStr">
+        <is>
+          <t>PRITAM PRATAP NAIK</t>
+        </is>
+      </c>
+      <c r="F692" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G692" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H692" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I692" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J692" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD2026585C0174G7110' does not match old vehicle chassis: 'COD2026055UP14AL7446'); New Chassis mismatch (Document Chassis: 'MAT1N2YP1D7G0738' does not match last 8 digits of dashboard: 'T2E32959')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K692" s="3" t="inlineStr"/>
+      <c r="L692" s="4" t="inlineStr">
+        <is>
+          <t>T2E32959</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B693" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000117</t>
+        </is>
+      </c>
+      <c r="C693" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D693" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E693" s="4" t="inlineStr">
+        <is>
+          <t>KONARK EARTHMOVER PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F693" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G693" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H693" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I693" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J693" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: Portal customer name 'KONARK EARTHMOVER PRIVATE LIMITED' not found from top to bottom in COD document (Extracted: 'HARISH KUMAR')
+COD Document Validation Failed: Portal customer name 'KONARK EARTHMOVER PRIVATE LIMITED' not found from top to bottom in COD document (Extracted: 'HARISH KUMAR')
+OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD202304700LTCF594' does not match old vehicle chassis: 'COD20260530DL7CC5657'); New Chassis mismatch (Document Chassis: 'MA1N2JVT2LC64777' does not match last 8 digits of dashboard: 'T5A19991')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K693" s="3" t="inlineStr"/>
+      <c r="L693" s="4" t="inlineStr">
+        <is>
+          <t>T5A19991</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B694" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000116</t>
+        </is>
+      </c>
+      <c r="C694" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D694" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E694" s="4" t="inlineStr">
+        <is>
+          <t>Dibyasom Puhan</t>
+        </is>
+      </c>
+      <c r="F694" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G694" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H694" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I694" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J694" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD20220714061_BCS7676' does not match old vehicle chassis: 'COD20260560DL9CF0176'); New Chassis mismatch (Document Chassis: 'MA1J2GC16F065407' does not match last 8 digits of dashboard: 'T6E57252')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K694" s="3" t="inlineStr"/>
+      <c r="L694" s="4" t="inlineStr">
+        <is>
+          <t>T6E57252</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B695" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000115</t>
+        </is>
+      </c>
+      <c r="C695" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D695" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E695" s="4" t="inlineStr">
+        <is>
+          <t>Dhananjay Das</t>
+        </is>
+      </c>
+      <c r="F695" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G695" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H695" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I695" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J695" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'
+COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'
+OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD2026585C0174G7110' does not match old vehicle chassis: 'COD20260520DL7CB8898'); New Chassis mismatch (Document Chassis: 'MAT1N2YP1D7C0738' does not match last 8 digits of dashboard: 'S2D13108')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K695" s="3" t="inlineStr"/>
+      <c r="L695" s="4" t="inlineStr">
+        <is>
+          <t>S2D13108</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B696" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000114</t>
+        </is>
+      </c>
+      <c r="C696" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D696" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E696" s="4" t="inlineStr">
+        <is>
+          <t>Deepak Kumar Verma</t>
+        </is>
+      </c>
+      <c r="F696" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G696" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H696" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I696" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J696" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'
+COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'
+OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD2026585C0T14G7110' does not match old vehicle chassis: 'COD2025114UP80BR8424'); New Chassis mismatch (Document Chassis: 'MAT1N2YP1D7C0738' does not match last 8 digits of dashboard: 'T6E59092')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K696" s="3" t="inlineStr"/>
+      <c r="L696" s="4" t="inlineStr">
+        <is>
+          <t>T6E59092</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B697" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000113</t>
+        </is>
+      </c>
+      <c r="C697" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D697" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E697" s="4" t="inlineStr">
+        <is>
+          <t>BIJAY KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F697" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G697" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H697" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I697" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J697" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: New Chassis mismatch (Document Chassis: 'MAT1RM2TVK5K31074' does not match last 8 digits of dashboard: 'T6D66629')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K697" s="3" t="inlineStr"/>
+      <c r="L697" s="4" t="inlineStr">
+        <is>
+          <t>T6D66629</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B698" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000112</t>
+        </is>
+      </c>
+      <c r="C698" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D698" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E698" s="4" t="inlineStr">
+        <is>
+          <t>Azhar Nawab</t>
+        </is>
+      </c>
+      <c r="F698" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G698" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H698" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I698" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J698" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'
+COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'
+OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD220507406LBC58766' does not match old vehicle chassis: 'COD2026036DL1CAK0982'); New Chassis mismatch (Document Chassis: 'MA1J2GC16F652752' does not match last 8 digits of dashboard: 'T2E73684')
+Missing Ledger Document
+Missing Invoice Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K698" s="3" t="inlineStr"/>
+      <c r="L698" s="4" t="inlineStr">
+        <is>
+          <t>T2E73684</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B699" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000049</t>
+        </is>
+      </c>
+      <c r="C699" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D699" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E699" s="4" t="inlineStr">
+        <is>
+          <t>Bhismadev Dhrua</t>
+        </is>
+      </c>
+      <c r="F699" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G699" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H699" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I699" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J699" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Invoice customer name 'Bhismadev Dhura' does not match claim customer 'bhismadev dhrua'
+Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
+        </is>
+      </c>
+      <c r="K699" s="3" t="inlineStr"/>
+      <c r="L699" s="4" t="inlineStr">
+        <is>
+          <t>T2D18346</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B700" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000048</t>
+        </is>
+      </c>
+      <c r="C700" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D700" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E700" s="4" t="inlineStr">
+        <is>
+          <t>PRITAM PRATAP NAIK</t>
+        </is>
+      </c>
+      <c r="F700" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G700" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H700" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I700" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J700" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
+        </is>
+      </c>
+      <c r="K700" s="3" t="inlineStr"/>
+      <c r="L700" s="4" t="inlineStr">
+        <is>
+          <t>T2E32959</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B701" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000117</t>
+        </is>
+      </c>
+      <c r="C701" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D701" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E701" s="4" t="inlineStr">
+        <is>
+          <t>KONARK EARTHMOVER PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F701" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G701" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H701" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I701" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J701" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
+        </is>
+      </c>
+      <c r="K701" s="3" t="inlineStr"/>
+      <c r="L701" s="4" t="inlineStr">
+        <is>
+          <t>T5A19991</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B702" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000116</t>
+        </is>
+      </c>
+      <c r="C702" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D702" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E702" s="4" t="inlineStr">
+        <is>
+          <t>Dibyasom Puhan</t>
+        </is>
+      </c>
+      <c r="F702" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G702" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H702" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I702" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J702" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'
+Invoice Validation Failed: Invoice customer name 'Dibyason Puhan' does not match claim customer 'dibyasom puhan'</t>
+        </is>
+      </c>
+      <c r="K702" s="3" t="inlineStr"/>
+      <c r="L702" s="4" t="inlineStr">
+        <is>
+          <t>T6E57252</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B703" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000115</t>
+        </is>
+      </c>
+      <c r="C703" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D703" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E703" s="4" t="inlineStr">
+        <is>
+          <t>Dhananjay Das</t>
+        </is>
+      </c>
+      <c r="F703" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G703" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H703" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I703" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J703" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'
+COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'
+Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'
+OEM Document Validation Failed: New Chassis mismatch (Document Chassis: 'MAT1YDYD6EJ656753' does not match last 8 digits of dashboard: 'S2D13108')</t>
+        </is>
+      </c>
+      <c r="K703" s="3" t="inlineStr"/>
+      <c r="L703" s="4" t="inlineStr">
+        <is>
+          <t>S2D13108</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B704" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000114</t>
+        </is>
+      </c>
+      <c r="C704" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D704" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E704" s="4" t="inlineStr">
+        <is>
+          <t>Deepak Kumar Verma</t>
+        </is>
+      </c>
+      <c r="F704" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G704" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H704" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I704" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J704" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'
+COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'
+Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
+        </is>
+      </c>
+      <c r="K704" s="3" t="inlineStr"/>
+      <c r="L704" s="4" t="inlineStr">
+        <is>
+          <t>T6E59092</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B705" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000113</t>
+        </is>
+      </c>
+      <c r="C705" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D705" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E705" s="4" t="inlineStr">
+        <is>
+          <t>BIJAY KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F705" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G705" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H705" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I705" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J705" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'; Disclaimer new vehicle model does not match portal model group 'BOLERO NEO PLUS' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO NEO+ P10 WHITE, Chassis Number: T6D66629, Engine Number: YXT4D47059')</t>
+        </is>
+      </c>
+      <c r="K705" s="3" t="inlineStr"/>
+      <c r="L705" s="4" t="inlineStr">
+        <is>
+          <t>T6D66629</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B706" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000112</t>
+        </is>
+      </c>
+      <c r="C706" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D706" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E706" s="4" t="inlineStr">
+        <is>
+          <t>Azhar Nawab</t>
+        </is>
+      </c>
+      <c r="F706" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G706" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H706" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I706" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J706" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document
+Missing Invoice Document
+Missing Certificate of Deposit (COD/OEM) Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K706" s="3" t="inlineStr"/>
+      <c r="L706" s="4" t="inlineStr">
+        <is>
+          <t>T2E73684</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B707" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000359</t>
+        </is>
+      </c>
+      <c r="C707" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D707" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E707" s="4" t="inlineStr">
+        <is>
+          <t>Stafford Valentine Redden</t>
+        </is>
+      </c>
+      <c r="F707" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G707" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H707" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I707" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J707" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K707" s="3" t="inlineStr"/>
+      <c r="L707" s="4" t="inlineStr">
+        <is>
+          <t>T6E58112</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B708" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000358</t>
+        </is>
+      </c>
+      <c r="C708" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D708" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E708" s="4" t="inlineStr">
+        <is>
+          <t>ALOK PRADHAN</t>
+        </is>
+      </c>
+      <c r="F708" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G708" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H708" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I708" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J708" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K708" s="3" t="inlineStr"/>
+      <c r="L708" s="4" t="inlineStr">
+        <is>
+          <t>T6E60743</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B709" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000357</t>
+        </is>
+      </c>
+      <c r="C709" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D709" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E709" s="4" t="inlineStr">
+        <is>
+          <t>Debasish Puthal</t>
+        </is>
+      </c>
+      <c r="F709" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G709" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H709" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I709" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J709" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K709" s="3" t="inlineStr"/>
+      <c r="L709" s="4" t="inlineStr">
+        <is>
+          <t>T2E27528</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B710" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000356</t>
+        </is>
+      </c>
+      <c r="C710" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D710" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E710" s="4" t="inlineStr">
+        <is>
+          <t>Bibhuti Bhusana Pradhan</t>
+        </is>
+      </c>
+      <c r="F710" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G710" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H710" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I710" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J710" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer new vehicle model does not match portal model group 'XUV3XO' (Extracted: 'New Vehicle Model: XUV3X0 AX5 PM MT RQ, Chassis Number: T2C60084, Engine Number: NPTZC74195')
+Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K710" s="3" t="inlineStr"/>
+      <c r="L710" s="4" t="inlineStr">
+        <is>
+          <t>T2C60084</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B711" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000354</t>
+        </is>
+      </c>
+      <c r="C711" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D711" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E711" s="4" t="inlineStr">
+        <is>
+          <t>Rashmirekha Biswal</t>
+        </is>
+      </c>
+      <c r="F711" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G711" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H711" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I711" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J711" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K711" s="3" t="inlineStr"/>
+      <c r="L711" s="4" t="inlineStr">
+        <is>
+          <t>T2B30390</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B712" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000359</t>
+        </is>
+      </c>
+      <c r="C712" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D712" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E712" s="4" t="inlineStr">
+        <is>
+          <t>Stafford Valentine Redden</t>
+        </is>
+      </c>
+      <c r="F712" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G712" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H712" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I712" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J712" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K712" s="3" t="inlineStr"/>
+      <c r="L712" s="4" t="inlineStr">
+        <is>
+          <t>T6E58112</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B713" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000358</t>
+        </is>
+      </c>
+      <c r="C713" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D713" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E713" s="4" t="inlineStr">
+        <is>
+          <t>ALOK PRADHAN</t>
+        </is>
+      </c>
+      <c r="F713" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G713" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H713" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I713" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J713" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K713" s="3" t="inlineStr"/>
+      <c r="L713" s="4" t="inlineStr">
+        <is>
+          <t>T6E60743</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B714" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000357</t>
+        </is>
+      </c>
+      <c r="C714" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D714" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E714" s="4" t="inlineStr">
+        <is>
+          <t>Debasish Puthal</t>
+        </is>
+      </c>
+      <c r="F714" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G714" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H714" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I714" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J714" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K714" s="3" t="inlineStr"/>
+      <c r="L714" s="4" t="inlineStr">
+        <is>
+          <t>T2E27528</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B715" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000356</t>
+        </is>
+      </c>
+      <c r="C715" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D715" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E715" s="4" t="inlineStr">
+        <is>
+          <t>Bibhuti Bhusana Pradhan</t>
+        </is>
+      </c>
+      <c r="F715" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G715" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H715" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I715" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J715" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer new vehicle model does not match portal model group 'XUV3XO' (Extracted: 'New Vehicle Model: XUV3X0 AX5 PM MT RQ, Chassis Number: T2C60084, Engine Number: NPTZC74195')
+Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K715" s="3" t="inlineStr"/>
+      <c r="L715" s="4" t="inlineStr">
+        <is>
+          <t>T2C60084</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B716" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000354</t>
+        </is>
+      </c>
+      <c r="C716" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D716" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E716" s="4" t="inlineStr">
+        <is>
+          <t>Rashmirekha Biswal</t>
+        </is>
+      </c>
+      <c r="F716" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G716" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H716" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I716" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J716" s="4" t="inlineStr">
+        <is>
+          <t>Missing Certificate of Deposit (COD/OEM) Document</t>
+        </is>
+      </c>
+      <c r="K716" s="3" t="inlineStr"/>
+      <c r="L716" s="4" t="inlineStr">
+        <is>
+          <t>T2B30390</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B717" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000109</t>
+        </is>
+      </c>
+      <c r="C717" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D717" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E717" s="4" t="inlineStr">
+        <is>
+          <t>GULSAN XESS</t>
+        </is>
+      </c>
+      <c r="F717" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G717" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H717" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I717" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J717" s="4" t="inlineStr"/>
+      <c r="K717" s="3" t="inlineStr"/>
+      <c r="L717" s="4" t="inlineStr">
+        <is>
+          <t>T2D99858</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B718" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000108</t>
+        </is>
+      </c>
+      <c r="C718" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D718" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E718" s="4" t="inlineStr">
+        <is>
+          <t>Jagynasenee Naik</t>
+        </is>
+      </c>
+      <c r="F718" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G718" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H718" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I718" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J718" s="4" t="inlineStr"/>
+      <c r="K718" s="3" t="inlineStr"/>
+      <c r="L718" s="4" t="inlineStr">
+        <is>
+          <t>T2E73806</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B719" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000017</t>
+        </is>
+      </c>
+      <c r="C719" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D719" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E719" s="4" t="inlineStr">
+        <is>
+          <t>Mayank .</t>
+        </is>
+      </c>
+      <c r="F719" s="4" t="inlineStr">
+        <is>
+          <t>B R BALAJI LLP</t>
+        </is>
+      </c>
+      <c r="G719" s="4" t="inlineStr">
+        <is>
+          <t>JAGDALPUR</t>
+        </is>
+      </c>
+      <c r="H719" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I719" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J719" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Model 'ZEN MPI LX' does not match expected old vehicle model 'Zen lx'
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K719" s="3" t="inlineStr"/>
+      <c r="L719" s="4" t="inlineStr">
+        <is>
+          <t>T2D85723</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B720" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000161</t>
+        </is>
+      </c>
+      <c r="C720" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D720" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E720" s="4" t="inlineStr">
+        <is>
+          <t>ANAND TULSIAN</t>
+        </is>
+      </c>
+      <c r="F720" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G720" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H720" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I720" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J720" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document</t>
+        </is>
+      </c>
+      <c r="K720" s="3" t="inlineStr"/>
+      <c r="L720" s="4" t="inlineStr">
+        <is>
+          <t>T1D88570</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B721" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000107</t>
+        </is>
+      </c>
+      <c r="C721" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D721" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E721" s="4" t="inlineStr">
+        <is>
+          <t>GUNABATI MAHANTO</t>
+        </is>
+      </c>
+      <c r="F721" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G721" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H721" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I721" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J721" s="4" t="inlineStr"/>
+      <c r="K721" s="3" t="inlineStr"/>
+      <c r="L721" s="4" t="inlineStr">
+        <is>
+          <t>T2E27927</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B722" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000049</t>
+        </is>
+      </c>
+      <c r="C722" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D722" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E722" s="4" t="inlineStr">
+        <is>
+          <t>Bhismadev Dhrua</t>
+        </is>
+      </c>
+      <c r="F722" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G722" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H722" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I722" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J722" s="4" t="inlineStr"/>
+      <c r="K722" s="3" t="inlineStr"/>
+      <c r="L722" s="4" t="inlineStr">
+        <is>
+          <t>T2D18346</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B723" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000048</t>
+        </is>
+      </c>
+      <c r="C723" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D723" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E723" s="4" t="inlineStr">
+        <is>
+          <t>PRITAM PRATAP NAIK</t>
+        </is>
+      </c>
+      <c r="F723" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G723" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H723" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I723" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J723" s="4" t="inlineStr"/>
+      <c r="K723" s="3" t="inlineStr"/>
+      <c r="L723" s="4" t="inlineStr">
+        <is>
+          <t>T2E32959</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B724" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000117</t>
+        </is>
+      </c>
+      <c r="C724" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D724" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E724" s="4" t="inlineStr">
+        <is>
+          <t>KONARK EARTHMOVER PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F724" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G724" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H724" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I724" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J724" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD20260530DL7CC6567' does not match expected old chassis 'COD20260530DL7CC5657'; COD Registration No 'DL7CC6567' does not match expected old vehicle registration 'DL7CC5657'</t>
+        </is>
+      </c>
+      <c r="K724" s="3" t="inlineStr"/>
+      <c r="L724" s="4" t="inlineStr">
+        <is>
+          <t>T5A19991</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B725" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000116</t>
+        </is>
+      </c>
+      <c r="C725" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D725" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E725" s="4" t="inlineStr">
+        <is>
+          <t>Dibyasom Puhan</t>
+        </is>
+      </c>
+      <c r="F725" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G725" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H725" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I725" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J725" s="4" t="inlineStr"/>
+      <c r="K725" s="3" t="inlineStr"/>
+      <c r="L725" s="4" t="inlineStr">
+        <is>
+          <t>T6E57252</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B726" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000115</t>
+        </is>
+      </c>
+      <c r="C726" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D726" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E726" s="4" t="inlineStr">
+        <is>
+          <t>Dhananjay Das</t>
+        </is>
+      </c>
+      <c r="F726" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G726" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H726" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I726" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J726" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'
+COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'</t>
+        </is>
+      </c>
+      <c r="K726" s="3" t="inlineStr"/>
+      <c r="L726" s="4" t="inlineStr">
+        <is>
+          <t>S2D13108</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B727" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000114</t>
+        </is>
+      </c>
+      <c r="C727" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D727" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E727" s="4" t="inlineStr">
+        <is>
+          <t>Deepak Kumar Verma</t>
+        </is>
+      </c>
+      <c r="F727" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G727" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H727" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I727" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J727" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'
+COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'</t>
+        </is>
+      </c>
+      <c r="K727" s="3" t="inlineStr"/>
+      <c r="L727" s="4" t="inlineStr">
+        <is>
+          <t>T6E59092</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B728" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000113</t>
+        </is>
+      </c>
+      <c r="C728" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D728" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E728" s="4" t="inlineStr">
+        <is>
+          <t>BIJAY KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F728" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G728" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H728" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I728" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J728" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer new vehicle model does not match portal model group 'BOLERO NEO PLUS' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO NEO+ P10 WHITE, Chassis Number: T6D66629, Engine Number: YXT4D47059')</t>
+        </is>
+      </c>
+      <c r="K728" s="3" t="inlineStr"/>
+      <c r="L728" s="4" t="inlineStr">
+        <is>
+          <t>T6D66629</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B729" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000112</t>
+        </is>
+      </c>
+      <c r="C729" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D729" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E729" s="4" t="inlineStr">
+        <is>
+          <t>Azhar Nawab</t>
+        </is>
+      </c>
+      <c r="F729" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G729" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H729" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I729" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J729" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'
+COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'</t>
+        </is>
+      </c>
+      <c r="K729" s="3" t="inlineStr"/>
+      <c r="L729" s="4" t="inlineStr">
+        <is>
+          <t>T2E73684</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B730" s="4" t="inlineStr">
+        <is>
+          <t>‌</t>
+        </is>
+      </c>
+      <c r="C730" s="4" t="inlineStr">
+        <is>
+          <t>‌</t>
+        </is>
+      </c>
+      <c r="D730" s="4" t="inlineStr">
+        <is>
+          <t>‌</t>
+        </is>
+      </c>
+      <c r="E730" s="4" t="inlineStr">
+        <is>
+          <t>Bhismadev Dhrua</t>
+        </is>
+      </c>
+      <c r="F730" s="4" t="inlineStr">
+        <is>
+          <t>‌</t>
+        </is>
+      </c>
+      <c r="G730" s="4" t="inlineStr">
+        <is>
+          <t>‌</t>
+        </is>
+      </c>
+      <c r="H730" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I730" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J730" s="4" t="inlineStr"/>
+      <c r="K730" s="3" t="inlineStr"/>
+      <c r="L730" s="4" t="inlineStr">
+        <is>
+          <t>T2D18346</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B731" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000048</t>
+        </is>
+      </c>
+      <c r="C731" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D731" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E731" s="4" t="inlineStr">
+        <is>
+          <t>PRITAM PRATAP NAIK</t>
+        </is>
+      </c>
+      <c r="F731" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G731" s="4" t="inlineStr">
+        <is>
+          <t>SUNDARGARH_SZS</t>
+        </is>
+      </c>
+      <c r="H731" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I731" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J731" s="4" t="inlineStr"/>
+      <c r="K731" s="3" t="inlineStr"/>
+      <c r="L731" s="4" t="inlineStr">
+        <is>
+          <t>T2E32959</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B732" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000117</t>
+        </is>
+      </c>
+      <c r="C732" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D732" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E732" s="4" t="inlineStr">
+        <is>
+          <t>KONARK EARTHMOVER PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F732" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G732" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H732" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I732" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J732" s="4" t="inlineStr"/>
+      <c r="K732" s="3" t="inlineStr"/>
+      <c r="L732" s="4" t="inlineStr">
+        <is>
+          <t>T5A19991</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B733" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000116</t>
+        </is>
+      </c>
+      <c r="C733" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D733" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E733" s="4" t="inlineStr">
+        <is>
+          <t>Dibyasom Puhan</t>
+        </is>
+      </c>
+      <c r="F733" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G733" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H733" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I733" s="6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J733" s="4" t="inlineStr"/>
+      <c r="K733" s="3" t="inlineStr"/>
+      <c r="L733" s="4" t="inlineStr">
+        <is>
+          <t>T6E57252</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B734" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000115</t>
+        </is>
+      </c>
+      <c r="C734" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D734" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E734" s="4" t="inlineStr">
+        <is>
+          <t>Dhananjay Das</t>
+        </is>
+      </c>
+      <c r="F734" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G734" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H734" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I734" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J734" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'
+COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'</t>
+        </is>
+      </c>
+      <c r="K734" s="3" t="inlineStr"/>
+      <c r="L734" s="4" t="inlineStr">
+        <is>
+          <t>S2D13108</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B735" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000114</t>
+        </is>
+      </c>
+      <c r="C735" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D735" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E735" s="4" t="inlineStr">
+        <is>
+          <t>Deepak Kumar Verma</t>
+        </is>
+      </c>
+      <c r="F735" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G735" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H735" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I735" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J735" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'
+COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'</t>
+        </is>
+      </c>
+      <c r="K735" s="3" t="inlineStr"/>
+      <c r="L735" s="4" t="inlineStr">
+        <is>
+          <t>T6E59092</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B736" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000113</t>
+        </is>
+      </c>
+      <c r="C736" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D736" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E736" s="4" t="inlineStr">
+        <is>
+          <t>BIJAY KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F736" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G736" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H736" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I736" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J736" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer new vehicle model does not match portal model group 'BOLERO NEO PLUS' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO NEO+ P10 WHITE, Chassis Number: T6D66629, Engine Number: YXT4D47059')</t>
+        </is>
+      </c>
+      <c r="K736" s="3" t="inlineStr"/>
+      <c r="L736" s="4" t="inlineStr">
+        <is>
+          <t>T6D66629</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B737" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000112</t>
+        </is>
+      </c>
+      <c r="C737" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D737" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E737" s="4" t="inlineStr">
+        <is>
+          <t>Azhar Nawab</t>
+        </is>
+      </c>
+      <c r="F737" s="4" t="inlineStr">
+        <is>
+          <t>KRISHNA AUTOMOTIVE</t>
+        </is>
+      </c>
+      <c r="G737" s="4" t="inlineStr">
+        <is>
+          <t>ROURKELA 3S</t>
+        </is>
+      </c>
+      <c r="H737" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I737" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J737" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'
+COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'</t>
+        </is>
+      </c>
+      <c r="K737" s="3" t="inlineStr"/>
+      <c r="L737" s="4" t="inlineStr">
+        <is>
+          <t>T2E73684</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="KYC Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,11 +27,29 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFB91C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF047857"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF92400E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -47,12 +64,6 @@
       <color rgb="00047857"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -63,8 +74,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="FF1E3A8A"/>
+        <bgColor rgb="FF1E3A8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,9 +114,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -468,24 +488,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L737"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L748"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="6"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="12"/>
     <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Row Number</t>
@@ -547,7 +567,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>3</v>
       </c>
@@ -607,7 +627,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -667,7 +687,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
@@ -727,7 +747,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -787,7 +807,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
@@ -847,7 +867,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -891,7 +911,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>2026-06-24 13:05:47</t>
@@ -903,7 +923,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
@@ -963,7 +983,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1007,7 +1027,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>2026-06-24 13:16:47</t>
@@ -1019,7 +1039,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>8</v>
       </c>
@@ -1063,7 +1083,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>2026-06-24 13:25:43</t>
@@ -1075,7 +1095,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1119,7 +1139,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>2026-06-24 13:27:06</t>
@@ -1131,7 +1151,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
@@ -1175,7 +1195,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>2026-06-24 13:28:28</t>
@@ -1187,7 +1207,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>8</v>
       </c>
@@ -1247,7 +1267,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>8</v>
       </c>
@@ -1291,7 +1311,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>2026-06-24 16:12:12</t>
@@ -1303,7 +1323,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>1</v>
       </c>
@@ -1363,7 +1383,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="16" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>2</v>
       </c>
@@ -1423,7 +1443,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>3</v>
       </c>
@@ -1483,7 +1503,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>4</v>
       </c>
@@ -1543,7 +1563,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>5</v>
       </c>
@@ -1603,7 +1623,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="16" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>6</v>
       </c>
@@ -1663,7 +1683,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="16" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>7</v>
       </c>
@@ -1723,7 +1743,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>8</v>
       </c>
@@ -1783,7 +1803,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>3</v>
       </c>
@@ -1843,7 +1863,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="16" customHeight="1">
       <c r="A24" s="3" t="n">
         <v>3</v>
       </c>
@@ -1903,7 +1923,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="16" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>6</v>
       </c>
@@ -1963,7 +1983,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="16" customHeight="1">
       <c r="A26" s="3" t="n">
         <v>7</v>
       </c>
@@ -2023,7 +2043,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>3</v>
       </c>
@@ -2083,7 +2103,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>7</v>
       </c>
@@ -2143,7 +2163,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>7</v>
       </c>
@@ -2203,7 +2223,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="16" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>7</v>
       </c>
@@ -2263,7 +2283,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="n">
         <v>7</v>
       </c>
@@ -2323,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="n">
         <v>7</v>
       </c>
@@ -2383,7 +2403,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" s="3" t="n">
         <v>7</v>
       </c>
@@ -2443,7 +2463,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>7</v>
       </c>
@@ -2503,7 +2523,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="16" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>1</v>
       </c>
@@ -2563,7 +2583,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="16" customHeight="1">
       <c r="A36" s="3" t="n">
         <v>2</v>
       </c>
@@ -2623,7 +2643,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="16" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>3</v>
       </c>
@@ -2683,7 +2703,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="16" customHeight="1">
       <c r="A38" s="3" t="n">
         <v>4</v>
       </c>
@@ -2743,7 +2763,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="n">
         <v>5</v>
       </c>
@@ -2803,7 +2823,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="n">
         <v>6</v>
       </c>
@@ -2863,7 +2883,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="n">
         <v>7</v>
       </c>
@@ -2923,7 +2943,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="n">
         <v>8</v>
       </c>
@@ -2983,7 +3003,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="n">
         <v>1</v>
       </c>
@@ -3043,7 +3063,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="n">
         <v>2</v>
       </c>
@@ -3103,7 +3123,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="n">
         <v>3</v>
       </c>
@@ -3163,7 +3183,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="n">
         <v>4</v>
       </c>
@@ -3223,7 +3243,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="n">
         <v>5</v>
       </c>
@@ -3283,7 +3303,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="n">
         <v>6</v>
       </c>
@@ -3343,7 +3363,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="n">
         <v>7</v>
       </c>
@@ -3403,7 +3423,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="n">
         <v>8</v>
       </c>
@@ -3463,7 +3483,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="16" customHeight="1">
       <c r="A51" s="3" t="n">
         <v>9</v>
       </c>
@@ -3523,7 +3543,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="n">
         <v>10</v>
       </c>
@@ -3583,7 +3603,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="n">
         <v>11</v>
       </c>
@@ -3643,7 +3663,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="n">
         <v>12</v>
       </c>
@@ -3703,7 +3723,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="n">
         <v>13</v>
       </c>
@@ -3763,7 +3783,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="n">
         <v>14</v>
       </c>
@@ -3823,7 +3843,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="n">
         <v>15</v>
       </c>
@@ -3883,7 +3903,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="n">
         <v>16</v>
       </c>
@@ -3943,7 +3963,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="n">
         <v>17</v>
       </c>
@@ -4003,7 +4023,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="n">
         <v>18</v>
       </c>
@@ -4063,7 +4083,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="n">
         <v>19</v>
       </c>
@@ -4123,7 +4143,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="n">
         <v>20</v>
       </c>
@@ -4183,7 +4203,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="n">
         <v>21</v>
       </c>
@@ -4243,7 +4263,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="16" customHeight="1">
       <c r="A64" s="3" t="n">
         <v>22</v>
       </c>
@@ -4303,7 +4323,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="16" customHeight="1">
       <c r="A65" s="3" t="n">
         <v>23</v>
       </c>
@@ -4363,7 +4383,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="16" customHeight="1">
       <c r="A66" s="3" t="n">
         <v>24</v>
       </c>
@@ -4423,7 +4443,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="16" customHeight="1">
       <c r="A67" s="3" t="n">
         <v>25</v>
       </c>
@@ -4483,7 +4503,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="16" customHeight="1">
       <c r="A68" s="3" t="n">
         <v>26</v>
       </c>
@@ -4527,7 +4547,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="n"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 00:51:27</t>
@@ -4539,7 +4559,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="16" customHeight="1">
       <c r="A69" s="3" t="n">
         <v>27</v>
       </c>
@@ -4599,7 +4619,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="16" customHeight="1">
       <c r="A70" s="3" t="n">
         <v>28</v>
       </c>
@@ -4659,7 +4679,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="16" customHeight="1">
       <c r="A71" s="3" t="n">
         <v>29</v>
       </c>
@@ -4719,7 +4739,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="16" customHeight="1">
       <c r="A72" s="3" t="n">
         <v>30</v>
       </c>
@@ -4779,7 +4799,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="16" customHeight="1">
       <c r="A73" s="3" t="n">
         <v>31</v>
       </c>
@@ -4839,7 +4859,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="16" customHeight="1">
       <c r="A74" s="3" t="n">
         <v>32</v>
       </c>
@@ -4899,7 +4919,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="16" customHeight="1">
       <c r="A75" s="3" t="n">
         <v>33</v>
       </c>
@@ -4959,7 +4979,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="16" customHeight="1">
       <c r="A76" s="3" t="n">
         <v>34</v>
       </c>
@@ -5019,7 +5039,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="16" customHeight="1">
       <c r="A77" s="3" t="n">
         <v>35</v>
       </c>
@@ -5079,7 +5099,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="16" customHeight="1">
       <c r="A78" s="3" t="n">
         <v>36</v>
       </c>
@@ -5139,7 +5159,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="16" customHeight="1">
       <c r="A79" s="3" t="n">
         <v>37</v>
       </c>
@@ -5199,7 +5219,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="16" customHeight="1">
       <c r="A80" s="3" t="n">
         <v>38</v>
       </c>
@@ -5259,7 +5279,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="16" customHeight="1">
       <c r="A81" s="3" t="n">
         <v>39</v>
       </c>
@@ -5319,7 +5339,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="16" customHeight="1">
       <c r="A82" s="3" t="n">
         <v>40</v>
       </c>
@@ -5379,7 +5399,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="16" customHeight="1">
       <c r="A83" s="3" t="n">
         <v>41</v>
       </c>
@@ -5439,7 +5459,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="16" customHeight="1">
       <c r="A84" s="3" t="n">
         <v>42</v>
       </c>
@@ -5499,7 +5519,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="16" customHeight="1">
       <c r="A85" s="3" t="n">
         <v>43</v>
       </c>
@@ -5543,7 +5563,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J85" s="4" t="inlineStr"/>
+      <c r="J85" s="4" t="n"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 00:54:18</t>
@@ -5555,7 +5575,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="16" customHeight="1">
       <c r="A86" s="3" t="n">
         <v>44</v>
       </c>
@@ -5599,7 +5619,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="n"/>
       <c r="K86" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 00:55:39</t>
@@ -5611,7 +5631,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="16" customHeight="1">
       <c r="A87" s="3" t="n">
         <v>45</v>
       </c>
@@ -5671,7 +5691,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="16" customHeight="1">
       <c r="A88" s="3" t="n">
         <v>46</v>
       </c>
@@ -5715,7 +5735,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="n"/>
       <c r="K88" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 00:57:06</t>
@@ -5727,7 +5747,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="16" customHeight="1">
       <c r="A89" s="3" t="n">
         <v>47</v>
       </c>
@@ -5787,7 +5807,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="16" customHeight="1">
       <c r="A90" s="3" t="n">
         <v>48</v>
       </c>
@@ -5847,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="16" customHeight="1">
       <c r="A91" s="3" t="n">
         <v>49</v>
       </c>
@@ -5907,7 +5927,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="16" customHeight="1">
       <c r="A92" s="3" t="n">
         <v>50</v>
       </c>
@@ -5951,7 +5971,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="n"/>
       <c r="K92" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 00:58:45</t>
@@ -5963,7 +5983,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="16" customHeight="1">
       <c r="A93" s="3" t="n">
         <v>51</v>
       </c>
@@ -6007,7 +6027,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J93" s="4" t="inlineStr"/>
+      <c r="J93" s="4" t="n"/>
       <c r="K93" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:00:07</t>
@@ -6019,7 +6039,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="16" customHeight="1">
       <c r="A94" s="3" t="n">
         <v>52</v>
       </c>
@@ -6079,7 +6099,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="16" customHeight="1">
       <c r="A95" s="3" t="n">
         <v>53</v>
       </c>
@@ -6123,7 +6143,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="n"/>
       <c r="K95" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:01:33</t>
@@ -6135,7 +6155,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="16" customHeight="1">
       <c r="A96" s="3" t="n">
         <v>54</v>
       </c>
@@ -6179,7 +6199,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="n"/>
       <c r="K96" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:02:55</t>
@@ -6191,7 +6211,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="16" customHeight="1">
       <c r="A97" s="3" t="n">
         <v>55</v>
       </c>
@@ -6251,7 +6271,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="16" customHeight="1">
       <c r="A98" s="3" t="n">
         <v>56</v>
       </c>
@@ -6311,7 +6331,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="16" customHeight="1">
       <c r="A99" s="3" t="n">
         <v>57</v>
       </c>
@@ -6371,7 +6391,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="16" customHeight="1">
       <c r="A100" s="3" t="n">
         <v>58</v>
       </c>
@@ -6415,7 +6435,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J100" s="4" t="inlineStr"/>
+      <c r="J100" s="4" t="n"/>
       <c r="K100" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:04:33</t>
@@ -6427,7 +6447,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="16" customHeight="1">
       <c r="A101" s="3" t="n">
         <v>59</v>
       </c>
@@ -6487,7 +6507,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="16" customHeight="1">
       <c r="A102" s="3" t="n">
         <v>60</v>
       </c>
@@ -6547,7 +6567,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="16" customHeight="1">
       <c r="A103" s="3" t="n">
         <v>61</v>
       </c>
@@ -6591,7 +6611,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="n"/>
       <c r="K103" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:06:05</t>
@@ -6603,7 +6623,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="16" customHeight="1">
       <c r="A104" s="3" t="n">
         <v>62</v>
       </c>
@@ -6663,7 +6683,7 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="16" customHeight="1">
       <c r="A105" s="3" t="n">
         <v>63</v>
       </c>
@@ -6707,7 +6727,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="n"/>
       <c r="K105" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:07:31</t>
@@ -6719,7 +6739,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="16" customHeight="1">
       <c r="A106" s="3" t="n">
         <v>64</v>
       </c>
@@ -6779,7 +6799,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="16" customHeight="1">
       <c r="A107" s="3" t="n">
         <v>65</v>
       </c>
@@ -6823,7 +6843,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr"/>
+      <c r="J107" s="4" t="n"/>
       <c r="K107" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:13:33</t>
@@ -6835,7 +6855,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="16" customHeight="1">
       <c r="A108" s="3" t="n">
         <v>66</v>
       </c>
@@ -6895,7 +6915,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="16" customHeight="1">
       <c r="A109" s="3" t="n">
         <v>67</v>
       </c>
@@ -6955,7 +6975,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="16" customHeight="1">
       <c r="A110" s="3" t="n">
         <v>68</v>
       </c>
@@ -7015,7 +7035,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="16" customHeight="1">
       <c r="A111" s="3" t="n">
         <v>69</v>
       </c>
@@ -7075,7 +7095,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="16" customHeight="1">
       <c r="A112" s="3" t="n">
         <v>70</v>
       </c>
@@ -7135,7 +7155,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="16" customHeight="1">
       <c r="A113" s="3" t="n">
         <v>71</v>
       </c>
@@ -7195,7 +7215,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="16" customHeight="1">
       <c r="A114" s="3" t="n">
         <v>72</v>
       </c>
@@ -7255,7 +7275,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="16" customHeight="1">
       <c r="A115" s="3" t="n">
         <v>73</v>
       </c>
@@ -7315,7 +7335,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="16" customHeight="1">
       <c r="A116" s="3" t="n">
         <v>74</v>
       </c>
@@ -7375,7 +7395,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="16" customHeight="1">
       <c r="A117" s="3" t="n">
         <v>75</v>
       </c>
@@ -7435,7 +7455,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="16" customHeight="1">
       <c r="A118" s="3" t="n">
         <v>76</v>
       </c>
@@ -7495,7 +7515,7 @@
         </is>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="16" customHeight="1">
       <c r="A119" s="3" t="n">
         <v>77</v>
       </c>
@@ -7555,7 +7575,7 @@
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="16" customHeight="1">
       <c r="A120" s="3" t="n">
         <v>78</v>
       </c>
@@ -7615,7 +7635,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="16" customHeight="1">
       <c r="A121" s="3" t="n">
         <v>79</v>
       </c>
@@ -7675,7 +7695,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="16" customHeight="1">
       <c r="A122" s="3" t="n">
         <v>80</v>
       </c>
@@ -7735,7 +7755,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="16" customHeight="1">
       <c r="A123" s="3" t="n">
         <v>81</v>
       </c>
@@ -7795,7 +7815,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="16" customHeight="1">
       <c r="A124" s="3" t="n">
         <v>82</v>
       </c>
@@ -7855,7 +7875,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="16" customHeight="1">
       <c r="A125" s="3" t="n">
         <v>83</v>
       </c>
@@ -7915,7 +7935,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="16" customHeight="1">
       <c r="A126" s="3" t="n">
         <v>84</v>
       </c>
@@ -7975,7 +7995,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="16" customHeight="1">
       <c r="A127" s="3" t="n">
         <v>85</v>
       </c>
@@ -8019,7 +8039,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J127" s="4" t="inlineStr"/>
+      <c r="J127" s="4" t="n"/>
       <c r="K127" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:16:45</t>
@@ -8031,7 +8051,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="16" customHeight="1">
       <c r="A128" s="3" t="n">
         <v>86</v>
       </c>
@@ -8091,7 +8111,7 @@
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="16" customHeight="1">
       <c r="A129" s="3" t="n">
         <v>87</v>
       </c>
@@ -8151,7 +8171,7 @@
         </is>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="16" customHeight="1">
       <c r="A130" s="3" t="n">
         <v>88</v>
       </c>
@@ -8211,7 +8231,7 @@
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="16" customHeight="1">
       <c r="A131" s="3" t="n">
         <v>89</v>
       </c>
@@ -8271,7 +8291,7 @@
         </is>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" s="3" t="n">
         <v>90</v>
       </c>
@@ -8315,7 +8335,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J132" s="4" t="inlineStr"/>
+      <c r="J132" s="4" t="n"/>
       <c r="K132" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:18:29</t>
@@ -8327,7 +8347,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="16" customHeight="1">
       <c r="A133" s="3" t="n">
         <v>91</v>
       </c>
@@ -8371,7 +8391,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J133" s="4" t="inlineStr"/>
+      <c r="J133" s="4" t="n"/>
       <c r="K133" s="3" t="inlineStr">
         <is>
           <t>2026-06-26 01:19:51</t>
@@ -8383,7 +8403,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="16" customHeight="1">
       <c r="A134" s="3" t="n">
         <v>92</v>
       </c>
@@ -8443,7 +8463,7 @@
         </is>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="16" customHeight="1">
       <c r="A135" s="3" t="n">
         <v>93</v>
       </c>
@@ -8503,7 +8523,7 @@
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="16" customHeight="1">
       <c r="A136" s="3" t="n">
         <v>94</v>
       </c>
@@ -8563,7 +8583,7 @@
         </is>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="16" customHeight="1">
       <c r="A137" s="3" t="n">
         <v>95</v>
       </c>
@@ -8623,7 +8643,7 @@
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="16" customHeight="1">
       <c r="A138" s="3" t="n">
         <v>96</v>
       </c>
@@ -8683,7 +8703,7 @@
         </is>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="16" customHeight="1">
       <c r="A139" s="3" t="n">
         <v>97</v>
       </c>
@@ -8743,7 +8763,7 @@
         </is>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="16" customHeight="1">
       <c r="A140" s="3" t="n">
         <v>98</v>
       </c>
@@ -8803,7 +8823,7 @@
         </is>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="16" customHeight="1">
       <c r="A141" s="3" t="n">
         <v>99</v>
       </c>
@@ -8863,7 +8883,7 @@
         </is>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="16" customHeight="1">
       <c r="A142" s="3" t="n">
         <v>100</v>
       </c>
@@ -8923,7 +8943,7 @@
         </is>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="16" customHeight="1">
       <c r="A143" s="3" t="n">
         <v>8</v>
       </c>
@@ -8983,7 +9003,7 @@
         </is>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="16" customHeight="1">
       <c r="A144" s="3" t="n">
         <v>1</v>
       </c>
@@ -9043,7 +9063,7 @@
         </is>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="16" customHeight="1">
       <c r="A145" s="3" t="n">
         <v>1</v>
       </c>
@@ -9103,7 +9123,7 @@
         </is>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="16" customHeight="1">
       <c r="A146" s="3" t="n">
         <v>2</v>
       </c>
@@ -9163,7 +9183,7 @@
         </is>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="16" customHeight="1">
       <c r="A147" s="3" t="n">
         <v>3</v>
       </c>
@@ -9223,7 +9243,7 @@
         </is>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" s="3" t="n">
         <v>4</v>
       </c>
@@ -9283,7 +9303,7 @@
         </is>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="16" customHeight="1">
       <c r="A149" s="3" t="n">
         <v>5</v>
       </c>
@@ -9343,7 +9363,7 @@
         </is>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="16" customHeight="1">
       <c r="A150" s="3" t="n">
         <v>6</v>
       </c>
@@ -9403,7 +9423,7 @@
         </is>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="16" customHeight="1">
       <c r="A151" s="3" t="n">
         <v>7</v>
       </c>
@@ -9463,7 +9483,7 @@
         </is>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="16" customHeight="1">
       <c r="A152" s="3" t="n">
         <v>8</v>
       </c>
@@ -9523,7 +9543,7 @@
         </is>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="16" customHeight="1">
       <c r="A153" s="3" t="n">
         <v>9</v>
       </c>
@@ -9583,7 +9603,7 @@
         </is>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="16" customHeight="1">
       <c r="A154" s="3" t="n">
         <v>10</v>
       </c>
@@ -9643,7 +9663,7 @@
         </is>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="16" customHeight="1">
       <c r="A155" s="3" t="n">
         <v>11</v>
       </c>
@@ -9703,7 +9723,7 @@
         </is>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="16" customHeight="1">
       <c r="A156" s="3" t="n">
         <v>12</v>
       </c>
@@ -9763,7 +9783,7 @@
         </is>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="16" customHeight="1">
       <c r="A157" s="3" t="n">
         <v>13</v>
       </c>
@@ -9823,7 +9843,7 @@
         </is>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="16" customHeight="1">
       <c r="A158" s="3" t="n">
         <v>14</v>
       </c>
@@ -9883,7 +9903,7 @@
         </is>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="16" customHeight="1">
       <c r="A159" s="3" t="n">
         <v>1</v>
       </c>
@@ -9943,7 +9963,7 @@
         </is>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="16" customHeight="1">
       <c r="A160" s="3" t="n">
         <v>2</v>
       </c>
@@ -10003,7 +10023,7 @@
         </is>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="16" customHeight="1">
       <c r="A161" s="3" t="n">
         <v>3</v>
       </c>
@@ -10063,7 +10083,7 @@
         </is>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="16" customHeight="1">
       <c r="A162" s="3" t="n">
         <v>4</v>
       </c>
@@ -10123,7 +10143,7 @@
         </is>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="16" customHeight="1">
       <c r="A163" s="3" t="n">
         <v>5</v>
       </c>
@@ -10183,7 +10203,7 @@
         </is>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="16" customHeight="1">
       <c r="A164" s="3" t="n">
         <v>6</v>
       </c>
@@ -10243,7 +10263,7 @@
         </is>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="16" customHeight="1">
       <c r="A165" s="3" t="n">
         <v>7</v>
       </c>
@@ -10303,7 +10323,7 @@
         </is>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="16" customHeight="1">
       <c r="A166" s="3" t="n">
         <v>8</v>
       </c>
@@ -10363,7 +10383,7 @@
         </is>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="16" customHeight="1">
       <c r="A167" s="3" t="n">
         <v>9</v>
       </c>
@@ -10423,7 +10443,7 @@
         </is>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="16" customHeight="1">
       <c r="A168" s="3" t="n">
         <v>10</v>
       </c>
@@ -10483,7 +10503,7 @@
         </is>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="16" customHeight="1">
       <c r="A169" s="3" t="n">
         <v>11</v>
       </c>
@@ -10543,7 +10563,7 @@
         </is>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="16" customHeight="1">
       <c r="A170" s="3" t="n">
         <v>12</v>
       </c>
@@ -10603,7 +10623,7 @@
         </is>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="16" customHeight="1">
       <c r="A171" s="3" t="n">
         <v>13</v>
       </c>
@@ -10663,7 +10683,7 @@
         </is>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="16" customHeight="1">
       <c r="A172" s="3" t="n">
         <v>14</v>
       </c>
@@ -10723,7 +10743,7 @@
         </is>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="16" customHeight="1">
       <c r="A173" s="3" t="n">
         <v>1</v>
       </c>
@@ -10783,7 +10803,7 @@
         </is>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="16" customHeight="1">
       <c r="A174" s="3" t="n">
         <v>2</v>
       </c>
@@ -10843,7 +10863,7 @@
         </is>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="16" customHeight="1">
       <c r="A175" s="3" t="n">
         <v>3</v>
       </c>
@@ -10903,7 +10923,7 @@
         </is>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="16" customHeight="1">
       <c r="A176" s="3" t="n">
         <v>8</v>
       </c>
@@ -10963,7 +10983,7 @@
         </is>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="16" customHeight="1">
       <c r="A177" s="3" t="n">
         <v>8</v>
       </c>
@@ -11023,7 +11043,7 @@
         </is>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="16" customHeight="1">
       <c r="A178" s="3" t="n">
         <v>1</v>
       </c>
@@ -11067,7 +11087,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J178" s="4" t="inlineStr"/>
+      <c r="J178" s="4" t="n"/>
       <c r="K178" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 14:31:36</t>
@@ -11079,7 +11099,7 @@
         </is>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="16" customHeight="1">
       <c r="A179" s="3" t="n">
         <v>1</v>
       </c>
@@ -11139,7 +11159,7 @@
         </is>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="16" customHeight="1">
       <c r="A180" s="3" t="n">
         <v>1</v>
       </c>
@@ -11183,7 +11203,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J180" s="4" t="inlineStr"/>
+      <c r="J180" s="4" t="n"/>
       <c r="K180" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 15:02:35</t>
@@ -11195,7 +11215,7 @@
         </is>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="16" customHeight="1">
       <c r="A181" s="3" t="n">
         <v>2</v>
       </c>
@@ -11255,7 +11275,7 @@
         </is>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="16" customHeight="1">
       <c r="A182" s="3" t="n">
         <v>1</v>
       </c>
@@ -11315,7 +11335,7 @@
         </is>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="16" customHeight="1">
       <c r="A183" s="3" t="n">
         <v>2</v>
       </c>
@@ -11375,7 +11395,7 @@
         </is>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="16" customHeight="1">
       <c r="A184" s="3" t="n">
         <v>3</v>
       </c>
@@ -11435,7 +11455,7 @@
         </is>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="16" customHeight="1">
       <c r="A185" s="3" t="n">
         <v>4</v>
       </c>
@@ -11495,7 +11515,7 @@
         </is>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="16" customHeight="1">
       <c r="A186" s="3" t="n">
         <v>5</v>
       </c>
@@ -11555,7 +11575,7 @@
         </is>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="16" customHeight="1">
       <c r="A187" s="3" t="n">
         <v>6</v>
       </c>
@@ -11615,7 +11635,7 @@
         </is>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="16" customHeight="1">
       <c r="A188" s="3" t="n">
         <v>7</v>
       </c>
@@ -11675,7 +11695,7 @@
         </is>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="16" customHeight="1">
       <c r="A189" s="3" t="n">
         <v>8</v>
       </c>
@@ -11735,7 +11755,7 @@
         </is>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="16" customHeight="1">
       <c r="A190" s="3" t="n">
         <v>9</v>
       </c>
@@ -11795,7 +11815,7 @@
         </is>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="16" customHeight="1">
       <c r="A191" s="3" t="n">
         <v>10</v>
       </c>
@@ -11855,7 +11875,7 @@
         </is>
       </c>
     </row>
-    <row r="192">
+    <row r="192" ht="16" customHeight="1">
       <c r="A192" s="3" t="n">
         <v>11</v>
       </c>
@@ -11915,7 +11935,7 @@
         </is>
       </c>
     </row>
-    <row r="193">
+    <row r="193" ht="16" customHeight="1">
       <c r="A193" s="3" t="n">
         <v>12</v>
       </c>
@@ -11975,7 +11995,7 @@
         </is>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="16" customHeight="1">
       <c r="A194" s="3" t="n">
         <v>13</v>
       </c>
@@ -12035,7 +12055,7 @@
         </is>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="16" customHeight="1">
       <c r="A195" s="3" t="n">
         <v>14</v>
       </c>
@@ -12095,7 +12115,7 @@
         </is>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="16" customHeight="1">
       <c r="A196" s="3" t="n">
         <v>15</v>
       </c>
@@ -12155,7 +12175,7 @@
         </is>
       </c>
     </row>
-    <row r="197">
+    <row r="197" ht="16" customHeight="1">
       <c r="A197" s="3" t="n">
         <v>16</v>
       </c>
@@ -12215,7 +12235,7 @@
         </is>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="16" customHeight="1">
       <c r="A198" s="3" t="n">
         <v>17</v>
       </c>
@@ -12275,7 +12295,7 @@
         </is>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="16" customHeight="1">
       <c r="A199" s="3" t="n">
         <v>1</v>
       </c>
@@ -12335,7 +12355,7 @@
         </is>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="16" customHeight="1">
       <c r="A200" s="3" t="n">
         <v>2</v>
       </c>
@@ -12395,7 +12415,7 @@
         </is>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="16" customHeight="1">
       <c r="A201" s="3" t="n">
         <v>3</v>
       </c>
@@ -12455,7 +12475,7 @@
         </is>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="16" customHeight="1">
       <c r="A202" s="3" t="n">
         <v>1</v>
       </c>
@@ -12499,7 +12519,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J202" s="4" t="inlineStr"/>
+      <c r="J202" s="4" t="n"/>
       <c r="K202" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 15:42:22</t>
@@ -12511,7 +12531,7 @@
         </is>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="16" customHeight="1">
       <c r="A203" s="3" t="n">
         <v>2</v>
       </c>
@@ -12571,7 +12591,7 @@
         </is>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="16" customHeight="1">
       <c r="A204" s="3" t="n">
         <v>1</v>
       </c>
@@ -12615,7 +12635,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J204" s="4" t="inlineStr"/>
+      <c r="J204" s="4" t="n"/>
       <c r="K204" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 15:54:45</t>
@@ -12627,7 +12647,7 @@
         </is>
       </c>
     </row>
-    <row r="205">
+    <row r="205" ht="16" customHeight="1">
       <c r="A205" s="3" t="n">
         <v>2</v>
       </c>
@@ -12687,7 +12707,7 @@
         </is>
       </c>
     </row>
-    <row r="206">
+    <row r="206" ht="16" customHeight="1">
       <c r="A206" s="3" t="n">
         <v>3</v>
       </c>
@@ -12747,7 +12767,7 @@
         </is>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="16" customHeight="1">
       <c r="A207" s="3" t="n">
         <v>1</v>
       </c>
@@ -12807,7 +12827,7 @@
         </is>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="16" customHeight="1">
       <c r="A208" s="3" t="n">
         <v>2</v>
       </c>
@@ -12867,7 +12887,7 @@
         </is>
       </c>
     </row>
-    <row r="209">
+    <row r="209" ht="16" customHeight="1">
       <c r="A209" s="3" t="n">
         <v>3</v>
       </c>
@@ -12927,7 +12947,7 @@
         </is>
       </c>
     </row>
-    <row r="210">
+    <row r="210" ht="16" customHeight="1">
       <c r="A210" s="3" t="n">
         <v>4</v>
       </c>
@@ -12987,7 +13007,7 @@
         </is>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="16" customHeight="1">
       <c r="A211" s="3" t="n">
         <v>5</v>
       </c>
@@ -13031,7 +13051,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J211" s="4" t="inlineStr"/>
+      <c r="J211" s="4" t="n"/>
       <c r="K211" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 16:36:46</t>
@@ -13043,7 +13063,7 @@
         </is>
       </c>
     </row>
-    <row r="212">
+    <row r="212" ht="16" customHeight="1">
       <c r="A212" s="3" t="n">
         <v>6</v>
       </c>
@@ -13103,7 +13123,7 @@
         </is>
       </c>
     </row>
-    <row r="213">
+    <row r="213" ht="16" customHeight="1">
       <c r="A213" s="3" t="n">
         <v>7</v>
       </c>
@@ -13147,7 +13167,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="n"/>
       <c r="K213" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 16:46:50</t>
@@ -13159,7 +13179,7 @@
         </is>
       </c>
     </row>
-    <row r="214">
+    <row r="214" ht="16" customHeight="1">
       <c r="A214" s="3" t="n">
         <v>8</v>
       </c>
@@ -13219,7 +13239,7 @@
         </is>
       </c>
     </row>
-    <row r="215">
+    <row r="215" ht="16" customHeight="1">
       <c r="A215" s="3" t="n">
         <v>9</v>
       </c>
@@ -13263,7 +13283,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J215" s="4" t="inlineStr"/>
+      <c r="J215" s="4" t="n"/>
       <c r="K215" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 16:58:32</t>
@@ -13275,7 +13295,7 @@
         </is>
       </c>
     </row>
-    <row r="216">
+    <row r="216" ht="16" customHeight="1">
       <c r="A216" s="3" t="n">
         <v>10</v>
       </c>
@@ -13335,7 +13355,7 @@
         </is>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="16" customHeight="1">
       <c r="A217" s="3" t="n">
         <v>11</v>
       </c>
@@ -13379,7 +13399,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J217" s="4" t="inlineStr"/>
+      <c r="J217" s="4" t="n"/>
       <c r="K217" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 17:10:58</t>
@@ -13391,7 +13411,7 @@
         </is>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="16" customHeight="1">
       <c r="A218" s="3" t="n">
         <v>12</v>
       </c>
@@ -13435,7 +13455,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J218" s="4" t="inlineStr"/>
+      <c r="J218" s="4" t="n"/>
       <c r="K218" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 17:12:19</t>
@@ -13447,7 +13467,7 @@
         </is>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="16" customHeight="1">
       <c r="A219" s="3" t="n">
         <v>13</v>
       </c>
@@ -13491,7 +13511,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J219" s="4" t="inlineStr"/>
+      <c r="J219" s="4" t="n"/>
       <c r="K219" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 17:14:02</t>
@@ -13503,7 +13523,7 @@
         </is>
       </c>
     </row>
-    <row r="220">
+    <row r="220" ht="16" customHeight="1">
       <c r="A220" s="3" t="n">
         <v>14</v>
       </c>
@@ -13547,7 +13567,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J220" s="4" t="inlineStr"/>
+      <c r="J220" s="4" t="n"/>
       <c r="K220" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 17:15:47</t>
@@ -13559,7 +13579,7 @@
         </is>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="16" customHeight="1">
       <c r="A221" s="3" t="n">
         <v>15</v>
       </c>
@@ -13603,7 +13623,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J221" s="4" t="inlineStr"/>
+      <c r="J221" s="4" t="n"/>
       <c r="K221" s="3" t="inlineStr">
         <is>
           <t>2026-06-27 17:17:33</t>
@@ -13615,7 +13635,7 @@
         </is>
       </c>
     </row>
-    <row r="222">
+    <row r="222" ht="16" customHeight="1">
       <c r="A222" s="3" t="n">
         <v>1</v>
       </c>
@@ -13675,7 +13695,7 @@
         </is>
       </c>
     </row>
-    <row r="223">
+    <row r="223" ht="16" customHeight="1">
       <c r="A223" s="3" t="n">
         <v>2</v>
       </c>
@@ -13735,7 +13755,7 @@
         </is>
       </c>
     </row>
-    <row r="224">
+    <row r="224" ht="16" customHeight="1">
       <c r="A224" s="3" t="n">
         <v>3</v>
       </c>
@@ -13795,7 +13815,7 @@
         </is>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="16" customHeight="1">
       <c r="A225" s="3" t="n">
         <v>1</v>
       </c>
@@ -13855,7 +13875,7 @@
         </is>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="16" customHeight="1">
       <c r="A226" s="3" t="n">
         <v>2</v>
       </c>
@@ -13915,7 +13935,7 @@
         </is>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="16" customHeight="1">
       <c r="A227" s="3" t="n">
         <v>3</v>
       </c>
@@ -13975,7 +13995,7 @@
         </is>
       </c>
     </row>
-    <row r="228">
+    <row r="228" ht="16" customHeight="1">
       <c r="A228" s="3" t="n">
         <v>4</v>
       </c>
@@ -14035,7 +14055,7 @@
         </is>
       </c>
     </row>
-    <row r="229">
+    <row r="229" ht="16" customHeight="1">
       <c r="A229" s="3" t="n">
         <v>5</v>
       </c>
@@ -14095,7 +14115,7 @@
         </is>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="16" customHeight="1">
       <c r="A230" s="3" t="n">
         <v>6</v>
       </c>
@@ -14155,7 +14175,7 @@
         </is>
       </c>
     </row>
-    <row r="231">
+    <row r="231" ht="16" customHeight="1">
       <c r="A231" s="3" t="n">
         <v>7</v>
       </c>
@@ -14215,7 +14235,7 @@
         </is>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="16" customHeight="1">
       <c r="A232" s="3" t="n">
         <v>8</v>
       </c>
@@ -14275,7 +14295,7 @@
         </is>
       </c>
     </row>
-    <row r="233">
+    <row r="233" ht="16" customHeight="1">
       <c r="A233" s="3" t="n">
         <v>9</v>
       </c>
@@ -14335,7 +14355,7 @@
         </is>
       </c>
     </row>
-    <row r="234">
+    <row r="234" ht="16" customHeight="1">
       <c r="A234" s="3" t="n">
         <v>10</v>
       </c>
@@ -14395,7 +14415,7 @@
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="16" customHeight="1">
       <c r="A235" s="3" t="n">
         <v>11</v>
       </c>
@@ -14455,7 +14475,7 @@
         </is>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="16" customHeight="1">
       <c r="A236" s="3" t="n">
         <v>12</v>
       </c>
@@ -14515,7 +14535,7 @@
         </is>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="16" customHeight="1">
       <c r="A237" s="3" t="n">
         <v>13</v>
       </c>
@@ -14575,7 +14595,7 @@
         </is>
       </c>
     </row>
-    <row r="238">
+    <row r="238" ht="16" customHeight="1">
       <c r="A238" s="3" t="n">
         <v>14</v>
       </c>
@@ -14635,7 +14655,7 @@
         </is>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="16" customHeight="1">
       <c r="A239" s="3" t="n">
         <v>15</v>
       </c>
@@ -14695,7 +14715,7 @@
         </is>
       </c>
     </row>
-    <row r="240">
+    <row r="240" ht="16" customHeight="1">
       <c r="A240" s="3" t="n">
         <v>16</v>
       </c>
@@ -14755,7 +14775,7 @@
         </is>
       </c>
     </row>
-    <row r="241">
+    <row r="241" ht="16" customHeight="1">
       <c r="A241" s="3" t="n">
         <v>17</v>
       </c>
@@ -14815,7 +14835,7 @@
         </is>
       </c>
     </row>
-    <row r="242">
+    <row r="242" ht="16" customHeight="1">
       <c r="A242" s="3" t="n">
         <v>18</v>
       </c>
@@ -14875,7 +14895,7 @@
         </is>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="16" customHeight="1">
       <c r="A243" s="3" t="n">
         <v>19</v>
       </c>
@@ -14935,7 +14955,7 @@
         </is>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="16" customHeight="1">
       <c r="A244" s="3" t="n">
         <v>20</v>
       </c>
@@ -14995,7 +15015,7 @@
         </is>
       </c>
     </row>
-    <row r="245">
+    <row r="245" ht="16" customHeight="1">
       <c r="A245" s="3" t="n">
         <v>21</v>
       </c>
@@ -15055,7 +15075,7 @@
         </is>
       </c>
     </row>
-    <row r="246">
+    <row r="246" ht="16" customHeight="1">
       <c r="A246" s="3" t="n">
         <v>22</v>
       </c>
@@ -15115,7 +15135,7 @@
         </is>
       </c>
     </row>
-    <row r="247">
+    <row r="247" ht="16" customHeight="1">
       <c r="A247" s="3" t="n">
         <v>23</v>
       </c>
@@ -15175,7 +15195,7 @@
         </is>
       </c>
     </row>
-    <row r="248">
+    <row r="248" ht="16" customHeight="1">
       <c r="A248" s="3" t="n">
         <v>24</v>
       </c>
@@ -15235,7 +15255,7 @@
         </is>
       </c>
     </row>
-    <row r="249">
+    <row r="249" ht="16" customHeight="1">
       <c r="A249" s="3" t="n">
         <v>25</v>
       </c>
@@ -15295,7 +15315,7 @@
         </is>
       </c>
     </row>
-    <row r="250">
+    <row r="250" ht="16" customHeight="1">
       <c r="A250" s="3" t="n">
         <v>26</v>
       </c>
@@ -15355,7 +15375,7 @@
         </is>
       </c>
     </row>
-    <row r="251">
+    <row r="251" ht="16" customHeight="1">
       <c r="A251" s="3" t="n">
         <v>27</v>
       </c>
@@ -15415,7 +15435,7 @@
         </is>
       </c>
     </row>
-    <row r="252">
+    <row r="252" ht="16" customHeight="1">
       <c r="A252" s="3" t="n">
         <v>28</v>
       </c>
@@ -15475,7 +15495,7 @@
         </is>
       </c>
     </row>
-    <row r="253">
+    <row r="253" ht="16" customHeight="1">
       <c r="A253" s="3" t="n">
         <v>29</v>
       </c>
@@ -15535,7 +15555,7 @@
         </is>
       </c>
     </row>
-    <row r="254">
+    <row r="254" ht="16" customHeight="1">
       <c r="A254" s="3" t="n">
         <v>30</v>
       </c>
@@ -15595,7 +15615,7 @@
         </is>
       </c>
     </row>
-    <row r="255">
+    <row r="255" ht="16" customHeight="1">
       <c r="A255" s="3" t="n">
         <v>31</v>
       </c>
@@ -15655,7 +15675,7 @@
         </is>
       </c>
     </row>
-    <row r="256">
+    <row r="256" ht="16" customHeight="1">
       <c r="A256" s="3" t="n">
         <v>32</v>
       </c>
@@ -15715,7 +15735,7 @@
         </is>
       </c>
     </row>
-    <row r="257">
+    <row r="257" ht="16" customHeight="1">
       <c r="A257" s="3" t="n">
         <v>33</v>
       </c>
@@ -15775,7 +15795,7 @@
         </is>
       </c>
     </row>
-    <row r="258">
+    <row r="258" ht="16" customHeight="1">
       <c r="A258" s="3" t="n">
         <v>34</v>
       </c>
@@ -15835,7 +15855,7 @@
         </is>
       </c>
     </row>
-    <row r="259">
+    <row r="259" ht="16" customHeight="1">
       <c r="A259" s="3" t="n">
         <v>35</v>
       </c>
@@ -15895,7 +15915,7 @@
         </is>
       </c>
     </row>
-    <row r="260">
+    <row r="260" ht="16" customHeight="1">
       <c r="A260" s="3" t="n">
         <v>36</v>
       </c>
@@ -15955,7 +15975,7 @@
         </is>
       </c>
     </row>
-    <row r="261">
+    <row r="261" ht="16" customHeight="1">
       <c r="A261" s="3" t="n">
         <v>37</v>
       </c>
@@ -16015,7 +16035,7 @@
         </is>
       </c>
     </row>
-    <row r="262">
+    <row r="262" ht="16" customHeight="1">
       <c r="A262" s="3" t="n">
         <v>38</v>
       </c>
@@ -16075,7 +16095,7 @@
         </is>
       </c>
     </row>
-    <row r="263">
+    <row r="263" ht="16" customHeight="1">
       <c r="A263" s="3" t="n">
         <v>39</v>
       </c>
@@ -16135,7 +16155,7 @@
         </is>
       </c>
     </row>
-    <row r="264">
+    <row r="264" ht="16" customHeight="1">
       <c r="A264" s="3" t="n">
         <v>1</v>
       </c>
@@ -16195,7 +16215,7 @@
         </is>
       </c>
     </row>
-    <row r="265">
+    <row r="265" ht="16" customHeight="1">
       <c r="A265" s="3" t="n">
         <v>2</v>
       </c>
@@ -16255,7 +16275,7 @@
         </is>
       </c>
     </row>
-    <row r="266">
+    <row r="266" ht="16" customHeight="1">
       <c r="A266" s="3" t="n">
         <v>3</v>
       </c>
@@ -16315,7 +16335,7 @@
         </is>
       </c>
     </row>
-    <row r="267">
+    <row r="267" ht="16" customHeight="1">
       <c r="A267" s="3" t="n">
         <v>4</v>
       </c>
@@ -16375,7 +16395,7 @@
         </is>
       </c>
     </row>
-    <row r="268">
+    <row r="268" ht="16" customHeight="1">
       <c r="A268" s="3" t="n">
         <v>5</v>
       </c>
@@ -16435,7 +16455,7 @@
         </is>
       </c>
     </row>
-    <row r="269">
+    <row r="269" ht="16" customHeight="1">
       <c r="A269" s="3" t="n">
         <v>6</v>
       </c>
@@ -16495,7 +16515,7 @@
         </is>
       </c>
     </row>
-    <row r="270">
+    <row r="270" ht="16" customHeight="1">
       <c r="A270" s="3" t="n">
         <v>7</v>
       </c>
@@ -16555,7 +16575,7 @@
         </is>
       </c>
     </row>
-    <row r="271">
+    <row r="271" ht="16" customHeight="1">
       <c r="A271" s="3" t="n">
         <v>8</v>
       </c>
@@ -16615,7 +16635,7 @@
         </is>
       </c>
     </row>
-    <row r="272">
+    <row r="272" ht="16" customHeight="1">
       <c r="A272" s="3" t="n">
         <v>9</v>
       </c>
@@ -16675,7 +16695,7 @@
         </is>
       </c>
     </row>
-    <row r="273">
+    <row r="273" ht="16" customHeight="1">
       <c r="A273" s="3" t="n">
         <v>10</v>
       </c>
@@ -16735,7 +16755,7 @@
         </is>
       </c>
     </row>
-    <row r="274">
+    <row r="274" ht="16" customHeight="1">
       <c r="A274" s="3" t="n">
         <v>11</v>
       </c>
@@ -16795,7 +16815,7 @@
         </is>
       </c>
     </row>
-    <row r="275">
+    <row r="275" ht="16" customHeight="1">
       <c r="A275" s="3" t="n">
         <v>12</v>
       </c>
@@ -16855,7 +16875,7 @@
         </is>
       </c>
     </row>
-    <row r="276">
+    <row r="276" ht="16" customHeight="1">
       <c r="A276" s="3" t="n">
         <v>13</v>
       </c>
@@ -16915,7 +16935,7 @@
         </is>
       </c>
     </row>
-    <row r="277">
+    <row r="277" ht="16" customHeight="1">
       <c r="A277" s="3" t="n">
         <v>14</v>
       </c>
@@ -16975,7 +16995,7 @@
         </is>
       </c>
     </row>
-    <row r="278">
+    <row r="278" ht="16" customHeight="1">
       <c r="A278" s="3" t="n">
         <v>1</v>
       </c>
@@ -17035,7 +17055,7 @@
         </is>
       </c>
     </row>
-    <row r="279">
+    <row r="279" ht="16" customHeight="1">
       <c r="A279" s="3" t="n">
         <v>1</v>
       </c>
@@ -17095,7 +17115,7 @@
         </is>
       </c>
     </row>
-    <row r="280">
+    <row r="280" ht="16" customHeight="1">
       <c r="A280" s="3" t="n">
         <v>2</v>
       </c>
@@ -17155,7 +17175,7 @@
         </is>
       </c>
     </row>
-    <row r="281">
+    <row r="281" ht="16" customHeight="1">
       <c r="A281" s="3" t="n">
         <v>3</v>
       </c>
@@ -17215,7 +17235,7 @@
         </is>
       </c>
     </row>
-    <row r="282">
+    <row r="282" ht="16" customHeight="1">
       <c r="A282" s="3" t="n">
         <v>4</v>
       </c>
@@ -17275,7 +17295,7 @@
         </is>
       </c>
     </row>
-    <row r="283">
+    <row r="283" ht="16" customHeight="1">
       <c r="A283" s="3" t="n">
         <v>5</v>
       </c>
@@ -17335,7 +17355,7 @@
         </is>
       </c>
     </row>
-    <row r="284">
+    <row r="284" ht="16" customHeight="1">
       <c r="A284" s="3" t="n">
         <v>6</v>
       </c>
@@ -17395,7 +17415,7 @@
         </is>
       </c>
     </row>
-    <row r="285">
+    <row r="285" ht="16" customHeight="1">
       <c r="A285" s="3" t="n">
         <v>7</v>
       </c>
@@ -17455,7 +17475,7 @@
         </is>
       </c>
     </row>
-    <row r="286">
+    <row r="286" ht="16" customHeight="1">
       <c r="A286" s="3" t="n">
         <v>8</v>
       </c>
@@ -17515,7 +17535,7 @@
         </is>
       </c>
     </row>
-    <row r="287">
+    <row r="287" ht="16" customHeight="1">
       <c r="A287" s="3" t="n">
         <v>1</v>
       </c>
@@ -17575,7 +17595,7 @@
         </is>
       </c>
     </row>
-    <row r="288">
+    <row r="288" ht="16" customHeight="1">
       <c r="A288" s="3" t="n">
         <v>2</v>
       </c>
@@ -17635,7 +17655,7 @@
         </is>
       </c>
     </row>
-    <row r="289">
+    <row r="289" ht="16" customHeight="1">
       <c r="A289" s="3" t="n">
         <v>3</v>
       </c>
@@ -17695,7 +17715,7 @@
         </is>
       </c>
     </row>
-    <row r="290">
+    <row r="290" ht="16" customHeight="1">
       <c r="A290" s="3" t="n">
         <v>4</v>
       </c>
@@ -17755,7 +17775,7 @@
         </is>
       </c>
     </row>
-    <row r="291">
+    <row r="291" ht="16" customHeight="1">
       <c r="A291" s="3" t="n">
         <v>5</v>
       </c>
@@ -17815,7 +17835,7 @@
         </is>
       </c>
     </row>
-    <row r="292">
+    <row r="292" ht="16" customHeight="1">
       <c r="A292" s="3" t="n">
         <v>6</v>
       </c>
@@ -17875,7 +17895,7 @@
         </is>
       </c>
     </row>
-    <row r="293">
+    <row r="293" ht="16" customHeight="1">
       <c r="A293" s="3" t="n">
         <v>7</v>
       </c>
@@ -17935,7 +17955,7 @@
         </is>
       </c>
     </row>
-    <row r="294">
+    <row r="294" ht="16" customHeight="1">
       <c r="A294" s="3" t="n">
         <v>8</v>
       </c>
@@ -17995,7 +18015,7 @@
         </is>
       </c>
     </row>
-    <row r="295">
+    <row r="295" ht="16" customHeight="1">
       <c r="A295" s="3" t="n">
         <v>1</v>
       </c>
@@ -18055,7 +18075,7 @@
         </is>
       </c>
     </row>
-    <row r="296">
+    <row r="296" ht="16" customHeight="1">
       <c r="A296" s="3" t="n">
         <v>2</v>
       </c>
@@ -18115,7 +18135,7 @@
         </is>
       </c>
     </row>
-    <row r="297">
+    <row r="297" ht="16" customHeight="1">
       <c r="A297" s="3" t="n">
         <v>3</v>
       </c>
@@ -18175,7 +18195,7 @@
         </is>
       </c>
     </row>
-    <row r="298">
+    <row r="298" ht="16" customHeight="1">
       <c r="A298" s="3" t="n">
         <v>4</v>
       </c>
@@ -18235,7 +18255,7 @@
         </is>
       </c>
     </row>
-    <row r="299">
+    <row r="299" ht="16" customHeight="1">
       <c r="A299" s="3" t="n">
         <v>5</v>
       </c>
@@ -18295,7 +18315,7 @@
         </is>
       </c>
     </row>
-    <row r="300">
+    <row r="300" ht="16" customHeight="1">
       <c r="A300" s="3" t="n">
         <v>6</v>
       </c>
@@ -18355,7 +18375,7 @@
         </is>
       </c>
     </row>
-    <row r="301">
+    <row r="301" ht="16" customHeight="1">
       <c r="A301" s="3" t="n">
         <v>7</v>
       </c>
@@ -18415,7 +18435,7 @@
         </is>
       </c>
     </row>
-    <row r="302">
+    <row r="302" ht="16" customHeight="1">
       <c r="A302" s="3" t="n">
         <v>8</v>
       </c>
@@ -18475,7 +18495,7 @@
         </is>
       </c>
     </row>
-    <row r="303">
+    <row r="303" ht="16" customHeight="1">
       <c r="A303" s="3" t="n">
         <v>9</v>
       </c>
@@ -18535,7 +18555,7 @@
         </is>
       </c>
     </row>
-    <row r="304">
+    <row r="304" ht="16" customHeight="1">
       <c r="A304" s="3" t="n">
         <v>10</v>
       </c>
@@ -18595,7 +18615,7 @@
         </is>
       </c>
     </row>
-    <row r="305">
+    <row r="305" ht="16" customHeight="1">
       <c r="A305" s="3" t="n">
         <v>11</v>
       </c>
@@ -18655,7 +18675,7 @@
         </is>
       </c>
     </row>
-    <row r="306">
+    <row r="306" ht="16" customHeight="1">
       <c r="A306" s="3" t="n">
         <v>12</v>
       </c>
@@ -18715,7 +18735,7 @@
         </is>
       </c>
     </row>
-    <row r="307">
+    <row r="307" ht="16" customHeight="1">
       <c r="A307" s="3" t="n">
         <v>13</v>
       </c>
@@ -18775,7 +18795,7 @@
         </is>
       </c>
     </row>
-    <row r="308">
+    <row r="308" ht="16" customHeight="1">
       <c r="A308" s="3" t="n">
         <v>14</v>
       </c>
@@ -18835,7 +18855,7 @@
         </is>
       </c>
     </row>
-    <row r="309">
+    <row r="309" ht="16" customHeight="1">
       <c r="A309" s="3" t="n">
         <v>15</v>
       </c>
@@ -18895,7 +18915,7 @@
         </is>
       </c>
     </row>
-    <row r="310">
+    <row r="310" ht="16" customHeight="1">
       <c r="A310" s="3" t="n">
         <v>16</v>
       </c>
@@ -18955,7 +18975,7 @@
         </is>
       </c>
     </row>
-    <row r="311">
+    <row r="311" ht="16" customHeight="1">
       <c r="A311" s="3" t="n">
         <v>17</v>
       </c>
@@ -19015,7 +19035,7 @@
         </is>
       </c>
     </row>
-    <row r="312">
+    <row r="312" ht="16" customHeight="1">
       <c r="A312" s="3" t="n">
         <v>18</v>
       </c>
@@ -19075,7 +19095,7 @@
         </is>
       </c>
     </row>
-    <row r="313">
+    <row r="313" ht="16" customHeight="1">
       <c r="A313" s="3" t="n">
         <v>19</v>
       </c>
@@ -19135,7 +19155,7 @@
         </is>
       </c>
     </row>
-    <row r="314">
+    <row r="314" ht="16" customHeight="1">
       <c r="A314" s="3" t="n">
         <v>20</v>
       </c>
@@ -19195,7 +19215,7 @@
         </is>
       </c>
     </row>
-    <row r="315">
+    <row r="315" ht="16" customHeight="1">
       <c r="A315" s="3" t="n">
         <v>21</v>
       </c>
@@ -19255,7 +19275,7 @@
         </is>
       </c>
     </row>
-    <row r="316">
+    <row r="316" ht="16" customHeight="1">
       <c r="A316" s="3" t="n">
         <v>22</v>
       </c>
@@ -19315,7 +19335,7 @@
         </is>
       </c>
     </row>
-    <row r="317">
+    <row r="317" ht="16" customHeight="1">
       <c r="A317" s="3" t="n">
         <v>23</v>
       </c>
@@ -19375,7 +19395,7 @@
         </is>
       </c>
     </row>
-    <row r="318">
+    <row r="318" ht="16" customHeight="1">
       <c r="A318" s="3" t="n">
         <v>24</v>
       </c>
@@ -19435,7 +19455,7 @@
         </is>
       </c>
     </row>
-    <row r="319">
+    <row r="319" ht="16" customHeight="1">
       <c r="A319" s="3" t="n">
         <v>25</v>
       </c>
@@ -19495,7 +19515,7 @@
         </is>
       </c>
     </row>
-    <row r="320">
+    <row r="320" ht="16" customHeight="1">
       <c r="A320" s="3" t="n">
         <v>26</v>
       </c>
@@ -19555,7 +19575,7 @@
         </is>
       </c>
     </row>
-    <row r="321">
+    <row r="321" ht="16" customHeight="1">
       <c r="A321" s="3" t="n">
         <v>27</v>
       </c>
@@ -19615,7 +19635,7 @@
         </is>
       </c>
     </row>
-    <row r="322">
+    <row r="322" ht="16" customHeight="1">
       <c r="A322" s="3" t="n">
         <v>28</v>
       </c>
@@ -19675,7 +19695,7 @@
         </is>
       </c>
     </row>
-    <row r="323">
+    <row r="323" ht="16" customHeight="1">
       <c r="A323" s="3" t="n">
         <v>29</v>
       </c>
@@ -19735,7 +19755,7 @@
         </is>
       </c>
     </row>
-    <row r="324">
+    <row r="324" ht="16" customHeight="1">
       <c r="A324" s="3" t="n">
         <v>30</v>
       </c>
@@ -19795,7 +19815,7 @@
         </is>
       </c>
     </row>
-    <row r="325">
+    <row r="325" ht="16" customHeight="1">
       <c r="A325" s="3" t="n">
         <v>31</v>
       </c>
@@ -19855,7 +19875,7 @@
         </is>
       </c>
     </row>
-    <row r="326">
+    <row r="326" ht="16" customHeight="1">
       <c r="A326" s="3" t="n">
         <v>32</v>
       </c>
@@ -19915,7 +19935,7 @@
         </is>
       </c>
     </row>
-    <row r="327">
+    <row r="327" ht="16" customHeight="1">
       <c r="A327" s="3" t="n">
         <v>33</v>
       </c>
@@ -19975,7 +19995,7 @@
         </is>
       </c>
     </row>
-    <row r="328">
+    <row r="328" ht="16" customHeight="1">
       <c r="A328" s="3" t="n">
         <v>34</v>
       </c>
@@ -20035,7 +20055,7 @@
         </is>
       </c>
     </row>
-    <row r="329">
+    <row r="329" ht="16" customHeight="1">
       <c r="A329" s="3" t="n">
         <v>35</v>
       </c>
@@ -20095,7 +20115,7 @@
         </is>
       </c>
     </row>
-    <row r="330">
+    <row r="330" ht="16" customHeight="1">
       <c r="A330" s="3" t="n">
         <v>36</v>
       </c>
@@ -20155,7 +20175,7 @@
         </is>
       </c>
     </row>
-    <row r="331">
+    <row r="331" ht="16" customHeight="1">
       <c r="A331" s="3" t="n">
         <v>37</v>
       </c>
@@ -20215,7 +20235,7 @@
         </is>
       </c>
     </row>
-    <row r="332">
+    <row r="332" ht="16" customHeight="1">
       <c r="A332" s="3" t="n">
         <v>38</v>
       </c>
@@ -20275,7 +20295,7 @@
         </is>
       </c>
     </row>
-    <row r="333">
+    <row r="333" ht="16" customHeight="1">
       <c r="A333" s="3" t="n">
         <v>39</v>
       </c>
@@ -20335,7 +20355,7 @@
         </is>
       </c>
     </row>
-    <row r="334">
+    <row r="334" ht="16" customHeight="1">
       <c r="A334" s="3" t="n">
         <v>40</v>
       </c>
@@ -20395,7 +20415,7 @@
         </is>
       </c>
     </row>
-    <row r="335">
+    <row r="335" ht="16" customHeight="1">
       <c r="A335" s="3" t="n">
         <v>41</v>
       </c>
@@ -20455,7 +20475,7 @@
         </is>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="16" customHeight="1">
       <c r="A336" s="3" t="n">
         <v>42</v>
       </c>
@@ -20515,7 +20535,7 @@
         </is>
       </c>
     </row>
-    <row r="337">
+    <row r="337" ht="16" customHeight="1">
       <c r="A337" s="3" t="n">
         <v>43</v>
       </c>
@@ -20559,7 +20579,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J337" s="4" t="inlineStr"/>
+      <c r="J337" s="4" t="n"/>
       <c r="K337" s="3" t="inlineStr">
         <is>
           <t>2026-06-29 14:11:32</t>
@@ -20571,7 +20591,7 @@
         </is>
       </c>
     </row>
-    <row r="338">
+    <row r="338" ht="16" customHeight="1">
       <c r="A338" s="3" t="n">
         <v>44</v>
       </c>
@@ -20615,7 +20635,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J338" s="4" t="inlineStr"/>
+      <c r="J338" s="4" t="n"/>
       <c r="K338" s="3" t="inlineStr">
         <is>
           <t>2026-06-29 14:12:53</t>
@@ -20627,7 +20647,7 @@
         </is>
       </c>
     </row>
-    <row r="339">
+    <row r="339" ht="16" customHeight="1">
       <c r="A339" s="3" t="n">
         <v>45</v>
       </c>
@@ -20687,7 +20707,7 @@
         </is>
       </c>
     </row>
-    <row r="340">
+    <row r="340" ht="16" customHeight="1">
       <c r="A340" s="3" t="n">
         <v>46</v>
       </c>
@@ -20731,7 +20751,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J340" s="4" t="inlineStr"/>
+      <c r="J340" s="4" t="n"/>
       <c r="K340" s="3" t="inlineStr">
         <is>
           <t>2026-06-29 14:14:19</t>
@@ -20743,7 +20763,7 @@
         </is>
       </c>
     </row>
-    <row r="341">
+    <row r="341" ht="16" customHeight="1">
       <c r="A341" s="3" t="n">
         <v>47</v>
       </c>
@@ -20803,7 +20823,7 @@
         </is>
       </c>
     </row>
-    <row r="342">
+    <row r="342" ht="16" customHeight="1">
       <c r="A342" s="3" t="n">
         <v>48</v>
       </c>
@@ -20863,7 +20883,7 @@
         </is>
       </c>
     </row>
-    <row r="343">
+    <row r="343" ht="16" customHeight="1">
       <c r="A343" s="3" t="n">
         <v>49</v>
       </c>
@@ -20923,7 +20943,7 @@
         </is>
       </c>
     </row>
-    <row r="344">
+    <row r="344" ht="16" customHeight="1">
       <c r="A344" s="3" t="n">
         <v>50</v>
       </c>
@@ -20967,7 +20987,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J344" s="4" t="inlineStr"/>
+      <c r="J344" s="4" t="n"/>
       <c r="K344" s="3" t="inlineStr">
         <is>
           <t>2026-06-29 14:15:58</t>
@@ -20979,7 +20999,7 @@
         </is>
       </c>
     </row>
-    <row r="345">
+    <row r="345" ht="16" customHeight="1">
       <c r="A345" s="3" t="n">
         <v>51</v>
       </c>
@@ -21039,7 +21059,7 @@
         </is>
       </c>
     </row>
-    <row r="346">
+    <row r="346" ht="16" customHeight="1">
       <c r="A346" s="3" t="n">
         <v>52</v>
       </c>
@@ -21083,7 +21103,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J346" s="4" t="inlineStr"/>
+      <c r="J346" s="4" t="n"/>
       <c r="K346" s="3" t="inlineStr">
         <is>
           <t>2026-06-29 14:17:25</t>
@@ -21095,7 +21115,7 @@
         </is>
       </c>
     </row>
-    <row r="347">
+    <row r="347" ht="16" customHeight="1">
       <c r="A347" s="3" t="n">
         <v>53</v>
       </c>
@@ -21139,7 +21159,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J347" s="4" t="inlineStr"/>
+      <c r="J347" s="4" t="n"/>
       <c r="K347" s="3" t="inlineStr">
         <is>
           <t>2026-06-29 14:18:45</t>
@@ -21151,7 +21171,7 @@
         </is>
       </c>
     </row>
-    <row r="348">
+    <row r="348" ht="16" customHeight="1">
       <c r="A348" s="3" t="n">
         <v>54</v>
       </c>
@@ -21211,7 +21231,7 @@
         </is>
       </c>
     </row>
-    <row r="349">
+    <row r="349" ht="16" customHeight="1">
       <c r="A349" s="3" t="n">
         <v>55</v>
       </c>
@@ -21271,7 +21291,7 @@
         </is>
       </c>
     </row>
-    <row r="350">
+    <row r="350" ht="16" customHeight="1">
       <c r="A350" s="3" t="n">
         <v>56</v>
       </c>
@@ -21331,7 +21351,7 @@
         </is>
       </c>
     </row>
-    <row r="351">
+    <row r="351" ht="16" customHeight="1">
       <c r="A351" s="3" t="n">
         <v>57</v>
       </c>
@@ -21391,7 +21411,7 @@
         </is>
       </c>
     </row>
-    <row r="352">
+    <row r="352" ht="16" customHeight="1">
       <c r="A352" s="3" t="n">
         <v>58</v>
       </c>
@@ -21451,7 +21471,7 @@
         </is>
       </c>
     </row>
-    <row r="353">
+    <row r="353" ht="16" customHeight="1">
       <c r="A353" s="3" t="n">
         <v>59</v>
       </c>
@@ -21511,7 +21531,7 @@
         </is>
       </c>
     </row>
-    <row r="354">
+    <row r="354" ht="16" customHeight="1">
       <c r="A354" s="3" t="n">
         <v>60</v>
       </c>
@@ -21571,7 +21591,7 @@
         </is>
       </c>
     </row>
-    <row r="355">
+    <row r="355" ht="16" customHeight="1">
       <c r="A355" s="3" t="n">
         <v>61</v>
       </c>
@@ -21631,7 +21651,7 @@
         </is>
       </c>
     </row>
-    <row r="356">
+    <row r="356" ht="16" customHeight="1">
       <c r="A356" s="3" t="n">
         <v>62</v>
       </c>
@@ -21691,7 +21711,7 @@
         </is>
       </c>
     </row>
-    <row r="357">
+    <row r="357" ht="16" customHeight="1">
       <c r="A357" s="3" t="n">
         <v>1</v>
       </c>
@@ -21751,7 +21771,7 @@
         </is>
       </c>
     </row>
-    <row r="358">
+    <row r="358" ht="16" customHeight="1">
       <c r="A358" s="3" t="n">
         <v>2</v>
       </c>
@@ -21811,7 +21831,7 @@
         </is>
       </c>
     </row>
-    <row r="359">
+    <row r="359" ht="16" customHeight="1">
       <c r="A359" s="3" t="n">
         <v>3</v>
       </c>
@@ -21871,7 +21891,7 @@
         </is>
       </c>
     </row>
-    <row r="360">
+    <row r="360" ht="16" customHeight="1">
       <c r="A360" s="3" t="n">
         <v>4</v>
       </c>
@@ -21931,7 +21951,7 @@
         </is>
       </c>
     </row>
-    <row r="361">
+    <row r="361" ht="16" customHeight="1">
       <c r="A361" s="3" t="n">
         <v>5</v>
       </c>
@@ -21991,7 +22011,7 @@
         </is>
       </c>
     </row>
-    <row r="362">
+    <row r="362" ht="16" customHeight="1">
       <c r="A362" s="3" t="n">
         <v>6</v>
       </c>
@@ -22051,7 +22071,7 @@
         </is>
       </c>
     </row>
-    <row r="363">
+    <row r="363" ht="16" customHeight="1">
       <c r="A363" s="3" t="n">
         <v>7</v>
       </c>
@@ -22111,7 +22131,7 @@
         </is>
       </c>
     </row>
-    <row r="364">
+    <row r="364" ht="16" customHeight="1">
       <c r="A364" s="3" t="n">
         <v>8</v>
       </c>
@@ -22171,7 +22191,7 @@
         </is>
       </c>
     </row>
-    <row r="365">
+    <row r="365" ht="16" customHeight="1">
       <c r="A365" s="3" t="n">
         <v>1</v>
       </c>
@@ -22231,7 +22251,7 @@
         </is>
       </c>
     </row>
-    <row r="366">
+    <row r="366" ht="16" customHeight="1">
       <c r="A366" s="3" t="n">
         <v>2</v>
       </c>
@@ -22291,7 +22311,7 @@
         </is>
       </c>
     </row>
-    <row r="367">
+    <row r="367" ht="16" customHeight="1">
       <c r="A367" s="3" t="n">
         <v>3</v>
       </c>
@@ -22351,7 +22371,7 @@
         </is>
       </c>
     </row>
-    <row r="368">
+    <row r="368" ht="16" customHeight="1">
       <c r="A368" s="3" t="n">
         <v>4</v>
       </c>
@@ -22411,7 +22431,7 @@
         </is>
       </c>
     </row>
-    <row r="369">
+    <row r="369" ht="16" customHeight="1">
       <c r="A369" s="3" t="n">
         <v>5</v>
       </c>
@@ -22471,7 +22491,7 @@
         </is>
       </c>
     </row>
-    <row r="370">
+    <row r="370" ht="16" customHeight="1">
       <c r="A370" s="3" t="n">
         <v>6</v>
       </c>
@@ -22531,7 +22551,7 @@
         </is>
       </c>
     </row>
-    <row r="371">
+    <row r="371" ht="16" customHeight="1">
       <c r="A371" s="3" t="n">
         <v>7</v>
       </c>
@@ -22591,7 +22611,7 @@
         </is>
       </c>
     </row>
-    <row r="372">
+    <row r="372" ht="16" customHeight="1">
       <c r="A372" s="3" t="n">
         <v>8</v>
       </c>
@@ -22651,7 +22671,7 @@
         </is>
       </c>
     </row>
-    <row r="373">
+    <row r="373" ht="16" customHeight="1">
       <c r="A373" s="3" t="n">
         <v>9</v>
       </c>
@@ -22711,7 +22731,7 @@
         </is>
       </c>
     </row>
-    <row r="374">
+    <row r="374" ht="16" customHeight="1">
       <c r="A374" s="3" t="n">
         <v>10</v>
       </c>
@@ -22771,7 +22791,7 @@
         </is>
       </c>
     </row>
-    <row r="375">
+    <row r="375" ht="16" customHeight="1">
       <c r="A375" s="3" t="n">
         <v>11</v>
       </c>
@@ -22831,7 +22851,7 @@
         </is>
       </c>
     </row>
-    <row r="376">
+    <row r="376" ht="16" customHeight="1">
       <c r="A376" s="3" t="n">
         <v>12</v>
       </c>
@@ -22891,7 +22911,7 @@
         </is>
       </c>
     </row>
-    <row r="377">
+    <row r="377" ht="16" customHeight="1">
       <c r="A377" s="3" t="n">
         <v>8</v>
       </c>
@@ -22951,7 +22971,7 @@
         </is>
       </c>
     </row>
-    <row r="378">
+    <row r="378" ht="16" customHeight="1">
       <c r="A378" s="3" t="n">
         <v>8</v>
       </c>
@@ -23011,7 +23031,7 @@
         </is>
       </c>
     </row>
-    <row r="379">
+    <row r="379" ht="16" customHeight="1">
       <c r="A379" s="3" t="n">
         <v>1</v>
       </c>
@@ -23071,7 +23091,7 @@
         </is>
       </c>
     </row>
-    <row r="380">
+    <row r="380" ht="16" customHeight="1">
       <c r="A380" s="3" t="n">
         <v>2</v>
       </c>
@@ -23131,7 +23151,7 @@
         </is>
       </c>
     </row>
-    <row r="381">
+    <row r="381" ht="16" customHeight="1">
       <c r="A381" s="3" t="n">
         <v>3</v>
       </c>
@@ -23191,7 +23211,7 @@
         </is>
       </c>
     </row>
-    <row r="382">
+    <row r="382" ht="16" customHeight="1">
       <c r="A382" s="3" t="n">
         <v>4</v>
       </c>
@@ -23251,7 +23271,7 @@
         </is>
       </c>
     </row>
-    <row r="383">
+    <row r="383" ht="16" customHeight="1">
       <c r="A383" s="3" t="n">
         <v>5</v>
       </c>
@@ -23311,7 +23331,7 @@
         </is>
       </c>
     </row>
-    <row r="384">
+    <row r="384" ht="16" customHeight="1">
       <c r="A384" s="3" t="n">
         <v>6</v>
       </c>
@@ -23371,7 +23391,7 @@
         </is>
       </c>
     </row>
-    <row r="385">
+    <row r="385" ht="16" customHeight="1">
       <c r="A385" s="3" t="n">
         <v>7</v>
       </c>
@@ -23431,7 +23451,7 @@
         </is>
       </c>
     </row>
-    <row r="386">
+    <row r="386" ht="16" customHeight="1">
       <c r="A386" s="3" t="n">
         <v>8</v>
       </c>
@@ -23491,7 +23511,7 @@
         </is>
       </c>
     </row>
-    <row r="387">
+    <row r="387" ht="16" customHeight="1">
       <c r="A387" s="3" t="n">
         <v>9</v>
       </c>
@@ -23551,7 +23571,7 @@
         </is>
       </c>
     </row>
-    <row r="388">
+    <row r="388" ht="16" customHeight="1">
       <c r="A388" s="3" t="n">
         <v>10</v>
       </c>
@@ -23611,7 +23631,7 @@
         </is>
       </c>
     </row>
-    <row r="389">
+    <row r="389" ht="16" customHeight="1">
       <c r="A389" s="3" t="n">
         <v>11</v>
       </c>
@@ -23671,7 +23691,7 @@
         </is>
       </c>
     </row>
-    <row r="390">
+    <row r="390" ht="16" customHeight="1">
       <c r="A390" s="3" t="n">
         <v>12</v>
       </c>
@@ -23731,7 +23751,7 @@
         </is>
       </c>
     </row>
-    <row r="391">
+    <row r="391" ht="16" customHeight="1">
       <c r="A391" s="3" t="n">
         <v>13</v>
       </c>
@@ -23791,7 +23811,7 @@
         </is>
       </c>
     </row>
-    <row r="392">
+    <row r="392" ht="16" customHeight="1">
       <c r="A392" s="3" t="n">
         <v>14</v>
       </c>
@@ -23851,7 +23871,7 @@
         </is>
       </c>
     </row>
-    <row r="393">
+    <row r="393" ht="16" customHeight="1">
       <c r="A393" s="3" t="n">
         <v>2</v>
       </c>
@@ -23911,7 +23931,7 @@
         </is>
       </c>
     </row>
-    <row r="394">
+    <row r="394" ht="16" customHeight="1">
       <c r="A394" s="3" t="n">
         <v>3</v>
       </c>
@@ -23971,7 +23991,7 @@
         </is>
       </c>
     </row>
-    <row r="395">
+    <row r="395" ht="16" customHeight="1">
       <c r="A395" s="3" t="n">
         <v>4</v>
       </c>
@@ -24031,7 +24051,7 @@
         </is>
       </c>
     </row>
-    <row r="396">
+    <row r="396" ht="16" customHeight="1">
       <c r="A396" s="3" t="n">
         <v>5</v>
       </c>
@@ -24091,7 +24111,7 @@
         </is>
       </c>
     </row>
-    <row r="397">
+    <row r="397" ht="16" customHeight="1">
       <c r="A397" s="3" t="n">
         <v>6</v>
       </c>
@@ -24151,7 +24171,7 @@
         </is>
       </c>
     </row>
-    <row r="398">
+    <row r="398" ht="16" customHeight="1">
       <c r="A398" s="3" t="n">
         <v>1</v>
       </c>
@@ -24211,7 +24231,7 @@
         </is>
       </c>
     </row>
-    <row r="399">
+    <row r="399" ht="16" customHeight="1">
       <c r="A399" s="3" t="n">
         <v>2</v>
       </c>
@@ -24271,7 +24291,7 @@
         </is>
       </c>
     </row>
-    <row r="400">
+    <row r="400" ht="16" customHeight="1">
       <c r="A400" s="3" t="n">
         <v>3</v>
       </c>
@@ -24331,7 +24351,7 @@
         </is>
       </c>
     </row>
-    <row r="401">
+    <row r="401" ht="16" customHeight="1">
       <c r="A401" s="3" t="n">
         <v>4</v>
       </c>
@@ -24391,7 +24411,7 @@
         </is>
       </c>
     </row>
-    <row r="402">
+    <row r="402" ht="16" customHeight="1">
       <c r="A402" s="3" t="n">
         <v>5</v>
       </c>
@@ -24451,7 +24471,7 @@
         </is>
       </c>
     </row>
-    <row r="403">
+    <row r="403" ht="16" customHeight="1">
       <c r="A403" s="3" t="n">
         <v>6</v>
       </c>
@@ -24511,7 +24531,7 @@
         </is>
       </c>
     </row>
-    <row r="404">
+    <row r="404" ht="16" customHeight="1">
       <c r="A404" s="3" t="n">
         <v>7</v>
       </c>
@@ -24571,7 +24591,7 @@
         </is>
       </c>
     </row>
-    <row r="405">
+    <row r="405" ht="16" customHeight="1">
       <c r="A405" s="3" t="n">
         <v>8</v>
       </c>
@@ -24631,7 +24651,7 @@
         </is>
       </c>
     </row>
-    <row r="406">
+    <row r="406" ht="16" customHeight="1">
       <c r="A406" s="3" t="n">
         <v>9</v>
       </c>
@@ -24691,7 +24711,7 @@
         </is>
       </c>
     </row>
-    <row r="407">
+    <row r="407" ht="16" customHeight="1">
       <c r="A407" s="3" t="n">
         <v>10</v>
       </c>
@@ -24751,7 +24771,7 @@
         </is>
       </c>
     </row>
-    <row r="408">
+    <row r="408" ht="16" customHeight="1">
       <c r="A408" s="3" t="n">
         <v>11</v>
       </c>
@@ -24811,7 +24831,7 @@
         </is>
       </c>
     </row>
-    <row r="409">
+    <row r="409" ht="16" customHeight="1">
       <c r="A409" s="3" t="n">
         <v>12</v>
       </c>
@@ -24871,7 +24891,7 @@
         </is>
       </c>
     </row>
-    <row r="410">
+    <row r="410" ht="16" customHeight="1">
       <c r="A410" s="3" t="n">
         <v>13</v>
       </c>
@@ -24931,7 +24951,7 @@
         </is>
       </c>
     </row>
-    <row r="411">
+    <row r="411" ht="16" customHeight="1">
       <c r="A411" s="3" t="n">
         <v>14</v>
       </c>
@@ -24991,7 +25011,7 @@
         </is>
       </c>
     </row>
-    <row r="412">
+    <row r="412" ht="16" customHeight="1">
       <c r="A412" s="3" t="n">
         <v>1</v>
       </c>
@@ -25051,7 +25071,7 @@
         </is>
       </c>
     </row>
-    <row r="413">
+    <row r="413" ht="16" customHeight="1">
       <c r="A413" s="3" t="n">
         <v>2</v>
       </c>
@@ -25111,7 +25131,7 @@
         </is>
       </c>
     </row>
-    <row r="414">
+    <row r="414" ht="16" customHeight="1">
       <c r="A414" s="3" t="n">
         <v>3</v>
       </c>
@@ -25171,7 +25191,7 @@
         </is>
       </c>
     </row>
-    <row r="415">
+    <row r="415" ht="16" customHeight="1">
       <c r="A415" s="3" t="n">
         <v>4</v>
       </c>
@@ -25231,7 +25251,7 @@
         </is>
       </c>
     </row>
-    <row r="416">
+    <row r="416" ht="16" customHeight="1">
       <c r="A416" s="3" t="n">
         <v>5</v>
       </c>
@@ -25291,7 +25311,7 @@
         </is>
       </c>
     </row>
-    <row r="417">
+    <row r="417" ht="16" customHeight="1">
       <c r="A417" s="3" t="n">
         <v>6</v>
       </c>
@@ -25351,7 +25371,7 @@
         </is>
       </c>
     </row>
-    <row r="418">
+    <row r="418" ht="16" customHeight="1">
       <c r="A418" s="3" t="n">
         <v>7</v>
       </c>
@@ -25411,7 +25431,7 @@
         </is>
       </c>
     </row>
-    <row r="419">
+    <row r="419" ht="16" customHeight="1">
       <c r="A419" s="3" t="n">
         <v>1</v>
       </c>
@@ -25471,7 +25491,7 @@
         </is>
       </c>
     </row>
-    <row r="420">
+    <row r="420" ht="16" customHeight="1">
       <c r="A420" s="3" t="n">
         <v>2</v>
       </c>
@@ -25531,7 +25551,7 @@
         </is>
       </c>
     </row>
-    <row r="421">
+    <row r="421" ht="16" customHeight="1">
       <c r="A421" s="3" t="n">
         <v>3</v>
       </c>
@@ -25591,7 +25611,7 @@
         </is>
       </c>
     </row>
-    <row r="422">
+    <row r="422" ht="16" customHeight="1">
       <c r="A422" s="3" t="n">
         <v>4</v>
       </c>
@@ -25651,7 +25671,7 @@
         </is>
       </c>
     </row>
-    <row r="423">
+    <row r="423" ht="16" customHeight="1">
       <c r="A423" s="3" t="n">
         <v>5</v>
       </c>
@@ -25711,7 +25731,7 @@
         </is>
       </c>
     </row>
-    <row r="424">
+    <row r="424" ht="16" customHeight="1">
       <c r="A424" s="3" t="n">
         <v>6</v>
       </c>
@@ -25771,7 +25791,7 @@
         </is>
       </c>
     </row>
-    <row r="425">
+    <row r="425" ht="16" customHeight="1">
       <c r="A425" s="3" t="n">
         <v>7</v>
       </c>
@@ -25831,7 +25851,7 @@
         </is>
       </c>
     </row>
-    <row r="426">
+    <row r="426" ht="16" customHeight="1">
       <c r="A426" s="3" t="n">
         <v>8</v>
       </c>
@@ -25891,7 +25911,7 @@
         </is>
       </c>
     </row>
-    <row r="427">
+    <row r="427" ht="16" customHeight="1">
       <c r="A427" s="3" t="n">
         <v>9</v>
       </c>
@@ -25951,7 +25971,7 @@
         </is>
       </c>
     </row>
-    <row r="428">
+    <row r="428" ht="16" customHeight="1">
       <c r="A428" s="3" t="n">
         <v>10</v>
       </c>
@@ -26011,7 +26031,7 @@
         </is>
       </c>
     </row>
-    <row r="429">
+    <row r="429" ht="16" customHeight="1">
       <c r="A429" s="3" t="n">
         <v>11</v>
       </c>
@@ -26071,7 +26091,7 @@
         </is>
       </c>
     </row>
-    <row r="430">
+    <row r="430" ht="16" customHeight="1">
       <c r="A430" s="3" t="n">
         <v>12</v>
       </c>
@@ -26131,7 +26151,7 @@
         </is>
       </c>
     </row>
-    <row r="431">
+    <row r="431" ht="16" customHeight="1">
       <c r="A431" s="3" t="n">
         <v>13</v>
       </c>
@@ -26191,7 +26211,7 @@
         </is>
       </c>
     </row>
-    <row r="432">
+    <row r="432" ht="16" customHeight="1">
       <c r="A432" s="3" t="n">
         <v>14</v>
       </c>
@@ -26251,7 +26271,7 @@
         </is>
       </c>
     </row>
-    <row r="433">
+    <row r="433" ht="16" customHeight="1">
       <c r="A433" s="3" t="n">
         <v>15</v>
       </c>
@@ -26311,7 +26331,7 @@
         </is>
       </c>
     </row>
-    <row r="434">
+    <row r="434" ht="16" customHeight="1">
       <c r="A434" s="3" t="n">
         <v>16</v>
       </c>
@@ -26371,7 +26391,7 @@
         </is>
       </c>
     </row>
-    <row r="435">
+    <row r="435" ht="16" customHeight="1">
       <c r="A435" s="3" t="n">
         <v>17</v>
       </c>
@@ -26431,7 +26451,7 @@
         </is>
       </c>
     </row>
-    <row r="436">
+    <row r="436" ht="16" customHeight="1">
       <c r="A436" s="3" t="n">
         <v>18</v>
       </c>
@@ -26491,7 +26511,7 @@
         </is>
       </c>
     </row>
-    <row r="437">
+    <row r="437" ht="16" customHeight="1">
       <c r="A437" s="3" t="n">
         <v>19</v>
       </c>
@@ -26551,7 +26571,7 @@
         </is>
       </c>
     </row>
-    <row r="438">
+    <row r="438" ht="16" customHeight="1">
       <c r="A438" s="3" t="n">
         <v>20</v>
       </c>
@@ -26611,7 +26631,7 @@
         </is>
       </c>
     </row>
-    <row r="439">
+    <row r="439" ht="16" customHeight="1">
       <c r="A439" s="3" t="n">
         <v>21</v>
       </c>
@@ -26671,7 +26691,7 @@
         </is>
       </c>
     </row>
-    <row r="440">
+    <row r="440" ht="16" customHeight="1">
       <c r="A440" s="3" t="n">
         <v>22</v>
       </c>
@@ -26731,7 +26751,7 @@
         </is>
       </c>
     </row>
-    <row r="441">
+    <row r="441" ht="16" customHeight="1">
       <c r="A441" s="3" t="n">
         <v>23</v>
       </c>
@@ -26791,7 +26811,7 @@
         </is>
       </c>
     </row>
-    <row r="442">
+    <row r="442" ht="16" customHeight="1">
       <c r="A442" s="3" t="n">
         <v>24</v>
       </c>
@@ -26851,7 +26871,7 @@
         </is>
       </c>
     </row>
-    <row r="443">
+    <row r="443" ht="16" customHeight="1">
       <c r="A443" s="3" t="n">
         <v>25</v>
       </c>
@@ -26911,7 +26931,7 @@
         </is>
       </c>
     </row>
-    <row r="444">
+    <row r="444" ht="16" customHeight="1">
       <c r="A444" s="3" t="n">
         <v>26</v>
       </c>
@@ -26971,7 +26991,7 @@
         </is>
       </c>
     </row>
-    <row r="445">
+    <row r="445" ht="16" customHeight="1">
       <c r="A445" s="3" t="n">
         <v>27</v>
       </c>
@@ -27031,7 +27051,7 @@
         </is>
       </c>
     </row>
-    <row r="446">
+    <row r="446" ht="16" customHeight="1">
       <c r="A446" s="3" t="n">
         <v>28</v>
       </c>
@@ -27091,7 +27111,7 @@
         </is>
       </c>
     </row>
-    <row r="447">
+    <row r="447" ht="16" customHeight="1">
       <c r="A447" s="3" t="n">
         <v>29</v>
       </c>
@@ -27151,7 +27171,7 @@
         </is>
       </c>
     </row>
-    <row r="448">
+    <row r="448" ht="16" customHeight="1">
       <c r="A448" s="3" t="n">
         <v>30</v>
       </c>
@@ -27211,7 +27231,7 @@
         </is>
       </c>
     </row>
-    <row r="449">
+    <row r="449" ht="16" customHeight="1">
       <c r="A449" s="3" t="n">
         <v>31</v>
       </c>
@@ -27271,7 +27291,7 @@
         </is>
       </c>
     </row>
-    <row r="450">
+    <row r="450" ht="16" customHeight="1">
       <c r="A450" s="3" t="n">
         <v>32</v>
       </c>
@@ -27331,7 +27351,7 @@
         </is>
       </c>
     </row>
-    <row r="451">
+    <row r="451" ht="16" customHeight="1">
       <c r="A451" s="3" t="n">
         <v>33</v>
       </c>
@@ -27391,7 +27411,7 @@
         </is>
       </c>
     </row>
-    <row r="452">
+    <row r="452" ht="16" customHeight="1">
       <c r="A452" s="3" t="n">
         <v>34</v>
       </c>
@@ -27451,7 +27471,7 @@
         </is>
       </c>
     </row>
-    <row r="453">
+    <row r="453" ht="16" customHeight="1">
       <c r="A453" s="3" t="n">
         <v>35</v>
       </c>
@@ -27511,7 +27531,7 @@
         </is>
       </c>
     </row>
-    <row r="454">
+    <row r="454" ht="16" customHeight="1">
       <c r="A454" s="3" t="n">
         <v>30</v>
       </c>
@@ -27571,7 +27591,7 @@
         </is>
       </c>
     </row>
-    <row r="455">
+    <row r="455" ht="16" customHeight="1">
       <c r="A455" s="3" t="n">
         <v>50</v>
       </c>
@@ -27631,7 +27651,7 @@
         </is>
       </c>
     </row>
-    <row r="456">
+    <row r="456" ht="16" customHeight="1">
       <c r="A456" s="3" t="n">
         <v>51</v>
       </c>
@@ -27691,7 +27711,7 @@
         </is>
       </c>
     </row>
-    <row r="457">
+    <row r="457" ht="16" customHeight="1">
       <c r="A457" s="3" t="n">
         <v>52</v>
       </c>
@@ -27751,7 +27771,7 @@
         </is>
       </c>
     </row>
-    <row r="458">
+    <row r="458" ht="16" customHeight="1">
       <c r="A458" s="3" t="n">
         <v>67</v>
       </c>
@@ -27811,7 +27831,7 @@
         </is>
       </c>
     </row>
-    <row r="459">
+    <row r="459" ht="16" customHeight="1">
       <c r="A459" s="3" t="n">
         <v>67</v>
       </c>
@@ -27871,7 +27891,7 @@
         </is>
       </c>
     </row>
-    <row r="460">
+    <row r="460" ht="16" customHeight="1">
       <c r="A460" s="3" t="n">
         <v>67</v>
       </c>
@@ -27931,7 +27951,7 @@
         </is>
       </c>
     </row>
-    <row r="461">
+    <row r="461" ht="16" customHeight="1">
       <c r="A461" s="3" t="n">
         <v>67</v>
       </c>
@@ -27991,7 +28011,7 @@
         </is>
       </c>
     </row>
-    <row r="462">
+    <row r="462" ht="16" customHeight="1">
       <c r="A462" s="3" t="n">
         <v>67</v>
       </c>
@@ -28051,7 +28071,7 @@
         </is>
       </c>
     </row>
-    <row r="463">
+    <row r="463" ht="16" customHeight="1">
       <c r="A463" s="3" t="n">
         <v>68</v>
       </c>
@@ -28111,7 +28131,7 @@
         </is>
       </c>
     </row>
-    <row r="464">
+    <row r="464" ht="16" customHeight="1">
       <c r="A464" s="3" t="n">
         <v>69</v>
       </c>
@@ -28171,7 +28191,7 @@
         </is>
       </c>
     </row>
-    <row r="465">
+    <row r="465" ht="16" customHeight="1">
       <c r="A465" s="3" t="n">
         <v>70</v>
       </c>
@@ -28231,7 +28251,7 @@
         </is>
       </c>
     </row>
-    <row r="466">
+    <row r="466" ht="16" customHeight="1">
       <c r="A466" s="3" t="n">
         <v>66</v>
       </c>
@@ -28291,7 +28311,7 @@
         </is>
       </c>
     </row>
-    <row r="467">
+    <row r="467" ht="16" customHeight="1">
       <c r="A467" s="3" t="n">
         <v>66</v>
       </c>
@@ -28351,7 +28371,7 @@
         </is>
       </c>
     </row>
-    <row r="468">
+    <row r="468" ht="16" customHeight="1">
       <c r="A468" s="3" t="n">
         <v>66</v>
       </c>
@@ -28411,7 +28431,7 @@
         </is>
       </c>
     </row>
-    <row r="469">
+    <row r="469" ht="16" customHeight="1">
       <c r="A469" s="3" t="n">
         <v>66</v>
       </c>
@@ -28471,7 +28491,7 @@
         </is>
       </c>
     </row>
-    <row r="470">
+    <row r="470" ht="16" customHeight="1">
       <c r="A470" s="3" t="n">
         <v>69</v>
       </c>
@@ -28531,7 +28551,7 @@
         </is>
       </c>
     </row>
-    <row r="471">
+    <row r="471" ht="16" customHeight="1">
       <c r="A471" s="3" t="n">
         <v>69</v>
       </c>
@@ -28591,7 +28611,7 @@
         </is>
       </c>
     </row>
-    <row r="472">
+    <row r="472" ht="16" customHeight="1">
       <c r="A472" s="3" t="n">
         <v>71</v>
       </c>
@@ -28651,7 +28671,7 @@
         </is>
       </c>
     </row>
-    <row r="473">
+    <row r="473" ht="16" customHeight="1">
       <c r="A473" s="3" t="n">
         <v>68</v>
       </c>
@@ -28711,7 +28731,7 @@
         </is>
       </c>
     </row>
-    <row r="474">
+    <row r="474" ht="16" customHeight="1">
       <c r="A474" s="3" t="n">
         <v>60</v>
       </c>
@@ -28771,7 +28791,7 @@
         </is>
       </c>
     </row>
-    <row r="475">
+    <row r="475" ht="16" customHeight="1">
       <c r="A475" s="3" t="n">
         <v>61</v>
       </c>
@@ -28815,7 +28835,7 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J475" s="4" t="inlineStr"/>
+      <c r="J475" s="4" t="n"/>
       <c r="K475" s="3" t="inlineStr">
         <is>
           <t>2026-07-01 13:11:03</t>
@@ -28827,7 +28847,7 @@
         </is>
       </c>
     </row>
-    <row r="476">
+    <row r="476" ht="16" customHeight="1">
       <c r="A476" s="3" t="n">
         <v>62</v>
       </c>
@@ -28887,7 +28907,7 @@
         </is>
       </c>
     </row>
-    <row r="477">
+    <row r="477" ht="16" customHeight="1">
       <c r="A477" s="3" t="n">
         <v>63</v>
       </c>
@@ -28947,7 +28967,7 @@
         </is>
       </c>
     </row>
-    <row r="478">
+    <row r="478" ht="16" customHeight="1">
       <c r="A478" s="3" t="n">
         <v>64</v>
       </c>
@@ -29007,7 +29027,7 @@
         </is>
       </c>
     </row>
-    <row r="479">
+    <row r="479" ht="16" customHeight="1">
       <c r="A479" s="3" t="n">
         <v>65</v>
       </c>
@@ -29067,7 +29087,7 @@
         </is>
       </c>
     </row>
-    <row r="480">
+    <row r="480" ht="16" customHeight="1">
       <c r="A480" s="3" t="n">
         <v>66</v>
       </c>
@@ -29127,7 +29147,7 @@
         </is>
       </c>
     </row>
-    <row r="481">
+    <row r="481" ht="16" customHeight="1">
       <c r="A481" s="3" t="n">
         <v>67</v>
       </c>
@@ -29187,7 +29207,7 @@
         </is>
       </c>
     </row>
-    <row r="482">
+    <row r="482" ht="16" customHeight="1">
       <c r="A482" s="3" t="n">
         <v>68</v>
       </c>
@@ -29247,7 +29267,7 @@
         </is>
       </c>
     </row>
-    <row r="483">
+    <row r="483" ht="16" customHeight="1">
       <c r="A483" s="3" t="n">
         <v>69</v>
       </c>
@@ -29307,7 +29327,7 @@
         </is>
       </c>
     </row>
-    <row r="484">
+    <row r="484" ht="16" customHeight="1">
       <c r="A484" s="3" t="n">
         <v>70</v>
       </c>
@@ -29367,7 +29387,7 @@
         </is>
       </c>
     </row>
-    <row r="485">
+    <row r="485" ht="16" customHeight="1">
       <c r="A485" s="3" t="n">
         <v>3</v>
       </c>
@@ -29427,7 +29447,7 @@
         </is>
       </c>
     </row>
-    <row r="486">
+    <row r="486" ht="16" customHeight="1">
       <c r="A486" s="3" t="n">
         <v>3</v>
       </c>
@@ -29487,7 +29507,7 @@
         </is>
       </c>
     </row>
-    <row r="487">
+    <row r="487" ht="16" customHeight="1">
       <c r="A487" s="3" t="n">
         <v>1</v>
       </c>
@@ -29531,15 +29551,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J487" s="4" t="inlineStr"/>
-      <c r="K487" s="3" t="inlineStr"/>
+      <c r="J487" s="4" t="n"/>
+      <c r="K487" s="3" t="n"/>
       <c r="L487" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="488">
+    <row r="488" ht="16" customHeight="1">
       <c r="A488" s="3" t="n">
         <v>2</v>
       </c>
@@ -29583,15 +29603,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J488" s="4" t="inlineStr"/>
-      <c r="K488" s="3" t="inlineStr"/>
+      <c r="J488" s="4" t="n"/>
+      <c r="K488" s="3" t="n"/>
       <c r="L488" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="489">
+    <row r="489" ht="16" customHeight="1">
       <c r="A489" s="3" t="n">
         <v>3</v>
       </c>
@@ -29635,15 +29655,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J489" s="4" t="inlineStr"/>
-      <c r="K489" s="3" t="inlineStr"/>
+      <c r="J489" s="4" t="n"/>
+      <c r="K489" s="3" t="n"/>
       <c r="L489" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="490">
+    <row r="490" ht="16" customHeight="1">
       <c r="A490" s="3" t="n">
         <v>4</v>
       </c>
@@ -29687,15 +29707,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J490" s="4" t="inlineStr"/>
-      <c r="K490" s="3" t="inlineStr"/>
+      <c r="J490" s="4" t="n"/>
+      <c r="K490" s="3" t="n"/>
       <c r="L490" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="491">
+    <row r="491" ht="16" customHeight="1">
       <c r="A491" s="3" t="n">
         <v>5</v>
       </c>
@@ -29739,15 +29759,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J491" s="4" t="inlineStr"/>
-      <c r="K491" s="3" t="inlineStr"/>
+      <c r="J491" s="4" t="n"/>
+      <c r="K491" s="3" t="n"/>
       <c r="L491" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="492">
+    <row r="492" ht="16" customHeight="1">
       <c r="A492" s="3" t="n">
         <v>6</v>
       </c>
@@ -29791,15 +29811,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J492" s="4" t="inlineStr"/>
-      <c r="K492" s="3" t="inlineStr"/>
+      <c r="J492" s="4" t="n"/>
+      <c r="K492" s="3" t="n"/>
       <c r="L492" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="493">
+    <row r="493" ht="16" customHeight="1">
       <c r="A493" s="3" t="n">
         <v>7</v>
       </c>
@@ -29843,15 +29863,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J493" s="4" t="inlineStr"/>
-      <c r="K493" s="3" t="inlineStr"/>
+      <c r="J493" s="4" t="n"/>
+      <c r="K493" s="3" t="n"/>
       <c r="L493" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="494">
+    <row r="494" ht="16" customHeight="1">
       <c r="A494" s="3" t="n">
         <v>8</v>
       </c>
@@ -29895,15 +29915,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J494" s="4" t="inlineStr"/>
-      <c r="K494" s="3" t="inlineStr"/>
+      <c r="J494" s="4" t="n"/>
+      <c r="K494" s="3" t="n"/>
       <c r="L494" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="495">
+    <row r="495" ht="16" customHeight="1">
       <c r="A495" s="3" t="n">
         <v>9</v>
       </c>
@@ -29947,15 +29967,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J495" s="4" t="inlineStr"/>
-      <c r="K495" s="3" t="inlineStr"/>
+      <c r="J495" s="4" t="n"/>
+      <c r="K495" s="3" t="n"/>
       <c r="L495" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="496">
+    <row r="496" ht="16" customHeight="1">
       <c r="A496" s="3" t="n">
         <v>10</v>
       </c>
@@ -29999,15 +30019,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J496" s="4" t="inlineStr"/>
-      <c r="K496" s="3" t="inlineStr"/>
+      <c r="J496" s="4" t="n"/>
+      <c r="K496" s="3" t="n"/>
       <c r="L496" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="497">
+    <row r="497" ht="16" customHeight="1">
       <c r="A497" s="3" t="n">
         <v>1</v>
       </c>
@@ -30051,15 +30071,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J497" s="4" t="inlineStr"/>
-      <c r="K497" s="3" t="inlineStr"/>
+      <c r="J497" s="4" t="n"/>
+      <c r="K497" s="3" t="n"/>
       <c r="L497" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="498">
+    <row r="498" ht="16" customHeight="1">
       <c r="A498" s="3" t="n">
         <v>2</v>
       </c>
@@ -30103,15 +30123,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J498" s="4" t="inlineStr"/>
-      <c r="K498" s="3" t="inlineStr"/>
+      <c r="J498" s="4" t="n"/>
+      <c r="K498" s="3" t="n"/>
       <c r="L498" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="499">
+    <row r="499" ht="16" customHeight="1">
       <c r="A499" s="3" t="n">
         <v>3</v>
       </c>
@@ -30155,15 +30175,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J499" s="4" t="inlineStr"/>
-      <c r="K499" s="3" t="inlineStr"/>
+      <c r="J499" s="4" t="n"/>
+      <c r="K499" s="3" t="n"/>
       <c r="L499" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="500">
+    <row r="500" ht="16" customHeight="1">
       <c r="A500" s="3" t="n">
         <v>4</v>
       </c>
@@ -30207,15 +30227,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J500" s="4" t="inlineStr"/>
-      <c r="K500" s="3" t="inlineStr"/>
+      <c r="J500" s="4" t="n"/>
+      <c r="K500" s="3" t="n"/>
       <c r="L500" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="501">
+    <row r="501" ht="16" customHeight="1">
       <c r="A501" s="3" t="n">
         <v>1</v>
       </c>
@@ -30264,14 +30284,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K501" s="3" t="inlineStr"/>
+      <c r="K501" s="3" t="n"/>
       <c r="L501" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="502">
+    <row r="502" ht="16" customHeight="1">
       <c r="A502" s="3" t="n">
         <v>2</v>
       </c>
@@ -30320,14 +30340,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K502" s="3" t="inlineStr"/>
+      <c r="K502" s="3" t="n"/>
       <c r="L502" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="503">
+    <row r="503" ht="16" customHeight="1">
       <c r="A503" s="3" t="n">
         <v>3</v>
       </c>
@@ -30376,14 +30396,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K503" s="3" t="inlineStr"/>
+      <c r="K503" s="3" t="n"/>
       <c r="L503" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="504">
+    <row r="504" ht="16" customHeight="1">
       <c r="A504" s="3" t="n">
         <v>1</v>
       </c>
@@ -30427,15 +30447,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J504" s="4" t="inlineStr"/>
-      <c r="K504" s="3" t="inlineStr"/>
+      <c r="J504" s="4" t="n"/>
+      <c r="K504" s="3" t="n"/>
       <c r="L504" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="505">
+    <row r="505" ht="16" customHeight="1">
       <c r="A505" s="3" t="n">
         <v>2</v>
       </c>
@@ -30479,15 +30499,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J505" s="4" t="inlineStr"/>
-      <c r="K505" s="3" t="inlineStr"/>
+      <c r="J505" s="4" t="n"/>
+      <c r="K505" s="3" t="n"/>
       <c r="L505" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="506">
+    <row r="506" ht="16" customHeight="1">
       <c r="A506" s="3" t="n">
         <v>3</v>
       </c>
@@ -30531,15 +30551,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J506" s="4" t="inlineStr"/>
-      <c r="K506" s="3" t="inlineStr"/>
+      <c r="J506" s="4" t="n"/>
+      <c r="K506" s="3" t="n"/>
       <c r="L506" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="507">
+    <row r="507" ht="16" customHeight="1">
       <c r="A507" s="3" t="n">
         <v>4</v>
       </c>
@@ -30583,15 +30603,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J507" s="4" t="inlineStr"/>
-      <c r="K507" s="3" t="inlineStr"/>
+      <c r="J507" s="4" t="n"/>
+      <c r="K507" s="3" t="n"/>
       <c r="L507" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="508">
+    <row r="508" ht="16" customHeight="1">
       <c r="A508" s="3" t="n">
         <v>5</v>
       </c>
@@ -30640,14 +30660,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K508" s="3" t="inlineStr"/>
+      <c r="K508" s="3" t="n"/>
       <c r="L508" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="509">
+    <row r="509" ht="16" customHeight="1">
       <c r="A509" s="3" t="n">
         <v>6</v>
       </c>
@@ -30696,14 +30716,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K509" s="3" t="inlineStr"/>
+      <c r="K509" s="3" t="n"/>
       <c r="L509" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="510">
+    <row r="510" ht="16" customHeight="1">
       <c r="A510" s="3" t="n">
         <v>7</v>
       </c>
@@ -30752,14 +30772,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K510" s="3" t="inlineStr"/>
+      <c r="K510" s="3" t="n"/>
       <c r="L510" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="511">
+    <row r="511" ht="16" customHeight="1">
       <c r="A511" s="3" t="n">
         <v>8</v>
       </c>
@@ -30808,14 +30828,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K511" s="3" t="inlineStr"/>
+      <c r="K511" s="3" t="n"/>
       <c r="L511" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="512">
+    <row r="512" ht="16" customHeight="1">
       <c r="A512" s="3" t="n">
         <v>9</v>
       </c>
@@ -30864,14 +30884,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K512" s="3" t="inlineStr"/>
+      <c r="K512" s="3" t="n"/>
       <c r="L512" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="513">
+    <row r="513" ht="16" customHeight="1">
       <c r="A513" s="3" t="n">
         <v>10</v>
       </c>
@@ -30920,14 +30940,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K513" s="3" t="inlineStr"/>
+      <c r="K513" s="3" t="n"/>
       <c r="L513" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="514">
+    <row r="514" ht="16" customHeight="1">
       <c r="A514" s="3" t="n">
         <v>11</v>
       </c>
@@ -30976,14 +30996,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K514" s="3" t="inlineStr"/>
+      <c r="K514" s="3" t="n"/>
       <c r="L514" s="4" t="inlineStr">
         <is>
           <t>T6A15194</t>
         </is>
       </c>
     </row>
-    <row r="515">
+    <row r="515" ht="16" customHeight="1">
       <c r="A515" s="3" t="n">
         <v>12</v>
       </c>
@@ -31032,14 +31052,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K515" s="3" t="inlineStr"/>
+      <c r="K515" s="3" t="n"/>
       <c r="L515" s="4" t="inlineStr">
         <is>
           <t>T6D24286</t>
         </is>
       </c>
     </row>
-    <row r="516">
+    <row r="516" ht="16" customHeight="1">
       <c r="A516" s="3" t="n">
         <v>13</v>
       </c>
@@ -31088,14 +31108,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K516" s="3" t="inlineStr"/>
+      <c r="K516" s="3" t="n"/>
       <c r="L516" s="4" t="inlineStr">
         <is>
           <t>T6E60920</t>
         </is>
       </c>
     </row>
-    <row r="517">
+    <row r="517" ht="16" customHeight="1">
       <c r="A517" s="3" t="n">
         <v>14</v>
       </c>
@@ -31144,14 +31164,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K517" s="3" t="inlineStr"/>
+      <c r="K517" s="3" t="n"/>
       <c r="L517" s="4" t="inlineStr">
         <is>
           <t>T2D71946</t>
         </is>
       </c>
     </row>
-    <row r="518">
+    <row r="518" ht="16" customHeight="1">
       <c r="A518" s="3" t="n">
         <v>15</v>
       </c>
@@ -31200,14 +31220,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K518" s="3" t="inlineStr"/>
+      <c r="K518" s="3" t="n"/>
       <c r="L518" s="4" t="inlineStr">
         <is>
           <t>S6C68602</t>
         </is>
       </c>
     </row>
-    <row r="519">
+    <row r="519" ht="16" customHeight="1">
       <c r="A519" s="3" t="n">
         <v>16</v>
       </c>
@@ -31256,14 +31276,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K519" s="3" t="inlineStr"/>
+      <c r="K519" s="3" t="n"/>
       <c r="L519" s="4" t="inlineStr">
         <is>
           <t>T2E26985</t>
         </is>
       </c>
     </row>
-    <row r="520">
+    <row r="520" ht="16" customHeight="1">
       <c r="A520" s="3" t="n">
         <v>17</v>
       </c>
@@ -31312,14 +31332,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K520" s="3" t="inlineStr"/>
+      <c r="K520" s="3" t="n"/>
       <c r="L520" s="4" t="inlineStr">
         <is>
           <t>T6D67907</t>
         </is>
       </c>
     </row>
-    <row r="521">
+    <row r="521" ht="16" customHeight="1">
       <c r="A521" s="3" t="n">
         <v>18</v>
       </c>
@@ -31368,14 +31388,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K521" s="3" t="inlineStr"/>
+      <c r="K521" s="3" t="n"/>
       <c r="L521" s="4" t="inlineStr">
         <is>
           <t>T6E56913</t>
         </is>
       </c>
     </row>
-    <row r="522">
+    <row r="522" ht="16" customHeight="1">
       <c r="A522" s="3" t="n">
         <v>19</v>
       </c>
@@ -31424,14 +31444,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K522" s="3" t="inlineStr"/>
+      <c r="K522" s="3" t="n"/>
       <c r="L522" s="4" t="inlineStr">
         <is>
           <t>T6D69218</t>
         </is>
       </c>
     </row>
-    <row r="523">
+    <row r="523" ht="16" customHeight="1">
       <c r="A523" s="3" t="n">
         <v>20</v>
       </c>
@@ -31480,14 +31500,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K523" s="3" t="inlineStr"/>
+      <c r="K523" s="3" t="n"/>
       <c r="L523" s="4" t="inlineStr">
         <is>
           <t>T1C78660</t>
         </is>
       </c>
     </row>
-    <row r="524">
+    <row r="524" ht="16" customHeight="1">
       <c r="A524" s="3" t="n">
         <v>21</v>
       </c>
@@ -31536,14 +31556,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K524" s="3" t="inlineStr"/>
+      <c r="K524" s="3" t="n"/>
       <c r="L524" s="4" t="inlineStr">
         <is>
           <t>T5E13622</t>
         </is>
       </c>
     </row>
-    <row r="525">
+    <row r="525" ht="16" customHeight="1">
       <c r="A525" s="3" t="n">
         <v>22</v>
       </c>
@@ -31592,14 +31612,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K525" s="3" t="inlineStr"/>
+      <c r="K525" s="3" t="n"/>
       <c r="L525" s="4" t="inlineStr">
         <is>
           <t>T1D78995</t>
         </is>
       </c>
     </row>
-    <row r="526">
+    <row r="526" ht="16" customHeight="1">
       <c r="A526" s="3" t="n">
         <v>23</v>
       </c>
@@ -31648,14 +31668,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K526" s="3" t="inlineStr"/>
+      <c r="K526" s="3" t="n"/>
       <c r="L526" s="4" t="inlineStr">
         <is>
           <t>T5D36149</t>
         </is>
       </c>
     </row>
-    <row r="527">
+    <row r="527" ht="16" customHeight="1">
       <c r="A527" s="3" t="n">
         <v>24</v>
       </c>
@@ -31704,14 +31724,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K527" s="3" t="inlineStr"/>
+      <c r="K527" s="3" t="n"/>
       <c r="L527" s="4" t="inlineStr">
         <is>
           <t>T6D68667</t>
         </is>
       </c>
     </row>
-    <row r="528">
+    <row r="528" ht="16" customHeight="1">
       <c r="A528" s="3" t="n">
         <v>25</v>
       </c>
@@ -31760,14 +31780,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K528" s="3" t="inlineStr"/>
+      <c r="K528" s="3" t="n"/>
       <c r="L528" s="4" t="inlineStr">
         <is>
           <t>T2D85502</t>
         </is>
       </c>
     </row>
-    <row r="529">
+    <row r="529" ht="16" customHeight="1">
       <c r="A529" s="3" t="n">
         <v>26</v>
       </c>
@@ -31816,14 +31836,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K529" s="3" t="inlineStr"/>
+      <c r="K529" s="3" t="n"/>
       <c r="L529" s="4" t="inlineStr">
         <is>
           <t>T6E16144</t>
         </is>
       </c>
     </row>
-    <row r="530">
+    <row r="530" ht="16" customHeight="1">
       <c r="A530" s="3" t="n">
         <v>27</v>
       </c>
@@ -31872,14 +31892,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K530" s="3" t="inlineStr"/>
+      <c r="K530" s="3" t="n"/>
       <c r="L530" s="4" t="inlineStr">
         <is>
           <t>T5E15967</t>
         </is>
       </c>
     </row>
-    <row r="531">
+    <row r="531" ht="16" customHeight="1">
       <c r="A531" s="3" t="n">
         <v>28</v>
       </c>
@@ -31928,14 +31948,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K531" s="3" t="inlineStr"/>
+      <c r="K531" s="3" t="n"/>
       <c r="L531" s="4" t="inlineStr">
         <is>
           <t>T6C11232</t>
         </is>
       </c>
     </row>
-    <row r="532">
+    <row r="532" ht="16" customHeight="1">
       <c r="A532" s="3" t="n">
         <v>29</v>
       </c>
@@ -31984,14 +32004,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K532" s="3" t="inlineStr"/>
+      <c r="K532" s="3" t="n"/>
       <c r="L532" s="4" t="inlineStr">
         <is>
           <t>T2E27168</t>
         </is>
       </c>
     </row>
-    <row r="533">
+    <row r="533" ht="16" customHeight="1">
       <c r="A533" s="3" t="n">
         <v>30</v>
       </c>
@@ -32040,14 +32060,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K533" s="3" t="inlineStr"/>
+      <c r="K533" s="3" t="n"/>
       <c r="L533" s="4" t="inlineStr">
         <is>
           <t>T2E33167</t>
         </is>
       </c>
     </row>
-    <row r="534">
+    <row r="534" ht="16" customHeight="1">
       <c r="A534" s="3" t="n">
         <v>31</v>
       </c>
@@ -32096,14 +32116,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K534" s="3" t="inlineStr"/>
+      <c r="K534" s="3" t="n"/>
       <c r="L534" s="4" t="inlineStr">
         <is>
           <t>T6D67029</t>
         </is>
       </c>
     </row>
-    <row r="535">
+    <row r="535" ht="16" customHeight="1">
       <c r="A535" s="3" t="n">
         <v>32</v>
       </c>
@@ -32152,14 +32172,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K535" s="3" t="inlineStr"/>
+      <c r="K535" s="3" t="n"/>
       <c r="L535" s="4" t="inlineStr">
         <is>
           <t>T6E15801</t>
         </is>
       </c>
     </row>
-    <row r="536">
+    <row r="536" ht="16" customHeight="1">
       <c r="A536" s="3" t="n">
         <v>33</v>
       </c>
@@ -32208,14 +32228,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K536" s="3" t="inlineStr"/>
+      <c r="K536" s="3" t="n"/>
       <c r="L536" s="4" t="inlineStr">
         <is>
           <t>R2K76480</t>
         </is>
       </c>
     </row>
-    <row r="537">
+    <row r="537" ht="16" customHeight="1">
       <c r="A537" s="3" t="n">
         <v>1</v>
       </c>
@@ -32259,15 +32279,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J537" s="4" t="inlineStr"/>
-      <c r="K537" s="3" t="inlineStr"/>
+      <c r="J537" s="4" t="n"/>
+      <c r="K537" s="3" t="n"/>
       <c r="L537" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="538">
+    <row r="538" ht="16" customHeight="1">
       <c r="A538" s="3" t="n">
         <v>2</v>
       </c>
@@ -32311,15 +32331,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J538" s="4" t="inlineStr"/>
-      <c r="K538" s="3" t="inlineStr"/>
+      <c r="J538" s="4" t="n"/>
+      <c r="K538" s="3" t="n"/>
       <c r="L538" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="539">
+    <row r="539" ht="16" customHeight="1">
       <c r="A539" s="3" t="n">
         <v>3</v>
       </c>
@@ -32363,15 +32383,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J539" s="4" t="inlineStr"/>
-      <c r="K539" s="3" t="inlineStr"/>
+      <c r="J539" s="4" t="n"/>
+      <c r="K539" s="3" t="n"/>
       <c r="L539" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="540">
+    <row r="540" ht="16" customHeight="1">
       <c r="A540" s="3" t="n">
         <v>4</v>
       </c>
@@ -32415,15 +32435,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J540" s="4" t="inlineStr"/>
-      <c r="K540" s="3" t="inlineStr"/>
+      <c r="J540" s="4" t="n"/>
+      <c r="K540" s="3" t="n"/>
       <c r="L540" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="541">
+    <row r="541" ht="16" customHeight="1">
       <c r="A541" s="3" t="n">
         <v>5</v>
       </c>
@@ -32472,14 +32492,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K541" s="3" t="inlineStr"/>
+      <c r="K541" s="3" t="n"/>
       <c r="L541" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="542">
+    <row r="542" ht="16" customHeight="1">
       <c r="A542" s="3" t="n">
         <v>6</v>
       </c>
@@ -32528,14 +32548,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K542" s="3" t="inlineStr"/>
+      <c r="K542" s="3" t="n"/>
       <c r="L542" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="543">
+    <row r="543" ht="16" customHeight="1">
       <c r="A543" s="3" t="n">
         <v>7</v>
       </c>
@@ -32584,14 +32604,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K543" s="3" t="inlineStr"/>
+      <c r="K543" s="3" t="n"/>
       <c r="L543" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="544">
+    <row r="544" ht="16" customHeight="1">
       <c r="A544" s="3" t="n">
         <v>8</v>
       </c>
@@ -32640,14 +32660,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K544" s="3" t="inlineStr"/>
+      <c r="K544" s="3" t="n"/>
       <c r="L544" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="545">
+    <row r="545" ht="16" customHeight="1">
       <c r="A545" s="3" t="n">
         <v>9</v>
       </c>
@@ -32696,14 +32716,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K545" s="3" t="inlineStr"/>
+      <c r="K545" s="3" t="n"/>
       <c r="L545" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="546">
+    <row r="546" ht="16" customHeight="1">
       <c r="A546" s="3" t="n">
         <v>10</v>
       </c>
@@ -32752,14 +32772,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K546" s="3" t="inlineStr"/>
+      <c r="K546" s="3" t="n"/>
       <c r="L546" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="547">
+    <row r="547" ht="16" customHeight="1">
       <c r="A547" s="3" t="n">
         <v>11</v>
       </c>
@@ -32808,14 +32828,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K547" s="3" t="inlineStr"/>
+      <c r="K547" s="3" t="n"/>
       <c r="L547" s="4" t="inlineStr">
         <is>
           <t>T6A15194</t>
         </is>
       </c>
     </row>
-    <row r="548">
+    <row r="548" ht="16" customHeight="1">
       <c r="A548" s="3" t="n">
         <v>12</v>
       </c>
@@ -32859,15 +32879,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J548" s="4" t="inlineStr"/>
-      <c r="K548" s="3" t="inlineStr"/>
+      <c r="J548" s="4" t="n"/>
+      <c r="K548" s="3" t="n"/>
       <c r="L548" s="4" t="inlineStr">
         <is>
           <t>T6D24286</t>
         </is>
       </c>
     </row>
-    <row r="549">
+    <row r="549" ht="16" customHeight="1">
       <c r="A549" s="3" t="n">
         <v>13</v>
       </c>
@@ -32911,15 +32931,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J549" s="4" t="inlineStr"/>
-      <c r="K549" s="3" t="inlineStr"/>
+      <c r="J549" s="4" t="n"/>
+      <c r="K549" s="3" t="n"/>
       <c r="L549" s="4" t="inlineStr">
         <is>
           <t>T6E60920</t>
         </is>
       </c>
     </row>
-    <row r="550">
+    <row r="550" ht="16" customHeight="1">
       <c r="A550" s="3" t="n">
         <v>14</v>
       </c>
@@ -32963,15 +32983,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J550" s="4" t="inlineStr"/>
-      <c r="K550" s="3" t="inlineStr"/>
+      <c r="J550" s="4" t="n"/>
+      <c r="K550" s="3" t="n"/>
       <c r="L550" s="4" t="inlineStr">
         <is>
           <t>T2D71946</t>
         </is>
       </c>
     </row>
-    <row r="551">
+    <row r="551" ht="16" customHeight="1">
       <c r="A551" s="3" t="n">
         <v>15</v>
       </c>
@@ -33015,15 +33035,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J551" s="4" t="inlineStr"/>
-      <c r="K551" s="3" t="inlineStr"/>
+      <c r="J551" s="4" t="n"/>
+      <c r="K551" s="3" t="n"/>
       <c r="L551" s="4" t="inlineStr">
         <is>
           <t>S6C68602</t>
         </is>
       </c>
     </row>
-    <row r="552">
+    <row r="552" ht="16" customHeight="1">
       <c r="A552" s="3" t="n">
         <v>16</v>
       </c>
@@ -33067,15 +33087,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J552" s="4" t="inlineStr"/>
-      <c r="K552" s="3" t="inlineStr"/>
+      <c r="J552" s="4" t="n"/>
+      <c r="K552" s="3" t="n"/>
       <c r="L552" s="4" t="inlineStr">
         <is>
           <t>T2E26985</t>
         </is>
       </c>
     </row>
-    <row r="553">
+    <row r="553" ht="16" customHeight="1">
       <c r="A553" s="3" t="n">
         <v>17</v>
       </c>
@@ -33124,14 +33144,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K553" s="3" t="inlineStr"/>
+      <c r="K553" s="3" t="n"/>
       <c r="L553" s="4" t="inlineStr">
         <is>
           <t>T6D67907</t>
         </is>
       </c>
     </row>
-    <row r="554">
+    <row r="554" ht="16" customHeight="1">
       <c r="A554" s="3" t="n">
         <v>18</v>
       </c>
@@ -33175,15 +33195,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J554" s="4" t="inlineStr"/>
-      <c r="K554" s="3" t="inlineStr"/>
+      <c r="J554" s="4" t="n"/>
+      <c r="K554" s="3" t="n"/>
       <c r="L554" s="4" t="inlineStr">
         <is>
           <t>T6E56913</t>
         </is>
       </c>
     </row>
-    <row r="555">
+    <row r="555" ht="16" customHeight="1">
       <c r="A555" s="3" t="n">
         <v>19</v>
       </c>
@@ -33232,14 +33252,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K555" s="3" t="inlineStr"/>
+      <c r="K555" s="3" t="n"/>
       <c r="L555" s="4" t="inlineStr">
         <is>
           <t>T6D69218</t>
         </is>
       </c>
     </row>
-    <row r="556">
+    <row r="556" ht="16" customHeight="1">
       <c r="A556" s="3" t="n">
         <v>20</v>
       </c>
@@ -33283,15 +33303,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J556" s="4" t="inlineStr"/>
-      <c r="K556" s="3" t="inlineStr"/>
+      <c r="J556" s="4" t="n"/>
+      <c r="K556" s="3" t="n"/>
       <c r="L556" s="4" t="inlineStr">
         <is>
           <t>T1C78660</t>
         </is>
       </c>
     </row>
-    <row r="557">
+    <row r="557" ht="16" customHeight="1">
       <c r="A557" s="3" t="n">
         <v>21</v>
       </c>
@@ -33340,14 +33360,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K557" s="3" t="inlineStr"/>
+      <c r="K557" s="3" t="n"/>
       <c r="L557" s="4" t="inlineStr">
         <is>
           <t>T5E13622</t>
         </is>
       </c>
     </row>
-    <row r="558">
+    <row r="558" ht="16" customHeight="1">
       <c r="A558" s="3" t="n">
         <v>1</v>
       </c>
@@ -33391,15 +33411,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J558" s="4" t="inlineStr"/>
-      <c r="K558" s="3" t="inlineStr"/>
+      <c r="J558" s="4" t="n"/>
+      <c r="K558" s="3" t="n"/>
       <c r="L558" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="559">
+    <row r="559" ht="16" customHeight="1">
       <c r="A559" s="3" t="n">
         <v>2</v>
       </c>
@@ -33443,15 +33463,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J559" s="4" t="inlineStr"/>
-      <c r="K559" s="3" t="inlineStr"/>
+      <c r="J559" s="4" t="n"/>
+      <c r="K559" s="3" t="n"/>
       <c r="L559" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="560">
+    <row r="560" ht="16" customHeight="1">
       <c r="A560" s="3" t="n">
         <v>3</v>
       </c>
@@ -33495,15 +33515,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J560" s="4" t="inlineStr"/>
-      <c r="K560" s="3" t="inlineStr"/>
+      <c r="J560" s="4" t="n"/>
+      <c r="K560" s="3" t="n"/>
       <c r="L560" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="561">
+    <row r="561" ht="16" customHeight="1">
       <c r="A561" s="3" t="n">
         <v>4</v>
       </c>
@@ -33547,15 +33567,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J561" s="4" t="inlineStr"/>
-      <c r="K561" s="3" t="inlineStr"/>
+      <c r="J561" s="4" t="n"/>
+      <c r="K561" s="3" t="n"/>
       <c r="L561" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="562">
+    <row r="562" ht="16" customHeight="1">
       <c r="A562" s="3" t="n">
         <v>5</v>
       </c>
@@ -33604,14 +33624,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K562" s="3" t="inlineStr"/>
+      <c r="K562" s="3" t="n"/>
       <c r="L562" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="563">
+    <row r="563" ht="16" customHeight="1">
       <c r="A563" s="3" t="n">
         <v>6</v>
       </c>
@@ -33660,14 +33680,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K563" s="3" t="inlineStr"/>
+      <c r="K563" s="3" t="n"/>
       <c r="L563" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="564">
+    <row r="564" ht="16" customHeight="1">
       <c r="A564" s="3" t="n">
         <v>1</v>
       </c>
@@ -33711,15 +33731,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J564" s="4" t="inlineStr"/>
-      <c r="K564" s="3" t="inlineStr"/>
+      <c r="J564" s="4" t="n"/>
+      <c r="K564" s="3" t="n"/>
       <c r="L564" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="565">
+    <row r="565" ht="16" customHeight="1">
       <c r="A565" s="3" t="n">
         <v>2</v>
       </c>
@@ -33763,15 +33783,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J565" s="4" t="inlineStr"/>
-      <c r="K565" s="3" t="inlineStr"/>
+      <c r="J565" s="4" t="n"/>
+      <c r="K565" s="3" t="n"/>
       <c r="L565" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="566">
+    <row r="566" ht="16" customHeight="1">
       <c r="A566" s="3" t="n">
         <v>3</v>
       </c>
@@ -33815,15 +33835,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J566" s="4" t="inlineStr"/>
-      <c r="K566" s="3" t="inlineStr"/>
+      <c r="J566" s="4" t="n"/>
+      <c r="K566" s="3" t="n"/>
       <c r="L566" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="567">
+    <row r="567" ht="16" customHeight="1">
       <c r="A567" s="3" t="n">
         <v>4</v>
       </c>
@@ -33867,15 +33887,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J567" s="4" t="inlineStr"/>
-      <c r="K567" s="3" t="inlineStr"/>
+      <c r="J567" s="4" t="n"/>
+      <c r="K567" s="3" t="n"/>
       <c r="L567" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="568">
+    <row r="568" ht="16" customHeight="1">
       <c r="A568" s="3" t="n">
         <v>5</v>
       </c>
@@ -33924,14 +33944,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K568" s="3" t="inlineStr"/>
+      <c r="K568" s="3" t="n"/>
       <c r="L568" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="569">
+    <row r="569" ht="16" customHeight="1">
       <c r="A569" s="3" t="n">
         <v>6</v>
       </c>
@@ -33980,14 +34000,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K569" s="3" t="inlineStr"/>
+      <c r="K569" s="3" t="n"/>
       <c r="L569" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="570">
+    <row r="570" ht="16" customHeight="1">
       <c r="A570" s="3" t="n">
         <v>7</v>
       </c>
@@ -34036,14 +34056,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K570" s="3" t="inlineStr"/>
+      <c r="K570" s="3" t="n"/>
       <c r="L570" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="571">
+    <row r="571" ht="16" customHeight="1">
       <c r="A571" s="3" t="n">
         <v>8</v>
       </c>
@@ -34092,14 +34112,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K571" s="3" t="inlineStr"/>
+      <c r="K571" s="3" t="n"/>
       <c r="L571" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="572">
+    <row r="572" ht="16" customHeight="1">
       <c r="A572" s="3" t="n">
         <v>9</v>
       </c>
@@ -34148,14 +34168,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K572" s="3" t="inlineStr"/>
+      <c r="K572" s="3" t="n"/>
       <c r="L572" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="573">
+    <row r="573" ht="16" customHeight="1">
       <c r="A573" s="3" t="n">
         <v>10</v>
       </c>
@@ -34204,14 +34224,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K573" s="3" t="inlineStr"/>
+      <c r="K573" s="3" t="n"/>
       <c r="L573" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="574">
+    <row r="574" ht="16" customHeight="1">
       <c r="A574" s="3" t="n">
         <v>1</v>
       </c>
@@ -34255,15 +34275,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J574" s="4" t="inlineStr"/>
-      <c r="K574" s="3" t="inlineStr"/>
+      <c r="J574" s="4" t="n"/>
+      <c r="K574" s="3" t="n"/>
       <c r="L574" s="4" t="inlineStr">
         <is>
           <t>T6C10044</t>
         </is>
       </c>
     </row>
-    <row r="575">
+    <row r="575" ht="16" customHeight="1">
       <c r="A575" s="3" t="n">
         <v>2</v>
       </c>
@@ -34307,15 +34327,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J575" s="4" t="inlineStr"/>
-      <c r="K575" s="3" t="inlineStr"/>
+      <c r="J575" s="4" t="n"/>
+      <c r="K575" s="3" t="n"/>
       <c r="L575" s="4" t="inlineStr">
         <is>
           <t>T6E16670</t>
         </is>
       </c>
     </row>
-    <row r="576">
+    <row r="576" ht="16" customHeight="1">
       <c r="A576" s="3" t="n">
         <v>3</v>
       </c>
@@ -34359,15 +34379,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J576" s="4" t="inlineStr"/>
-      <c r="K576" s="3" t="inlineStr"/>
+      <c r="J576" s="4" t="n"/>
+      <c r="K576" s="3" t="n"/>
       <c r="L576" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="577">
+    <row r="577" ht="16" customHeight="1">
       <c r="A577" s="3" t="n">
         <v>3</v>
       </c>
@@ -34411,15 +34431,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J577" s="4" t="inlineStr"/>
-      <c r="K577" s="3" t="inlineStr"/>
+      <c r="J577" s="4" t="n"/>
+      <c r="K577" s="3" t="n"/>
       <c r="L577" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="578">
+    <row r="578" ht="16" customHeight="1">
       <c r="A578" s="3" t="n">
         <v>4</v>
       </c>
@@ -34463,15 +34483,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J578" s="4" t="inlineStr"/>
-      <c r="K578" s="3" t="inlineStr"/>
+      <c r="J578" s="4" t="n"/>
+      <c r="K578" s="3" t="n"/>
       <c r="L578" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="579">
+    <row r="579" ht="16" customHeight="1">
       <c r="A579" s="3" t="n">
         <v>5</v>
       </c>
@@ -34520,14 +34540,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K579" s="3" t="inlineStr"/>
+      <c r="K579" s="3" t="n"/>
       <c r="L579" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="580">
+    <row r="580" ht="16" customHeight="1">
       <c r="A580" s="3" t="n">
         <v>6</v>
       </c>
@@ -34576,14 +34596,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K580" s="3" t="inlineStr"/>
+      <c r="K580" s="3" t="n"/>
       <c r="L580" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="581">
+    <row r="581" ht="16" customHeight="1">
       <c r="A581" s="3" t="n">
         <v>7</v>
       </c>
@@ -34632,14 +34652,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K581" s="3" t="inlineStr"/>
+      <c r="K581" s="3" t="n"/>
       <c r="L581" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="582">
+    <row r="582" ht="16" customHeight="1">
       <c r="A582" s="3" t="n">
         <v>8</v>
       </c>
@@ -34688,14 +34708,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K582" s="3" t="inlineStr"/>
+      <c r="K582" s="3" t="n"/>
       <c r="L582" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="583">
+    <row r="583" ht="16" customHeight="1">
       <c r="A583" s="3" t="n">
         <v>3</v>
       </c>
@@ -34739,15 +34759,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J583" s="4" t="inlineStr"/>
-      <c r="K583" s="3" t="inlineStr"/>
+      <c r="J583" s="4" t="n"/>
+      <c r="K583" s="3" t="n"/>
       <c r="L583" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="584">
+    <row r="584" ht="16" customHeight="1">
       <c r="A584" s="3" t="n">
         <v>4</v>
       </c>
@@ -34791,15 +34811,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J584" s="4" t="inlineStr"/>
-      <c r="K584" s="3" t="inlineStr"/>
+      <c r="J584" s="4" t="n"/>
+      <c r="K584" s="3" t="n"/>
       <c r="L584" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="585">
+    <row r="585" ht="16" customHeight="1">
       <c r="A585" s="3" t="n">
         <v>3</v>
       </c>
@@ -34843,15 +34863,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J585" s="4" t="inlineStr"/>
-      <c r="K585" s="3" t="inlineStr"/>
+      <c r="J585" s="4" t="n"/>
+      <c r="K585" s="3" t="n"/>
       <c r="L585" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="586">
+    <row r="586" ht="16" customHeight="1">
       <c r="A586" s="3" t="n">
         <v>4</v>
       </c>
@@ -34895,15 +34915,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J586" s="4" t="inlineStr"/>
-      <c r="K586" s="3" t="inlineStr"/>
+      <c r="J586" s="4" t="n"/>
+      <c r="K586" s="3" t="n"/>
       <c r="L586" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="587">
+    <row r="587" ht="16" customHeight="1">
       <c r="A587" s="3" t="n">
         <v>5</v>
       </c>
@@ -34952,14 +34972,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K587" s="3" t="inlineStr"/>
+      <c r="K587" s="3" t="n"/>
       <c r="L587" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="588">
+    <row r="588" ht="16" customHeight="1">
       <c r="A588" s="3" t="n">
         <v>6</v>
       </c>
@@ -35008,14 +35028,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K588" s="3" t="inlineStr"/>
+      <c r="K588" s="3" t="n"/>
       <c r="L588" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="589">
+    <row r="589" ht="16" customHeight="1">
       <c r="A589" s="3" t="n">
         <v>3</v>
       </c>
@@ -35059,15 +35079,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J589" s="4" t="inlineStr"/>
-      <c r="K589" s="3" t="inlineStr"/>
+      <c r="J589" s="4" t="n"/>
+      <c r="K589" s="3" t="n"/>
       <c r="L589" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="590">
+    <row r="590" ht="16" customHeight="1">
       <c r="A590" s="3" t="n">
         <v>4</v>
       </c>
@@ -35111,15 +35131,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J590" s="4" t="inlineStr"/>
-      <c r="K590" s="3" t="inlineStr"/>
+      <c r="J590" s="4" t="n"/>
+      <c r="K590" s="3" t="n"/>
       <c r="L590" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="591">
+    <row r="591" ht="16" customHeight="1">
       <c r="A591" s="3" t="n">
         <v>5</v>
       </c>
@@ -35168,14 +35188,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K591" s="3" t="inlineStr"/>
+      <c r="K591" s="3" t="n"/>
       <c r="L591" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="592">
+    <row r="592" ht="16" customHeight="1">
       <c r="A592" s="3" t="n">
         <v>6</v>
       </c>
@@ -35224,14 +35244,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K592" s="3" t="inlineStr"/>
+      <c r="K592" s="3" t="n"/>
       <c r="L592" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="593">
+    <row r="593" ht="16" customHeight="1">
       <c r="A593" s="3" t="n">
         <v>7</v>
       </c>
@@ -35280,14 +35300,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K593" s="3" t="inlineStr"/>
+      <c r="K593" s="3" t="n"/>
       <c r="L593" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="594">
+    <row r="594" ht="16" customHeight="1">
       <c r="A594" s="3" t="n">
         <v>8</v>
       </c>
@@ -35336,14 +35356,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K594" s="3" t="inlineStr"/>
+      <c r="K594" s="3" t="n"/>
       <c r="L594" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="595">
+    <row r="595" ht="16" customHeight="1">
       <c r="A595" s="3" t="n">
         <v>9</v>
       </c>
@@ -35392,14 +35412,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K595" s="3" t="inlineStr"/>
+      <c r="K595" s="3" t="n"/>
       <c r="L595" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="596">
+    <row r="596" ht="16" customHeight="1">
       <c r="A596" s="3" t="n">
         <v>10</v>
       </c>
@@ -35448,14 +35468,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K596" s="3" t="inlineStr"/>
+      <c r="K596" s="3" t="n"/>
       <c r="L596" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="597">
+    <row r="597" ht="16" customHeight="1">
       <c r="A597" s="3" t="n">
         <v>12</v>
       </c>
@@ -35499,15 +35519,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J597" s="4" t="inlineStr"/>
-      <c r="K597" s="3" t="inlineStr"/>
+      <c r="J597" s="4" t="n"/>
+      <c r="K597" s="3" t="n"/>
       <c r="L597" s="4" t="inlineStr">
         <is>
           <t>T6D24286</t>
         </is>
       </c>
     </row>
-    <row r="598">
+    <row r="598" ht="16" customHeight="1">
       <c r="A598" s="3" t="n">
         <v>13</v>
       </c>
@@ -35551,15 +35571,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J598" s="4" t="inlineStr"/>
-      <c r="K598" s="3" t="inlineStr"/>
+      <c r="J598" s="4" t="n"/>
+      <c r="K598" s="3" t="n"/>
       <c r="L598" s="4" t="inlineStr">
         <is>
           <t>T6E60920</t>
         </is>
       </c>
     </row>
-    <row r="599">
+    <row r="599" ht="16" customHeight="1">
       <c r="A599" s="3" t="n">
         <v>14</v>
       </c>
@@ -35603,15 +35623,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J599" s="4" t="inlineStr"/>
-      <c r="K599" s="3" t="inlineStr"/>
+      <c r="J599" s="4" t="n"/>
+      <c r="K599" s="3" t="n"/>
       <c r="L599" s="4" t="inlineStr">
         <is>
           <t>T2D71946</t>
         </is>
       </c>
     </row>
-    <row r="600">
+    <row r="600" ht="16" customHeight="1">
       <c r="A600" s="3" t="n">
         <v>15</v>
       </c>
@@ -35655,15 +35675,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J600" s="4" t="inlineStr"/>
-      <c r="K600" s="3" t="inlineStr"/>
+      <c r="J600" s="4" t="n"/>
+      <c r="K600" s="3" t="n"/>
       <c r="L600" s="4" t="inlineStr">
         <is>
           <t>S6C68602</t>
         </is>
       </c>
     </row>
-    <row r="601">
+    <row r="601" ht="16" customHeight="1">
       <c r="A601" s="3" t="n">
         <v>16</v>
       </c>
@@ -35707,15 +35727,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J601" s="4" t="inlineStr"/>
-      <c r="K601" s="3" t="inlineStr"/>
+      <c r="J601" s="4" t="n"/>
+      <c r="K601" s="3" t="n"/>
       <c r="L601" s="4" t="inlineStr">
         <is>
           <t>T2E26985</t>
         </is>
       </c>
     </row>
-    <row r="602">
+    <row r="602" ht="16" customHeight="1">
       <c r="A602" s="3" t="n">
         <v>17</v>
       </c>
@@ -35764,14 +35784,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K602" s="3" t="inlineStr"/>
+      <c r="K602" s="3" t="n"/>
       <c r="L602" s="4" t="inlineStr">
         <is>
           <t>T6D67907</t>
         </is>
       </c>
     </row>
-    <row r="603">
+    <row r="603" ht="16" customHeight="1">
       <c r="A603" s="3" t="n">
         <v>18</v>
       </c>
@@ -35815,15 +35835,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J603" s="4" t="inlineStr"/>
-      <c r="K603" s="3" t="inlineStr"/>
+      <c r="J603" s="4" t="n"/>
+      <c r="K603" s="3" t="n"/>
       <c r="L603" s="4" t="inlineStr">
         <is>
           <t>T6E56913</t>
         </is>
       </c>
     </row>
-    <row r="604">
+    <row r="604" ht="16" customHeight="1">
       <c r="A604" s="3" t="n">
         <v>19</v>
       </c>
@@ -35872,14 +35892,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K604" s="3" t="inlineStr"/>
+      <c r="K604" s="3" t="n"/>
       <c r="L604" s="4" t="inlineStr">
         <is>
           <t>T6D69218</t>
         </is>
       </c>
     </row>
-    <row r="605">
+    <row r="605" ht="16" customHeight="1">
       <c r="A605" s="3" t="n">
         <v>21</v>
       </c>
@@ -35928,14 +35948,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K605" s="3" t="inlineStr"/>
+      <c r="K605" s="3" t="n"/>
       <c r="L605" s="4" t="inlineStr">
         <is>
           <t>T5E13622</t>
         </is>
       </c>
     </row>
-    <row r="606">
+    <row r="606" ht="16" customHeight="1">
       <c r="A606" s="3" t="n">
         <v>23</v>
       </c>
@@ -35984,14 +36004,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K606" s="3" t="inlineStr"/>
+      <c r="K606" s="3" t="n"/>
       <c r="L606" s="4" t="inlineStr">
         <is>
           <t>T5D36149</t>
         </is>
       </c>
     </row>
-    <row r="607">
+    <row r="607" ht="16" customHeight="1">
       <c r="A607" s="3" t="n">
         <v>24</v>
       </c>
@@ -36035,15 +36055,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J607" s="4" t="inlineStr"/>
-      <c r="K607" s="3" t="inlineStr"/>
+      <c r="J607" s="4" t="n"/>
+      <c r="K607" s="3" t="n"/>
       <c r="L607" s="4" t="inlineStr">
         <is>
           <t>T6D68667</t>
         </is>
       </c>
     </row>
-    <row r="608">
+    <row r="608" ht="16" customHeight="1">
       <c r="A608" s="3" t="n">
         <v>25</v>
       </c>
@@ -36087,15 +36107,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J608" s="4" t="inlineStr"/>
-      <c r="K608" s="3" t="inlineStr"/>
+      <c r="J608" s="4" t="n"/>
+      <c r="K608" s="3" t="n"/>
       <c r="L608" s="4" t="inlineStr">
         <is>
           <t>T2D85502</t>
         </is>
       </c>
     </row>
-    <row r="609">
+    <row r="609" ht="16" customHeight="1">
       <c r="A609" s="3" t="n">
         <v>27</v>
       </c>
@@ -36139,15 +36159,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J609" s="4" t="inlineStr"/>
-      <c r="K609" s="3" t="inlineStr"/>
+      <c r="J609" s="4" t="n"/>
+      <c r="K609" s="3" t="n"/>
       <c r="L609" s="4" t="inlineStr">
         <is>
           <t>T5E15967</t>
         </is>
       </c>
     </row>
-    <row r="610">
+    <row r="610" ht="16" customHeight="1">
       <c r="A610" s="3" t="n">
         <v>29</v>
       </c>
@@ -36191,15 +36211,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J610" s="4" t="inlineStr"/>
-      <c r="K610" s="3" t="inlineStr"/>
+      <c r="J610" s="4" t="n"/>
+      <c r="K610" s="3" t="n"/>
       <c r="L610" s="4" t="inlineStr">
         <is>
           <t>T2E27168</t>
         </is>
       </c>
     </row>
-    <row r="611">
+    <row r="611" ht="16" customHeight="1">
       <c r="A611" s="3" t="n">
         <v>30</v>
       </c>
@@ -36248,14 +36268,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K611" s="3" t="inlineStr"/>
+      <c r="K611" s="3" t="n"/>
       <c r="L611" s="4" t="inlineStr">
         <is>
           <t>T2E33167</t>
         </is>
       </c>
     </row>
-    <row r="612">
+    <row r="612" ht="16" customHeight="1">
       <c r="A612" s="3" t="n">
         <v>31</v>
       </c>
@@ -36299,15 +36319,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J612" s="4" t="inlineStr"/>
-      <c r="K612" s="3" t="inlineStr"/>
+      <c r="J612" s="4" t="n"/>
+      <c r="K612" s="3" t="n"/>
       <c r="L612" s="4" t="inlineStr">
         <is>
           <t>T6D67029</t>
         </is>
       </c>
     </row>
-    <row r="613">
+    <row r="613" ht="16" customHeight="1">
       <c r="A613" s="3" t="n">
         <v>33</v>
       </c>
@@ -36356,14 +36376,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K613" s="3" t="inlineStr"/>
+      <c r="K613" s="3" t="n"/>
       <c r="L613" s="4" t="inlineStr">
         <is>
           <t>R2K76480</t>
         </is>
       </c>
     </row>
-    <row r="614">
+    <row r="614" ht="16" customHeight="1">
       <c r="A614" s="3" t="n">
         <v>39</v>
       </c>
@@ -36412,14 +36432,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K614" s="3" t="inlineStr"/>
+      <c r="K614" s="3" t="n"/>
       <c r="L614" s="4" t="inlineStr">
         <is>
           <t>T2C53244</t>
         </is>
       </c>
     </row>
-    <row r="615">
+    <row r="615" ht="16" customHeight="1">
       <c r="A615" s="3" t="n">
         <v>40</v>
       </c>
@@ -36468,14 +36488,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K615" s="3" t="inlineStr"/>
+      <c r="K615" s="3" t="n"/>
       <c r="L615" s="4" t="inlineStr">
         <is>
           <t>T2E74095</t>
         </is>
       </c>
     </row>
-    <row r="616">
+    <row r="616" ht="16" customHeight="1">
       <c r="A616" s="3" t="n">
         <v>43</v>
       </c>
@@ -36519,15 +36539,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J616" s="4" t="inlineStr"/>
-      <c r="K616" s="3" t="inlineStr"/>
+      <c r="J616" s="4" t="n"/>
+      <c r="K616" s="3" t="n"/>
       <c r="L616" s="4" t="inlineStr">
         <is>
           <t>T1D86919</t>
         </is>
       </c>
     </row>
-    <row r="617">
+    <row r="617" ht="16" customHeight="1">
       <c r="A617" s="3" t="n">
         <v>44</v>
       </c>
@@ -36571,15 +36591,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J617" s="4" t="inlineStr"/>
-      <c r="K617" s="3" t="inlineStr"/>
+      <c r="J617" s="4" t="n"/>
+      <c r="K617" s="3" t="n"/>
       <c r="L617" s="4" t="inlineStr">
         <is>
           <t>T6D23022</t>
         </is>
       </c>
     </row>
-    <row r="618">
+    <row r="618" ht="16" customHeight="1">
       <c r="A618" s="3" t="n">
         <v>49</v>
       </c>
@@ -36623,15 +36643,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J618" s="4" t="inlineStr"/>
-      <c r="K618" s="3" t="inlineStr"/>
+      <c r="J618" s="4" t="n"/>
+      <c r="K618" s="3" t="n"/>
       <c r="L618" s="4" t="inlineStr">
         <is>
           <t>T2D85914</t>
         </is>
       </c>
     </row>
-    <row r="619">
+    <row r="619" ht="16" customHeight="1">
       <c r="A619" s="3" t="n">
         <v>58</v>
       </c>
@@ -36680,14 +36700,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K619" s="3" t="inlineStr"/>
+      <c r="K619" s="3" t="n"/>
       <c r="L619" s="4" t="inlineStr">
         <is>
           <t>T6C65254</t>
         </is>
       </c>
     </row>
-    <row r="620">
+    <row r="620" ht="16" customHeight="1">
       <c r="A620" s="3" t="n">
         <v>59</v>
       </c>
@@ -36736,14 +36756,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K620" s="3" t="inlineStr"/>
+      <c r="K620" s="3" t="n"/>
       <c r="L620" s="4" t="inlineStr">
         <is>
           <t>T6D65036</t>
         </is>
       </c>
     </row>
-    <row r="621">
+    <row r="621" ht="16" customHeight="1">
       <c r="A621" s="3" t="n">
         <v>61</v>
       </c>
@@ -36792,14 +36812,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K621" s="3" t="inlineStr"/>
+      <c r="K621" s="3" t="n"/>
       <c r="L621" s="4" t="inlineStr">
         <is>
           <t>T2C59638</t>
         </is>
       </c>
     </row>
-    <row r="622">
+    <row r="622" ht="16" customHeight="1">
       <c r="A622" s="3" t="n">
         <v>64</v>
       </c>
@@ -36848,14 +36868,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K622" s="3" t="inlineStr"/>
+      <c r="K622" s="3" t="n"/>
       <c r="L622" s="4" t="inlineStr">
         <is>
           <t>T6D61847</t>
         </is>
       </c>
     </row>
-    <row r="623">
+    <row r="623" ht="16" customHeight="1">
       <c r="A623" s="3" t="n">
         <v>65</v>
       </c>
@@ -36904,14 +36924,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K623" s="3" t="inlineStr"/>
+      <c r="K623" s="3" t="n"/>
       <c r="L623" s="4" t="inlineStr">
         <is>
           <t>T1E93833</t>
         </is>
       </c>
     </row>
-    <row r="624">
+    <row r="624" ht="16" customHeight="1">
       <c r="A624" s="3" t="n">
         <v>72</v>
       </c>
@@ -36960,14 +36980,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K624" s="3" t="inlineStr"/>
+      <c r="K624" s="3" t="n"/>
       <c r="L624" s="4" t="inlineStr">
         <is>
           <t>T2E26887</t>
         </is>
       </c>
     </row>
-    <row r="625">
+    <row r="625" ht="16" customHeight="1">
       <c r="A625" s="3" t="n">
         <v>3</v>
       </c>
@@ -37011,15 +37031,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J625" s="4" t="inlineStr"/>
-      <c r="K625" s="3" t="inlineStr"/>
+      <c r="J625" s="4" t="n"/>
+      <c r="K625" s="3" t="n"/>
       <c r="L625" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="626">
+    <row r="626" ht="16" customHeight="1">
       <c r="A626" s="3" t="n">
         <v>4</v>
       </c>
@@ -37063,15 +37083,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J626" s="4" t="inlineStr"/>
-      <c r="K626" s="3" t="inlineStr"/>
+      <c r="J626" s="4" t="n"/>
+      <c r="K626" s="3" t="n"/>
       <c r="L626" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="627">
+    <row r="627" ht="16" customHeight="1">
       <c r="A627" s="3" t="n">
         <v>5</v>
       </c>
@@ -37120,14 +37140,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K627" s="3" t="inlineStr"/>
+      <c r="K627" s="3" t="n"/>
       <c r="L627" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="628">
+    <row r="628" ht="16" customHeight="1">
       <c r="A628" s="3" t="n">
         <v>6</v>
       </c>
@@ -37176,14 +37196,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K628" s="3" t="inlineStr"/>
+      <c r="K628" s="3" t="n"/>
       <c r="L628" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="629">
+    <row r="629" ht="16" customHeight="1">
       <c r="A629" s="3" t="n">
         <v>7</v>
       </c>
@@ -37232,14 +37252,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K629" s="3" t="inlineStr"/>
+      <c r="K629" s="3" t="n"/>
       <c r="L629" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="630">
+    <row r="630" ht="16" customHeight="1">
       <c r="A630" s="3" t="n">
         <v>8</v>
       </c>
@@ -37288,14 +37308,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K630" s="3" t="inlineStr"/>
+      <c r="K630" s="3" t="n"/>
       <c r="L630" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="631">
+    <row r="631" ht="16" customHeight="1">
       <c r="A631" s="3" t="n">
         <v>9</v>
       </c>
@@ -37344,14 +37364,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K631" s="3" t="inlineStr"/>
+      <c r="K631" s="3" t="n"/>
       <c r="L631" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="632">
+    <row r="632" ht="16" customHeight="1">
       <c r="A632" s="3" t="n">
         <v>10</v>
       </c>
@@ -37400,14 +37420,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K632" s="3" t="inlineStr"/>
+      <c r="K632" s="3" t="n"/>
       <c r="L632" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="633">
+    <row r="633" ht="16" customHeight="1">
       <c r="A633" s="3" t="n">
         <v>12</v>
       </c>
@@ -37451,15 +37471,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J633" s="4" t="inlineStr"/>
-      <c r="K633" s="3" t="inlineStr"/>
+      <c r="J633" s="4" t="n"/>
+      <c r="K633" s="3" t="n"/>
       <c r="L633" s="4" t="inlineStr">
         <is>
           <t>T6D24286</t>
         </is>
       </c>
     </row>
-    <row r="634">
+    <row r="634" ht="16" customHeight="1">
       <c r="A634" s="3" t="n">
         <v>3</v>
       </c>
@@ -37503,15 +37523,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J634" s="4" t="inlineStr"/>
-      <c r="K634" s="3" t="inlineStr"/>
+      <c r="J634" s="4" t="n"/>
+      <c r="K634" s="3" t="n"/>
       <c r="L634" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="635">
+    <row r="635" ht="16" customHeight="1">
       <c r="A635" s="3" t="n">
         <v>4</v>
       </c>
@@ -37555,15 +37575,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J635" s="4" t="inlineStr"/>
-      <c r="K635" s="3" t="inlineStr"/>
+      <c r="J635" s="4" t="n"/>
+      <c r="K635" s="3" t="n"/>
       <c r="L635" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="636">
+    <row r="636" ht="16" customHeight="1">
       <c r="A636" s="3" t="n">
         <v>5</v>
       </c>
@@ -37612,14 +37632,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K636" s="3" t="inlineStr"/>
+      <c r="K636" s="3" t="n"/>
       <c r="L636" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="637">
+    <row r="637" ht="16" customHeight="1">
       <c r="A637" s="3" t="n">
         <v>6</v>
       </c>
@@ -37668,14 +37688,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K637" s="3" t="inlineStr"/>
+      <c r="K637" s="3" t="n"/>
       <c r="L637" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="638">
+    <row r="638" ht="16" customHeight="1">
       <c r="A638" s="3" t="n">
         <v>7</v>
       </c>
@@ -37724,14 +37744,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K638" s="3" t="inlineStr"/>
+      <c r="K638" s="3" t="n"/>
       <c r="L638" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="639">
+    <row r="639" ht="16" customHeight="1">
       <c r="A639" s="3" t="n">
         <v>8</v>
       </c>
@@ -37780,14 +37800,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K639" s="3" t="inlineStr"/>
+      <c r="K639" s="3" t="n"/>
       <c r="L639" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="640">
+    <row r="640" ht="16" customHeight="1">
       <c r="A640" s="3" t="n">
         <v>9</v>
       </c>
@@ -37836,14 +37856,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K640" s="3" t="inlineStr"/>
+      <c r="K640" s="3" t="n"/>
       <c r="L640" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="641">
+    <row r="641" ht="16" customHeight="1">
       <c r="A641" s="3" t="n">
         <v>10</v>
       </c>
@@ -37892,14 +37912,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K641" s="3" t="inlineStr"/>
+      <c r="K641" s="3" t="n"/>
       <c r="L641" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="642">
+    <row r="642" ht="16" customHeight="1">
       <c r="A642" s="3" t="n">
         <v>12</v>
       </c>
@@ -37943,15 +37963,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J642" s="4" t="inlineStr"/>
-      <c r="K642" s="3" t="inlineStr"/>
+      <c r="J642" s="4" t="n"/>
+      <c r="K642" s="3" t="n"/>
       <c r="L642" s="4" t="inlineStr">
         <is>
           <t>T6D24286</t>
         </is>
       </c>
     </row>
-    <row r="643">
+    <row r="643" ht="16" customHeight="1">
       <c r="A643" s="3" t="n">
         <v>13</v>
       </c>
@@ -37995,15 +38015,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J643" s="4" t="inlineStr"/>
-      <c r="K643" s="3" t="inlineStr"/>
+      <c r="J643" s="4" t="n"/>
+      <c r="K643" s="3" t="n"/>
       <c r="L643" s="4" t="inlineStr">
         <is>
           <t>T6E60920</t>
         </is>
       </c>
     </row>
-    <row r="644">
+    <row r="644" ht="16" customHeight="1">
       <c r="A644" s="3" t="n">
         <v>14</v>
       </c>
@@ -38047,15 +38067,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J644" s="4" t="inlineStr"/>
-      <c r="K644" s="3" t="inlineStr"/>
+      <c r="J644" s="4" t="n"/>
+      <c r="K644" s="3" t="n"/>
       <c r="L644" s="4" t="inlineStr">
         <is>
           <t>T2D71946</t>
         </is>
       </c>
     </row>
-    <row r="645">
+    <row r="645" ht="16" customHeight="1">
       <c r="A645" s="3" t="n">
         <v>15</v>
       </c>
@@ -38099,15 +38119,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J645" s="4" t="inlineStr"/>
-      <c r="K645" s="3" t="inlineStr"/>
+      <c r="J645" s="4" t="n"/>
+      <c r="K645" s="3" t="n"/>
       <c r="L645" s="4" t="inlineStr">
         <is>
           <t>S6C68602</t>
         </is>
       </c>
     </row>
-    <row r="646">
+    <row r="646" ht="16" customHeight="1">
       <c r="A646" s="3" t="n">
         <v>16</v>
       </c>
@@ -38151,15 +38171,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J646" s="4" t="inlineStr"/>
-      <c r="K646" s="3" t="inlineStr"/>
+      <c r="J646" s="4" t="n"/>
+      <c r="K646" s="3" t="n"/>
       <c r="L646" s="4" t="inlineStr">
         <is>
           <t>T2E26985</t>
         </is>
       </c>
     </row>
-    <row r="647">
+    <row r="647" ht="16" customHeight="1">
       <c r="A647" s="3" t="n">
         <v>17</v>
       </c>
@@ -38208,14 +38228,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K647" s="3" t="inlineStr"/>
+      <c r="K647" s="3" t="n"/>
       <c r="L647" s="4" t="inlineStr">
         <is>
           <t>T6D67907</t>
         </is>
       </c>
     </row>
-    <row r="648">
+    <row r="648" ht="16" customHeight="1">
       <c r="A648" s="3" t="n">
         <v>18</v>
       </c>
@@ -38259,15 +38279,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J648" s="4" t="inlineStr"/>
-      <c r="K648" s="3" t="inlineStr"/>
+      <c r="J648" s="4" t="n"/>
+      <c r="K648" s="3" t="n"/>
       <c r="L648" s="4" t="inlineStr">
         <is>
           <t>T6E56913</t>
         </is>
       </c>
     </row>
-    <row r="649">
+    <row r="649" ht="16" customHeight="1">
       <c r="A649" s="3" t="n">
         <v>19</v>
       </c>
@@ -38316,14 +38336,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K649" s="3" t="inlineStr"/>
+      <c r="K649" s="3" t="n"/>
       <c r="L649" s="4" t="inlineStr">
         <is>
           <t>T6D69218</t>
         </is>
       </c>
     </row>
-    <row r="650">
+    <row r="650" ht="16" customHeight="1">
       <c r="A650" s="3" t="n">
         <v>3</v>
       </c>
@@ -38372,14 +38392,14 @@
           <t>Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K650" s="3" t="inlineStr"/>
+      <c r="K650" s="3" t="n"/>
       <c r="L650" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="651">
+    <row r="651" ht="16" customHeight="1">
       <c r="A651" s="3" t="n">
         <v>4</v>
       </c>
@@ -38428,14 +38448,14 @@
           <t>Invoice Validation Failed: Invoice customer name 'CHANDRASHEKHAR SAHU' does not match claim customer 'rohit gajendra'</t>
         </is>
       </c>
-      <c r="K651" s="3" t="inlineStr"/>
+      <c r="K651" s="3" t="n"/>
       <c r="L651" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="652">
+    <row r="652" ht="16" customHeight="1">
       <c r="A652" s="3" t="n">
         <v>5</v>
       </c>
@@ -38484,14 +38504,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K652" s="3" t="inlineStr"/>
+      <c r="K652" s="3" t="n"/>
       <c r="L652" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="653">
+    <row r="653" ht="16" customHeight="1">
       <c r="A653" s="3" t="n">
         <v>6</v>
       </c>
@@ -38540,14 +38560,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K653" s="3" t="inlineStr"/>
+      <c r="K653" s="3" t="n"/>
       <c r="L653" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="654">
+    <row r="654" ht="16" customHeight="1">
       <c r="A654" s="3" t="n">
         <v>7</v>
       </c>
@@ -38596,14 +38616,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K654" s="3" t="inlineStr"/>
+      <c r="K654" s="3" t="n"/>
       <c r="L654" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="655">
+    <row r="655" ht="16" customHeight="1">
       <c r="A655" s="3" t="n">
         <v>8</v>
       </c>
@@ -38652,14 +38672,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K655" s="3" t="inlineStr"/>
+      <c r="K655" s="3" t="n"/>
       <c r="L655" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="656">
+    <row r="656" ht="16" customHeight="1">
       <c r="A656" s="3" t="n">
         <v>9</v>
       </c>
@@ -38708,14 +38728,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K656" s="3" t="inlineStr"/>
+      <c r="K656" s="3" t="n"/>
       <c r="L656" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="657">
+    <row r="657" ht="16" customHeight="1">
       <c r="A657" s="3" t="n">
         <v>10</v>
       </c>
@@ -38764,14 +38784,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K657" s="3" t="inlineStr"/>
+      <c r="K657" s="3" t="n"/>
       <c r="L657" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="658">
+    <row r="658" ht="16" customHeight="1">
       <c r="A658" s="3" t="n">
         <v>3</v>
       </c>
@@ -38820,14 +38840,14 @@
           <t>Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K658" s="3" t="inlineStr"/>
+      <c r="K658" s="3" t="n"/>
       <c r="L658" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="659">
+    <row r="659" ht="16" customHeight="1">
       <c r="A659" s="3" t="n">
         <v>4</v>
       </c>
@@ -38876,14 +38896,14 @@
           <t>Invoice Validation Failed: Invoice customer name 'CHANDRASHEKHAR SAHU' does not match claim customer 'rohit gajendra'</t>
         </is>
       </c>
-      <c r="K659" s="3" t="inlineStr"/>
+      <c r="K659" s="3" t="n"/>
       <c r="L659" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="660">
+    <row r="660" ht="16" customHeight="1">
       <c r="A660" s="3" t="n">
         <v>5</v>
       </c>
@@ -38932,14 +38952,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K660" s="3" t="inlineStr"/>
+      <c r="K660" s="3" t="n"/>
       <c r="L660" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="661">
+    <row r="661" ht="16" customHeight="1">
       <c r="A661" s="3" t="n">
         <v>6</v>
       </c>
@@ -38989,14 +39009,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K661" s="3" t="inlineStr"/>
+      <c r="K661" s="3" t="n"/>
       <c r="L661" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="662">
+    <row r="662" ht="16" customHeight="1">
       <c r="A662" s="3" t="n">
         <v>3</v>
       </c>
@@ -39045,14 +39065,14 @@
           <t>Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K662" s="3" t="inlineStr"/>
+      <c r="K662" s="3" t="n"/>
       <c r="L662" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="663">
+    <row r="663" ht="16" customHeight="1">
       <c r="A663" s="3" t="n">
         <v>4</v>
       </c>
@@ -39101,14 +39121,14 @@
           <t>Invoice Validation Failed: Invoice customer name 'CHANDRASHEKHAR SAHU' does not match claim customer 'rohit gajendra'</t>
         </is>
       </c>
-      <c r="K663" s="3" t="inlineStr"/>
+      <c r="K663" s="3" t="n"/>
       <c r="L663" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="664">
+    <row r="664" ht="16" customHeight="1">
       <c r="A664" s="3" t="n">
         <v>5</v>
       </c>
@@ -39157,14 +39177,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K664" s="3" t="inlineStr"/>
+      <c r="K664" s="3" t="n"/>
       <c r="L664" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="665">
+    <row r="665" ht="16" customHeight="1">
       <c r="A665" s="3" t="n">
         <v>6</v>
       </c>
@@ -39213,14 +39233,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K665" s="3" t="inlineStr"/>
+      <c r="K665" s="3" t="n"/>
       <c r="L665" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="666">
+    <row r="666" ht="16" customHeight="1">
       <c r="A666" s="3" t="n">
         <v>7</v>
       </c>
@@ -39269,14 +39289,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K666" s="3" t="inlineStr"/>
+      <c r="K666" s="3" t="n"/>
       <c r="L666" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="667">
+    <row r="667" ht="16" customHeight="1">
       <c r="A667" s="3" t="n">
         <v>8</v>
       </c>
@@ -39325,14 +39345,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K667" s="3" t="inlineStr"/>
+      <c r="K667" s="3" t="n"/>
       <c r="L667" s="4" t="inlineStr">
         <is>
           <t>T6E58673</t>
         </is>
       </c>
     </row>
-    <row r="668">
+    <row r="668" ht="16" customHeight="1">
       <c r="A668" s="3" t="n">
         <v>9</v>
       </c>
@@ -39381,14 +39401,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K668" s="3" t="inlineStr"/>
+      <c r="K668" s="3" t="n"/>
       <c r="L668" s="4" t="inlineStr">
         <is>
           <t>R6L61743</t>
         </is>
       </c>
     </row>
-    <row r="669">
+    <row r="669" ht="16" customHeight="1">
       <c r="A669" s="3" t="n">
         <v>10</v>
       </c>
@@ -39437,14 +39457,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K669" s="3" t="inlineStr"/>
+      <c r="K669" s="3" t="n"/>
       <c r="L669" s="4" t="inlineStr">
         <is>
           <t>S2L23209</t>
         </is>
       </c>
     </row>
-    <row r="670">
+    <row r="670" ht="16" customHeight="1">
       <c r="A670" s="3" t="n">
         <v>3</v>
       </c>
@@ -39494,14 +39514,14 @@
 Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K670" s="3" t="inlineStr"/>
+      <c r="K670" s="3" t="n"/>
       <c r="L670" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="671">
+    <row r="671" ht="16" customHeight="1">
       <c r="A671" s="3" t="n">
         <v>4</v>
       </c>
@@ -39552,14 +39572,14 @@
 OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD20260520HR43B6163' does not match old vehicle chassis: 'COD20260520UP16Q3936'); New Chassis mismatch (Document Chassis: 'HR4386163' does not match last 8 digits of dashboard: 'T2D72269')</t>
         </is>
       </c>
-      <c r="K671" s="3" t="inlineStr"/>
+      <c r="K671" s="3" t="n"/>
       <c r="L671" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="672">
+    <row r="672" ht="16" customHeight="1">
       <c r="A672" s="3" t="n">
         <v>5</v>
       </c>
@@ -39610,14 +39630,14 @@
 Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K672" s="3" t="inlineStr"/>
+      <c r="K672" s="3" t="n"/>
       <c r="L672" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="673">
+    <row r="673" ht="16" customHeight="1">
       <c r="A673" s="3" t="n">
         <v>6</v>
       </c>
@@ -39668,14 +39688,14 @@
 Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K673" s="3" t="inlineStr"/>
+      <c r="K673" s="3" t="n"/>
       <c r="L673" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="674">
+    <row r="674" ht="16" customHeight="1">
       <c r="A674" s="3" t="n">
         <v>1</v>
       </c>
@@ -39727,14 +39747,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K674" s="3" t="inlineStr"/>
+      <c r="K674" s="3" t="n"/>
       <c r="L674" s="4" t="inlineStr">
         <is>
           <t>T2D18346</t>
         </is>
       </c>
     </row>
-    <row r="675">
+    <row r="675" ht="16" customHeight="1">
       <c r="A675" s="3" t="n">
         <v>2</v>
       </c>
@@ -39786,14 +39806,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K675" s="3" t="inlineStr"/>
+      <c r="K675" s="3" t="n"/>
       <c r="L675" s="4" t="inlineStr">
         <is>
           <t>T2E32959</t>
         </is>
       </c>
     </row>
-    <row r="676">
+    <row r="676" ht="16" customHeight="1">
       <c r="A676" s="3" t="n">
         <v>3</v>
       </c>
@@ -39845,14 +39865,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K676" s="3" t="inlineStr"/>
+      <c r="K676" s="3" t="n"/>
       <c r="L676" s="4" t="inlineStr">
         <is>
           <t>T5A19991</t>
         </is>
       </c>
     </row>
-    <row r="677">
+    <row r="677" ht="16" customHeight="1">
       <c r="A677" s="3" t="n">
         <v>4</v>
       </c>
@@ -39904,14 +39924,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K677" s="3" t="inlineStr"/>
+      <c r="K677" s="3" t="n"/>
       <c r="L677" s="4" t="inlineStr">
         <is>
           <t>T6E57252</t>
         </is>
       </c>
     </row>
-    <row r="678">
+    <row r="678" ht="16" customHeight="1">
       <c r="A678" s="3" t="n">
         <v>1</v>
       </c>
@@ -39964,14 +39984,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K678" s="3" t="inlineStr"/>
+      <c r="K678" s="3" t="n"/>
       <c r="L678" s="4" t="inlineStr">
         <is>
           <t>T2D18346</t>
         </is>
       </c>
     </row>
-    <row r="679">
+    <row r="679" ht="16" customHeight="1">
       <c r="A679" s="3" t="n">
         <v>2</v>
       </c>
@@ -40024,14 +40044,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K679" s="3" t="inlineStr"/>
+      <c r="K679" s="3" t="n"/>
       <c r="L679" s="4" t="inlineStr">
         <is>
           <t>T2E32959</t>
         </is>
       </c>
     </row>
-    <row r="680">
+    <row r="680" ht="16" customHeight="1">
       <c r="A680" s="3" t="n">
         <v>3</v>
       </c>
@@ -40084,14 +40104,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K680" s="3" t="inlineStr"/>
+      <c r="K680" s="3" t="n"/>
       <c r="L680" s="4" t="inlineStr">
         <is>
           <t>T5A19991</t>
         </is>
       </c>
     </row>
-    <row r="681">
+    <row r="681" ht="16" customHeight="1">
       <c r="A681" s="3" t="n">
         <v>4</v>
       </c>
@@ -40144,14 +40164,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K681" s="3" t="inlineStr"/>
+      <c r="K681" s="3" t="n"/>
       <c r="L681" s="4" t="inlineStr">
         <is>
           <t>T6E57252</t>
         </is>
       </c>
     </row>
-    <row r="682">
+    <row r="682" ht="16" customHeight="1">
       <c r="A682" s="3" t="n">
         <v>5</v>
       </c>
@@ -40204,14 +40224,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K682" s="3" t="inlineStr"/>
+      <c r="K682" s="3" t="n"/>
       <c r="L682" s="4" t="inlineStr">
         <is>
           <t>S2D13108</t>
         </is>
       </c>
     </row>
-    <row r="683">
+    <row r="683" ht="16" customHeight="1">
       <c r="A683" s="3" t="n">
         <v>6</v>
       </c>
@@ -40264,14 +40284,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K683" s="3" t="inlineStr"/>
+      <c r="K683" s="3" t="n"/>
       <c r="L683" s="4" t="inlineStr">
         <is>
           <t>T6E59092</t>
         </is>
       </c>
     </row>
-    <row r="684">
+    <row r="684" ht="16" customHeight="1">
       <c r="A684" s="3" t="n">
         <v>7</v>
       </c>
@@ -40324,14 +40344,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K684" s="3" t="inlineStr"/>
+      <c r="K684" s="3" t="n"/>
       <c r="L684" s="4" t="inlineStr">
         <is>
           <t>T6D66629</t>
         </is>
       </c>
     </row>
-    <row r="685">
+    <row r="685" ht="16" customHeight="1">
       <c r="A685" s="3" t="n">
         <v>8</v>
       </c>
@@ -40384,14 +40404,14 @@
 Missing Invoice Document</t>
         </is>
       </c>
-      <c r="K685" s="3" t="inlineStr"/>
+      <c r="K685" s="3" t="n"/>
       <c r="L685" s="4" t="inlineStr">
         <is>
           <t>T2E73684</t>
         </is>
       </c>
     </row>
-    <row r="686">
+    <row r="686" ht="16" customHeight="1">
       <c r="A686" s="3" t="n">
         <v>3</v>
       </c>
@@ -40442,14 +40462,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K686" s="3" t="inlineStr"/>
+      <c r="K686" s="3" t="n"/>
       <c r="L686" s="4" t="inlineStr">
         <is>
           <t>T2C48500</t>
         </is>
       </c>
     </row>
-    <row r="687">
+    <row r="687" ht="16" customHeight="1">
       <c r="A687" s="3" t="n">
         <v>4</v>
       </c>
@@ -40501,14 +40521,14 @@
 OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD20260520HR43B6163' does not match old vehicle chassis: 'COD20260520UP16Q3936'); New Chassis mismatch (Document Chassis: 'HR4386163' does not match last 8 digits of dashboard: 'T2D72269')</t>
         </is>
       </c>
-      <c r="K687" s="3" t="inlineStr"/>
+      <c r="K687" s="3" t="n"/>
       <c r="L687" s="4" t="inlineStr">
         <is>
           <t>T2D72269</t>
         </is>
       </c>
     </row>
-    <row r="688">
+    <row r="688" ht="16" customHeight="1">
       <c r="A688" s="3" t="n">
         <v>5</v>
       </c>
@@ -40560,14 +40580,14 @@
 Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K688" s="3" t="inlineStr"/>
+      <c r="K688" s="3" t="n"/>
       <c r="L688" s="4" t="inlineStr">
         <is>
           <t>T1E90124</t>
         </is>
       </c>
     </row>
-    <row r="689">
+    <row r="689" ht="16" customHeight="1">
       <c r="A689" s="3" t="n">
         <v>6</v>
       </c>
@@ -40619,14 +40639,14 @@
 Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K689" s="3" t="inlineStr"/>
+      <c r="K689" s="3" t="n"/>
       <c r="L689" s="4" t="inlineStr">
         <is>
           <t>T6E25145</t>
         </is>
       </c>
     </row>
-    <row r="690">
+    <row r="690" ht="16" customHeight="1">
       <c r="A690" s="3" t="n">
         <v>7</v>
       </c>
@@ -40678,14 +40698,14 @@
 Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K690" s="3" t="inlineStr"/>
+      <c r="K690" s="3" t="n"/>
       <c r="L690" s="4" t="inlineStr">
         <is>
           <t>T1D87625</t>
         </is>
       </c>
     </row>
-    <row r="691">
+    <row r="691" ht="16" customHeight="1">
       <c r="A691" s="3" t="n">
         <v>1</v>
       </c>
@@ -40737,14 +40757,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K691" s="3" t="inlineStr"/>
+      <c r="K691" s="3" t="n"/>
       <c r="L691" s="4" t="inlineStr">
         <is>
           <t>T2D18346</t>
         </is>
       </c>
     </row>
-    <row r="692">
+    <row r="692" ht="16" customHeight="1">
       <c r="A692" s="3" t="n">
         <v>2</v>
       </c>
@@ -40796,14 +40816,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K692" s="3" t="inlineStr"/>
+      <c r="K692" s="3" t="n"/>
       <c r="L692" s="4" t="inlineStr">
         <is>
           <t>T2E32959</t>
         </is>
       </c>
     </row>
-    <row r="693">
+    <row r="693" ht="16" customHeight="1">
       <c r="A693" s="3" t="n">
         <v>3</v>
       </c>
@@ -40857,14 +40877,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K693" s="3" t="inlineStr"/>
+      <c r="K693" s="3" t="n"/>
       <c r="L693" s="4" t="inlineStr">
         <is>
           <t>T5A19991</t>
         </is>
       </c>
     </row>
-    <row r="694">
+    <row r="694" ht="16" customHeight="1">
       <c r="A694" s="3" t="n">
         <v>4</v>
       </c>
@@ -40916,14 +40936,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K694" s="3" t="inlineStr"/>
+      <c r="K694" s="3" t="n"/>
       <c r="L694" s="4" t="inlineStr">
         <is>
           <t>T6E57252</t>
         </is>
       </c>
     </row>
-    <row r="695">
+    <row r="695" ht="16" customHeight="1">
       <c r="A695" s="3" t="n">
         <v>5</v>
       </c>
@@ -40977,14 +40997,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K695" s="3" t="inlineStr"/>
+      <c r="K695" s="3" t="n"/>
       <c r="L695" s="4" t="inlineStr">
         <is>
           <t>S2D13108</t>
         </is>
       </c>
     </row>
-    <row r="696">
+    <row r="696" ht="16" customHeight="1">
       <c r="A696" s="3" t="n">
         <v>6</v>
       </c>
@@ -41038,14 +41058,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K696" s="3" t="inlineStr"/>
+      <c r="K696" s="3" t="n"/>
       <c r="L696" s="4" t="inlineStr">
         <is>
           <t>T6E59092</t>
         </is>
       </c>
     </row>
-    <row r="697">
+    <row r="697" ht="16" customHeight="1">
       <c r="A697" s="3" t="n">
         <v>7</v>
       </c>
@@ -41097,14 +41117,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K697" s="3" t="inlineStr"/>
+      <c r="K697" s="3" t="n"/>
       <c r="L697" s="4" t="inlineStr">
         <is>
           <t>T6D66629</t>
         </is>
       </c>
     </row>
-    <row r="698">
+    <row r="698" ht="16" customHeight="1">
       <c r="A698" s="3" t="n">
         <v>8</v>
       </c>
@@ -41158,14 +41178,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K698" s="3" t="inlineStr"/>
+      <c r="K698" s="3" t="n"/>
       <c r="L698" s="4" t="inlineStr">
         <is>
           <t>T2E73684</t>
         </is>
       </c>
     </row>
-    <row r="699">
+    <row r="699" ht="16" customHeight="1">
       <c r="A699" s="3" t="n">
         <v>1</v>
       </c>
@@ -41215,14 +41235,14 @@
 Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
         </is>
       </c>
-      <c r="K699" s="3" t="inlineStr"/>
+      <c r="K699" s="3" t="n"/>
       <c r="L699" s="4" t="inlineStr">
         <is>
           <t>T2D18346</t>
         </is>
       </c>
     </row>
-    <row r="700">
+    <row r="700" ht="16" customHeight="1">
       <c r="A700" s="3" t="n">
         <v>2</v>
       </c>
@@ -41271,14 +41291,14 @@
           <t>Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
         </is>
       </c>
-      <c r="K700" s="3" t="inlineStr"/>
+      <c r="K700" s="3" t="n"/>
       <c r="L700" s="4" t="inlineStr">
         <is>
           <t>T2E32959</t>
         </is>
       </c>
     </row>
-    <row r="701">
+    <row r="701" ht="16" customHeight="1">
       <c r="A701" s="3" t="n">
         <v>3</v>
       </c>
@@ -41327,14 +41347,14 @@
           <t>Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
         </is>
       </c>
-      <c r="K701" s="3" t="inlineStr"/>
+      <c r="K701" s="3" t="n"/>
       <c r="L701" s="4" t="inlineStr">
         <is>
           <t>T5A19991</t>
         </is>
       </c>
     </row>
-    <row r="702">
+    <row r="702" ht="16" customHeight="1">
       <c r="A702" s="3" t="n">
         <v>4</v>
       </c>
@@ -41384,14 +41404,14 @@
 Invoice Validation Failed: Invoice customer name 'Dibyason Puhan' does not match claim customer 'dibyasom puhan'</t>
         </is>
       </c>
-      <c r="K702" s="3" t="inlineStr"/>
+      <c r="K702" s="3" t="n"/>
       <c r="L702" s="4" t="inlineStr">
         <is>
           <t>T6E57252</t>
         </is>
       </c>
     </row>
-    <row r="703">
+    <row r="703" ht="16" customHeight="1">
       <c r="A703" s="3" t="n">
         <v>5</v>
       </c>
@@ -41443,14 +41463,14 @@
 OEM Document Validation Failed: New Chassis mismatch (Document Chassis: 'MAT1YDYD6EJ656753' does not match last 8 digits of dashboard: 'S2D13108')</t>
         </is>
       </c>
-      <c r="K703" s="3" t="inlineStr"/>
+      <c r="K703" s="3" t="n"/>
       <c r="L703" s="4" t="inlineStr">
         <is>
           <t>S2D13108</t>
         </is>
       </c>
     </row>
-    <row r="704">
+    <row r="704" ht="16" customHeight="1">
       <c r="A704" s="3" t="n">
         <v>6</v>
       </c>
@@ -41501,14 +41521,14 @@
 Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'</t>
         </is>
       </c>
-      <c r="K704" s="3" t="inlineStr"/>
+      <c r="K704" s="3" t="n"/>
       <c r="L704" s="4" t="inlineStr">
         <is>
           <t>T6E59092</t>
         </is>
       </c>
     </row>
-    <row r="705">
+    <row r="705" ht="16" customHeight="1">
       <c r="A705" s="3" t="n">
         <v>7</v>
       </c>
@@ -41557,14 +41577,14 @@
           <t>Disclaimer Validation Failed: Disclaimer dealership name 'KRISHNA AUTOMOTIVE' does not match portal dealer '0'; Disclaimer new vehicle model does not match portal model group 'BOLERO NEO PLUS' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO NEO+ P10 WHITE, Chassis Number: T6D66629, Engine Number: YXT4D47059')</t>
         </is>
       </c>
-      <c r="K705" s="3" t="inlineStr"/>
+      <c r="K705" s="3" t="n"/>
       <c r="L705" s="4" t="inlineStr">
         <is>
           <t>T6D66629</t>
         </is>
       </c>
     </row>
-    <row r="706">
+    <row r="706" ht="16" customHeight="1">
       <c r="A706" s="3" t="n">
         <v>8</v>
       </c>
@@ -41616,14 +41636,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K706" s="3" t="inlineStr"/>
+      <c r="K706" s="3" t="n"/>
       <c r="L706" s="4" t="inlineStr">
         <is>
           <t>T2E73684</t>
         </is>
       </c>
     </row>
-    <row r="707">
+    <row r="707" ht="16" customHeight="1">
       <c r="A707" s="3" t="n">
         <v>16</v>
       </c>
@@ -41672,14 +41692,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K707" s="3" t="inlineStr"/>
+      <c r="K707" s="3" t="n"/>
       <c r="L707" s="4" t="inlineStr">
         <is>
           <t>T6E58112</t>
         </is>
       </c>
     </row>
-    <row r="708">
+    <row r="708" ht="16" customHeight="1">
       <c r="A708" s="3" t="n">
         <v>17</v>
       </c>
@@ -41728,14 +41748,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K708" s="3" t="inlineStr"/>
+      <c r="K708" s="3" t="n"/>
       <c r="L708" s="4" t="inlineStr">
         <is>
           <t>T6E60743</t>
         </is>
       </c>
     </row>
-    <row r="709">
+    <row r="709" ht="16" customHeight="1">
       <c r="A709" s="3" t="n">
         <v>18</v>
       </c>
@@ -41784,14 +41804,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K709" s="3" t="inlineStr"/>
+      <c r="K709" s="3" t="n"/>
       <c r="L709" s="4" t="inlineStr">
         <is>
           <t>T2E27528</t>
         </is>
       </c>
     </row>
-    <row r="710">
+    <row r="710" ht="16" customHeight="1">
       <c r="A710" s="3" t="n">
         <v>19</v>
       </c>
@@ -41841,14 +41861,14 @@
 Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K710" s="3" t="inlineStr"/>
+      <c r="K710" s="3" t="n"/>
       <c r="L710" s="4" t="inlineStr">
         <is>
           <t>T2C60084</t>
         </is>
       </c>
     </row>
-    <row r="711">
+    <row r="711" ht="16" customHeight="1">
       <c r="A711" s="3" t="n">
         <v>20</v>
       </c>
@@ -41897,14 +41917,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K711" s="3" t="inlineStr"/>
+      <c r="K711" s="3" t="n"/>
       <c r="L711" s="4" t="inlineStr">
         <is>
           <t>T2B30390</t>
         </is>
       </c>
     </row>
-    <row r="712">
+    <row r="712" ht="16" customHeight="1">
       <c r="A712" s="3" t="n">
         <v>16</v>
       </c>
@@ -41953,14 +41973,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K712" s="3" t="inlineStr"/>
+      <c r="K712" s="3" t="n"/>
       <c r="L712" s="4" t="inlineStr">
         <is>
           <t>T6E58112</t>
         </is>
       </c>
     </row>
-    <row r="713">
+    <row r="713" ht="16" customHeight="1">
       <c r="A713" s="3" t="n">
         <v>17</v>
       </c>
@@ -42009,14 +42029,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K713" s="3" t="inlineStr"/>
+      <c r="K713" s="3" t="n"/>
       <c r="L713" s="4" t="inlineStr">
         <is>
           <t>T6E60743</t>
         </is>
       </c>
     </row>
-    <row r="714">
+    <row r="714" ht="16" customHeight="1">
       <c r="A714" s="3" t="n">
         <v>18</v>
       </c>
@@ -42065,14 +42085,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K714" s="3" t="inlineStr"/>
+      <c r="K714" s="3" t="n"/>
       <c r="L714" s="4" t="inlineStr">
         <is>
           <t>T2E27528</t>
         </is>
       </c>
     </row>
-    <row r="715">
+    <row r="715" ht="16" customHeight="1">
       <c r="A715" s="3" t="n">
         <v>19</v>
       </c>
@@ -42122,14 +42142,14 @@
 Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K715" s="3" t="inlineStr"/>
+      <c r="K715" s="3" t="n"/>
       <c r="L715" s="4" t="inlineStr">
         <is>
           <t>T2C60084</t>
         </is>
       </c>
     </row>
-    <row r="716">
+    <row r="716" ht="16" customHeight="1">
       <c r="A716" s="3" t="n">
         <v>20</v>
       </c>
@@ -42178,14 +42198,14 @@
           <t>Missing Certificate of Deposit (COD/OEM) Document</t>
         </is>
       </c>
-      <c r="K716" s="3" t="inlineStr"/>
+      <c r="K716" s="3" t="n"/>
       <c r="L716" s="4" t="inlineStr">
         <is>
           <t>T2B30390</t>
         </is>
       </c>
     </row>
-    <row r="717">
+    <row r="717" ht="16" customHeight="1">
       <c r="A717" s="3" t="n">
         <v>30</v>
       </c>
@@ -42229,15 +42249,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J717" s="4" t="inlineStr"/>
-      <c r="K717" s="3" t="inlineStr"/>
+      <c r="J717" s="4" t="n"/>
+      <c r="K717" s="3" t="n"/>
       <c r="L717" s="4" t="inlineStr">
         <is>
           <t>T2D99858</t>
         </is>
       </c>
     </row>
-    <row r="718">
+    <row r="718" ht="16" customHeight="1">
       <c r="A718" s="3" t="n">
         <v>31</v>
       </c>
@@ -42281,15 +42301,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J718" s="4" t="inlineStr"/>
-      <c r="K718" s="3" t="inlineStr"/>
+      <c r="J718" s="4" t="n"/>
+      <c r="K718" s="3" t="n"/>
       <c r="L718" s="4" t="inlineStr">
         <is>
           <t>T2E73806</t>
         </is>
       </c>
     </row>
-    <row r="719">
+    <row r="719" ht="16" customHeight="1">
       <c r="A719" s="3" t="n">
         <v>32</v>
       </c>
@@ -42339,14 +42359,14 @@
 Missing Disclaimer Document</t>
         </is>
       </c>
-      <c r="K719" s="3" t="inlineStr"/>
+      <c r="K719" s="3" t="n"/>
       <c r="L719" s="4" t="inlineStr">
         <is>
           <t>T2D85723</t>
         </is>
       </c>
     </row>
-    <row r="720">
+    <row r="720" ht="16" customHeight="1">
       <c r="A720" s="3" t="n">
         <v>35</v>
       </c>
@@ -42395,14 +42415,14 @@
           <t>Missing Ledger Document</t>
         </is>
       </c>
-      <c r="K720" s="3" t="inlineStr"/>
+      <c r="K720" s="3" t="n"/>
       <c r="L720" s="4" t="inlineStr">
         <is>
           <t>T1D88570</t>
         </is>
       </c>
     </row>
-    <row r="721">
+    <row r="721" ht="16" customHeight="1">
       <c r="A721" s="3" t="n">
         <v>36</v>
       </c>
@@ -42446,15 +42466,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J721" s="4" t="inlineStr"/>
-      <c r="K721" s="3" t="inlineStr"/>
+      <c r="J721" s="4" t="n"/>
+      <c r="K721" s="3" t="n"/>
       <c r="L721" s="4" t="inlineStr">
         <is>
           <t>T2E27927</t>
         </is>
       </c>
     </row>
-    <row r="722">
+    <row r="722" ht="16" customHeight="1">
       <c r="A722" s="3" t="n">
         <v>1</v>
       </c>
@@ -42498,15 +42518,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J722" s="4" t="inlineStr"/>
-      <c r="K722" s="3" t="inlineStr"/>
+      <c r="J722" s="4" t="n"/>
+      <c r="K722" s="3" t="n"/>
       <c r="L722" s="4" t="inlineStr">
         <is>
           <t>T2D18346</t>
         </is>
       </c>
     </row>
-    <row r="723">
+    <row r="723" ht="16" customHeight="1">
       <c r="A723" s="3" t="n">
         <v>2</v>
       </c>
@@ -42550,15 +42570,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J723" s="4" t="inlineStr"/>
-      <c r="K723" s="3" t="inlineStr"/>
+      <c r="J723" s="4" t="n"/>
+      <c r="K723" s="3" t="n"/>
       <c r="L723" s="4" t="inlineStr">
         <is>
           <t>T2E32959</t>
         </is>
       </c>
     </row>
-    <row r="724">
+    <row r="724" ht="16" customHeight="1">
       <c r="A724" s="3" t="n">
         <v>3</v>
       </c>
@@ -42607,14 +42627,14 @@
           <t>COD Document Validation Failed: COD Certificate No 'COD20260530DL7CC6567' does not match expected old chassis 'COD20260530DL7CC5657'; COD Registration No 'DL7CC6567' does not match expected old vehicle registration 'DL7CC5657'</t>
         </is>
       </c>
-      <c r="K724" s="3" t="inlineStr"/>
+      <c r="K724" s="3" t="n"/>
       <c r="L724" s="4" t="inlineStr">
         <is>
           <t>T5A19991</t>
         </is>
       </c>
     </row>
-    <row r="725">
+    <row r="725" ht="16" customHeight="1">
       <c r="A725" s="3" t="n">
         <v>4</v>
       </c>
@@ -42658,15 +42678,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J725" s="4" t="inlineStr"/>
-      <c r="K725" s="3" t="inlineStr"/>
+      <c r="J725" s="4" t="n"/>
+      <c r="K725" s="3" t="n"/>
       <c r="L725" s="4" t="inlineStr">
         <is>
           <t>T6E57252</t>
         </is>
       </c>
     </row>
-    <row r="726">
+    <row r="726" ht="16" customHeight="1">
       <c r="A726" s="3" t="n">
         <v>5</v>
       </c>
@@ -42716,14 +42736,14 @@
 COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'</t>
         </is>
       </c>
-      <c r="K726" s="3" t="inlineStr"/>
+      <c r="K726" s="3" t="n"/>
       <c r="L726" s="4" t="inlineStr">
         <is>
           <t>S2D13108</t>
         </is>
       </c>
     </row>
-    <row r="727">
+    <row r="727" ht="16" customHeight="1">
       <c r="A727" s="3" t="n">
         <v>6</v>
       </c>
@@ -42773,14 +42793,14 @@
 COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'</t>
         </is>
       </c>
-      <c r="K727" s="3" t="inlineStr"/>
+      <c r="K727" s="3" t="n"/>
       <c r="L727" s="4" t="inlineStr">
         <is>
           <t>T6E59092</t>
         </is>
       </c>
     </row>
-    <row r="728">
+    <row r="728" ht="16" customHeight="1">
       <c r="A728" s="3" t="n">
         <v>7</v>
       </c>
@@ -42829,14 +42849,14 @@
           <t>Disclaimer Validation Failed: Disclaimer new vehicle model does not match portal model group 'BOLERO NEO PLUS' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO NEO+ P10 WHITE, Chassis Number: T6D66629, Engine Number: YXT4D47059')</t>
         </is>
       </c>
-      <c r="K728" s="3" t="inlineStr"/>
+      <c r="K728" s="3" t="n"/>
       <c r="L728" s="4" t="inlineStr">
         <is>
           <t>T6D66629</t>
         </is>
       </c>
     </row>
-    <row r="729">
+    <row r="729" ht="16" customHeight="1">
       <c r="A729" s="3" t="n">
         <v>8</v>
       </c>
@@ -42886,14 +42906,14 @@
 COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'</t>
         </is>
       </c>
-      <c r="K729" s="3" t="inlineStr"/>
+      <c r="K729" s="3" t="n"/>
       <c r="L729" s="4" t="inlineStr">
         <is>
           <t>T2E73684</t>
         </is>
       </c>
     </row>
-    <row r="730">
+    <row r="730" ht="16" customHeight="1">
       <c r="A730" s="3" t="n">
         <v>1</v>
       </c>
@@ -42937,15 +42957,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J730" s="4" t="inlineStr"/>
-      <c r="K730" s="3" t="inlineStr"/>
+      <c r="J730" s="4" t="n"/>
+      <c r="K730" s="3" t="n"/>
       <c r="L730" s="4" t="inlineStr">
         <is>
           <t>T2D18346</t>
         </is>
       </c>
     </row>
-    <row r="731">
+    <row r="731" ht="16" customHeight="1">
       <c r="A731" s="3" t="n">
         <v>2</v>
       </c>
@@ -42989,15 +43009,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J731" s="4" t="inlineStr"/>
-      <c r="K731" s="3" t="inlineStr"/>
+      <c r="J731" s="4" t="n"/>
+      <c r="K731" s="3" t="n"/>
       <c r="L731" s="4" t="inlineStr">
         <is>
           <t>T2E32959</t>
         </is>
       </c>
     </row>
-    <row r="732">
+    <row r="732" ht="16" customHeight="1">
       <c r="A732" s="3" t="n">
         <v>3</v>
       </c>
@@ -43041,15 +43061,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J732" s="4" t="inlineStr"/>
-      <c r="K732" s="3" t="inlineStr"/>
+      <c r="J732" s="4" t="n"/>
+      <c r="K732" s="3" t="n"/>
       <c r="L732" s="4" t="inlineStr">
         <is>
           <t>T5A19991</t>
         </is>
       </c>
     </row>
-    <row r="733">
+    <row r="733" ht="16" customHeight="1">
       <c r="A733" s="3" t="n">
         <v>4</v>
       </c>
@@ -43093,15 +43113,15 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="J733" s="4" t="inlineStr"/>
-      <c r="K733" s="3" t="inlineStr"/>
+      <c r="J733" s="4" t="n"/>
+      <c r="K733" s="3" t="n"/>
       <c r="L733" s="4" t="inlineStr">
         <is>
           <t>T6E57252</t>
         </is>
       </c>
     </row>
-    <row r="734">
+    <row r="734" ht="128" customHeight="1">
       <c r="A734" s="3" t="n">
         <v>5</v>
       </c>
@@ -43145,20 +43165,20 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J734" s="4" t="inlineStr">
+      <c r="J734" s="8" t="inlineStr">
         <is>
           <t>COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'
 COD Document Validation Failed: COD Certificate No 'COD20260520DL7CBB898' does not match expected old chassis 'COD20260520DL7CB8898'; COD Registration No 'DL7CBB898' does not match expected old vehicle registration 'DL7CB8898'</t>
         </is>
       </c>
-      <c r="K734" s="3" t="inlineStr"/>
+      <c r="K734" s="3" t="n"/>
       <c r="L734" s="4" t="inlineStr">
         <is>
           <t>S2D13108</t>
         </is>
       </c>
     </row>
-    <row r="735">
+    <row r="735" ht="128" customHeight="1">
       <c r="A735" s="3" t="n">
         <v>6</v>
       </c>
@@ -43202,20 +43222,20 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J735" s="4" t="inlineStr">
+      <c r="J735" s="8" t="inlineStr">
         <is>
           <t>COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'
 COD Document Validation Failed: COD Certificate No 'COD2025114UPB08RB8424' does not match expected old chassis 'COD2025114UP80BR8424'; COD Registration No 'UPB08RB8424' does not match expected old vehicle registration 'UP80BR8424'</t>
         </is>
       </c>
-      <c r="K735" s="3" t="inlineStr"/>
+      <c r="K735" s="3" t="n"/>
       <c r="L735" s="4" t="inlineStr">
         <is>
           <t>T6E59092</t>
         </is>
       </c>
     </row>
-    <row r="736">
+    <row r="736" ht="16" customHeight="1">
       <c r="A736" s="3" t="n">
         <v>7</v>
       </c>
@@ -43264,14 +43284,14 @@
           <t>Disclaimer Validation Failed: Disclaimer new vehicle model does not match portal model group 'BOLERO NEO PLUS' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO NEO+ P10 WHITE, Chassis Number: T6D66629, Engine Number: YXT4D47059')</t>
         </is>
       </c>
-      <c r="K736" s="3" t="inlineStr"/>
+      <c r="K736" s="3" t="n"/>
       <c r="L736" s="4" t="inlineStr">
         <is>
           <t>T6D66629</t>
         </is>
       </c>
     </row>
-    <row r="737">
+    <row r="737" ht="16" customHeight="1">
       <c r="A737" s="3" t="n">
         <v>8</v>
       </c>
@@ -43321,10 +43341,601 @@
 COD Document Validation Failed: COD Vehicle Make 'VOLKSWAGEN INDIA PVT LTD' does not match expected old vehicle make 'VolksWagon'</t>
         </is>
       </c>
-      <c r="K737" s="3" t="inlineStr"/>
+      <c r="K737" s="3" t="n"/>
       <c r="L737" s="4" t="inlineStr">
         <is>
           <t>T2E73684</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B738" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000357</t>
+        </is>
+      </c>
+      <c r="C738" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D738" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E738" s="4" t="inlineStr">
+        <is>
+          <t>Debasish Puthal</t>
+        </is>
+      </c>
+      <c r="F738" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G738" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H738" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I738" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J738" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: JSONDecodeError: OpenAI returned non-JSON text: I need to find the row matching either "COD2026053UP81CJ3167" or chassis containing "T2E27528".
+Loo...</t>
+        </is>
+      </c>
+      <c r="K738" s="3" t="inlineStr"/>
+      <c r="L738" s="4" t="inlineStr">
+        <is>
+          <t>T2E27528</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B739" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000357</t>
+        </is>
+      </c>
+      <c r="C739" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D739" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E739" s="4" t="inlineStr">
+        <is>
+          <t>Debasish Puthal</t>
+        </is>
+      </c>
+      <c r="F739" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G739" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H739" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I739" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J739" s="4" t="inlineStr"/>
+      <c r="K739" s="3" t="inlineStr"/>
+      <c r="L739" s="4" t="inlineStr">
+        <is>
+          <t>T2E27528</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B740" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000356</t>
+        </is>
+      </c>
+      <c r="C740" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D740" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E740" s="4" t="inlineStr">
+        <is>
+          <t>Bibhuti Bhusana Pradhan</t>
+        </is>
+      </c>
+      <c r="F740" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G740" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H740" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I740" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J740" s="4" t="inlineStr"/>
+      <c r="K740" s="3" t="inlineStr"/>
+      <c r="L740" s="4" t="inlineStr">
+        <is>
+          <t>T2C60084</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B741" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000354</t>
+        </is>
+      </c>
+      <c r="C741" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D741" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E741" s="4" t="inlineStr">
+        <is>
+          <t>Rashmirekha Biswal</t>
+        </is>
+      </c>
+      <c r="F741" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G741" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H741" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I741" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J741" s="4" t="inlineStr"/>
+      <c r="K741" s="3" t="inlineStr"/>
+      <c r="L741" s="4" t="inlineStr">
+        <is>
+          <t>T2B30390</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B742" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000053</t>
+        </is>
+      </c>
+      <c r="C742" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D742" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E742" s="4" t="inlineStr">
+        <is>
+          <t>Chandrashekhar Sahu</t>
+        </is>
+      </c>
+      <c r="F742" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G742" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H742" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I742" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J742" s="4" t="inlineStr"/>
+      <c r="K742" s="3" t="inlineStr"/>
+      <c r="L742" s="4" t="inlineStr">
+        <is>
+          <t>T6D23737</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B743" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000052</t>
+        </is>
+      </c>
+      <c r="C743" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D743" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E743" s="4" t="inlineStr">
+        <is>
+          <t>Birendra Kumar Netam</t>
+        </is>
+      </c>
+      <c r="F743" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G743" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H743" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I743" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J743" s="4" t="inlineStr"/>
+      <c r="K743" s="3" t="inlineStr"/>
+      <c r="L743" s="4" t="inlineStr">
+        <is>
+          <t>S6L23814</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B744" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000051</t>
+        </is>
+      </c>
+      <c r="C744" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D744" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E744" s="4" t="inlineStr">
+        <is>
+          <t>Ahmed Rameez Raza</t>
+        </is>
+      </c>
+      <c r="F744" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G744" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H744" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I744" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J744" s="4" t="inlineStr"/>
+      <c r="K744" s="3" t="inlineStr"/>
+      <c r="L744" s="4" t="inlineStr">
+        <is>
+          <t>T2A19904</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B745" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000050</t>
+        </is>
+      </c>
+      <c r="C745" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D745" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E745" s="4" t="inlineStr">
+        <is>
+          <t>Mohanish Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="F745" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G745" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H745" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I745" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J745" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Make 'MARUTI SUZUKI INDIA LTD' does not match expected old vehicle make 'Others'; COD Vehicle Model 'MARUTI 800 STD' does not match expected old vehicle model 'Others'
+COD Document Validation Failed: COD Vehicle Make 'MARUTI SUZUKI INDIA LTD' does not match expected old vehicle make 'Others'; COD Vehicle Model 'MARUTI 800 STD' does not match expected old vehicle model 'Others'</t>
+        </is>
+      </c>
+      <c r="K745" s="3" t="inlineStr"/>
+      <c r="L745" s="4" t="inlineStr">
+        <is>
+          <t>T2D86537</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B746" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000049</t>
+        </is>
+      </c>
+      <c r="C746" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D746" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E746" s="4" t="inlineStr">
+        <is>
+          <t>DINESH SONI</t>
+        </is>
+      </c>
+      <c r="F746" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G746" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H746" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I746" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J746" s="4" t="inlineStr"/>
+      <c r="K746" s="3" t="inlineStr"/>
+      <c r="L746" s="4" t="inlineStr">
+        <is>
+          <t>T6E56018</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B747" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000048</t>
+        </is>
+      </c>
+      <c r="C747" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D747" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E747" s="4" t="inlineStr">
+        <is>
+          <t>TILAK CHAND DEWANGAN</t>
+        </is>
+      </c>
+      <c r="F747" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G747" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H747" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I747" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J747" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Model 'TATA ECE' does not match expected old vehicle model 'Ace'</t>
+        </is>
+      </c>
+      <c r="K747" s="3" t="inlineStr"/>
+      <c r="L747" s="4" t="inlineStr">
+        <is>
+          <t>T1E91511</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B748" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000017</t>
+        </is>
+      </c>
+      <c r="C748" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D748" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E748" s="4" t="inlineStr">
+        <is>
+          <t>Mayank .</t>
+        </is>
+      </c>
+      <c r="F748" s="4" t="inlineStr">
+        <is>
+          <t>B R BALAJI LLP</t>
+        </is>
+      </c>
+      <c r="G748" s="4" t="inlineStr">
+        <is>
+          <t>JAGDALPUR</t>
+        </is>
+      </c>
+      <c r="H748" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I748" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J748" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Model 'ZEN MPI LX' does not match expected old vehicle model 'Zen lx'
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K748" s="3" t="inlineStr"/>
+      <c r="L748" s="4" t="inlineStr">
+        <is>
+          <t>T2D85723</t>
         </is>
       </c>
     </row>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L748"/>
+  <dimension ref="A1:L758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43939,6 +43939,550 @@
         </is>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B749" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000050</t>
+        </is>
+      </c>
+      <c r="C749" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D749" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E749" s="4" t="inlineStr">
+        <is>
+          <t>Mohanish Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="F749" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G749" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H749" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I749" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J749" s="4" t="inlineStr"/>
+      <c r="K749" s="3" t="inlineStr"/>
+      <c r="L749" s="4" t="inlineStr">
+        <is>
+          <t>T2D86537</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B750" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000049</t>
+        </is>
+      </c>
+      <c r="C750" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D750" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E750" s="4" t="inlineStr">
+        <is>
+          <t>DINESH SONI</t>
+        </is>
+      </c>
+      <c r="F750" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G750" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H750" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I750" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J750" s="4" t="inlineStr"/>
+      <c r="K750" s="3" t="inlineStr"/>
+      <c r="L750" s="4" t="inlineStr">
+        <is>
+          <t>T6E56018</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B751" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000048</t>
+        </is>
+      </c>
+      <c r="C751" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D751" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E751" s="4" t="inlineStr">
+        <is>
+          <t>TILAK CHAND DEWANGAN</t>
+        </is>
+      </c>
+      <c r="F751" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G751" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H751" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I751" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J751" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Model 'TATA ECE' does not match expected old vehicle model 'Ace'</t>
+        </is>
+      </c>
+      <c r="K751" s="3" t="inlineStr"/>
+      <c r="L751" s="4" t="inlineStr">
+        <is>
+          <t>T1E91511</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B752" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000017</t>
+        </is>
+      </c>
+      <c r="C752" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D752" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E752" s="4" t="inlineStr">
+        <is>
+          <t>Mayank .</t>
+        </is>
+      </c>
+      <c r="F752" s="4" t="inlineStr">
+        <is>
+          <t>B R BALAJI LLP</t>
+        </is>
+      </c>
+      <c r="G752" s="4" t="inlineStr">
+        <is>
+          <t>JAGDALPUR</t>
+        </is>
+      </c>
+      <c r="H752" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I752" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J752" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: COD Vehicle Model 'ZEN MPI LX' does not match expected old vehicle model 'Zen lx'
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K752" s="3" t="inlineStr"/>
+      <c r="L752" s="4" t="inlineStr">
+        <is>
+          <t>T2D85723</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B753" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000161</t>
+        </is>
+      </c>
+      <c r="C753" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D753" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E753" s="4" t="inlineStr">
+        <is>
+          <t>ANAND TULSIAN</t>
+        </is>
+      </c>
+      <c r="F753" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G753" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H753" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I753" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J753" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document</t>
+        </is>
+      </c>
+      <c r="K753" s="3" t="inlineStr"/>
+      <c r="L753" s="4" t="inlineStr">
+        <is>
+          <t>T1D88570</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B754" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000048</t>
+        </is>
+      </c>
+      <c r="C754" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D754" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E754" s="4" t="inlineStr">
+        <is>
+          <t>TILAK CHAND DEWANGAN</t>
+        </is>
+      </c>
+      <c r="F754" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G754" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H754" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I754" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J754" s="4" t="inlineStr"/>
+      <c r="K754" s="3" t="inlineStr"/>
+      <c r="L754" s="4" t="inlineStr">
+        <is>
+          <t>T1E91511</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B755" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000017</t>
+        </is>
+      </c>
+      <c r="C755" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D755" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E755" s="4" t="inlineStr">
+        <is>
+          <t>Mayank .</t>
+        </is>
+      </c>
+      <c r="F755" s="4" t="inlineStr">
+        <is>
+          <t>B R BALAJI LLP</t>
+        </is>
+      </c>
+      <c r="G755" s="4" t="inlineStr">
+        <is>
+          <t>JAGDALPUR</t>
+        </is>
+      </c>
+      <c r="H755" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I755" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J755" s="4" t="inlineStr">
+        <is>
+          <t>Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K755" s="3" t="inlineStr"/>
+      <c r="L755" s="4" t="inlineStr">
+        <is>
+          <t>T2D85723</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B756" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000161</t>
+        </is>
+      </c>
+      <c r="C756" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D756" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E756" s="4" t="inlineStr">
+        <is>
+          <t>ANAND TULSIAN</t>
+        </is>
+      </c>
+      <c r="F756" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G756" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H756" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I756" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J756" s="4" t="inlineStr"/>
+      <c r="K756" s="3" t="inlineStr"/>
+      <c r="L756" s="4" t="inlineStr">
+        <is>
+          <t>T1D88570</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B757" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000355</t>
+        </is>
+      </c>
+      <c r="C757" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D757" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E757" s="4" t="inlineStr">
+        <is>
+          <t>Rakesh Nigam</t>
+        </is>
+      </c>
+      <c r="F757" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G757" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H757" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I757" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J757" s="4" t="inlineStr"/>
+      <c r="K757" s="3" t="inlineStr"/>
+      <c r="L757" s="4" t="inlineStr">
+        <is>
+          <t>T2C48500</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B758" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C758" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D758" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E758" s="4" t="inlineStr">
+        <is>
+          <t>Rohit Gajendra</t>
+        </is>
+      </c>
+      <c r="F758" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G758" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H758" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I758" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J758" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer customer name 'Chandrashekhar Sahu' does not match claim customer 'Rohit Gajendra'; Disclaimer old vehicle registration number does not match portal registration 'UP16Q3936'; Disclaimer new vehicle chassis does not match claim chassis 'T2D72269' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO B6 BS-VI | Chassis Number: T6D23737 | Engine Number: TVT6D49262'); Disclaimer new vehicle model does not match portal model group 'XUV3XO' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO B6 BS-VI | Chassis Number: T6D23737 | Engine Number: TVT6D49262')
+Invoice Validation Failed: Invoice customer name 'CHANDRASHEKHAR SAHU' does not match claim customer 'Rohit Gajendra'
+OEM Document Validation Failed: New Chassis mismatch (Document Chassis: 'MA1XL2TVXT6D23737' does not match last 8 digits of dashboard: 'T2D72269')
+COD Document Validation Failed: COD Certificate No 'COD20260520HR43B6163' does not match expected old chassis 'COD20260520UP16Q3936'; Portal customer name 'Rohit Gajendra' not found from top to bottom in COD document (Extracted: 'CHANDRASHEKHAR SAHU'); COD Registration No 'HR43B6163' does not match expected old vehicle registration 'UP16Q3936'</t>
+        </is>
+      </c>
+      <c r="K758" s="3" t="inlineStr"/>
+      <c r="L758" s="4" t="inlineStr">
+        <is>
+          <t>T2D72269</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L758"/>
+  <dimension ref="A1:L796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44483,6 +44483,2096 @@
         </is>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B759" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000141</t>
+        </is>
+      </c>
+      <c r="C759" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D759" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E759" s="4" t="inlineStr">
+        <is>
+          <t>Arun Kumar Nayak</t>
+        </is>
+      </c>
+      <c r="F759" s="4" t="inlineStr">
+        <is>
+          <t>BASANTI AUTO AGENCY</t>
+        </is>
+      </c>
+      <c r="G759" s="4" t="inlineStr">
+        <is>
+          <t>BALASORE SALES</t>
+        </is>
+      </c>
+      <c r="H759" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I759" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J759" s="4" t="inlineStr"/>
+      <c r="K759" s="3" t="inlineStr"/>
+      <c r="L759" s="4" t="inlineStr">
+        <is>
+          <t>T6C56694</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B760" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000324</t>
+        </is>
+      </c>
+      <c r="C760" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D760" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E760" s="4" t="inlineStr">
+        <is>
+          <t>Bipin Khatua</t>
+        </is>
+      </c>
+      <c r="F760" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G760" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H760" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I760" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J760" s="4" t="inlineStr"/>
+      <c r="K760" s="3" t="inlineStr"/>
+      <c r="L760" s="4" t="inlineStr">
+        <is>
+          <t>T2D64783</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B761" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000057</t>
+        </is>
+      </c>
+      <c r="C761" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D761" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E761" s="4" t="inlineStr">
+        <is>
+          <t>Digambar Aamde</t>
+        </is>
+      </c>
+      <c r="F761" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G761" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H761" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I761" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J761" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: LLM Extraction Failed: JSONDecodeError: OpenAI returned non-JSON text: ```json
+{
+  "certificate_no": {
+    "text": "COD2026053UP32DP1313",
+    "line": 3,
+    "crop": {"top...</t>
+        </is>
+      </c>
+      <c r="K761" s="3" t="inlineStr"/>
+      <c r="L761" s="4" t="inlineStr">
+        <is>
+          <t>T6D24239</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B762" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000057</t>
+        </is>
+      </c>
+      <c r="C762" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D762" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E762" s="4" t="inlineStr">
+        <is>
+          <t>Digambar Aamde</t>
+        </is>
+      </c>
+      <c r="F762" s="4" t="inlineStr">
+        <is>
+          <t>SHIVNATH MOTORS (I) PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G762" s="4" t="inlineStr">
+        <is>
+          <t>LABHANDIH_3S</t>
+        </is>
+      </c>
+      <c r="H762" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I762" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J762" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: LLM Extraction Failed: JSONDecodeError: OpenAI returned non-JSON text: ```json
+{
+  "certificate_no": {
+    "text": "COD2026053UP32DP1313",
+    "line": 3,
+    "crop": {"top...</t>
+        </is>
+      </c>
+      <c r="K762" s="3" t="inlineStr"/>
+      <c r="L762" s="4" t="inlineStr">
+        <is>
+          <t>T6D24239</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B763" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000150</t>
+        </is>
+      </c>
+      <c r="C763" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D763" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E763" s="4" t="inlineStr">
+        <is>
+          <t>Anish Das</t>
+        </is>
+      </c>
+      <c r="F763" s="4" t="inlineStr">
+        <is>
+          <t>G N AUTONATION LLP</t>
+        </is>
+      </c>
+      <c r="G763" s="4" t="inlineStr">
+        <is>
+          <t>NEW_SAMBALPUR</t>
+        </is>
+      </c>
+      <c r="H763" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I763" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J763" s="4" t="inlineStr">
+        <is>
+          <t>COD Document Validation Failed: LLM Extraction Failed: JSONDecodeError: OpenAI returned non-JSON text: ```json
+{
+  "certificate_no": {
+    "text": "COD2026052GJ09BB1378",
+    "line": 3,
+    "crop": {"top...</t>
+        </is>
+      </c>
+      <c r="K763" s="3" t="inlineStr"/>
+      <c r="L763" s="4" t="inlineStr">
+        <is>
+          <t>T2D22457</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B764" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000141</t>
+        </is>
+      </c>
+      <c r="C764" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D764" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E764" s="4" t="inlineStr">
+        <is>
+          <t>Arun Kumar Nayak</t>
+        </is>
+      </c>
+      <c r="F764" s="4" t="inlineStr">
+        <is>
+          <t>BASANTI AUTO AGENCY</t>
+        </is>
+      </c>
+      <c r="G764" s="4" t="inlineStr">
+        <is>
+          <t>BALASORE SALES</t>
+        </is>
+      </c>
+      <c r="H764" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I764" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J764" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document
+Missing Invoice Document
+Missing Certificate of Deposit (COD/OEM) Document
+Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K764" s="3" t="inlineStr"/>
+      <c r="L764" s="4" t="inlineStr">
+        <is>
+          <t>T6C56694</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B765" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000315</t>
+        </is>
+      </c>
+      <c r="C765" s="4" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D765" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E765" s="4" t="inlineStr">
+        <is>
+          <t>PRASANNA KUMAR MAHARANA</t>
+        </is>
+      </c>
+      <c r="F765" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G765" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H765" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I765" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J765" s="4" t="inlineStr"/>
+      <c r="K765" s="3" t="inlineStr"/>
+      <c r="L765" s="4" t="inlineStr">
+        <is>
+          <t>T5E15967</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B766" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000217</t>
+        </is>
+      </c>
+      <c r="C766" s="4" t="inlineStr">
+        <is>
+          <t>22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D766" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E766" s="4" t="inlineStr">
+        <is>
+          <t>Deekeshwar .</t>
+        </is>
+      </c>
+      <c r="F766" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CENTRE</t>
+        </is>
+      </c>
+      <c r="G766" s="4" t="inlineStr">
+        <is>
+          <t>BILASPUR</t>
+        </is>
+      </c>
+      <c r="H766" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I766" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J766" s="4" t="inlineStr">
+        <is>
+          <t>Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K766" s="3" t="inlineStr"/>
+      <c r="L766" s="4" t="inlineStr">
+        <is>
+          <t>T2D85914</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B767" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000217</t>
+        </is>
+      </c>
+      <c r="C767" s="4" t="inlineStr">
+        <is>
+          <t>22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D767" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E767" s="4" t="inlineStr">
+        <is>
+          <t>Deekeshwar .</t>
+        </is>
+      </c>
+      <c r="F767" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CENTRE</t>
+        </is>
+      </c>
+      <c r="G767" s="4" t="inlineStr">
+        <is>
+          <t>BILASPUR</t>
+        </is>
+      </c>
+      <c r="H767" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I767" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J767" s="4" t="inlineStr">
+        <is>
+          <t>Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K767" s="3" t="inlineStr"/>
+      <c r="L767" s="4" t="inlineStr">
+        <is>
+          <t>T2D85914</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B768" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000217</t>
+        </is>
+      </c>
+      <c r="C768" s="4" t="inlineStr">
+        <is>
+          <t>22 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D768" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E768" s="4" t="inlineStr">
+        <is>
+          <t>Deekeshwar .</t>
+        </is>
+      </c>
+      <c r="F768" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CENTRE</t>
+        </is>
+      </c>
+      <c r="G768" s="4" t="inlineStr">
+        <is>
+          <t>BILASPUR</t>
+        </is>
+      </c>
+      <c r="H768" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I768" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J768" s="4" t="inlineStr"/>
+      <c r="K768" s="3" t="inlineStr"/>
+      <c r="L768" s="4" t="inlineStr">
+        <is>
+          <t>T2D85914</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B769" s="4" t="inlineStr">
+        <is>
+          <t>LYL27O000011</t>
+        </is>
+      </c>
+      <c r="C769" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D769" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E769" s="4" t="inlineStr">
+        <is>
+          <t>Smruti Ranjan Jena</t>
+        </is>
+      </c>
+      <c r="F769" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G769" s="4" t="inlineStr">
+        <is>
+          <t>CSA_SEC_10_SH</t>
+        </is>
+      </c>
+      <c r="H769" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I769" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J769" s="4" t="inlineStr"/>
+      <c r="K769" s="3" t="inlineStr"/>
+      <c r="L769" s="4" t="inlineStr">
+        <is>
+          <t>T2F94074</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B770" s="4" t="inlineStr">
+        <is>
+          <t>LYL27O000010</t>
+        </is>
+      </c>
+      <c r="C770" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D770" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E770" s="4" t="inlineStr">
+        <is>
+          <t>Lasit Baran Mohanty</t>
+        </is>
+      </c>
+      <c r="F770" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G770" s="4" t="inlineStr">
+        <is>
+          <t>CSA_SEC_10_SH</t>
+        </is>
+      </c>
+      <c r="H770" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I770" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J770" s="4" t="inlineStr"/>
+      <c r="K770" s="3" t="inlineStr"/>
+      <c r="L770" s="4" t="inlineStr">
+        <is>
+          <t>T2E36703</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B771" s="4" t="inlineStr">
+        <is>
+          <t>LYL27M000005</t>
+        </is>
+      </c>
+      <c r="C771" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D771" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E771" s="4" t="inlineStr">
+        <is>
+          <t>Gourisankar Sahoo</t>
+        </is>
+      </c>
+      <c r="F771" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G771" s="4" t="inlineStr">
+        <is>
+          <t>CUBE_UNIT3</t>
+        </is>
+      </c>
+      <c r="H771" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I771" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J771" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Customer signature is MISSING on the invoice</t>
+        </is>
+      </c>
+      <c r="K771" s="3" t="inlineStr"/>
+      <c r="L771" s="4" t="inlineStr">
+        <is>
+          <t>T6E59687</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B772" s="4" t="inlineStr">
+        <is>
+          <t>LYL27M000004</t>
+        </is>
+      </c>
+      <c r="C772" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D772" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E772" s="4" t="inlineStr">
+        <is>
+          <t>SNEHALATA BEHERA</t>
+        </is>
+      </c>
+      <c r="F772" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G772" s="4" t="inlineStr">
+        <is>
+          <t>CUBE_UNIT3</t>
+        </is>
+      </c>
+      <c r="H772" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I772" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J772" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Customer signature is MISSING on the invoice</t>
+        </is>
+      </c>
+      <c r="K772" s="3" t="inlineStr"/>
+      <c r="L772" s="4" t="inlineStr">
+        <is>
+          <t>T2D22078</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B773" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000072</t>
+        </is>
+      </c>
+      <c r="C773" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D773" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E773" s="4" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR MALLIK</t>
+        </is>
+      </c>
+      <c r="F773" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G773" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H773" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I773" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J773" s="4" t="inlineStr"/>
+      <c r="K773" s="3" t="inlineStr"/>
+      <c r="L773" s="4" t="inlineStr">
+        <is>
+          <t>T2E92976</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B774" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000071</t>
+        </is>
+      </c>
+      <c r="C774" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D774" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E774" s="4" t="inlineStr">
+        <is>
+          <t>JAYARAM TRIPATHY</t>
+        </is>
+      </c>
+      <c r="F774" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G774" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H774" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I774" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J774" s="4" t="inlineStr"/>
+      <c r="K774" s="3" t="inlineStr"/>
+      <c r="L774" s="4" t="inlineStr">
+        <is>
+          <t>T2F93697</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B775" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000070</t>
+        </is>
+      </c>
+      <c r="C775" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D775" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E775" s="4" t="inlineStr">
+        <is>
+          <t>Sankarsan Mohapatra</t>
+        </is>
+      </c>
+      <c r="F775" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G775" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H775" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I775" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J775" s="4" t="inlineStr"/>
+      <c r="K775" s="3" t="inlineStr"/>
+      <c r="L775" s="4" t="inlineStr">
+        <is>
+          <t>T2E31081</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B776" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000069</t>
+        </is>
+      </c>
+      <c r="C776" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D776" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E776" s="4" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Mohanty</t>
+        </is>
+      </c>
+      <c r="F776" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G776" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H776" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I776" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J776" s="4" t="inlineStr"/>
+      <c r="K776" s="3" t="inlineStr"/>
+      <c r="L776" s="4" t="inlineStr">
+        <is>
+          <t>T2F80929</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B777" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000068</t>
+        </is>
+      </c>
+      <c r="C777" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D777" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E777" s="4" t="inlineStr">
+        <is>
+          <t>Susanta Kumar Nayak</t>
+        </is>
+      </c>
+      <c r="F777" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G777" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H777" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I777" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J777" s="4" t="inlineStr"/>
+      <c r="K777" s="3" t="inlineStr"/>
+      <c r="L777" s="4" t="inlineStr">
+        <is>
+          <t>T2E37368</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B778" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000067</t>
+        </is>
+      </c>
+      <c r="C778" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D778" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E778" s="4" t="inlineStr">
+        <is>
+          <t>Sasmita Panda</t>
+        </is>
+      </c>
+      <c r="F778" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G778" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H778" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I778" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J778" s="4" t="inlineStr"/>
+      <c r="K778" s="3" t="inlineStr"/>
+      <c r="L778" s="4" t="inlineStr">
+        <is>
+          <t>T2A22489</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B779" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000066</t>
+        </is>
+      </c>
+      <c r="C779" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D779" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E779" s="4" t="inlineStr">
+        <is>
+          <t>ALOK KUMAR PRUSTI</t>
+        </is>
+      </c>
+      <c r="F779" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G779" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H779" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I779" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J779" s="4" t="inlineStr"/>
+      <c r="K779" s="3" t="inlineStr"/>
+      <c r="L779" s="4" t="inlineStr">
+        <is>
+          <t>T2A19531</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B780" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000065</t>
+        </is>
+      </c>
+      <c r="C780" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D780" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E780" s="4" t="inlineStr">
+        <is>
+          <t>SUJATA SAMAL</t>
+        </is>
+      </c>
+      <c r="F780" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G780" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H780" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I780" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J780" s="4" t="inlineStr"/>
+      <c r="K780" s="3" t="inlineStr"/>
+      <c r="L780" s="4" t="inlineStr">
+        <is>
+          <t>T6B68528</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B781" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000064</t>
+        </is>
+      </c>
+      <c r="C781" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D781" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E781" s="4" t="inlineStr">
+        <is>
+          <t>Abhisek Dixit</t>
+        </is>
+      </c>
+      <c r="F781" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G781" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H781" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I781" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J781" s="4" t="inlineStr"/>
+      <c r="K781" s="3" t="inlineStr"/>
+      <c r="L781" s="4" t="inlineStr">
+        <is>
+          <t>T2B34302</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B782" s="4" t="inlineStr">
+        <is>
+          <t>LYL27M000004</t>
+        </is>
+      </c>
+      <c r="C782" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D782" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E782" s="4" t="inlineStr">
+        <is>
+          <t>SNEHALATA BEHERA</t>
+        </is>
+      </c>
+      <c r="F782" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G782" s="4" t="inlineStr">
+        <is>
+          <t>CUBE_UNIT3</t>
+        </is>
+      </c>
+      <c r="H782" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I782" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J782" s="4" t="inlineStr"/>
+      <c r="K782" s="3" t="inlineStr"/>
+      <c r="L782" s="4" t="inlineStr">
+        <is>
+          <t>T2D22078</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B783" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000072</t>
+        </is>
+      </c>
+      <c r="C783" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D783" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E783" s="4" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR MALLIK</t>
+        </is>
+      </c>
+      <c r="F783" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G783" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H783" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I783" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J783" s="4" t="inlineStr"/>
+      <c r="K783" s="3" t="inlineStr"/>
+      <c r="L783" s="4" t="inlineStr">
+        <is>
+          <t>T2E92976</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B784" s="4" t="inlineStr">
+        <is>
+          <t>LYL27M000004</t>
+        </is>
+      </c>
+      <c r="C784" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D784" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E784" s="4" t="inlineStr">
+        <is>
+          <t>SNEHALATA BEHERA</t>
+        </is>
+      </c>
+      <c r="F784" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G784" s="4" t="inlineStr">
+        <is>
+          <t>CUBE_UNIT3</t>
+        </is>
+      </c>
+      <c r="H784" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I784" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J784" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: No authorised signature found on/near dealer stamp, and no 'Digitally Signed' indication present
+OEM Document Validation Failed: New Chassis mismatch (Document Chassis: 'MAT626429FZC48514' does not match last 8 digits of dashboard: 'T2D22078')</t>
+        </is>
+      </c>
+      <c r="K784" s="3" t="inlineStr"/>
+      <c r="L784" s="4" t="inlineStr">
+        <is>
+          <t>T2D22078</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B785" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000072</t>
+        </is>
+      </c>
+      <c r="C785" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D785" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E785" s="4" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR MALLIK</t>
+        </is>
+      </c>
+      <c r="F785" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G785" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H785" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I785" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J785" s="4" t="inlineStr"/>
+      <c r="K785" s="3" t="inlineStr"/>
+      <c r="L785" s="4" t="inlineStr">
+        <is>
+          <t>T2E92976</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B786" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000071</t>
+        </is>
+      </c>
+      <c r="C786" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D786" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E786" s="4" t="inlineStr">
+        <is>
+          <t>JAYARAM TRIPATHY</t>
+        </is>
+      </c>
+      <c r="F786" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G786" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H786" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I786" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J786" s="4" t="inlineStr"/>
+      <c r="K786" s="3" t="inlineStr"/>
+      <c r="L786" s="4" t="inlineStr">
+        <is>
+          <t>T2F93697</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B787" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000070</t>
+        </is>
+      </c>
+      <c r="C787" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D787" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E787" s="4" t="inlineStr">
+        <is>
+          <t>Sankarsan Mohapatra</t>
+        </is>
+      </c>
+      <c r="F787" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G787" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H787" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I787" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J787" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: No authorised signature found on/near dealer stamp, and no 'Digitally Signed' indication present</t>
+        </is>
+      </c>
+      <c r="K787" s="3" t="inlineStr"/>
+      <c r="L787" s="4" t="inlineStr">
+        <is>
+          <t>T2E31081</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B788" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000069</t>
+        </is>
+      </c>
+      <c r="C788" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D788" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E788" s="4" t="inlineStr">
+        <is>
+          <t>Sunil Kumar Mohanty</t>
+        </is>
+      </c>
+      <c r="F788" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G788" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H788" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I788" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J788" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: No authorised signature found on/near dealer stamp, and no 'Digitally Signed' indication present</t>
+        </is>
+      </c>
+      <c r="K788" s="3" t="inlineStr"/>
+      <c r="L788" s="4" t="inlineStr">
+        <is>
+          <t>T2F80929</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B789" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000068</t>
+        </is>
+      </c>
+      <c r="C789" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D789" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E789" s="4" t="inlineStr">
+        <is>
+          <t>Susanta Kumar Nayak</t>
+        </is>
+      </c>
+      <c r="F789" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G789" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H789" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I789" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J789" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: No authorised signature found on/near dealer stamp, and no 'Digitally Signed' indication present</t>
+        </is>
+      </c>
+      <c r="K789" s="3" t="inlineStr"/>
+      <c r="L789" s="4" t="inlineStr">
+        <is>
+          <t>T2E37368</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B790" s="4" t="inlineStr">
+        <is>
+          <t>LYL27M000005</t>
+        </is>
+      </c>
+      <c r="C790" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D790" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E790" s="4" t="inlineStr">
+        <is>
+          <t>Gourisankar Sahoo</t>
+        </is>
+      </c>
+      <c r="F790" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G790" s="4" t="inlineStr">
+        <is>
+          <t>CUBE_UNIT3</t>
+        </is>
+      </c>
+      <c r="H790" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I790" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J790" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: LLM Extraction Failed
+Invoice Validation Failed: LLM Extraction Failed
+Ledger Validation Failed: LLM Extraction Failed
+OEM Document Validation Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K790" s="3" t="inlineStr"/>
+      <c r="L790" s="4" t="inlineStr">
+        <is>
+          <t>T6E59687</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B791" s="4" t="inlineStr">
+        <is>
+          <t>LYL27M000004</t>
+        </is>
+      </c>
+      <c r="C791" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D791" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E791" s="4" t="inlineStr">
+        <is>
+          <t>SNEHALATA BEHERA</t>
+        </is>
+      </c>
+      <c r="F791" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G791" s="4" t="inlineStr">
+        <is>
+          <t>CUBE_UNIT3</t>
+        </is>
+      </c>
+      <c r="H791" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I791" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J791" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: LLM Extraction Failed
+Invoice Validation Failed: LLM Extraction Failed
+Ledger Validation Failed: LLM Extraction Failed
+OEM Document Validation Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K791" s="3" t="inlineStr"/>
+      <c r="L791" s="4" t="inlineStr">
+        <is>
+          <t>T2D22078</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B792" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000072</t>
+        </is>
+      </c>
+      <c r="C792" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D792" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E792" s="4" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR MALLIK</t>
+        </is>
+      </c>
+      <c r="F792" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G792" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H792" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I792" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J792" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: LLM Extraction Failed
+Invoice Validation Failed: LLM Extraction Failed
+Ledger Validation Failed: LLM Extraction Failed
+OEM Document Validation Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K792" s="3" t="inlineStr"/>
+      <c r="L792" s="4" t="inlineStr">
+        <is>
+          <t>T2E92976</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B793" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000071</t>
+        </is>
+      </c>
+      <c r="C793" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D793" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E793" s="4" t="inlineStr">
+        <is>
+          <t>JAYARAM TRIPATHY</t>
+        </is>
+      </c>
+      <c r="F793" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G793" s="4" t="inlineStr">
+        <is>
+          <t>MANCHESWAR FULLRANGE SR NPAHAL WS 2ND FL</t>
+        </is>
+      </c>
+      <c r="H793" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I793" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J793" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: LLM Extraction Failed
+Invoice Validation Failed: LLM Extraction Failed
+Ledger Validation Failed: LLM Extraction Failed
+OEM Document Validation Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions
+COD Document Validation Failed: LLM Extraction Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.openai.com/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="K793" s="3" t="inlineStr"/>
+      <c r="L793" s="4" t="inlineStr">
+        <is>
+          <t>T2F93697</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B794" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C794" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D794" s="4" t="inlineStr">
+        <is>
+          <t>AD Raipur</t>
+        </is>
+      </c>
+      <c r="E794" s="4" t="inlineStr">
+        <is>
+          <t>Rohit Gajendra</t>
+        </is>
+      </c>
+      <c r="F794" s="4" t="inlineStr">
+        <is>
+          <t>RALAS AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G794" s="4" t="inlineStr">
+        <is>
+          <t>DHAMTARI</t>
+        </is>
+      </c>
+      <c r="H794" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I794" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J794" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Disclaimer customer name 'Chandrashekhar Sahu' does not match claim customer 'Rohit Gajendra'; Disclaimer old vehicle registration number does not match portal registration 'UP16Q3936'; Disclaimer new vehicle chassis does not match claim chassis 'T2D72269' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO B6 BS-VI | Chassis Number: T6D23737 | Engine Number: TVT6D49262'); Disclaimer new vehicle model does not match portal model group 'XUV3XO' (Extracted: 'New Vehicle Model: MAHINDRA BOLERO B6 BS-VI | Chassis Number: T6D23737 | Engine Number: TVT6D49262')
+Invoice Validation Failed: Invoice customer name 'CHANDRASHEKHAR SAHU' does not match claim customer 'Rohit Gajendra'
+OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD20260520HR43B6163' does not match old vehicle chassis: 'COD20260520UP16Q3936'); New Chassis mismatch (Document Chassis: 'MA1XL2TVXT6D23737' does not match last 8 digits of dashboard: 'T2D72269')
+COD Document Validation Failed: COD Certificate No 'COD20260520HR43B6163' does not match expected old chassis 'COD20260520UP16Q3936'; Portal customer name 'Rohit Gajendra' not found from top to bottom in COD document (Extracted: 'CHANDRASHEKHAR SAHU'); COD Registration No 'HR43B6163' does not match expected old vehicle registration 'UP16Q3936'</t>
+        </is>
+      </c>
+      <c r="K794" s="3" t="inlineStr"/>
+      <c r="L794" s="4" t="inlineStr">
+        <is>
+          <t>T2D72269</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B795" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000069</t>
+        </is>
+      </c>
+      <c r="C795" s="4" t="inlineStr">
+        <is>
+          <t>08 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D795" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E795" s="4" t="inlineStr">
+        <is>
+          <t>Ajit Majumdar</t>
+        </is>
+      </c>
+      <c r="F795" s="4" t="inlineStr">
+        <is>
+          <t>PODDAR AUTOCORP PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G795" s="4" t="inlineStr">
+        <is>
+          <t>GUWAHATI 3S</t>
+        </is>
+      </c>
+      <c r="H795" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I795" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J795" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'AS01GU7475' does not match old vehicle registration: 'AS01AD1927')</t>
+        </is>
+      </c>
+      <c r="K795" s="3" t="inlineStr"/>
+      <c r="L795" s="4" t="inlineStr">
+        <is>
+          <t>T2E91998</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B796" s="4" t="inlineStr">
+        <is>
+          <t>LYL27O000011</t>
+        </is>
+      </c>
+      <c r="C796" s="4" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D796" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E796" s="4" t="inlineStr">
+        <is>
+          <t>Smruti Ranjan Jena</t>
+        </is>
+      </c>
+      <c r="F796" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G796" s="4" t="inlineStr">
+        <is>
+          <t>CSA_SEC_10_SH</t>
+        </is>
+      </c>
+      <c r="H796" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I796" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J796" s="4" t="inlineStr"/>
+      <c r="K796" s="3" t="inlineStr"/>
+      <c r="L796" s="4" t="inlineStr">
+        <is>
+          <t>T2F94074</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L796"/>
+  <dimension ref="A1:L800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46573,6 +46573,228 @@
         </is>
       </c>
     </row>
+    <row r="797">
+      <c r="A797" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B797" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000069</t>
+        </is>
+      </c>
+      <c r="C797" s="4" t="inlineStr">
+        <is>
+          <t>08 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D797" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E797" s="4" t="inlineStr">
+        <is>
+          <t>Ajit Majumdar</t>
+        </is>
+      </c>
+      <c r="F797" s="4" t="inlineStr">
+        <is>
+          <t>PODDAR AUTOCORP PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G797" s="4" t="inlineStr">
+        <is>
+          <t>GUWAHATI 3S</t>
+        </is>
+      </c>
+      <c r="H797" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I797" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J797" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'COD20250034S01AD1927' does not match old vehicle registration: 'AS01AD1927')</t>
+        </is>
+      </c>
+      <c r="K797" s="3" t="inlineStr"/>
+      <c r="L797" s="4" t="inlineStr">
+        <is>
+          <t>T2E91998</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B798" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000069</t>
+        </is>
+      </c>
+      <c r="C798" s="4" t="inlineStr">
+        <is>
+          <t>08 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D798" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E798" s="4" t="inlineStr">
+        <is>
+          <t>Ajit Majumdar</t>
+        </is>
+      </c>
+      <c r="F798" s="4" t="inlineStr">
+        <is>
+          <t>PODDAR AUTOCORP PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G798" s="4" t="inlineStr">
+        <is>
+          <t>GUWAHATI 3S</t>
+        </is>
+      </c>
+      <c r="H798" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I798" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J798" s="4" t="inlineStr">
+        <is>
+          <t>OEM Document Validation Failed: Certificate No mismatch (Document Certificate No: 'AS01GU7475' does not match old vehicle registration: 'AS01AD1927')</t>
+        </is>
+      </c>
+      <c r="K798" s="3" t="inlineStr"/>
+      <c r="L798" s="4" t="inlineStr">
+        <is>
+          <t>T2E91998</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B799" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000069</t>
+        </is>
+      </c>
+      <c r="C799" s="4" t="inlineStr">
+        <is>
+          <t>08 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D799" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E799" s="4" t="inlineStr">
+        <is>
+          <t>Ajit Majumdar</t>
+        </is>
+      </c>
+      <c r="F799" s="4" t="inlineStr">
+        <is>
+          <t>PODDAR AUTOCORP PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G799" s="4" t="inlineStr">
+        <is>
+          <t>GUWAHATI 3S</t>
+        </is>
+      </c>
+      <c r="H799" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I799" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J799" s="4" t="inlineStr"/>
+      <c r="K799" s="3" t="inlineStr"/>
+      <c r="L799" s="4" t="inlineStr">
+        <is>
+          <t>T2E91998</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B800" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000069</t>
+        </is>
+      </c>
+      <c r="C800" s="4" t="inlineStr">
+        <is>
+          <t>08 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D800" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E800" s="4" t="inlineStr">
+        <is>
+          <t>Ajit Majumdar</t>
+        </is>
+      </c>
+      <c r="F800" s="4" t="inlineStr">
+        <is>
+          <t>PODDAR AUTOCORP PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G800" s="4" t="inlineStr">
+        <is>
+          <t>GUWAHATI 3S</t>
+        </is>
+      </c>
+      <c r="H800" s="4" t="inlineStr">
+        <is>
+          <t>Scrappage Bonus</t>
+        </is>
+      </c>
+      <c r="I800" s="9" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J800" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: LLM Extraction Failed
+Ledger Validation Failed: LLM Extraction Failed
+OEM Document Validation Failed: OpenAI Error: 400 Client Error: Bad Request for url: https://api.anthropic.com/v1/messages</t>
+        </is>
+      </c>
+      <c r="K800" s="3" t="inlineStr"/>
+      <c r="L800" s="4" t="inlineStr">
+        <is>
+          <t>T2E91998</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M965"/>
+  <dimension ref="A1:M966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56662,6 +56662,65 @@
         <v>109.63</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B966" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000038</t>
+        </is>
+      </c>
+      <c r="C966" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D966" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E966" s="4" t="inlineStr">
+        <is>
+          <t>RAJU HAZAM</t>
+        </is>
+      </c>
+      <c r="F966" s="4" t="inlineStr">
+        <is>
+          <t>NEXGEN SOLUTIONS TECHNOLOGIES (P)</t>
+        </is>
+      </c>
+      <c r="G966" s="4" t="inlineStr">
+        <is>
+          <t>RANCHI-SHOWROOM</t>
+        </is>
+      </c>
+      <c r="H966" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I966" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J966" s="4" t="inlineStr"/>
+      <c r="K966" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:38:08</t>
+        </is>
+      </c>
+      <c r="L966" s="4" t="inlineStr">
+        <is>
+          <t>T6E12664</t>
+        </is>
+      </c>
+      <c r="M966" s="3" t="n">
+        <v>100.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M966"/>
+  <dimension ref="A1:M992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56721,6 +56721,1624 @@
         <v>100.14</v>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B967" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000055</t>
+        </is>
+      </c>
+      <c r="C967" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D967" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E967" s="4" t="inlineStr">
+        <is>
+          <t>Rajen Basumatary</t>
+        </is>
+      </c>
+      <c r="F967" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G967" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H967" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I967" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J967" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Invoice Number mismatch. Document: 'InVRA', Portal: 'INV27A000726'; Could not parse Invoice Date: ''; Customer Name not found in invoice</t>
+        </is>
+      </c>
+      <c r="K967" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:42:28</t>
+        </is>
+      </c>
+      <c r="L967" s="4" t="inlineStr">
+        <is>
+          <t>T6E15846</t>
+        </is>
+      </c>
+      <c r="M967" s="3" t="n">
+        <v>116.52</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B968" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C968" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D968" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E968" s="4" t="inlineStr">
+        <is>
+          <t>Hamidul islam</t>
+        </is>
+      </c>
+      <c r="F968" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G968" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H968" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I968" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J968" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Invoice Chassis Number mismatch. Document: 'Ph. No +91 03664 242424, einail :hatorki mahind€@gmail conl', Portal: 'S6A11007'; Invoice Number not found in invoice; Could not parse Invoice Date: ''; Customer Name not found in invoice, Ledger Validation Failed: Welcome Bonus Row credit amount mismatch. Row: 500000.0 (text: '500000'), Portal/Scheme: 5000.0</t>
+        </is>
+      </c>
+      <c r="K968" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:44:29</t>
+        </is>
+      </c>
+      <c r="L968" s="4" t="inlineStr">
+        <is>
+          <t>S6A11007</t>
+        </is>
+      </c>
+      <c r="M968" s="3" t="n">
+        <v>107.69</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B969" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000055</t>
+        </is>
+      </c>
+      <c r="C969" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D969" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E969" s="4" t="inlineStr">
+        <is>
+          <t>Rajen Basumatary</t>
+        </is>
+      </c>
+      <c r="F969" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G969" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H969" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I969" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J969" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Invoice Number mismatch. Document: 'InVRA', Portal: 'INV27A000726'; Could not parse Invoice Date: ''; Customer Name not found in invoice</t>
+        </is>
+      </c>
+      <c r="K969" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:50:02</t>
+        </is>
+      </c>
+      <c r="L969" s="4" t="inlineStr">
+        <is>
+          <t>T6E15846</t>
+        </is>
+      </c>
+      <c r="M969" s="3" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B970" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C970" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D970" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E970" s="4" t="inlineStr">
+        <is>
+          <t>Hamidul islam</t>
+        </is>
+      </c>
+      <c r="F970" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G970" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H970" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I970" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J970" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K970" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:51:44</t>
+        </is>
+      </c>
+      <c r="L970" s="4" t="inlineStr">
+        <is>
+          <t>S6A11007</t>
+        </is>
+      </c>
+      <c r="M970" s="3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B971" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000053</t>
+        </is>
+      </c>
+      <c r="C971" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D971" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E971" s="4" t="inlineStr">
+        <is>
+          <t>SANIN ROY</t>
+        </is>
+      </c>
+      <c r="F971" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G971" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H971" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I971" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J971" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K971" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:53:22</t>
+        </is>
+      </c>
+      <c r="L971" s="4" t="inlineStr">
+        <is>
+          <t>S6L12665</t>
+        </is>
+      </c>
+      <c r="M971" s="3" t="n">
+        <v>84.48999999999999</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B972" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000365</t>
+        </is>
+      </c>
+      <c r="C972" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D972" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E972" s="4" t="inlineStr">
+        <is>
+          <t>SONALI NAYAK</t>
+        </is>
+      </c>
+      <c r="F972" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G972" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H972" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I972" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J972" s="4" t="inlineStr"/>
+      <c r="K972" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:23:24</t>
+        </is>
+      </c>
+      <c r="L972" s="4" t="inlineStr">
+        <is>
+          <t>T6C10044</t>
+        </is>
+      </c>
+      <c r="M972" s="3" t="n">
+        <v>202.16</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B973" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000364</t>
+        </is>
+      </c>
+      <c r="C973" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D973" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E973" s="4" t="inlineStr">
+        <is>
+          <t>SATYABHAMA PRADHAN</t>
+        </is>
+      </c>
+      <c r="F973" s="4" t="inlineStr">
+        <is>
+          <t>ADITYA MOTORS</t>
+        </is>
+      </c>
+      <c r="G973" s="4" t="inlineStr">
+        <is>
+          <t>CUTTACK</t>
+        </is>
+      </c>
+      <c r="H973" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I973" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J973" s="4" t="inlineStr"/>
+      <c r="K973" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:27:42</t>
+        </is>
+      </c>
+      <c r="L973" s="4" t="inlineStr">
+        <is>
+          <t>T6E16670</t>
+        </is>
+      </c>
+      <c r="M973" s="3" t="n">
+        <v>226.74</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B974" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000038</t>
+        </is>
+      </c>
+      <c r="C974" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D974" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E974" s="4" t="inlineStr">
+        <is>
+          <t>RAJU HAZAM</t>
+        </is>
+      </c>
+      <c r="F974" s="4" t="inlineStr">
+        <is>
+          <t>NEXGEN SOLUTIONS TECHNOLOGIES (P)</t>
+        </is>
+      </c>
+      <c r="G974" s="4" t="inlineStr">
+        <is>
+          <t>RANCHI-SHOWROOM</t>
+        </is>
+      </c>
+      <c r="H974" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I974" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J974" s="4" t="inlineStr"/>
+      <c r="K974" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:31:10</t>
+        </is>
+      </c>
+      <c r="L974" s="4" t="inlineStr">
+        <is>
+          <t>T6E12664</t>
+        </is>
+      </c>
+      <c r="M974" s="3" t="n">
+        <v>125.64</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B975" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000055</t>
+        </is>
+      </c>
+      <c r="C975" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D975" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E975" s="4" t="inlineStr">
+        <is>
+          <t>Rajen Basumatary</t>
+        </is>
+      </c>
+      <c r="F975" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G975" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H975" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I975" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J975" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Invoice Number mismatch. Document: 'InVRA', Portal: 'INV27A000726'; Could not parse Invoice Date: ''; Customer Name not found in invoice</t>
+        </is>
+      </c>
+      <c r="K975" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:37:56</t>
+        </is>
+      </c>
+      <c r="L975" s="4" t="inlineStr">
+        <is>
+          <t>T6E15846</t>
+        </is>
+      </c>
+      <c r="M975" s="3" t="n">
+        <v>207.61</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B976" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000054</t>
+        </is>
+      </c>
+      <c r="C976" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D976" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E976" s="4" t="inlineStr">
+        <is>
+          <t>Hamidul islam</t>
+        </is>
+      </c>
+      <c r="F976" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G976" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H976" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I976" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J976" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Invoice Chassis Number mismatch. Document: 'Ph. No +91 03664 242424, einail :hatorki mahind€@gmail conl', Portal: 'S6A11007'; Invoice Number not found in invoice; Could not parse Invoice Date: ''; Customer Name not found in invoice, Ledger Validation Failed: Welcome Bonus Row credit amount mismatch. Row: 500000.0 (text: '500000'), Portal/Scheme: 5000.0</t>
+        </is>
+      </c>
+      <c r="K976" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:41:20</t>
+        </is>
+      </c>
+      <c r="L976" s="4" t="inlineStr">
+        <is>
+          <t>S6A11007</t>
+        </is>
+      </c>
+      <c r="M976" s="3" t="n">
+        <v>180.44</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B977" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000053</t>
+        </is>
+      </c>
+      <c r="C977" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D977" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E977" s="4" t="inlineStr">
+        <is>
+          <t>SANIN ROY</t>
+        </is>
+      </c>
+      <c r="F977" s="4" t="inlineStr">
+        <is>
+          <t>HATORKI MOTORS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G977" s="4" t="inlineStr">
+        <is>
+          <t>BONGAIGAON</t>
+        </is>
+      </c>
+      <c r="H977" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I977" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J977" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Chassis Number mismatch. Document: 'SCLJDECD', Portal: 'S6L12665'; Dealership Name not found in document; Vehicle Model mismatch. Document: 'SupuopuabiL luuck -', Portal Model Group: 'SUPRO-MT', Invoice Validation Failed: Document heading is not a Tax Invoice; Could not parse Invoice Date: ''; Customer Name not found in invoice; Vehicle Model not found in invoice</t>
+        </is>
+      </c>
+      <c r="K977" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:47:04</t>
+        </is>
+      </c>
+      <c r="L977" s="4" t="inlineStr">
+        <is>
+          <t>S6L12665</t>
+        </is>
+      </c>
+      <c r="M977" s="3" t="n">
+        <v>308.52</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B978" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000078</t>
+        </is>
+      </c>
+      <c r="C978" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D978" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E978" s="4" t="inlineStr">
+        <is>
+          <t>GANESH ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="F978" s="4" t="inlineStr">
+        <is>
+          <t>SIDDHI LAXMI MOTORS</t>
+        </is>
+      </c>
+      <c r="G978" s="4" t="inlineStr">
+        <is>
+          <t>KARADAGADIA, ANGUL.</t>
+        </is>
+      </c>
+      <c r="H978" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I978" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J978" s="4" t="inlineStr"/>
+      <c r="K978" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:50:05</t>
+        </is>
+      </c>
+      <c r="L978" s="4" t="inlineStr">
+        <is>
+          <t>T6A15561</t>
+        </is>
+      </c>
+      <c r="M978" s="3" t="n">
+        <v>127.16</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B979" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000076</t>
+        </is>
+      </c>
+      <c r="C979" s="4" t="inlineStr">
+        <is>
+          <t>25 Jun 2026</t>
+        </is>
+      </c>
+      <c r="D979" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E979" s="4" t="inlineStr">
+        <is>
+          <t>DHARMENDRA SAHU</t>
+        </is>
+      </c>
+      <c r="F979" s="4" t="inlineStr">
+        <is>
+          <t>SIDDHI LAXMI MOTORS</t>
+        </is>
+      </c>
+      <c r="G979" s="4" t="inlineStr">
+        <is>
+          <t>KARADAGADIA, ANGUL.</t>
+        </is>
+      </c>
+      <c r="H979" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I979" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J979" s="4" t="inlineStr"/>
+      <c r="K979" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:53:16</t>
+        </is>
+      </c>
+      <c r="L979" s="4" t="inlineStr">
+        <is>
+          <t>R6K18755</t>
+        </is>
+      </c>
+      <c r="M979" s="3" t="n">
+        <v>158.3</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B980" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000123</t>
+        </is>
+      </c>
+      <c r="C980" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D980" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E980" s="4" t="inlineStr">
+        <is>
+          <t>ANIL PALAKIA</t>
+        </is>
+      </c>
+      <c r="F980" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G980" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H980" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I980" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J980" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K980" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:05:52</t>
+        </is>
+      </c>
+      <c r="L980" s="4" t="inlineStr">
+        <is>
+          <t>T6E10310</t>
+        </is>
+      </c>
+      <c r="M980" s="3" t="n">
+        <v>110.02</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B981" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000089</t>
+        </is>
+      </c>
+      <c r="C981" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D981" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E981" s="4" t="inlineStr">
+        <is>
+          <t>Manaj Kumar Malik</t>
+        </is>
+      </c>
+      <c r="F981" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G981" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H981" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I981" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J981" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Chassis Number mismatch. Document: 'Iilodel SUPRO PROFITTRUCK EXCEL Ghassis no MAlFN2XUWT6E10642', Portal: 'T6E10642'; Dealership stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice Date mismatch. Document: '20106120', Portal: '20 Jun 2026'; Invoice stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K981" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:07:43</t>
+        </is>
+      </c>
+      <c r="L981" s="4" t="inlineStr">
+        <is>
+          <t>T6E10642</t>
+        </is>
+      </c>
+      <c r="M981" s="3" t="n">
+        <v>73.67</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B982" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000088</t>
+        </is>
+      </c>
+      <c r="C982" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D982" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E982" s="4" t="inlineStr">
+        <is>
+          <t>SIKHARANI DHADA</t>
+        </is>
+      </c>
+      <c r="F982" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G982" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H982" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I982" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J982" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice Date mismatch. Document: '10106120', Portal: '10 Jun 2026'; Vehicle Model mismatch. Document: 'THAR', Portal Model Group: 'SUPRO-MT'; Invoice stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Welcome Bonus Row credit amount mismatch. Row: 2026.0 (text: '2026'), Portal/Scheme: 5000.0; Ledger stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K982" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:09:14</t>
+        </is>
+      </c>
+      <c r="L982" s="4" t="inlineStr">
+        <is>
+          <t>T6E12972</t>
+        </is>
+      </c>
+      <c r="M982" s="3" t="n">
+        <v>72.11</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B983" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000122</t>
+        </is>
+      </c>
+      <c r="C983" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D983" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E983" s="4" t="inlineStr">
+        <is>
+          <t>BANTI KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F983" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G983" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H983" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I983" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J983" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Could not parse Invoice Date: ''; Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K983" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:11:36</t>
+        </is>
+      </c>
+      <c r="L983" s="4" t="inlineStr">
+        <is>
+          <t>T6F14147</t>
+        </is>
+      </c>
+      <c r="M983" s="3" t="n">
+        <v>100.42</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B984" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000121</t>
+        </is>
+      </c>
+      <c r="C984" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D984" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E984" s="4" t="inlineStr">
+        <is>
+          <t>CHUDAMANI BEHERA</t>
+        </is>
+      </c>
+      <c r="F984" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G984" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H984" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I984" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J984" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K984" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:13:13</t>
+        </is>
+      </c>
+      <c r="L984" s="4" t="inlineStr">
+        <is>
+          <t>T6F11448</t>
+        </is>
+      </c>
+      <c r="M984" s="3" t="n">
+        <v>75.79000000000001</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B985" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000060</t>
+        </is>
+      </c>
+      <c r="C985" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D985" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E985" s="4" t="inlineStr">
+        <is>
+          <t>INDAL PRASAD YADAV</t>
+        </is>
+      </c>
+      <c r="F985" s="4" t="inlineStr">
+        <is>
+          <t>SHREE R C ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G985" s="4" t="inlineStr">
+        <is>
+          <t>MOTIHARI</t>
+        </is>
+      </c>
+      <c r="H985" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I985" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J985" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: Vehicle Model mismatch. Document: 'THAR', Portal Model Group: 'VEERO'; Invoice stamp/seal does not belong to dealer 'SHREE R C ENTERPRISES' (Stamp text: 'Present (Python mock stamp)'), Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'SHREE R C ENTERPRISES' (Stamp text: 'Present (Python mock stamp signature)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'SHREE R C ENTERPRISES' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K985" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:16:30</t>
+        </is>
+      </c>
+      <c r="L985" s="4" t="inlineStr">
+        <is>
+          <t>T6D14831</t>
+        </is>
+      </c>
+      <c r="M985" s="3" t="n">
+        <v>166.78</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B986" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000120</t>
+        </is>
+      </c>
+      <c r="C986" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D986" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E986" s="4" t="inlineStr">
+        <is>
+          <t>JOSHISH KOSALIA</t>
+        </is>
+      </c>
+      <c r="F986" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G986" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H986" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I986" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J986" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Invoice Validation Failed: Vehicle Model mismatch. Document: 'THAR', Portal Model Group: 'SUPRO-MT'; Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K986" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:18:40</t>
+        </is>
+      </c>
+      <c r="L986" s="4" t="inlineStr">
+        <is>
+          <t>T6F11544</t>
+        </is>
+      </c>
+      <c r="M986" s="3" t="n">
+        <v>110.86</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B987" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000119</t>
+        </is>
+      </c>
+      <c r="C987" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D987" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E987" s="4" t="inlineStr">
+        <is>
+          <t>KURUKSHETRA POD</t>
+        </is>
+      </c>
+      <c r="F987" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G987" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H987" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I987" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J987" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K987" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:20:34</t>
+        </is>
+      </c>
+      <c r="L987" s="4" t="inlineStr">
+        <is>
+          <t>T6D12255</t>
+        </is>
+      </c>
+      <c r="M987" s="3" t="n">
+        <v>89.63</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B988" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000118</t>
+        </is>
+      </c>
+      <c r="C988" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D988" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E988" s="4" t="inlineStr">
+        <is>
+          <t>JOGINDRA BAG</t>
+        </is>
+      </c>
+      <c r="F988" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G988" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H988" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I988" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J988" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K988" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:22:06</t>
+        </is>
+      </c>
+      <c r="L988" s="4" t="inlineStr">
+        <is>
+          <t>T6F11637</t>
+        </is>
+      </c>
+      <c r="M988" s="3" t="n">
+        <v>85.67</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B989" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000117</t>
+        </is>
+      </c>
+      <c r="C989" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D989" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E989" s="4" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR MISHRA</t>
+        </is>
+      </c>
+      <c r="F989" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G989" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H989" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I989" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J989" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K989" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:23:45</t>
+        </is>
+      </c>
+      <c r="L989" s="4" t="inlineStr">
+        <is>
+          <t>T6E10315</t>
+        </is>
+      </c>
+      <c r="M989" s="3" t="n">
+        <v>84.36</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B990" s="4" t="inlineStr">
+        <is>
+          <t>LYL27F000003</t>
+        </is>
+      </c>
+      <c r="C990" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D990" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E990" s="4" t="inlineStr">
+        <is>
+          <t>SUNIL PRASAD CHAURACIYA</t>
+        </is>
+      </c>
+      <c r="F990" s="4" t="inlineStr">
+        <is>
+          <t>SHREE R C ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G990" s="4" t="inlineStr">
+        <is>
+          <t>RAXAUL_SZ</t>
+        </is>
+      </c>
+      <c r="H990" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I990" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J990" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K990" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:25:28</t>
+        </is>
+      </c>
+      <c r="L990" s="4" t="inlineStr">
+        <is>
+          <t>T6B12543</t>
+        </is>
+      </c>
+      <c r="M990" s="3" t="n">
+        <v>84.33</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B991" s="4" t="inlineStr">
+        <is>
+          <t>LYL27E000008</t>
+        </is>
+      </c>
+      <c r="C991" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D991" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E991" s="4" t="inlineStr">
+        <is>
+          <t>MD TAUFIK AHAMAD</t>
+        </is>
+      </c>
+      <c r="F991" s="4" t="inlineStr">
+        <is>
+          <t>SHREE R C ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G991" s="4" t="inlineStr">
+        <is>
+          <t>CHAKIA_SZZ</t>
+        </is>
+      </c>
+      <c r="H991" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I991" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J991" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K991" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:27:00</t>
+        </is>
+      </c>
+      <c r="L991" s="4" t="inlineStr">
+        <is>
+          <t>T6A10086</t>
+        </is>
+      </c>
+      <c r="M991" s="3" t="n">
+        <v>84.61</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B992" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000116</t>
+        </is>
+      </c>
+      <c r="C992" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D992" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E992" s="4" t="inlineStr">
+        <is>
+          <t>M/s PREETU MOTORS</t>
+        </is>
+      </c>
+      <c r="F992" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G992" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H992" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I992" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J992" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K992" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:28:30</t>
+        </is>
+      </c>
+      <c r="L992" s="4" t="inlineStr">
+        <is>
+          <t>T6E10314</t>
+        </is>
+      </c>
+      <c r="M992" s="3" t="n">
+        <v>83.98999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kyc_process_results.xlsx
+++ b/kyc_process_results.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M992"/>
+  <dimension ref="A1:M1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -58339,6 +58339,4971 @@
         <v>83.98999999999999</v>
       </c>
     </row>
+    <row r="993">
+      <c r="A993" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B993" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000123</t>
+        </is>
+      </c>
+      <c r="C993" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D993" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E993" s="4" t="inlineStr">
+        <is>
+          <t>ANIL PALAKIA</t>
+        </is>
+      </c>
+      <c r="F993" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G993" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H993" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I993" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J993" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K993" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:43:31</t>
+        </is>
+      </c>
+      <c r="L993" s="4" t="inlineStr">
+        <is>
+          <t>T6E10310</t>
+        </is>
+      </c>
+      <c r="M993" s="3" t="n">
+        <v>75.43000000000001</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B994" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000089</t>
+        </is>
+      </c>
+      <c r="C994" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D994" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E994" s="4" t="inlineStr">
+        <is>
+          <t>Manaj Kumar Malik</t>
+        </is>
+      </c>
+      <c r="F994" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G994" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H994" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I994" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J994" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Chassis Number mismatch. Document: 'Iilodel SUPRO PROFITTRUCK EXCEL Ghassis no MAlFN2XUWT6E10642', Portal: 'T6E10642'; Dealership stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice Date mismatch. Document: '20106120', Portal: '20 Jun 2026'; Invoice stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K994" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:45:41</t>
+        </is>
+      </c>
+      <c r="L994" s="4" t="inlineStr">
+        <is>
+          <t>T6E10642</t>
+        </is>
+      </c>
+      <c r="M994" s="3" t="n">
+        <v>94.65000000000001</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B995" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000088</t>
+        </is>
+      </c>
+      <c r="C995" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D995" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E995" s="4" t="inlineStr">
+        <is>
+          <t>SIKHARANI DHADA</t>
+        </is>
+      </c>
+      <c r="F995" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G995" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H995" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I995" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J995" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice Date mismatch. Document: '10106120', Portal: '10 Jun 2026'; Vehicle Model mismatch. Document: 'THAR', Portal Model Group: 'SUPRO-MT'; Invoice stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Welcome Bonus Row credit amount mismatch. Row: 2026.0 (text: '2026'), Portal/Scheme: 5000.0; Ledger stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K995" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:47:21</t>
+        </is>
+      </c>
+      <c r="L995" s="4" t="inlineStr">
+        <is>
+          <t>T6E12972</t>
+        </is>
+      </c>
+      <c r="M995" s="3" t="n">
+        <v>78.94</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B996" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000122</t>
+        </is>
+      </c>
+      <c r="C996" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D996" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E996" s="4" t="inlineStr">
+        <is>
+          <t>BANTI KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F996" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G996" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H996" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I996" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J996" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Could not parse Invoice Date: ''; Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K996" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:49:47</t>
+        </is>
+      </c>
+      <c r="L996" s="4" t="inlineStr">
+        <is>
+          <t>T6F14147</t>
+        </is>
+      </c>
+      <c r="M996" s="3" t="n">
+        <v>109.25</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B997" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000121</t>
+        </is>
+      </c>
+      <c r="C997" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D997" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E997" s="4" t="inlineStr">
+        <is>
+          <t>CHUDAMANI BEHERA</t>
+        </is>
+      </c>
+      <c r="F997" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G997" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H997" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I997" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J997" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K997" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:51:55</t>
+        </is>
+      </c>
+      <c r="L997" s="4" t="inlineStr">
+        <is>
+          <t>T6F11448</t>
+        </is>
+      </c>
+      <c r="M997" s="3" t="n">
+        <v>103.88</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B998" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000123</t>
+        </is>
+      </c>
+      <c r="C998" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D998" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E998" s="4" t="inlineStr">
+        <is>
+          <t>ANIL PALAKIA</t>
+        </is>
+      </c>
+      <c r="F998" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G998" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H998" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I998" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J998" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Document heading is not a Tax Invoice; Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K998" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 18:58:43</t>
+        </is>
+      </c>
+      <c r="L998" s="4" t="inlineStr">
+        <is>
+          <t>T6E10310</t>
+        </is>
+      </c>
+      <c r="M998" s="3" t="n">
+        <v>152.72</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B999" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000089</t>
+        </is>
+      </c>
+      <c r="C999" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D999" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E999" s="4" t="inlineStr">
+        <is>
+          <t>Manaj Kumar Malik</t>
+        </is>
+      </c>
+      <c r="F999" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G999" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H999" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I999" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J999" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Chassis Number mismatch. Document: 'Iilodel SUPRO PROFITTRUCK EXCEL Ghassis no MAlFN2XUWT6E10642', Portal: 'T6E10642'; Invoice Number not found in document; Welcome Bonus Amount mismatch. Document: 5.0, Portal/Scheme: 5000.0; Dealership stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Document heading is not a Tax Invoice; Invoice Date mismatch. Document: '20106120', Portal: '20 Jun 2026'; Customer Name not found in invoice; Invoice stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Customer Name mismatch. Document: 'S/O.EKADASI MALIK CHAUKIYA SAHI AUNRI BINJHARPUR JAJPUR 755013', Portal: 'Manaj Kumar Malik'; Welcome Bonus row entry not found in ledger; Ledger stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K999" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:00:48</t>
+        </is>
+      </c>
+      <c r="L999" s="4" t="inlineStr">
+        <is>
+          <t>T6E10642</t>
+        </is>
+      </c>
+      <c r="M999" s="3" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B1000" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000088</t>
+        </is>
+      </c>
+      <c r="C1000" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1000" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1000" s="4" t="inlineStr">
+        <is>
+          <t>SIKHARANI DHADA</t>
+        </is>
+      </c>
+      <c r="F1000" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1000" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H1000" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1000" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1000" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice Date mismatch. Document: '10106120', Portal: '10 Jun 2026'; Invoice stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Welcome Bonus Row credit amount mismatch. Row: 2026.0 (text: '2026'), Portal/Scheme: 5000.0; Ledger stamp/seal does not belong to dealer 'UTKAL AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K1000" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:01:41</t>
+        </is>
+      </c>
+      <c r="L1000" s="4" t="inlineStr">
+        <is>
+          <t>T6E12972</t>
+        </is>
+      </c>
+      <c r="M1000" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B1001" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000122</t>
+        </is>
+      </c>
+      <c r="C1001" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1001" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1001" s="4" t="inlineStr">
+        <is>
+          <t>BANTI KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F1001" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1001" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1001" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1001" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1001" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K1001" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:05:13</t>
+        </is>
+      </c>
+      <c r="L1001" s="4" t="inlineStr">
+        <is>
+          <t>T6F14147</t>
+        </is>
+      </c>
+      <c r="M1001" s="3" t="n">
+        <v>175.99</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B1002" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000121</t>
+        </is>
+      </c>
+      <c r="C1002" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1002" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1002" s="4" t="inlineStr">
+        <is>
+          <t>CHUDAMANI BEHERA</t>
+        </is>
+      </c>
+      <c r="F1002" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1002" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1002" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1002" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1002" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: Dealership stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp signature)'), Invoice Validation Failed: Invoice stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)'), Ledger Validation Failed: Ledger stamp/seal does not belong to dealer 'MINERVA AUTOMOBILES PVT. LTD.' (Stamp text: 'Present (Python mock stamp)')</t>
+        </is>
+      </c>
+      <c r="K1002" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:21:07</t>
+        </is>
+      </c>
+      <c r="L1002" s="4" t="inlineStr">
+        <is>
+          <t>T6F11448</t>
+        </is>
+      </c>
+      <c r="M1002" s="3" t="n">
+        <v>141330.3</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B1003" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000060</t>
+        </is>
+      </c>
+      <c r="C1003" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1003" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1003" s="4" t="inlineStr">
+        <is>
+          <t>INDAL PRASAD YADAV</t>
+        </is>
+      </c>
+      <c r="F1003" s="4" t="inlineStr">
+        <is>
+          <t>SHREE R C ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G1003" s="4" t="inlineStr">
+        <is>
+          <t>MOTIHARI</t>
+        </is>
+      </c>
+      <c r="H1003" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1003" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1003" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1003" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:23:15</t>
+        </is>
+      </c>
+      <c r="L1003" s="4" t="inlineStr">
+        <is>
+          <t>T6D14831</t>
+        </is>
+      </c>
+      <c r="M1003" s="3" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1004" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000095</t>
+        </is>
+      </c>
+      <c r="C1004" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1004" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1004" s="4" t="inlineStr">
+        <is>
+          <t>LALITA DEVI</t>
+        </is>
+      </c>
+      <c r="F1004" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1004" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1004" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1004" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1004" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: [customer_name] Rule evaluation error: name 'is_name_in_text' is not defined</t>
+        </is>
+      </c>
+      <c r="K1004" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:25:05</t>
+        </is>
+      </c>
+      <c r="L1004" s="4" t="inlineStr">
+        <is>
+          <t>T6E12876</t>
+        </is>
+      </c>
+      <c r="M1004" s="3" t="n">
+        <v>183.81</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B1005" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000094</t>
+        </is>
+      </c>
+      <c r="C1005" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1005" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1005" s="4" t="inlineStr">
+        <is>
+          <t>BIPIN KUMAR MANDAL</t>
+        </is>
+      </c>
+      <c r="F1005" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1005" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1005" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1005" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1005" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: [invoice_date] Invoice Date mismatch. Document: '09106190', Portal: '09 Jun 2026', Invoice Validation Failed: [customer_name] Rule evaluation error: name 'is_name_in_text' is not defined, Missing Ledger Document</t>
+        </is>
+      </c>
+      <c r="K1005" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:27:59</t>
+        </is>
+      </c>
+      <c r="L1005" s="4" t="inlineStr">
+        <is>
+          <t>T6E13082</t>
+        </is>
+      </c>
+      <c r="M1005" s="3" t="n">
+        <v>158.39</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1006" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000097</t>
+        </is>
+      </c>
+      <c r="C1006" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1006" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1006" s="4" t="inlineStr">
+        <is>
+          <t>WASIKUL ISLAM</t>
+        </is>
+      </c>
+      <c r="F1006" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1006" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1006" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1006" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1006" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: [customer_name] Rule evaluation error: name 'is_name_in_text' is not defined, Missing Ledger Document</t>
+        </is>
+      </c>
+      <c r="K1006" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:33:09</t>
+        </is>
+      </c>
+      <c r="L1006" s="4" t="inlineStr">
+        <is>
+          <t>T6E13052</t>
+        </is>
+      </c>
+      <c r="M1006" s="3" t="n">
+        <v>179.1</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B1007" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000096</t>
+        </is>
+      </c>
+      <c r="C1007" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1007" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1007" s="4" t="inlineStr">
+        <is>
+          <t>SWADESH KUMAR</t>
+        </is>
+      </c>
+      <c r="F1007" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1007" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1007" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1007" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1007" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: [customer_name] Rule evaluation error: name 'is_name_in_text' is not defined, Missing Ledger Document</t>
+        </is>
+      </c>
+      <c r="K1007" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:36:00</t>
+        </is>
+      </c>
+      <c r="L1007" s="4" t="inlineStr">
+        <is>
+          <t>T6E16463</t>
+        </is>
+      </c>
+      <c r="M1007" s="3" t="n">
+        <v>157.04</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B1008" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000095</t>
+        </is>
+      </c>
+      <c r="C1008" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1008" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1008" s="4" t="inlineStr">
+        <is>
+          <t>LALITA DEVI</t>
+        </is>
+      </c>
+      <c r="F1008" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1008" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1008" s="4" t="inlineStr"/>
+      <c r="I1008" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1008" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Validation Failed: [customer_name] Rule evaluation error: name 'is_name_in_text' is not defined</t>
+        </is>
+      </c>
+      <c r="K1008" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:45:05</t>
+        </is>
+      </c>
+      <c r="L1008" s="4" t="inlineStr">
+        <is>
+          <t>T6E12876</t>
+        </is>
+      </c>
+      <c r="M1008" s="3" t="n">
+        <v>523.78</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1009" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000037</t>
+        </is>
+      </c>
+      <c r="C1009" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1009" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1009" s="4" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="F1009" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1009" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1009" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1009" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1009" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: [invoice_date] Invoice Date mismatch. Document: '27DOO0173', Portal: '17 Jun 2026', Ledger Validation Failed: [customer_name] Customer Name mismatch. Document: '', Portal: 'MANOJ KUMAR'</t>
+        </is>
+      </c>
+      <c r="K1009" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:49</t>
+        </is>
+      </c>
+      <c r="L1009" s="4" t="inlineStr">
+        <is>
+          <t>T6E10064</t>
+        </is>
+      </c>
+      <c r="M1009" s="3" t="n">
+        <v>183.04</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B1010" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000036</t>
+        </is>
+      </c>
+      <c r="C1010" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1010" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1010" s="4" t="inlineStr">
+        <is>
+          <t>MD IRSAD</t>
+        </is>
+      </c>
+      <c r="F1010" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1010" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1010" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1010" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1010" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: [invoice_date] Invoice Date mismatch. Document: '27DOO0172', Portal: '17 Jun 2026', Ledger Validation Failed: [customer_name] Customer Name mismatch. Document: '', Portal: 'MD IRSAD'</t>
+        </is>
+      </c>
+      <c r="K1010" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:58:21</t>
+        </is>
+      </c>
+      <c r="L1010" s="4" t="inlineStr">
+        <is>
+          <t>T6D15470</t>
+        </is>
+      </c>
+      <c r="M1010" s="3" t="n">
+        <v>199.54</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B1011" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000035</t>
+        </is>
+      </c>
+      <c r="C1011" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1011" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1011" s="4" t="inlineStr">
+        <is>
+          <t>MD AMIL</t>
+        </is>
+      </c>
+      <c r="F1011" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1011" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1011" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1011" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1011" s="4" t="inlineStr">
+        <is>
+          <t>Ledger Validation Failed: [customer_name] Customer Name mismatch. Document: '', Portal: 'MD AMIL'</t>
+        </is>
+      </c>
+      <c r="K1011" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:03:49</t>
+        </is>
+      </c>
+      <c r="L1011" s="4" t="inlineStr">
+        <is>
+          <t>T6E10380</t>
+        </is>
+      </c>
+      <c r="M1011" s="3" t="n">
+        <v>314.91</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1012" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000127</t>
+        </is>
+      </c>
+      <c r="C1012" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1012" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E1012" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE KUMAR</t>
+        </is>
+      </c>
+      <c r="F1012" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CARRIAGE PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1012" s="4" t="inlineStr">
+        <is>
+          <t>TOLLYGUNJ</t>
+        </is>
+      </c>
+      <c r="H1012" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1012" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1012" s="4" t="inlineStr">
+        <is>
+          <t>Ledger Validation Failed: [welcome_bonus_amount] Welcome Bonus Row amount mismatch. Row: '2026', Portal: 0.0</t>
+        </is>
+      </c>
+      <c r="K1012" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:27:40</t>
+        </is>
+      </c>
+      <c r="L1012" s="4" t="inlineStr">
+        <is>
+          <t>T6F13920</t>
+        </is>
+      </c>
+      <c r="M1012" s="3" t="n">
+        <v>128.99</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B1013" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000126</t>
+        </is>
+      </c>
+      <c r="C1013" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1013" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E1013" s="4" t="inlineStr">
+        <is>
+          <t>AVIJIT MAL</t>
+        </is>
+      </c>
+      <c r="F1013" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CARRIAGE PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1013" s="4" t="inlineStr">
+        <is>
+          <t>TOLLYGUNJ</t>
+        </is>
+      </c>
+      <c r="H1013" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1013" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1013" s="4" t="inlineStr">
+        <is>
+          <t>Ledger Validation Failed: [welcome_bonus_amount] Welcome Bonus Row amount mismatch. Row: '2026', Portal: 30000.0</t>
+        </is>
+      </c>
+      <c r="K1013" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:31:24</t>
+        </is>
+      </c>
+      <c r="L1013" s="4" t="inlineStr">
+        <is>
+          <t>T6F14207</t>
+        </is>
+      </c>
+      <c r="M1013" s="3" t="n">
+        <v>201.95</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B1014" s="4" t="inlineStr">
+        <is>
+          <t>LYL27I000050</t>
+        </is>
+      </c>
+      <c r="C1014" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1014" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1014" s="4" t="inlineStr">
+        <is>
+          <t>SUBI DEVI</t>
+        </is>
+      </c>
+      <c r="F1014" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1014" s="4" t="inlineStr">
+        <is>
+          <t>SUPAUL_SS</t>
+        </is>
+      </c>
+      <c r="H1014" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1014" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1014" s="4" t="inlineStr">
+        <is>
+          <t>Ledger Validation Failed: [ledger_heading] Document heading 'Tax Invoice' is not classified as a Ledger or Statement, Missing Invoice Document</t>
+        </is>
+      </c>
+      <c r="K1014" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:35:32</t>
+        </is>
+      </c>
+      <c r="L1014" s="4" t="inlineStr">
+        <is>
+          <t>T6F18696</t>
+        </is>
+      </c>
+      <c r="M1014" s="3" t="n">
+        <v>230.94</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B1015" s="4" t="inlineStr">
+        <is>
+          <t>LYL27I000049</t>
+        </is>
+      </c>
+      <c r="C1015" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1015" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1015" s="4" t="inlineStr">
+        <is>
+          <t>Vikram Kumar</t>
+        </is>
+      </c>
+      <c r="F1015" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1015" s="4" t="inlineStr">
+        <is>
+          <t>SUPAUL_SS</t>
+        </is>
+      </c>
+      <c r="H1015" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1015" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1015" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: [chassis_number] Chassis Number mismatch. Document: 'XUTGE15055', Portal: 'T6E12770'; [invoice_date] Invoice Date mismatch. Document: '02-JUN-26', Portal: '05 Jun 2026', Ledger Validation Failed: [customer_name] Customer Name mismatch. Document: 'Mahanand', Portal: 'Vikram Kumar'; [welcome_bonus_row_present] Welcome Bonus row entry not found in ledger; [welcome_bonus_amount] Welcome Bonus amount not found in row '' — manual review needed</t>
+        </is>
+      </c>
+      <c r="K1015" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:47:21</t>
+        </is>
+      </c>
+      <c r="L1015" s="4" t="inlineStr">
+        <is>
+          <t>T6E12770</t>
+        </is>
+      </c>
+      <c r="M1015" s="3" t="n">
+        <v>704.1</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B1016" s="4" t="inlineStr">
+        <is>
+          <t>LYL27I000048</t>
+        </is>
+      </c>
+      <c r="C1016" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1016" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1016" s="4" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AKBAR</t>
+        </is>
+      </c>
+      <c r="F1016" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1016" s="4" t="inlineStr">
+        <is>
+          <t>SUPAUL_SS</t>
+        </is>
+      </c>
+      <c r="H1016" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1016" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1016" s="4" t="inlineStr">
+        <is>
+          <t>Disclaimer Validation Failed: [chassis_number] Chassis Number mismatch. Document: 'Chassis no MAIFNZPXWT6E1O091', Portal: 'T6E10091', Ledger Validation Failed: [customer_name] Customer Name mismatch. Document: 'INV271000125', Portal: 'MOHAMMAD AKBAR'; [welcome_bonus_amount] Welcome Bonus Row amount mismatch. Row: '1', Portal: 5000.0</t>
+        </is>
+      </c>
+      <c r="K1016" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:53:03</t>
+        </is>
+      </c>
+      <c r="L1016" s="4" t="inlineStr">
+        <is>
+          <t>T6E10091</t>
+        </is>
+      </c>
+      <c r="M1016" s="3" t="n">
+        <v>326.53</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B1017" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000037</t>
+        </is>
+      </c>
+      <c r="C1017" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1017" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1017" s="4" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="F1017" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1017" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1017" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1017" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1017" s="4" t="inlineStr">
+        <is>
+          <t>Ledger Validation Failed: [customer_name] Customer Name mismatch. Document: '', Portal: 'MANOJ KUMAR'</t>
+        </is>
+      </c>
+      <c r="K1017" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:56:46</t>
+        </is>
+      </c>
+      <c r="L1017" s="4" t="inlineStr">
+        <is>
+          <t>T6E10064</t>
+        </is>
+      </c>
+      <c r="M1017" s="3" t="n">
+        <v>209.56</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1018" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000059</t>
+        </is>
+      </c>
+      <c r="C1018" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1018" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E1018" s="4" t="inlineStr">
+        <is>
+          <t>Akash Samanta</t>
+        </is>
+      </c>
+      <c r="F1018" s="4" t="inlineStr">
+        <is>
+          <t>NR Autos ( A UNIT OF NARBHERAM LEASING CO PVT LTD)</t>
+        </is>
+      </c>
+      <c r="G1018" s="4" t="inlineStr">
+        <is>
+          <t>KOLKATA_SR</t>
+        </is>
+      </c>
+      <c r="H1018" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1018" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J1018" s="4" t="inlineStr"/>
+      <c r="K1018" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:01:16</t>
+        </is>
+      </c>
+      <c r="L1018" s="4" t="inlineStr">
+        <is>
+          <t>T6D14796</t>
+        </is>
+      </c>
+      <c r="M1018" s="3" t="n">
+        <v>162.94</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B1019" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000127</t>
+        </is>
+      </c>
+      <c r="C1019" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1019" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E1019" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE KUMAR</t>
+        </is>
+      </c>
+      <c r="F1019" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CARRIAGE PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1019" s="4" t="inlineStr">
+        <is>
+          <t>TOLLYGUNJ</t>
+        </is>
+      </c>
+      <c r="H1019" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1019" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1019" s="4" t="inlineStr">
+        <is>
+          <t>Ledger Validation Failed: [welcome_bonus_amount] Welcome Bonus Row amount mismatch. Row: '30000.001', Portal: 0.0</t>
+        </is>
+      </c>
+      <c r="K1019" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:04:03</t>
+        </is>
+      </c>
+      <c r="L1019" s="4" t="inlineStr">
+        <is>
+          <t>T6F13920</t>
+        </is>
+      </c>
+      <c r="M1019" s="3" t="n">
+        <v>147.15</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B1020" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000126</t>
+        </is>
+      </c>
+      <c r="C1020" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1020" s="4" t="inlineStr">
+        <is>
+          <t>AD Kolkata</t>
+        </is>
+      </c>
+      <c r="E1020" s="4" t="inlineStr">
+        <is>
+          <t>AVIJIT MAL</t>
+        </is>
+      </c>
+      <c r="F1020" s="4" t="inlineStr">
+        <is>
+          <t>AUTO CARRIAGE PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1020" s="4" t="inlineStr">
+        <is>
+          <t>TOLLYGUNJ</t>
+        </is>
+      </c>
+      <c r="H1020" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1020" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="J1020" s="4" t="inlineStr"/>
+      <c r="K1020" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:25:01</t>
+        </is>
+      </c>
+      <c r="L1020" s="4" t="inlineStr">
+        <is>
+          <t>T6F14207</t>
+        </is>
+      </c>
+      <c r="M1020" s="3" t="n">
+        <v>1240.35</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B1021" s="4" t="inlineStr">
+        <is>
+          <t>LYL27I000050</t>
+        </is>
+      </c>
+      <c r="C1021" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1021" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1021" s="4" t="inlineStr">
+        <is>
+          <t>SUBI DEVI</t>
+        </is>
+      </c>
+      <c r="F1021" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1021" s="4" t="inlineStr">
+        <is>
+          <t>SUPAUL_SS</t>
+        </is>
+      </c>
+      <c r="H1021" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1021" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1021" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1021" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:26:53</t>
+        </is>
+      </c>
+      <c r="L1021" s="4" t="inlineStr">
+        <is>
+          <t>T6F18696</t>
+        </is>
+      </c>
+      <c r="M1021" s="3" t="n">
+        <v>90.66</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B1022" s="4" t="inlineStr">
+        <is>
+          <t>LYL27I000049</t>
+        </is>
+      </c>
+      <c r="C1022" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1022" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1022" s="4" t="inlineStr">
+        <is>
+          <t>Vikram Kumar</t>
+        </is>
+      </c>
+      <c r="F1022" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1022" s="4" t="inlineStr">
+        <is>
+          <t>SUPAUL_SS</t>
+        </is>
+      </c>
+      <c r="H1022" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1022" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1022" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1022" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:28:24</t>
+        </is>
+      </c>
+      <c r="L1022" s="4" t="inlineStr">
+        <is>
+          <t>T6E12770</t>
+        </is>
+      </c>
+      <c r="M1022" s="3" t="n">
+        <v>84.23999999999999</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B1023" s="4" t="inlineStr">
+        <is>
+          <t>LYL27I000048</t>
+        </is>
+      </c>
+      <c r="C1023" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1023" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1023" s="4" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AKBAR</t>
+        </is>
+      </c>
+      <c r="F1023" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1023" s="4" t="inlineStr">
+        <is>
+          <t>SUPAUL_SS</t>
+        </is>
+      </c>
+      <c r="H1023" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1023" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1023" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1023" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:29:54</t>
+        </is>
+      </c>
+      <c r="L1023" s="4" t="inlineStr">
+        <is>
+          <t>T6E10091</t>
+        </is>
+      </c>
+      <c r="M1023" s="3" t="n">
+        <v>84.36</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B1024" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000037</t>
+        </is>
+      </c>
+      <c r="C1024" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1024" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1024" s="4" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="F1024" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1024" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1024" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1024" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1024" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document</t>
+        </is>
+      </c>
+      <c r="K1024" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:32:04</t>
+        </is>
+      </c>
+      <c r="L1024" s="4" t="inlineStr">
+        <is>
+          <t>T6E10064</t>
+        </is>
+      </c>
+      <c r="M1024" s="3" t="n">
+        <v>123.16</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B1025" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000036</t>
+        </is>
+      </c>
+      <c r="C1025" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1025" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1025" s="4" t="inlineStr">
+        <is>
+          <t>MD IRSAD</t>
+        </is>
+      </c>
+      <c r="F1025" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1025" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1025" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1025" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1025" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1025" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:33:36</t>
+        </is>
+      </c>
+      <c r="L1025" s="4" t="inlineStr">
+        <is>
+          <t>T6D15470</t>
+        </is>
+      </c>
+      <c r="M1025" s="3" t="n">
+        <v>85.67</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B1026" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000035</t>
+        </is>
+      </c>
+      <c r="C1026" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1026" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1026" s="4" t="inlineStr">
+        <is>
+          <t>MD AMIL</t>
+        </is>
+      </c>
+      <c r="F1026" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1026" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1026" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1026" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1026" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1026" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:35:09</t>
+        </is>
+      </c>
+      <c r="L1026" s="4" t="inlineStr">
+        <is>
+          <t>T6E10380</t>
+        </is>
+      </c>
+      <c r="M1026" s="3" t="n">
+        <v>84.93000000000001</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B1027" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000034</t>
+        </is>
+      </c>
+      <c r="C1027" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1027" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1027" s="4" t="inlineStr">
+        <is>
+          <t>MD SHAHID ANWAR</t>
+        </is>
+      </c>
+      <c r="F1027" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1027" s="4" t="inlineStr">
+        <is>
+          <t>FORBESGANJ (3S)</t>
+        </is>
+      </c>
+      <c r="H1027" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1027" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1027" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1027" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:36:39</t>
+        </is>
+      </c>
+      <c r="L1027" s="4" t="inlineStr">
+        <is>
+          <t>T6E10067</t>
+        </is>
+      </c>
+      <c r="M1027" s="3" t="n">
+        <v>84.36</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B1028" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000040</t>
+        </is>
+      </c>
+      <c r="C1028" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1028" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1028" s="4" t="inlineStr">
+        <is>
+          <t>SATYA KUMAR MANDAL</t>
+        </is>
+      </c>
+      <c r="F1028" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1028" s="4" t="inlineStr">
+        <is>
+          <t>SAHARSA MADB</t>
+        </is>
+      </c>
+      <c r="H1028" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1028" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1028" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1028" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:38:09</t>
+        </is>
+      </c>
+      <c r="L1028" s="4" t="inlineStr">
+        <is>
+          <t>T6E13080</t>
+        </is>
+      </c>
+      <c r="M1028" s="3" t="n">
+        <v>84.13</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B1029" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000039</t>
+        </is>
+      </c>
+      <c r="C1029" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1029" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1029" s="4" t="inlineStr">
+        <is>
+          <t>DEEPAK KUMAR</t>
+        </is>
+      </c>
+      <c r="F1029" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1029" s="4" t="inlineStr">
+        <is>
+          <t>SAHARSA MADB</t>
+        </is>
+      </c>
+      <c r="H1029" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1029" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1029" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1029" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:39:39</t>
+        </is>
+      </c>
+      <c r="L1029" s="4" t="inlineStr">
+        <is>
+          <t>T6E10305</t>
+        </is>
+      </c>
+      <c r="M1029" s="3" t="n">
+        <v>83.61</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B1030" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000038</t>
+        </is>
+      </c>
+      <c r="C1030" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1030" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1030" s="4" t="inlineStr">
+        <is>
+          <t>RAJA KUMAR</t>
+        </is>
+      </c>
+      <c r="F1030" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1030" s="4" t="inlineStr">
+        <is>
+          <t>SAHARSA MADB</t>
+        </is>
+      </c>
+      <c r="H1030" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1030" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1030" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1030" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:41:09</t>
+        </is>
+      </c>
+      <c r="L1030" s="4" t="inlineStr">
+        <is>
+          <t>T6F18435</t>
+        </is>
+      </c>
+      <c r="M1030" s="3" t="n">
+        <v>84.05</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B1031" s="4" t="inlineStr">
+        <is>
+          <t>LYL27C000037</t>
+        </is>
+      </c>
+      <c r="C1031" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1031" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1031" s="4" t="inlineStr">
+        <is>
+          <t>AJAY MALLAH</t>
+        </is>
+      </c>
+      <c r="F1031" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1031" s="4" t="inlineStr">
+        <is>
+          <t>SAHARSA MADB</t>
+        </is>
+      </c>
+      <c r="H1031" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1031" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1031" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1031" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:42:39</t>
+        </is>
+      </c>
+      <c r="L1031" s="4" t="inlineStr">
+        <is>
+          <t>T6F18437</t>
+        </is>
+      </c>
+      <c r="M1031" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B1032" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000097</t>
+        </is>
+      </c>
+      <c r="C1032" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1032" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1032" s="4" t="inlineStr">
+        <is>
+          <t>WASIKUL ISLAM</t>
+        </is>
+      </c>
+      <c r="F1032" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1032" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1032" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1032" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1032" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1032" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:44:09</t>
+        </is>
+      </c>
+      <c r="L1032" s="4" t="inlineStr">
+        <is>
+          <t>T6E13052</t>
+        </is>
+      </c>
+      <c r="M1032" s="3" t="n">
+        <v>84.11</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B1033" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000096</t>
+        </is>
+      </c>
+      <c r="C1033" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1033" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1033" s="4" t="inlineStr">
+        <is>
+          <t>SWADESH KUMAR</t>
+        </is>
+      </c>
+      <c r="F1033" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1033" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1033" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1033" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1033" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1033" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:45:39</t>
+        </is>
+      </c>
+      <c r="L1033" s="4" t="inlineStr">
+        <is>
+          <t>T6E16463</t>
+        </is>
+      </c>
+      <c r="M1033" s="3" t="n">
+        <v>83.76000000000001</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B1034" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000095</t>
+        </is>
+      </c>
+      <c r="C1034" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1034" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1034" s="4" t="inlineStr">
+        <is>
+          <t>LALITA DEVI</t>
+        </is>
+      </c>
+      <c r="F1034" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1034" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1034" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1034" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1034" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1034" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:47:16</t>
+        </is>
+      </c>
+      <c r="L1034" s="4" t="inlineStr">
+        <is>
+          <t>T6E12876</t>
+        </is>
+      </c>
+      <c r="M1034" s="3" t="n">
+        <v>84.27</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B1035" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000094</t>
+        </is>
+      </c>
+      <c r="C1035" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1035" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1035" s="4" t="inlineStr">
+        <is>
+          <t>BIPIN KUMAR MANDAL</t>
+        </is>
+      </c>
+      <c r="F1035" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1035" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1035" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1035" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1035" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1035" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:48:47</t>
+        </is>
+      </c>
+      <c r="L1035" s="4" t="inlineStr">
+        <is>
+          <t>T6E13082</t>
+        </is>
+      </c>
+      <c r="M1035" s="3" t="n">
+        <v>83.93000000000001</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B1036" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000093</t>
+        </is>
+      </c>
+      <c r="C1036" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1036" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1036" s="4" t="inlineStr">
+        <is>
+          <t>GULAM ALI</t>
+        </is>
+      </c>
+      <c r="F1036" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1036" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1036" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1036" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1036" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1036" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:50:17</t>
+        </is>
+      </c>
+      <c r="L1036" s="4" t="inlineStr">
+        <is>
+          <t>T6E16464</t>
+        </is>
+      </c>
+      <c r="M1036" s="3" t="n">
+        <v>83.68000000000001</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B1037" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000092</t>
+        </is>
+      </c>
+      <c r="C1037" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1037" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1037" s="4" t="inlineStr">
+        <is>
+          <t>CHANDNI KHATOON</t>
+        </is>
+      </c>
+      <c r="F1037" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1037" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1037" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1037" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1037" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1037" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:51:46</t>
+        </is>
+      </c>
+      <c r="L1037" s="4" t="inlineStr">
+        <is>
+          <t>T6D15458</t>
+        </is>
+      </c>
+      <c r="M1037" s="3" t="n">
+        <v>83.48999999999999</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B1038" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000091</t>
+        </is>
+      </c>
+      <c r="C1038" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1038" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1038" s="4" t="inlineStr">
+        <is>
+          <t>SONU KUMAR SHARMA</t>
+        </is>
+      </c>
+      <c r="F1038" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1038" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1038" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1038" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1038" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1038" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:53:16</t>
+        </is>
+      </c>
+      <c r="L1038" s="4" t="inlineStr">
+        <is>
+          <t>T6E10063</t>
+        </is>
+      </c>
+      <c r="M1038" s="3" t="n">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B1039" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000090</t>
+        </is>
+      </c>
+      <c r="C1039" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1039" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1039" s="4" t="inlineStr">
+        <is>
+          <t>Nazir Hussain</t>
+        </is>
+      </c>
+      <c r="F1039" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1039" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1039" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1039" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1039" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1039" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:54:46</t>
+        </is>
+      </c>
+      <c r="L1039" s="4" t="inlineStr">
+        <is>
+          <t>T6D11319</t>
+        </is>
+      </c>
+      <c r="M1039" s="3" t="n">
+        <v>83.78</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B1040" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000089</t>
+        </is>
+      </c>
+      <c r="C1040" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1040" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1040" s="4" t="inlineStr">
+        <is>
+          <t>MOHAMMAD ANVARUL</t>
+        </is>
+      </c>
+      <c r="F1040" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1040" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1040" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1040" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1040" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1040" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:56:17</t>
+        </is>
+      </c>
+      <c r="L1040" s="4" t="inlineStr">
+        <is>
+          <t>T6D11321</t>
+        </is>
+      </c>
+      <c r="M1040" s="3" t="n">
+        <v>84.66</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B1041" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000088</t>
+        </is>
+      </c>
+      <c r="C1041" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1041" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1041" s="4" t="inlineStr">
+        <is>
+          <t>NARASINHA YADAV</t>
+        </is>
+      </c>
+      <c r="F1041" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1041" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1041" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1041" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1041" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1041" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:57:46</t>
+        </is>
+      </c>
+      <c r="L1041" s="4" t="inlineStr">
+        <is>
+          <t>T6E13079</t>
+        </is>
+      </c>
+      <c r="M1041" s="3" t="n">
+        <v>83.72</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B1042" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000087</t>
+        </is>
+      </c>
+      <c r="C1042" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1042" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1042" s="4" t="inlineStr">
+        <is>
+          <t>HEMANT KASHYAP</t>
+        </is>
+      </c>
+      <c r="F1042" s="4" t="inlineStr">
+        <is>
+          <t>BRAJESH AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1042" s="4" t="inlineStr">
+        <is>
+          <t>PURNEA</t>
+        </is>
+      </c>
+      <c r="H1042" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1042" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1042" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1042" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:59:17</t>
+        </is>
+      </c>
+      <c r="L1042" s="4" t="inlineStr">
+        <is>
+          <t>T6E10126</t>
+        </is>
+      </c>
+      <c r="M1042" s="3" t="n">
+        <v>83.92</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B1043" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000047</t>
+        </is>
+      </c>
+      <c r="C1043" s="4" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1043" s="4" t="inlineStr">
+        <is>
+          <t>AD Guwahati</t>
+        </is>
+      </c>
+      <c r="E1043" s="4" t="inlineStr">
+        <is>
+          <t>HUSAIN AKAN</t>
+        </is>
+      </c>
+      <c r="F1043" s="4" t="inlineStr">
+        <is>
+          <t>ICONIC AUTOMOBILES</t>
+        </is>
+      </c>
+      <c r="G1043" s="4" t="inlineStr">
+        <is>
+          <t>NAHARLAGAN SR</t>
+        </is>
+      </c>
+      <c r="H1043" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1043" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1043" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1043" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:00:59</t>
+        </is>
+      </c>
+      <c r="L1043" s="4" t="inlineStr">
+        <is>
+          <t>T6B12787</t>
+        </is>
+      </c>
+      <c r="M1043" s="3" t="n">
+        <v>83.41</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B1044" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000042</t>
+        </is>
+      </c>
+      <c r="C1044" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1044" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1044" s="4" t="inlineStr">
+        <is>
+          <t>PRAKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="F1044" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1044" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H1044" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1044" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1044" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1044" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:02:28</t>
+        </is>
+      </c>
+      <c r="L1044" s="4" t="inlineStr">
+        <is>
+          <t>T6E10068</t>
+        </is>
+      </c>
+      <c r="M1044" s="3" t="n">
+        <v>83.47</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B1045" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000041</t>
+        </is>
+      </c>
+      <c r="C1045" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1045" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1045" s="4" t="inlineStr">
+        <is>
+          <t>PKCE INFRAPROJECTS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="F1045" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1045" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H1045" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1045" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1045" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1045" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:03:58</t>
+        </is>
+      </c>
+      <c r="L1045" s="4" t="inlineStr">
+        <is>
+          <t>T6F13634</t>
+        </is>
+      </c>
+      <c r="M1045" s="3" t="n">
+        <v>83.27</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B1046" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000040</t>
+        </is>
+      </c>
+      <c r="C1046" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1046" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1046" s="4" t="inlineStr">
+        <is>
+          <t>RAVI KUMAR</t>
+        </is>
+      </c>
+      <c r="F1046" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1046" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H1046" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1046" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1046" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1046" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:05:12</t>
+        </is>
+      </c>
+      <c r="L1046" s="4" t="inlineStr">
+        <is>
+          <t>T5C84801</t>
+        </is>
+      </c>
+      <c r="M1046" s="3" t="n">
+        <v>68.67</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B1047" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000039</t>
+        </is>
+      </c>
+      <c r="C1047" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1047" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1047" s="4" t="inlineStr">
+        <is>
+          <t>PRAKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="F1047" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1047" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H1047" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1047" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1047" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1047" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:06:45</t>
+        </is>
+      </c>
+      <c r="L1047" s="4" t="inlineStr">
+        <is>
+          <t>T6E10095</t>
+        </is>
+      </c>
+      <c r="M1047" s="3" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B1048" s="4" t="inlineStr">
+        <is>
+          <t>LYL27D000038</t>
+        </is>
+      </c>
+      <c r="C1048" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1048" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1048" s="4" t="inlineStr">
+        <is>
+          <t>PUTUL KUMARI</t>
+        </is>
+      </c>
+      <c r="F1048" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1048" s="4" t="inlineStr">
+        <is>
+          <t>CHHAPRA</t>
+        </is>
+      </c>
+      <c r="H1048" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1048" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1048" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1048" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:08:15</t>
+        </is>
+      </c>
+      <c r="L1048" s="4" t="inlineStr">
+        <is>
+          <t>T6E12729</t>
+        </is>
+      </c>
+      <c r="M1048" s="3" t="n">
+        <v>84.17</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B1049" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000084</t>
+        </is>
+      </c>
+      <c r="C1049" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1049" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1049" s="4" t="inlineStr">
+        <is>
+          <t>DHIRAJ KUMAR GUPTA</t>
+        </is>
+      </c>
+      <c r="F1049" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1049" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1049" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1049" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1049" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1049" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:09:45</t>
+        </is>
+      </c>
+      <c r="L1049" s="4" t="inlineStr">
+        <is>
+          <t>T6F18759</t>
+        </is>
+      </c>
+      <c r="M1049" s="3" t="n">
+        <v>83.88</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B1050" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000083</t>
+        </is>
+      </c>
+      <c r="C1050" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1050" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1050" s="4" t="inlineStr">
+        <is>
+          <t>KAMAL INDUSTRY</t>
+        </is>
+      </c>
+      <c r="F1050" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1050" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1050" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1050" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1050" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1050" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:11:15</t>
+        </is>
+      </c>
+      <c r="L1050" s="4" t="inlineStr">
+        <is>
+          <t>T6F13631</t>
+        </is>
+      </c>
+      <c r="M1050" s="3" t="n">
+        <v>83.64</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B1051" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000082</t>
+        </is>
+      </c>
+      <c r="C1051" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1051" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1051" s="4" t="inlineStr">
+        <is>
+          <t>NIRAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="F1051" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1051" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1051" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1051" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1051" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1051" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:12:29</t>
+        </is>
+      </c>
+      <c r="L1051" s="4" t="inlineStr">
+        <is>
+          <t>T5C84828</t>
+        </is>
+      </c>
+      <c r="M1051" s="3" t="n">
+        <v>67.77</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B1052" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000081</t>
+        </is>
+      </c>
+      <c r="C1052" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1052" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1052" s="4" t="inlineStr">
+        <is>
+          <t>ROHIT KUMAR</t>
+        </is>
+      </c>
+      <c r="F1052" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1052" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1052" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1052" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1052" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1052" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:13:43</t>
+        </is>
+      </c>
+      <c r="L1052" s="4" t="inlineStr">
+        <is>
+          <t>T5C84832</t>
+        </is>
+      </c>
+      <c r="M1052" s="3" t="n">
+        <v>68.19</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B1053" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000080</t>
+        </is>
+      </c>
+      <c r="C1053" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1053" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1053" s="4" t="inlineStr">
+        <is>
+          <t>MIRA DEVI</t>
+        </is>
+      </c>
+      <c r="F1053" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1053" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1053" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1053" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1053" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1053" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:14:57</t>
+        </is>
+      </c>
+      <c r="L1053" s="4" t="inlineStr">
+        <is>
+          <t>T5C84796</t>
+        </is>
+      </c>
+      <c r="M1053" s="3" t="n">
+        <v>67.81999999999999</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B1054" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000079</t>
+        </is>
+      </c>
+      <c r="C1054" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1054" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1054" s="4" t="inlineStr">
+        <is>
+          <t>SANJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="F1054" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1054" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1054" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1054" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1054" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1054" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:16:11</t>
+        </is>
+      </c>
+      <c r="L1054" s="4" t="inlineStr">
+        <is>
+          <t>T5C84797</t>
+        </is>
+      </c>
+      <c r="M1054" s="3" t="n">
+        <v>67.81</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B1055" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000078</t>
+        </is>
+      </c>
+      <c r="C1055" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1055" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1055" s="4" t="inlineStr">
+        <is>
+          <t>KHUSHBU DEVI</t>
+        </is>
+      </c>
+      <c r="F1055" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1055" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1055" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1055" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1055" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1055" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:17:24</t>
+        </is>
+      </c>
+      <c r="L1055" s="4" t="inlineStr">
+        <is>
+          <t>T5B79192</t>
+        </is>
+      </c>
+      <c r="M1055" s="3" t="n">
+        <v>67.69</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B1056" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000077</t>
+        </is>
+      </c>
+      <c r="C1056" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1056" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1056" s="4" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR</t>
+        </is>
+      </c>
+      <c r="F1056" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1056" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1056" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1056" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1056" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1056" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:18:37</t>
+        </is>
+      </c>
+      <c r="L1056" s="4" t="inlineStr">
+        <is>
+          <t>T5C84830</t>
+        </is>
+      </c>
+      <c r="M1056" s="3" t="n">
+        <v>67.41</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B1057" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000076</t>
+        </is>
+      </c>
+      <c r="C1057" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1057" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1057" s="4" t="inlineStr">
+        <is>
+          <t>NIBHA DEVI</t>
+        </is>
+      </c>
+      <c r="F1057" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1057" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1057" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1057" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1057" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1057" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:19:51</t>
+        </is>
+      </c>
+      <c r="L1057" s="4" t="inlineStr">
+        <is>
+          <t>T5C84831</t>
+        </is>
+      </c>
+      <c r="M1057" s="3" t="n">
+        <v>67.31999999999999</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B1058" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000075</t>
+        </is>
+      </c>
+      <c r="C1058" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1058" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1058" s="4" t="inlineStr">
+        <is>
+          <t>AJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="F1058" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1058" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1058" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1058" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1058" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1058" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:21:10</t>
+        </is>
+      </c>
+      <c r="L1058" s="4" t="inlineStr">
+        <is>
+          <t>T5C83825</t>
+        </is>
+      </c>
+      <c r="M1058" s="3" t="n">
+        <v>72.75</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B1059" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000074</t>
+        </is>
+      </c>
+      <c r="C1059" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1059" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1059" s="4" t="inlineStr">
+        <is>
+          <t>RAHUL RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="F1059" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1059" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1059" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1059" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1059" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1059" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:24:53</t>
+        </is>
+      </c>
+      <c r="L1059" s="4" t="inlineStr">
+        <is>
+          <t>T6C18692</t>
+        </is>
+      </c>
+      <c r="M1059" s="3" t="n">
+        <v>211.77</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B1060" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000073</t>
+        </is>
+      </c>
+      <c r="C1060" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1060" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1060" s="4" t="inlineStr">
+        <is>
+          <t>MUKESH PRASAD</t>
+        </is>
+      </c>
+      <c r="F1060" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1060" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1060" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1060" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1060" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1060" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:26:11</t>
+        </is>
+      </c>
+      <c r="L1060" s="4" t="inlineStr">
+        <is>
+          <t>T5B78578</t>
+        </is>
+      </c>
+      <c r="M1060" s="3" t="n">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B1061" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000072</t>
+        </is>
+      </c>
+      <c r="C1061" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1061" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1061" s="4" t="inlineStr">
+        <is>
+          <t>SHREE SHYAM POLYMERS</t>
+        </is>
+      </c>
+      <c r="F1061" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1061" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1061" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1061" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1061" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1061" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:27:43</t>
+        </is>
+      </c>
+      <c r="L1061" s="4" t="inlineStr">
+        <is>
+          <t>T6D15236</t>
+        </is>
+      </c>
+      <c r="M1061" s="3" t="n">
+        <v>85.44</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B1062" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000071</t>
+        </is>
+      </c>
+      <c r="C1062" s="4" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1062" s="4" t="inlineStr">
+        <is>
+          <t>LMM Patna</t>
+        </is>
+      </c>
+      <c r="E1062" s="4" t="inlineStr">
+        <is>
+          <t>SONI DEVI</t>
+        </is>
+      </c>
+      <c r="F1062" s="4" t="inlineStr">
+        <is>
+          <t>KIRAN AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1062" s="4" t="inlineStr">
+        <is>
+          <t>PATNA_ZERO MILE_3S</t>
+        </is>
+      </c>
+      <c r="H1062" s="4" t="inlineStr">
+        <is>
+          <t>Xmart WELCOME BONUS</t>
+        </is>
+      </c>
+      <c r="I1062" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1062" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1062" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:28:58</t>
+        </is>
+      </c>
+      <c r="L1062" s="4" t="inlineStr">
+        <is>
+          <t>T5C83837</t>
+        </is>
+      </c>
+      <c r="M1062" s="3" t="n">
+        <v>68.81999999999999</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B1063" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000123</t>
+        </is>
+      </c>
+      <c r="C1063" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1063" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1063" s="4" t="inlineStr">
+        <is>
+          <t>ANIL PALAKIA</t>
+        </is>
+      </c>
+      <c r="F1063" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1063" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1063" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1063" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1063" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1063" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:30:51</t>
+        </is>
+      </c>
+      <c r="L1063" s="4" t="inlineStr">
+        <is>
+          <t>T6E10310</t>
+        </is>
+      </c>
+      <c r="M1063" s="3" t="n">
+        <v>86.48999999999999</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B1064" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000089</t>
+        </is>
+      </c>
+      <c r="C1064" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1064" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1064" s="4" t="inlineStr">
+        <is>
+          <t>Manaj Kumar Malik</t>
+        </is>
+      </c>
+      <c r="F1064" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1064" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H1064" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1064" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1064" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1064" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:32:43</t>
+        </is>
+      </c>
+      <c r="L1064" s="4" t="inlineStr">
+        <is>
+          <t>T6E10642</t>
+        </is>
+      </c>
+      <c r="M1064" s="3" t="n">
+        <v>88.43000000000001</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B1065" s="4" t="inlineStr">
+        <is>
+          <t>LYL27P000088</t>
+        </is>
+      </c>
+      <c r="C1065" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1065" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1065" s="4" t="inlineStr">
+        <is>
+          <t>SIKHARANI DHADA</t>
+        </is>
+      </c>
+      <c r="F1065" s="4" t="inlineStr">
+        <is>
+          <t>UTKAL AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1065" s="4" t="inlineStr">
+        <is>
+          <t>MANGULI_SH</t>
+        </is>
+      </c>
+      <c r="H1065" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1065" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1065" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1065" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:34:22</t>
+        </is>
+      </c>
+      <c r="L1065" s="4" t="inlineStr">
+        <is>
+          <t>T6E12972</t>
+        </is>
+      </c>
+      <c r="M1065" s="3" t="n">
+        <v>88.84</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B1066" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000122</t>
+        </is>
+      </c>
+      <c r="C1066" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1066" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1066" s="4" t="inlineStr">
+        <is>
+          <t>BANTI KUMAR SAHU</t>
+        </is>
+      </c>
+      <c r="F1066" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1066" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1066" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1066" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1066" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1066" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:36:16</t>
+        </is>
+      </c>
+      <c r="L1066" s="4" t="inlineStr">
+        <is>
+          <t>T6F14147</t>
+        </is>
+      </c>
+      <c r="M1066" s="3" t="n">
+        <v>89.48999999999999</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B1067" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000121</t>
+        </is>
+      </c>
+      <c r="C1067" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1067" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1067" s="4" t="inlineStr">
+        <is>
+          <t>CHUDAMANI BEHERA</t>
+        </is>
+      </c>
+      <c r="F1067" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1067" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1067" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1067" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1067" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1067" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:37:54</t>
+        </is>
+      </c>
+      <c r="L1067" s="4" t="inlineStr">
+        <is>
+          <t>T6F11448</t>
+        </is>
+      </c>
+      <c r="M1067" s="3" t="n">
+        <v>89.23999999999999</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B1068" s="4" t="inlineStr">
+        <is>
+          <t>LYL27A000060</t>
+        </is>
+      </c>
+      <c r="C1068" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1068" s="4" t="inlineStr">
+        <is>
+          <t>AD Patna</t>
+        </is>
+      </c>
+      <c r="E1068" s="4" t="inlineStr">
+        <is>
+          <t>INDAL PRASAD YADAV</t>
+        </is>
+      </c>
+      <c r="F1068" s="4" t="inlineStr">
+        <is>
+          <t>SHREE R C ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G1068" s="4" t="inlineStr">
+        <is>
+          <t>MOTIHARI</t>
+        </is>
+      </c>
+      <c r="H1068" s="4" t="inlineStr">
+        <is>
+          <t>VEERO Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1068" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1068" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1068" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:39:40</t>
+        </is>
+      </c>
+      <c r="L1068" s="4" t="inlineStr">
+        <is>
+          <t>T6D14831</t>
+        </is>
+      </c>
+      <c r="M1068" s="3" t="n">
+        <v>88.68000000000001</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B1069" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000120</t>
+        </is>
+      </c>
+      <c r="C1069" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1069" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1069" s="4" t="inlineStr">
+        <is>
+          <t>JOSHISH KOSALIA</t>
+        </is>
+      </c>
+      <c r="F1069" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1069" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1069" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1069" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1069" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1069" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:41:19</t>
+        </is>
+      </c>
+      <c r="L1069" s="4" t="inlineStr">
+        <is>
+          <t>T6F11544</t>
+        </is>
+      </c>
+      <c r="M1069" s="3" t="n">
+        <v>90.34999999999999</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B1070" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000119</t>
+        </is>
+      </c>
+      <c r="C1070" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1070" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1070" s="4" t="inlineStr">
+        <is>
+          <t>KURUKSHETRA POD</t>
+        </is>
+      </c>
+      <c r="F1070" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1070" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1070" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1070" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1070" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1070" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:42:56</t>
+        </is>
+      </c>
+      <c r="L1070" s="4" t="inlineStr">
+        <is>
+          <t>T6D12255</t>
+        </is>
+      </c>
+      <c r="M1070" s="3" t="n">
+        <v>88.64</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B1071" s="4" t="inlineStr">
+        <is>
+          <t>LYL27B000118</t>
+        </is>
+      </c>
+      <c r="C1071" s="4" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1071" s="4" t="inlineStr">
+        <is>
+          <t>AD Bhubaneshwar</t>
+        </is>
+      </c>
+      <c r="E1071" s="4" t="inlineStr">
+        <is>
+          <t>JOGINDRA BAG</t>
+        </is>
+      </c>
+      <c r="F1071" s="4" t="inlineStr">
+        <is>
+          <t>MINERVA AUTOMOBILES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="G1071" s="4" t="inlineStr">
+        <is>
+          <t>BHAVANIPATNA MADB</t>
+        </is>
+      </c>
+      <c r="H1071" s="4" t="inlineStr">
+        <is>
+          <t>Welcome Bonus</t>
+        </is>
+      </c>
+      <c r="I1071" s="11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J1071" s="4" t="inlineStr">
+        <is>
+          <t>Missing Ledger Document, Missing Invoice Document, Missing Disclaimer Document</t>
+        </is>
+      </c>
+      <c r="K1071" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="L1071" s="4" t="inlineStr">
+        <is>
+          <t>T6F11637</t>
+        </is>
+      </c>
+      <c r="M1071" s="3" t="n">
+        <v>88.15000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
